--- a/corporates/FC_Urban_London_after_work_leads.xlsx
+++ b/corporates/FC_Urban_London_after_work_leads.xlsx
@@ -2640,18 +2640,18 @@
       </c>
       <c r="P12" s="15" t="inlineStr">
         <is>
-          <t>Shad</t>
+          <t>Melanie</t>
         </is>
       </c>
       <c r="Q12" s="15" t="inlineStr">
         <is>
-          <t>Shad Ameen</t>
+          <t>Melanie Reid</t>
         </is>
       </c>
       <c r="R12" s="15" t="n"/>
       <c r="S12" s="15" t="inlineStr">
         <is>
-          <t>shad.ameen@stantonhouse.com</t>
+          <t>melanie.reid@stantonhouse.com</t>
         </is>
       </c>
       <c r="T12" s="15" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AH12" s="15" t="inlineStr">
         <is>
-          <t>team of 50 professionals</t>
+          <t>team of 50 people</t>
         </is>
       </c>
       <c r="AI12" s="16" t="inlineStr">
@@ -3315,27 +3315,27 @@
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Tech / software</t>
+          <t>Finance / accounting</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>EC1M</t>
+          <t>EC2M</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>Container Solutions Software Group Ltd</t>
+          <t>Guy Butler Limited</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
         <is>
-          <t>Container Solutions Software</t>
+          <t>Guy Butler</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>
-          <t>https://www.container-solutions.com</t>
+          <t>https://guybutler.co.uk</t>
         </is>
       </c>
       <c r="H16" s="15" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
-          <t>14061734</t>
+          <t>03869802</t>
         </is>
       </c>
       <c r="J16" s="16" t="inlineStr">
@@ -3360,17 +3360,17 @@
       </c>
       <c r="L16" s="15" t="inlineStr">
         <is>
-          <t>22/04/2022</t>
+          <t>02/11/1999</t>
         </is>
       </c>
       <c r="M16" s="15" t="inlineStr">
         <is>
-          <t>29 Clerkenwell Road, London</t>
+          <t>4Th Floor, 95 Gresham Street, London</t>
         </is>
       </c>
       <c r="N16" s="15" t="inlineStr">
         <is>
-          <t>EC1M 5RN</t>
+          <t>EC2V 7AB</t>
         </is>
       </c>
       <c r="O16" s="15" t="inlineStr">
@@ -3380,18 +3380,22 @@
       </c>
       <c r="P16" s="15" t="inlineStr">
         <is>
-          <t>Container</t>
+          <t>Jamie</t>
         </is>
       </c>
       <c r="Q16" s="15" t="inlineStr">
         <is>
-          <t>Container Solutions</t>
-        </is>
-      </c>
-      <c r="R16" s="15" t="n"/>
+          <t>Jamie Macfarlane</t>
+        </is>
+      </c>
+      <c r="R16" s="15" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
       <c r="S16" s="15" t="inlineStr">
         <is>
-          <t>info@container-solutions.com</t>
+          <t>jamie.macfarlane@guybutler.co.uk</t>
         </is>
       </c>
       <c r="T16" s="15" t="inlineStr">
@@ -3401,40 +3405,40 @@
       </c>
       <c r="U16" s="16" t="inlineStr">
         <is>
-          <t>https://www.container-solutions.com/</t>
+          <t>https://guybutler.co.uk/</t>
         </is>
       </c>
       <c r="X16" s="15" t="inlineStr">
         <is>
-          <t>29 CLERKENWELL ROAD</t>
+          <t>14th Floor, Dashwood House, 69 Old Broad Street</t>
         </is>
       </c>
       <c r="Y16" s="15" t="inlineStr">
         <is>
-          <t>EC1M 5RN</t>
+          <t>EC2M 1QS</t>
         </is>
       </c>
       <c r="Z16" s="15" t="inlineStr">
         <is>
-          <t>Website (29 CLERKENWELL ROAD)</t>
+          <t>Website (14th Floor, Dashwood House, 69 Old Broad Street)</t>
         </is>
       </c>
       <c r="AA16" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AB16" s="15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC16" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AD16" s="15" t="inlineStr">
         <is>
-          <t>Monday 12 October at 18:00</t>
+          <t>Monday 28 September at 17:40</t>
         </is>
       </c>
       <c r="AE16" s="15" t="inlineStr">
@@ -3444,7 +3448,7 @@
       </c>
       <c r="AF16" s="15" t="inlineStr">
         <is>
-          <t>6-a-side</t>
+          <t>5-a-side</t>
         </is>
       </c>
       <c r="AG16" s="17">
@@ -3495,37 +3499,35 @@
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>Finance / accounting</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>EC2M</t>
+          <t>EC1A</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>Guy Butler Limited</t>
+          <t>Goodman Masson Limited</t>
         </is>
       </c>
       <c r="F17" s="15" t="inlineStr">
         <is>
-          <t>Guy Butler</t>
+          <t>Goodman Masson</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
         <is>
-          <t>https://guybutler.co.uk</t>
-        </is>
-      </c>
-      <c r="H17" s="15" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
+          <t>https://www.goodmanmasson.com</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>100</v>
       </c>
       <c r="I17" s="15" t="inlineStr">
         <is>
-          <t>03869802</t>
+          <t>02769447</t>
         </is>
       </c>
       <c r="J17" s="16" t="inlineStr">
@@ -3535,22 +3537,22 @@
       </c>
       <c r="K17" s="15" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="L17" s="15" t="inlineStr">
         <is>
-          <t>02/11/1999</t>
+          <t>01/12/1992</t>
         </is>
       </c>
       <c r="M17" s="15" t="inlineStr">
         <is>
-          <t>4Th Floor, 95 Gresham Street, London</t>
+          <t>Fourth Floor, 120 Aldersgate Street, London</t>
         </is>
       </c>
       <c r="N17" s="15" t="inlineStr">
         <is>
-          <t>EC2V 7AB</t>
+          <t>EC1A 4JQ</t>
         </is>
       </c>
       <c r="O17" s="15" t="inlineStr">
@@ -3560,22 +3562,18 @@
       </c>
       <c r="P17" s="15" t="inlineStr">
         <is>
-          <t>Jamie</t>
+          <t>Iain</t>
         </is>
       </c>
       <c r="Q17" s="15" t="inlineStr">
         <is>
-          <t>Jamie Macfarlane</t>
-        </is>
-      </c>
-      <c r="R17" s="15" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
+          <t>Iain Mcgill</t>
+        </is>
+      </c>
+      <c r="R17" s="15" t="n"/>
       <c r="S17" s="15" t="inlineStr">
         <is>
-          <t>jamie.macfarlane@guybutler.co.uk</t>
+          <t>iain.mcgill@goodmanmasson.com</t>
         </is>
       </c>
       <c r="T17" s="15" t="inlineStr">
@@ -3585,27 +3583,27 @@
       </c>
       <c r="U17" s="16" t="inlineStr">
         <is>
-          <t>https://guybutler.co.uk/</t>
+          <t>https://www.goodmanmasson.com/aca-careers-hub</t>
         </is>
       </c>
       <c r="X17" s="15" t="inlineStr">
         <is>
-          <t>14th Floor, Dashwood House, 69 Old Broad Street</t>
+          <t>120 Aldersgate Street</t>
         </is>
       </c>
       <c r="Y17" s="15" t="inlineStr">
         <is>
-          <t>EC2M 1QS</t>
+          <t>EC1A 4JQ</t>
         </is>
       </c>
       <c r="Z17" s="15" t="inlineStr">
         <is>
-          <t>Website (14th Floor, Dashwood House, 69 Old Broad Street)</t>
+          <t>Website (120 Aldersgate Street)</t>
         </is>
       </c>
       <c r="AA17" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AB17" s="15" t="n">
@@ -3613,12 +3611,12 @@
       </c>
       <c r="AC17" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AD17" s="15" t="inlineStr">
         <is>
-          <t>Monday 28 September at 17:40</t>
+          <t>Monday 12 October at 18:00</t>
         </is>
       </c>
       <c r="AE17" s="15" t="inlineStr">
@@ -3628,15 +3626,23 @@
       </c>
       <c r="AF17" s="15" t="inlineStr">
         <is>
-          <t>5-a-side</t>
+          <t>6-a-side</t>
         </is>
       </c>
       <c r="AG17" s="17">
         <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
         <v/>
       </c>
-      <c r="AH17" s="15" t="n"/>
-      <c r="AI17" s="15" t="n"/>
+      <c r="AH17" s="15" t="inlineStr">
+        <is>
+          <t>team of 23</t>
+        </is>
+      </c>
+      <c r="AI17" s="16" t="inlineStr">
+        <is>
+          <t>https://www.goodmanmasson.com/aca-careers-hub</t>
+        </is>
+      </c>
       <c r="AJ17" s="18">
         <f>IF(V17&lt;&gt;"",V17,S17)</f>
         <v/>
@@ -3679,35 +3685,37 @@
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Tech / software</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>EC1A</t>
+          <t>EC3A</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>Goodman Masson Limited</t>
+          <t>Travelfusion Limited</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
         <is>
-          <t>Goodman Masson</t>
+          <t>Travelfusion</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr">
         <is>
-          <t>https://www.goodmanmasson.com</t>
-        </is>
-      </c>
-      <c r="H18" s="15" t="n">
-        <v>100</v>
+          <t>https://corporate.travelfusion.com</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
       </c>
       <c r="I18" s="15" t="inlineStr">
         <is>
-          <t>02769447</t>
+          <t>03880175</t>
         </is>
       </c>
       <c r="J18" s="16" t="inlineStr">
@@ -3717,22 +3725,22 @@
       </c>
       <c r="K18" s="15" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="L18" s="15" t="inlineStr">
         <is>
-          <t>01/12/1992</t>
+          <t>16/11/1999</t>
         </is>
       </c>
       <c r="M18" s="15" t="inlineStr">
         <is>
-          <t>Fourth Floor, 120 Aldersgate Street, London</t>
+          <t>70 St Mary Axe, London</t>
         </is>
       </c>
       <c r="N18" s="15" t="inlineStr">
         <is>
-          <t>EC1A 4JQ</t>
+          <t>EC3A 8BE</t>
         </is>
       </c>
       <c r="O18" s="15" t="inlineStr">
@@ -3740,20 +3748,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P18" s="15" t="inlineStr">
-        <is>
-          <t>Iain</t>
-        </is>
-      </c>
-      <c r="Q18" s="15" t="inlineStr">
-        <is>
-          <t>Iain Mcgill</t>
-        </is>
-      </c>
+      <c r="P18" s="15" t="n"/>
+      <c r="Q18" s="15" t="n"/>
       <c r="R18" s="15" t="n"/>
       <c r="S18" s="15" t="inlineStr">
         <is>
-          <t>iain.mcgill@goodmanmasson.com</t>
+          <t>hr@travelfusion.com</t>
         </is>
       </c>
       <c r="T18" s="15" t="inlineStr">
@@ -3763,40 +3763,40 @@
       </c>
       <c r="U18" s="16" t="inlineStr">
         <is>
-          <t>https://www.goodmanmasson.com/aca-careers-hub</t>
+          <t>https://corporate.travelfusion.com/company/contact-us</t>
         </is>
       </c>
       <c r="X18" s="15" t="inlineStr">
         <is>
-          <t>120 Aldersgate Street</t>
+          <t>70 St Mary Axe</t>
         </is>
       </c>
       <c r="Y18" s="15" t="inlineStr">
         <is>
-          <t>EC1A 4JQ</t>
+          <t>EC3A 8BE</t>
         </is>
       </c>
       <c r="Z18" s="15" t="inlineStr">
         <is>
-          <t>Website (120 Aldersgate Street)</t>
+          <t>Website (70 St Mary Axe)</t>
         </is>
       </c>
       <c r="AA18" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AB18" s="15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC18" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AD18" s="15" t="inlineStr">
         <is>
-          <t>Monday 12 October at 18:00</t>
+          <t>Monday 28 September at 17:40</t>
         </is>
       </c>
       <c r="AE18" s="15" t="inlineStr">
@@ -3806,23 +3806,15 @@
       </c>
       <c r="AF18" s="15" t="inlineStr">
         <is>
-          <t>6-a-side</t>
+          <t>5-a-side</t>
         </is>
       </c>
       <c r="AG18" s="17">
         <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
         <v/>
       </c>
-      <c r="AH18" s="15" t="inlineStr">
-        <is>
-          <t>team of 23</t>
-        </is>
-      </c>
-      <c r="AI18" s="16" t="inlineStr">
-        <is>
-          <t>https://www.goodmanmasson.com/aca-careers-hub</t>
-        </is>
-      </c>
+      <c r="AH18" s="15" t="n"/>
+      <c r="AI18" s="15" t="n"/>
       <c r="AJ18" s="18">
         <f>IF(V18&lt;&gt;"",V18,S18)</f>
         <v/>
@@ -3861,31 +3853,31 @@
         <v>17</v>
       </c>
       <c r="B19" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>Tech / software</t>
+          <t>Marketing / agency</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>EC3A</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>Travelfusion Limited</t>
+          <t>Mother London Limited</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
-          <t>Travelfusion</t>
+          <t>Mother London</t>
         </is>
       </c>
       <c r="G19" s="16" t="inlineStr">
         <is>
-          <t>https://corporate.travelfusion.com</t>
+          <t>https://mother.com</t>
         </is>
       </c>
       <c r="H19" s="15" t="inlineStr">
@@ -3895,7 +3887,7 @@
       </c>
       <c r="I19" s="15" t="inlineStr">
         <is>
-          <t>03880175</t>
+          <t>04983564</t>
         </is>
       </c>
       <c r="J19" s="16" t="inlineStr">
@@ -3905,22 +3897,22 @@
       </c>
       <c r="K19" s="15" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="L19" s="15" t="inlineStr">
         <is>
-          <t>16/11/1999</t>
+          <t>03/12/2003</t>
         </is>
       </c>
       <c r="M19" s="15" t="inlineStr">
         <is>
-          <t>70 St Mary Axe, London</t>
+          <t>Biscuit Building, 10 Redchurch Street, London</t>
         </is>
       </c>
       <c r="N19" s="15" t="inlineStr">
         <is>
-          <t>EC3A 8BE</t>
+          <t>E2 7DD</t>
         </is>
       </c>
       <c r="O19" s="15" t="inlineStr">
@@ -3928,37 +3920,45 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P19" s="15" t="n"/>
-      <c r="Q19" s="15" t="n"/>
+      <c r="P19" s="15" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q19" s="15" t="inlineStr">
+        <is>
+          <t>Home Courses</t>
+        </is>
+      </c>
       <c r="R19" s="15" t="n"/>
       <c r="S19" s="15" t="inlineStr">
         <is>
-          <t>hr@travelfusion.com</t>
+          <t>hello@mother.com</t>
         </is>
       </c>
       <c r="T19" s="15" t="inlineStr">
         <is>
-          <t>a/b named person</t>
+          <t>a/b named person via general inbox</t>
         </is>
       </c>
       <c r="U19" s="16" t="inlineStr">
         <is>
-          <t>https://corporate.travelfusion.com/company/contact-us</t>
+          <t>https://mother.com/contact/</t>
         </is>
       </c>
       <c r="X19" s="15" t="inlineStr">
         <is>
-          <t>70 St Mary Axe</t>
+          <t>BISCUIT BUILDING, 10 REDCHURCH STREET</t>
         </is>
       </c>
       <c r="Y19" s="15" t="inlineStr">
         <is>
-          <t>EC3A 8BE</t>
+          <t>E2 7DD</t>
         </is>
       </c>
       <c r="Z19" s="15" t="inlineStr">
         <is>
-          <t>Website (70 St Mary Axe)</t>
+          <t>Website (BISCUIT BUILDING, 10 REDCHURCH STREET)</t>
         </is>
       </c>
       <c r="AA19" s="15" t="inlineStr">
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="AB19" s="15" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AC19" s="15" t="inlineStr">
         <is>
@@ -4037,27 +4037,27 @@
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>Marketing / agency</t>
+          <t>Tech / software</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>Mother London Limited</t>
+          <t>Quant Network Ltd</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
         <is>
-          <t>Mother London</t>
+          <t>Quant Network</t>
         </is>
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
-          <t>https://mother.com</t>
+          <t>https://www.quant.ai</t>
         </is>
       </c>
       <c r="H20" s="15" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="I20" s="15" t="inlineStr">
         <is>
-          <t>04983564</t>
+          <t>09798383</t>
         </is>
       </c>
       <c r="J20" s="16" t="inlineStr">
@@ -4077,22 +4077,22 @@
       </c>
       <c r="K20" s="15" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="L20" s="15" t="inlineStr">
         <is>
-          <t>03/12/2003</t>
+          <t>28/09/2015</t>
         </is>
       </c>
       <c r="M20" s="15" t="inlineStr">
         <is>
-          <t>Biscuit Building, 10 Redchurch Street, London</t>
+          <t>20-22 Wenlock Road, London</t>
         </is>
       </c>
       <c r="N20" s="15" t="inlineStr">
         <is>
-          <t>E2 7DD</t>
+          <t>N1 7GU</t>
         </is>
       </c>
       <c r="O20" s="15" t="inlineStr">
@@ -4102,18 +4102,22 @@
       </c>
       <c r="P20" s="15" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Chetan</t>
         </is>
       </c>
       <c r="Q20" s="15" t="inlineStr">
         <is>
-          <t>Home Courses</t>
-        </is>
-      </c>
-      <c r="R20" s="15" t="n"/>
+          <t>Chetan Dube</t>
+        </is>
+      </c>
+      <c r="R20" s="15" t="inlineStr">
+        <is>
+          <t>CEO and Chairman</t>
+        </is>
+      </c>
       <c r="S20" s="15" t="inlineStr">
         <is>
-          <t>hello@mother.com</t>
+          <t>technology@quant.ai</t>
         </is>
       </c>
       <c r="T20" s="15" t="inlineStr">
@@ -4123,40 +4127,36 @@
       </c>
       <c r="U20" s="16" t="inlineStr">
         <is>
-          <t>https://mother.com/contact/</t>
-        </is>
-      </c>
-      <c r="X20" s="15" t="inlineStr">
-        <is>
-          <t>BISCUIT BUILDING, 10 REDCHURCH STREET</t>
-        </is>
-      </c>
+          <t>https://www.quant.ai/en/contact</t>
+        </is>
+      </c>
+      <c r="X20" s="15" t="n"/>
       <c r="Y20" s="15" t="inlineStr">
         <is>
-          <t>E2 7DD</t>
+          <t>N1 7GU</t>
         </is>
       </c>
       <c r="Z20" s="15" t="inlineStr">
         <is>
-          <t>Website (BISCUIT BUILDING, 10 REDCHURCH STREET)</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="AA20" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AB20" s="15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AC20" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AD20" s="15" t="inlineStr">
         <is>
-          <t>Monday 28 September at 17:40</t>
+          <t>Monday 12 October at 18:00</t>
         </is>
       </c>
       <c r="AE20" s="15" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AF20" s="15" t="inlineStr">
         <is>
-          <t>5-a-side</t>
+          <t>6-a-side</t>
         </is>
       </c>
       <c r="AG20" s="17">
@@ -4217,27 +4217,27 @@
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>Tech / software</t>
+          <t>Professional services (LLP)</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>EC2A</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>Quant Network Ltd</t>
+          <t>Paloma II (Industrial) I LLP</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>Quant Network</t>
+          <t>Paloma II I</t>
         </is>
       </c>
       <c r="G21" s="16" t="inlineStr">
         <is>
-          <t>https://www.quant.ai</t>
+          <t>https://www.paloma.com</t>
         </is>
       </c>
       <c r="H21" s="15" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="I21" s="15" t="inlineStr">
         <is>
-          <t>09798383</t>
+          <t>OC423581</t>
         </is>
       </c>
       <c r="J21" s="16" t="inlineStr">
@@ -4262,17 +4262,17 @@
       </c>
       <c r="L21" s="15" t="inlineStr">
         <is>
-          <t>28/09/2015</t>
+          <t>31/07/2018</t>
         </is>
       </c>
       <c r="M21" s="15" t="inlineStr">
         <is>
-          <t>20-22 Wenlock Road, London</t>
+          <t>Broadwalk House 5 Appold Street, Broadgate, London</t>
         </is>
       </c>
       <c r="N21" s="15" t="inlineStr">
         <is>
-          <t>N1 7GU</t>
+          <t>EC2A 2DA</t>
         </is>
       </c>
       <c r="O21" s="15" t="inlineStr">
@@ -4282,22 +4282,22 @@
       </c>
       <c r="P21" s="15" t="inlineStr">
         <is>
-          <t>Chetan</t>
+          <t>Donald</t>
         </is>
       </c>
       <c r="Q21" s="15" t="inlineStr">
         <is>
-          <t>Chetan Dube</t>
+          <t>Donald Sussman</t>
         </is>
       </c>
       <c r="R21" s="15" t="inlineStr">
         <is>
-          <t>CEO and Chairman</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="S21" s="15" t="inlineStr">
         <is>
-          <t>technology@quant.ai</t>
+          <t>info@paloma.com</t>
         </is>
       </c>
       <c r="T21" s="15" t="inlineStr">
@@ -4307,13 +4307,13 @@
       </c>
       <c r="U21" s="16" t="inlineStr">
         <is>
-          <t>https://www.quant.ai/en/contact</t>
+          <t>https://www.paloma.com/contact</t>
         </is>
       </c>
       <c r="X21" s="15" t="n"/>
       <c r="Y21" s="15" t="inlineStr">
         <is>
-          <t>N1 7GU</t>
+          <t>EC2A 2DA</t>
         </is>
       </c>
       <c r="Z21" s="15" t="inlineStr">
@@ -4323,20 +4323,20 @@
       </c>
       <c r="AA21" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AB21" s="15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC21" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AD21" s="15" t="inlineStr">
         <is>
-          <t>Monday 12 October at 18:00</t>
+          <t>Monday 28 September at 17:40</t>
         </is>
       </c>
       <c r="AE21" s="15" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="AF21" s="15" t="inlineStr">
         <is>
-          <t>6-a-side</t>
+          <t>5-a-side</t>
         </is>
       </c>
       <c r="AG21" s="17">
@@ -4397,27 +4397,27 @@
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Professional services (LLP)</t>
+          <t>Marketing / agency</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>EC2A</t>
+          <t>EC1V</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>Paloma II (Industrial) I LLP</t>
+          <t>Turbine Studios Limited</t>
         </is>
       </c>
       <c r="F22" s="15" t="inlineStr">
         <is>
-          <t>Paloma II I</t>
+          <t>Turbine Studios</t>
         </is>
       </c>
       <c r="G22" s="16" t="inlineStr">
         <is>
-          <t>https://www.paloma.com</t>
+          <t>https://turbinestudios.co.uk</t>
         </is>
       </c>
       <c r="H22" s="15" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>OC423581</t>
+          <t>10994901</t>
         </is>
       </c>
       <c r="J22" s="16" t="inlineStr">
@@ -4437,22 +4437,22 @@
       </c>
       <c r="K22" s="15" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="L22" s="15" t="inlineStr">
         <is>
-          <t>31/07/2018</t>
+          <t>04/10/2017</t>
         </is>
       </c>
       <c r="M22" s="15" t="inlineStr">
         <is>
-          <t>Broadwalk House 5 Appold Street, Broadgate, London</t>
+          <t>9A Dallington Street, London</t>
         </is>
       </c>
       <c r="N22" s="15" t="inlineStr">
         <is>
-          <t>EC2A 2DA</t>
+          <t>EC1V 0BQ</t>
         </is>
       </c>
       <c r="O22" s="15" t="inlineStr">
@@ -4462,22 +4462,22 @@
       </c>
       <c r="P22" s="15" t="inlineStr">
         <is>
-          <t>Donald</t>
+          <t>Tracey</t>
         </is>
       </c>
       <c r="Q22" s="15" t="inlineStr">
         <is>
-          <t>Donald Sussman</t>
+          <t>Tracey Scoffield</t>
         </is>
       </c>
       <c r="R22" s="15" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Founder &amp; Exec Producer</t>
         </is>
       </c>
       <c r="S22" s="15" t="inlineStr">
         <is>
-          <t>info@paloma.com</t>
+          <t>mail@turbinestudios.co.uk</t>
         </is>
       </c>
       <c r="T22" s="15" t="inlineStr">
@@ -4487,36 +4487,40 @@
       </c>
       <c r="U22" s="16" t="inlineStr">
         <is>
-          <t>https://www.paloma.com/contact</t>
-        </is>
-      </c>
-      <c r="X22" s="15" t="n"/>
+          <t>https://turbinestudios.co.uk/</t>
+        </is>
+      </c>
+      <c r="X22" s="15" t="inlineStr">
+        <is>
+          <t>9A Dallington Street</t>
+        </is>
+      </c>
       <c r="Y22" s="15" t="inlineStr">
         <is>
-          <t>EC2A 2DA</t>
+          <t>EC1V 0BQ</t>
         </is>
       </c>
       <c r="Z22" s="15" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Website (9A Dallington Street)</t>
         </is>
       </c>
       <c r="AA22" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AB22" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC22" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AD22" s="15" t="inlineStr">
         <is>
-          <t>Monday 28 September at 17:40</t>
+          <t>Monday 12 October at 18:00</t>
         </is>
       </c>
       <c r="AE22" s="15" t="inlineStr">
@@ -4526,7 +4530,7 @@
       </c>
       <c r="AF22" s="15" t="inlineStr">
         <is>
-          <t>5-a-side</t>
+          <t>6-a-side</t>
         </is>
       </c>
       <c r="AG22" s="17">
@@ -4577,27 +4581,27 @@
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>Marketing / agency</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>EC1V</t>
+          <t>N7</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>Turbine Studios Limited</t>
+          <t>Oribiotech Ltd</t>
         </is>
       </c>
       <c r="F23" s="15" t="inlineStr">
         <is>
-          <t>Turbine Studios</t>
+          <t>Oribiotech</t>
         </is>
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
-          <t>https://turbinestudios.co.uk</t>
+          <t>https://oribiotech.com</t>
         </is>
       </c>
       <c r="H23" s="15" t="inlineStr">
@@ -4607,7 +4611,7 @@
       </c>
       <c r="I23" s="15" t="inlineStr">
         <is>
-          <t>10994901</t>
+          <t>09757696</t>
         </is>
       </c>
       <c r="J23" s="16" t="inlineStr">
@@ -4622,17 +4626,17 @@
       </c>
       <c r="L23" s="15" t="inlineStr">
         <is>
-          <t>04/10/2017</t>
+          <t>02/09/2015</t>
         </is>
       </c>
       <c r="M23" s="15" t="inlineStr">
         <is>
-          <t>9A Dallington Street, London</t>
+          <t>Mayde, 5-10 Brandon Road, London</t>
         </is>
       </c>
       <c r="N23" s="15" t="inlineStr">
         <is>
-          <t>EC1V 0BQ</t>
+          <t>N7 9AA</t>
         </is>
       </c>
       <c r="O23" s="15" t="inlineStr">
@@ -4642,22 +4646,22 @@
       </c>
       <c r="P23" s="15" t="inlineStr">
         <is>
-          <t>Tracey</t>
+          <t>Nick</t>
         </is>
       </c>
       <c r="Q23" s="15" t="inlineStr">
         <is>
-          <t>Tracey Scoffield</t>
+          <t>Nick Treuil</t>
         </is>
       </c>
       <c r="R23" s="15" t="inlineStr">
         <is>
-          <t>Founder &amp; Exec Producer</t>
+          <t>Chief of Staff</t>
         </is>
       </c>
       <c r="S23" s="15" t="inlineStr">
         <is>
-          <t>mail@turbinestudios.co.uk</t>
+          <t>info@oribiotech.com</t>
         </is>
       </c>
       <c r="T23" s="15" t="inlineStr">
@@ -4667,40 +4671,36 @@
       </c>
       <c r="U23" s="16" t="inlineStr">
         <is>
-          <t>https://turbinestudios.co.uk/</t>
-        </is>
-      </c>
-      <c r="X23" s="15" t="inlineStr">
-        <is>
-          <t>9A Dallington Street</t>
-        </is>
-      </c>
+          <t>https://oribiotech.com/about/careers</t>
+        </is>
+      </c>
+      <c r="X23" s="15" t="n"/>
       <c r="Y23" s="15" t="inlineStr">
         <is>
-          <t>EC1V 0BQ</t>
+          <t>N7 9AA</t>
         </is>
       </c>
       <c r="Z23" s="15" t="inlineStr">
         <is>
-          <t>Website (9A Dallington Street)</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="AA23" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Market Road</t>
         </is>
       </c>
       <c r="AB23" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC23" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Market Road</t>
         </is>
       </c>
       <c r="AD23" s="15" t="inlineStr">
         <is>
-          <t>Monday 12 October at 18:00</t>
+          <t>Monday 28 September at 18:00</t>
         </is>
       </c>
       <c r="AE23" s="15" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="AF23" s="15" t="inlineStr">
         <is>
-          <t>6-a-side</t>
+          <t>5-a-side</t>
         </is>
       </c>
       <c r="AG23" s="17">
@@ -4761,27 +4761,27 @@
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>EC2A</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>Oribiotech Ltd</t>
+          <t>Simply Education Limited</t>
         </is>
       </c>
       <c r="F24" s="15" t="inlineStr">
         <is>
-          <t>Oribiotech</t>
+          <t>Simply Education</t>
         </is>
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
-          <t>https://oribiotech.com</t>
+          <t>https://simplyeducation.co.uk</t>
         </is>
       </c>
       <c r="H24" s="15" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="I24" s="15" t="inlineStr">
         <is>
-          <t>09757696</t>
+          <t>05532608</t>
         </is>
       </c>
       <c r="J24" s="16" t="inlineStr">
@@ -4801,22 +4801,22 @@
       </c>
       <c r="K24" s="15" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="L24" s="15" t="inlineStr">
         <is>
-          <t>02/09/2015</t>
+          <t>10/08/2005</t>
         </is>
       </c>
       <c r="M24" s="15" t="inlineStr">
         <is>
-          <t>Mayde, 5-10 Brandon Road, London</t>
+          <t>66 Paul Street, London</t>
         </is>
       </c>
       <c r="N24" s="15" t="inlineStr">
         <is>
-          <t>N7 9AA</t>
+          <t>EC2A 4NA</t>
         </is>
       </c>
       <c r="O24" s="15" t="inlineStr">
@@ -4826,22 +4826,22 @@
       </c>
       <c r="P24" s="15" t="inlineStr">
         <is>
-          <t>Nick</t>
+          <t>Hollie</t>
         </is>
       </c>
       <c r="Q24" s="15" t="inlineStr">
         <is>
-          <t>Nick Treuil</t>
+          <t>Hollie Murtagh</t>
         </is>
       </c>
       <c r="R24" s="15" t="inlineStr">
         <is>
-          <t>Chief of Staff</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="S24" s="15" t="inlineStr">
         <is>
-          <t>info@oribiotech.com</t>
+          <t>info@simplyeducation.co.uk</t>
         </is>
       </c>
       <c r="T24" s="15" t="inlineStr">
@@ -4851,36 +4851,40 @@
       </c>
       <c r="U24" s="16" t="inlineStr">
         <is>
-          <t>https://oribiotech.com/about/careers</t>
-        </is>
-      </c>
-      <c r="X24" s="15" t="n"/>
+          <t>https://simplyeducation.co.uk/</t>
+        </is>
+      </c>
+      <c r="X24" s="15" t="inlineStr">
+        <is>
+          <t>66 Paul Street</t>
+        </is>
+      </c>
       <c r="Y24" s="15" t="inlineStr">
         <is>
-          <t>N7 9AA</t>
+          <t>EC2A 4NA</t>
         </is>
       </c>
       <c r="Z24" s="15" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Website (66 Paul Street)</t>
         </is>
       </c>
       <c r="AA24" s="15" t="inlineStr">
         <is>
-          <t>Market Road</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AB24" s="15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC24" s="15" t="inlineStr">
         <is>
-          <t>Market Road</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AD24" s="15" t="inlineStr">
         <is>
-          <t>Monday 28 September at 18:00</t>
+          <t>Monday 28 September at 17:40</t>
         </is>
       </c>
       <c r="AE24" s="15" t="inlineStr">
@@ -4941,7 +4945,7 @@
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Tech / software</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
@@ -4951,17 +4955,17 @@
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>Simply Education Limited</t>
+          <t>Ecodriver Ltd</t>
         </is>
       </c>
       <c r="F25" s="15" t="inlineStr">
         <is>
-          <t>Simply Education</t>
+          <t>Ecodriver</t>
         </is>
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
-          <t>https://simplyeducation.co.uk</t>
+          <t>https://ecodriver.co.uk</t>
         </is>
       </c>
       <c r="H25" s="15" t="inlineStr">
@@ -4971,7 +4975,7 @@
       </c>
       <c r="I25" s="15" t="inlineStr">
         <is>
-          <t>05532608</t>
+          <t>05258662</t>
         </is>
       </c>
       <c r="J25" s="16" t="inlineStr">
@@ -4986,17 +4990,17 @@
       </c>
       <c r="L25" s="15" t="inlineStr">
         <is>
-          <t>10/08/2005</t>
+          <t>13/10/2004</t>
         </is>
       </c>
       <c r="M25" s="15" t="inlineStr">
         <is>
-          <t>66 Paul Street, London</t>
+          <t>10 Bonhill Street, London</t>
         </is>
       </c>
       <c r="N25" s="15" t="inlineStr">
         <is>
-          <t>EC2A 4NA</t>
+          <t>EC2A 4PE</t>
         </is>
       </c>
       <c r="O25" s="15" t="inlineStr">
@@ -5006,12 +5010,12 @@
       </c>
       <c r="P25" s="15" t="inlineStr">
         <is>
-          <t>Hollie</t>
+          <t>Jamie</t>
         </is>
       </c>
       <c r="Q25" s="15" t="inlineStr">
         <is>
-          <t>Hollie Murtagh</t>
+          <t>Jamie Finnan</t>
         </is>
       </c>
       <c r="R25" s="15" t="inlineStr">
@@ -5021,7 +5025,7 @@
       </c>
       <c r="S25" s="15" t="inlineStr">
         <is>
-          <t>info@simplyeducation.co.uk</t>
+          <t>info@ecodriver.co.uk</t>
         </is>
       </c>
       <c r="T25" s="15" t="inlineStr">
@@ -5031,22 +5035,22 @@
       </c>
       <c r="U25" s="16" t="inlineStr">
         <is>
-          <t>https://simplyeducation.co.uk/</t>
+          <t>https://ecodriver.co.uk/</t>
         </is>
       </c>
       <c r="X25" s="15" t="inlineStr">
         <is>
-          <t>66 Paul Street</t>
+          <t>10 Bonhill Street</t>
         </is>
       </c>
       <c r="Y25" s="15" t="inlineStr">
         <is>
-          <t>EC2A 4NA</t>
+          <t>EC2A 4PE</t>
         </is>
       </c>
       <c r="Z25" s="15" t="inlineStr">
         <is>
-          <t>Website (66 Paul Street)</t>
+          <t>Website (10 Bonhill Street)</t>
         </is>
       </c>
       <c r="AA25" s="15" t="inlineStr">
@@ -5130,22 +5134,22 @@
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>EC2A</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>Ecodriver Ltd</t>
+          <t>Human Made Machine Limited</t>
         </is>
       </c>
       <c r="F26" s="15" t="inlineStr">
         <is>
-          <t>Ecodriver</t>
+          <t>Human Made Machine</t>
         </is>
       </c>
       <c r="G26" s="16" t="inlineStr">
         <is>
-          <t>https://ecodriver.co.uk</t>
+          <t>https://www.humanmademachine.com</t>
         </is>
       </c>
       <c r="H26" s="15" t="inlineStr">
@@ -5155,7 +5159,7 @@
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
-          <t>05258662</t>
+          <t>09338935</t>
         </is>
       </c>
       <c r="J26" s="16" t="inlineStr">
@@ -5165,22 +5169,22 @@
       </c>
       <c r="K26" s="15" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="L26" s="15" t="inlineStr">
         <is>
-          <t>13/10/2004</t>
+          <t>03/12/2014</t>
         </is>
       </c>
       <c r="M26" s="15" t="inlineStr">
         <is>
-          <t>10 Bonhill Street, London</t>
+          <t>2-4 Hoxton Square, London</t>
         </is>
       </c>
       <c r="N26" s="15" t="inlineStr">
         <is>
-          <t>EC2A 4PE</t>
+          <t>N1 6NU</t>
         </is>
       </c>
       <c r="O26" s="15" t="inlineStr">
@@ -5190,22 +5194,22 @@
       </c>
       <c r="P26" s="15" t="inlineStr">
         <is>
-          <t>Jamie</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="Q26" s="15" t="inlineStr">
         <is>
-          <t>Jamie Finnan</t>
+          <t>Sabrina Talma</t>
         </is>
       </c>
       <c r="R26" s="15" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Founder / Chief Executive Officer</t>
         </is>
       </c>
       <c r="S26" s="15" t="inlineStr">
         <is>
-          <t>info@ecodriver.co.uk</t>
+          <t>talkto@humanmademachine.com</t>
         </is>
       </c>
       <c r="T26" s="15" t="inlineStr">
@@ -5215,22 +5219,22 @@
       </c>
       <c r="U26" s="16" t="inlineStr">
         <is>
-          <t>https://ecodriver.co.uk/</t>
+          <t>https://www.humanmademachine.com/contact</t>
         </is>
       </c>
       <c r="X26" s="15" t="inlineStr">
         <is>
-          <t>10 Bonhill Street</t>
+          <t>Unit 6, 2-4 Hoxton Square</t>
         </is>
       </c>
       <c r="Y26" s="15" t="inlineStr">
         <is>
-          <t>EC2A 4PE</t>
+          <t>N1 6NU</t>
         </is>
       </c>
       <c r="Z26" s="15" t="inlineStr">
         <is>
-          <t>Website (10 Bonhill Street)</t>
+          <t>Website (Unit 6, 2-4 Hoxton Square)</t>
         </is>
       </c>
       <c r="AA26" s="15" t="inlineStr">
@@ -5239,7 +5243,7 @@
         </is>
       </c>
       <c r="AB26" s="15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AC26" s="15" t="inlineStr">
         <is>
@@ -5309,37 +5313,35 @@
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>Tech / software</t>
+          <t>Marketing / agency</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>EC1V</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>Human Made Machine Limited</t>
+          <t>Artiq Limited</t>
         </is>
       </c>
       <c r="F27" s="15" t="inlineStr">
         <is>
-          <t>Human Made Machine</t>
+          <t>Artiq</t>
         </is>
       </c>
       <c r="G27" s="16" t="inlineStr">
         <is>
-          <t>https://www.humanmademachine.com</t>
-        </is>
-      </c>
-      <c r="H27" s="15" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
+          <t>https://artiq.co</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>40</v>
       </c>
       <c r="I27" s="15" t="inlineStr">
         <is>
-          <t>09338935</t>
+          <t>07080437</t>
         </is>
       </c>
       <c r="J27" s="16" t="inlineStr">
@@ -5354,17 +5356,17 @@
       </c>
       <c r="L27" s="15" t="inlineStr">
         <is>
-          <t>03/12/2014</t>
+          <t>18/11/2009</t>
         </is>
       </c>
       <c r="M27" s="15" t="inlineStr">
         <is>
-          <t>2-4 Hoxton Square, London</t>
+          <t>1St Floor, 23-25 Great Sutton Street, London</t>
         </is>
       </c>
       <c r="N27" s="15" t="inlineStr">
         <is>
-          <t>N1 6NU</t>
+          <t>EC1V 0DN</t>
         </is>
       </c>
       <c r="O27" s="15" t="inlineStr">
@@ -5374,22 +5376,22 @@
       </c>
       <c r="P27" s="15" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="Q27" s="15" t="inlineStr">
         <is>
-          <t>Sabrina Talma</t>
+          <t>Patrick McCrae</t>
         </is>
       </c>
       <c r="R27" s="15" t="inlineStr">
         <is>
-          <t>Founder / Chief Executive Officer</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="S27" s="15" t="inlineStr">
         <is>
-          <t>talkto@humanmademachine.com</t>
+          <t>hello@artiq.co</t>
         </is>
       </c>
       <c r="T27" s="15" t="inlineStr">
@@ -5399,27 +5401,27 @@
       </c>
       <c r="U27" s="16" t="inlineStr">
         <is>
-          <t>https://www.humanmademachine.com/contact</t>
+          <t>https://artiq.co/</t>
         </is>
       </c>
       <c r="X27" s="15" t="inlineStr">
         <is>
-          <t>Unit 6, 2-4 Hoxton Square</t>
+          <t>1st Floor, 23-25 Great Sutton Street</t>
         </is>
       </c>
       <c r="Y27" s="15" t="inlineStr">
         <is>
-          <t>N1 6NU</t>
+          <t>EC1V 0DN</t>
         </is>
       </c>
       <c r="Z27" s="15" t="inlineStr">
         <is>
-          <t>Website (Unit 6, 2-4 Hoxton Square)</t>
+          <t>Website (1st Floor, 23-25 Great Sutton Street)</t>
         </is>
       </c>
       <c r="AA27" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AB27" s="15" t="n">
@@ -5427,12 +5429,12 @@
       </c>
       <c r="AC27" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AD27" s="15" t="inlineStr">
         <is>
-          <t>Monday 28 September at 17:40</t>
+          <t>Monday 12 October at 18:00</t>
         </is>
       </c>
       <c r="AE27" s="15" t="inlineStr">
@@ -5442,7 +5444,7 @@
       </c>
       <c r="AF27" s="15" t="inlineStr">
         <is>
-          <t>5-a-side</t>
+          <t>6-a-side</t>
         </is>
       </c>
       <c r="AG27" s="17">
@@ -5493,7 +5495,7 @@
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>Marketing / agency</t>
+          <t>Professional services (LLP)</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
@@ -5503,25 +5505,25 @@
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>Artiq Limited</t>
+          <t>Creditex Brokerage LLP</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr">
         <is>
-          <t>Artiq</t>
+          <t>Creditex Brokerage</t>
         </is>
       </c>
       <c r="G28" s="16" t="inlineStr">
         <is>
-          <t>https://artiq.co</t>
+          <t>https://creditexbrokeragellp.com</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
-          <t>07080437</t>
+          <t>OC315800</t>
         </is>
       </c>
       <c r="J28" s="16" t="inlineStr">
@@ -5531,22 +5533,22 @@
       </c>
       <c r="K28" s="15" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="L28" s="15" t="inlineStr">
         <is>
-          <t>18/11/2009</t>
+          <t>25/10/2005</t>
         </is>
       </c>
       <c r="M28" s="15" t="inlineStr">
         <is>
-          <t>1St Floor, 23-25 Great Sutton Street, London</t>
+          <t>2Nd Floor, Sancroft Rose Street, Paternoster Square, London</t>
         </is>
       </c>
       <c r="N28" s="15" t="inlineStr">
         <is>
-          <t>EC1V 0DN</t>
+          <t>EC4M 7DQ</t>
         </is>
       </c>
       <c r="O28" s="15" t="inlineStr">
@@ -5556,22 +5558,22 @@
       </c>
       <c r="P28" s="15" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="Q28" s="15" t="inlineStr">
         <is>
-          <t>Patrick McCrae</t>
+          <t>Emma Schneider</t>
         </is>
       </c>
       <c r="R28" s="15" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>PARTNER | UK &amp; EUROPE</t>
         </is>
       </c>
       <c r="S28" s="15" t="inlineStr">
         <is>
-          <t>hello@artiq.co</t>
+          <t>contact@creditexbrokeragellp.com</t>
         </is>
       </c>
       <c r="T28" s="15" t="inlineStr">
@@ -5581,22 +5583,22 @@
       </c>
       <c r="U28" s="16" t="inlineStr">
         <is>
-          <t>https://artiq.co/</t>
+          <t>https://creditexbrokeragellp.com/</t>
         </is>
       </c>
       <c r="X28" s="15" t="inlineStr">
         <is>
-          <t>1st Floor, 23-25 Great Sutton Street</t>
+          <t>Kemp House, 160 City Road</t>
         </is>
       </c>
       <c r="Y28" s="15" t="inlineStr">
         <is>
-          <t>EC1V 0DN</t>
+          <t>EC1V 2NX</t>
         </is>
       </c>
       <c r="Z28" s="15" t="inlineStr">
         <is>
-          <t>Website (1st Floor, 23-25 Great Sutton Street)</t>
+          <t>Website (Kemp House, 160 City Road)</t>
         </is>
       </c>
       <c r="AA28" s="15" t="inlineStr">
@@ -5631,8 +5633,16 @@
         <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
         <v/>
       </c>
-      <c r="AH28" s="15" t="n"/>
-      <c r="AI28" s="15" t="n"/>
+      <c r="AH28" s="15" t="inlineStr">
+        <is>
+          <t>office at Kemp House, 160 City Road</t>
+        </is>
+      </c>
+      <c r="AI28" s="16" t="inlineStr">
+        <is>
+          <t>https://creditexbrokeragellp.com/about/</t>
+        </is>
+      </c>
       <c r="AJ28" s="18">
         <f>IF(V28&lt;&gt;"",V28,S28)</f>
         <v/>
@@ -5675,35 +5685,37 @@
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>Professional services (LLP)</t>
+          <t>Tech / software</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>EC1V</t>
+          <t>EC2A</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>Creditex Brokerage LLP</t>
+          <t>Osf Digital UK Ltd</t>
         </is>
       </c>
       <c r="F29" s="15" t="inlineStr">
         <is>
-          <t>Creditex Brokerage</t>
+          <t>Osf Digital</t>
         </is>
       </c>
       <c r="G29" s="16" t="inlineStr">
         <is>
-          <t>https://creditexbrokeragellp.com</t>
-        </is>
-      </c>
-      <c r="H29" s="15" t="n">
-        <v>25</v>
+          <t>https://osf.digital</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
       </c>
       <c r="I29" s="15" t="inlineStr">
         <is>
-          <t>OC315800</t>
+          <t>03844574</t>
         </is>
       </c>
       <c r="J29" s="16" t="inlineStr">
@@ -5718,17 +5730,17 @@
       </c>
       <c r="L29" s="15" t="inlineStr">
         <is>
-          <t>25/10/2005</t>
+          <t>20/09/1999</t>
         </is>
       </c>
       <c r="M29" s="15" t="inlineStr">
         <is>
-          <t>2Nd Floor, Sancroft Rose Street, Paternoster Square, London</t>
+          <t>First Floor, 28-30 Worship Street, London</t>
         </is>
       </c>
       <c r="N29" s="15" t="inlineStr">
         <is>
-          <t>EC4M 7DQ</t>
+          <t>EC2A 2AH</t>
         </is>
       </c>
       <c r="O29" s="15" t="inlineStr">
@@ -5738,22 +5750,22 @@
       </c>
       <c r="P29" s="15" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>David</t>
         </is>
       </c>
       <c r="Q29" s="15" t="inlineStr">
         <is>
-          <t>Emma Schneider</t>
+          <t>David Northington</t>
         </is>
       </c>
       <c r="R29" s="15" t="inlineStr">
         <is>
-          <t>PARTNER | UK &amp; EUROPE</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="S29" s="15" t="inlineStr">
         <is>
-          <t>contact@creditexbrokeragellp.com</t>
+          <t>request@osf.digital</t>
         </is>
       </c>
       <c r="T29" s="15" t="inlineStr">
@@ -5763,27 +5775,27 @@
       </c>
       <c r="U29" s="16" t="inlineStr">
         <is>
-          <t>https://creditexbrokeragellp.com/</t>
+          <t>https://osf.digital/</t>
         </is>
       </c>
       <c r="X29" s="15" t="inlineStr">
         <is>
-          <t>Kemp House, 160 City Road</t>
+          <t>Sixth Floor, 28-30 Worship Street</t>
         </is>
       </c>
       <c r="Y29" s="15" t="inlineStr">
         <is>
-          <t>EC1V 2NX</t>
+          <t>EC2A 2AH</t>
         </is>
       </c>
       <c r="Z29" s="15" t="inlineStr">
         <is>
-          <t>Website (Kemp House, 160 City Road)</t>
+          <t>Website (Sixth Floor, 28-30 Worship Street)</t>
         </is>
       </c>
       <c r="AA29" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AB29" s="15" t="n">
@@ -5791,12 +5803,12 @@
       </c>
       <c r="AC29" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AD29" s="15" t="inlineStr">
         <is>
-          <t>Monday 12 October at 18:00</t>
+          <t>Monday 28 September at 17:40</t>
         </is>
       </c>
       <c r="AE29" s="15" t="inlineStr">
@@ -5806,23 +5818,15 @@
       </c>
       <c r="AF29" s="15" t="inlineStr">
         <is>
-          <t>6-a-side</t>
+          <t>5-a-side</t>
         </is>
       </c>
       <c r="AG29" s="17">
         <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
         <v/>
       </c>
-      <c r="AH29" s="15" t="inlineStr">
-        <is>
-          <t>office at Kemp House, 160 City Road</t>
-        </is>
-      </c>
-      <c r="AI29" s="16" t="inlineStr">
-        <is>
-          <t>https://creditexbrokeragellp.com/about/</t>
-        </is>
-      </c>
+      <c r="AH29" s="15" t="n"/>
+      <c r="AI29" s="15" t="n"/>
       <c r="AJ29" s="18">
         <f>IF(V29&lt;&gt;"",V29,S29)</f>
         <v/>
@@ -5865,37 +5869,35 @@
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Tech / software</t>
+          <t>Marketing / agency</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>EC2A</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>Osf Digital UK Ltd</t>
+          <t>Windfall Films Limited</t>
         </is>
       </c>
       <c r="F30" s="15" t="inlineStr">
         <is>
-          <t>Osf Digital</t>
+          <t>Windfall Films</t>
         </is>
       </c>
       <c r="G30" s="16" t="inlineStr">
         <is>
-          <t>https://osf.digital</t>
-        </is>
-      </c>
-      <c r="H30" s="15" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
+          <t>https://windfallfilms.com</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>20</v>
       </c>
       <c r="I30" s="15" t="inlineStr">
         <is>
-          <t>03844574</t>
+          <t>02205891</t>
         </is>
       </c>
       <c r="J30" s="16" t="inlineStr">
@@ -5910,17 +5912,17 @@
       </c>
       <c r="L30" s="15" t="inlineStr">
         <is>
-          <t>20/09/1999</t>
+          <t>16/12/1987</t>
         </is>
       </c>
       <c r="M30" s="15" t="inlineStr">
         <is>
-          <t>First Floor, 28-30 Worship Street, London</t>
+          <t>1-3 St. Peter'S Street, London</t>
         </is>
       </c>
       <c r="N30" s="15" t="inlineStr">
         <is>
-          <t>EC2A 2AH</t>
+          <t>N1 8JD</t>
         </is>
       </c>
       <c r="O30" s="15" t="inlineStr">
@@ -5930,22 +5932,22 @@
       </c>
       <c r="P30" s="15" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Carlo</t>
         </is>
       </c>
       <c r="Q30" s="15" t="inlineStr">
         <is>
-          <t>David Northington</t>
+          <t>Carlo Massarella</t>
         </is>
       </c>
       <c r="R30" s="15" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="S30" s="15" t="inlineStr">
         <is>
-          <t>request@osf.digital</t>
+          <t>enquiries@windfallfilms.com</t>
         </is>
       </c>
       <c r="T30" s="15" t="inlineStr">
@@ -5955,40 +5957,40 @@
       </c>
       <c r="U30" s="16" t="inlineStr">
         <is>
-          <t>https://osf.digital/</t>
+          <t>https://windfallfilms.com/contact</t>
         </is>
       </c>
       <c r="X30" s="15" t="inlineStr">
         <is>
-          <t>Sixth Floor, 28-30 Worship Street</t>
+          <t>1-3 St. Peter's Street</t>
         </is>
       </c>
       <c r="Y30" s="15" t="inlineStr">
         <is>
-          <t>EC2A 2AH</t>
+          <t>N1 8JD</t>
         </is>
       </c>
       <c r="Z30" s="15" t="inlineStr">
         <is>
-          <t>Website (Sixth Floor, 28-30 Worship Street)</t>
+          <t>Website (1-3 St. Peter's Street)</t>
         </is>
       </c>
       <c r="AA30" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AB30" s="15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AC30" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AD30" s="15" t="inlineStr">
         <is>
-          <t>Monday 28 September at 17:40</t>
+          <t>Monday 12 October at 18:00</t>
         </is>
       </c>
       <c r="AE30" s="15" t="inlineStr">
@@ -5998,7 +6000,7 @@
       </c>
       <c r="AF30" s="15" t="inlineStr">
         <is>
-          <t>5-a-side</t>
+          <t>6-a-side</t>
         </is>
       </c>
       <c r="AG30" s="17">
@@ -6054,30 +6056,30 @@
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>EC1R</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
-          <t>Windfall Films Limited</t>
+          <t>72 Films Limited</t>
         </is>
       </c>
       <c r="F31" s="15" t="inlineStr">
         <is>
-          <t>Windfall Films</t>
+          <t>72 Films</t>
         </is>
       </c>
       <c r="G31" s="16" t="inlineStr">
         <is>
-          <t>https://windfallfilms.com</t>
+          <t>https://72films.com</t>
         </is>
       </c>
       <c r="H31" s="15" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I31" s="15" t="inlineStr">
         <is>
-          <t>02205891</t>
+          <t>10075517</t>
         </is>
       </c>
       <c r="J31" s="16" t="inlineStr">
@@ -6087,22 +6089,22 @@
       </c>
       <c r="K31" s="15" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="L31" s="15" t="inlineStr">
         <is>
-          <t>16/12/1987</t>
+          <t>21/03/2016</t>
         </is>
       </c>
       <c r="M31" s="15" t="inlineStr">
         <is>
-          <t>1-3 St. Peter'S Street, London</t>
+          <t>1St Floor, No.1, Amwell Street, London</t>
         </is>
       </c>
       <c r="N31" s="15" t="inlineStr">
         <is>
-          <t>N1 8JD</t>
+          <t>EC1R 1UL</t>
         </is>
       </c>
       <c r="O31" s="15" t="inlineStr">
@@ -6112,22 +6114,22 @@
       </c>
       <c r="P31" s="15" t="inlineStr">
         <is>
-          <t>Carlo</t>
+          <t>David</t>
         </is>
       </c>
       <c r="Q31" s="15" t="inlineStr">
         <is>
-          <t>Carlo Massarella</t>
+          <t>David Glover</t>
         </is>
       </c>
       <c r="R31" s="15" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Founder/CEO</t>
         </is>
       </c>
       <c r="S31" s="15" t="inlineStr">
         <is>
-          <t>enquiries@windfallfilms.com</t>
+          <t>info@72films.com</t>
         </is>
       </c>
       <c r="T31" s="15" t="inlineStr">
@@ -6137,22 +6139,22 @@
       </c>
       <c r="U31" s="16" t="inlineStr">
         <is>
-          <t>https://windfallfilms.com/contact</t>
+          <t>https://72films.com/contact/</t>
         </is>
       </c>
       <c r="X31" s="15" t="inlineStr">
         <is>
-          <t>1-3 St. Peter's Street</t>
+          <t>1st Floor, 1 Amwell Street</t>
         </is>
       </c>
       <c r="Y31" s="15" t="inlineStr">
         <is>
-          <t>N1 8JD</t>
+          <t>EC1R 1UL</t>
         </is>
       </c>
       <c r="Z31" s="15" t="inlineStr">
         <is>
-          <t>Website (1-3 St. Peter's Street)</t>
+          <t>Website (1st Floor, 1 Amwell Street)</t>
         </is>
       </c>
       <c r="AA31" s="15" t="inlineStr">
@@ -6231,35 +6233,37 @@
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Marketing / agency</t>
+          <t>Tech / software</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>EC1R</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>72 Films Limited</t>
+          <t>Testingxperts Limited</t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr">
         <is>
-          <t>72 Films</t>
+          <t>Testingxperts</t>
         </is>
       </c>
       <c r="G32" s="16" t="inlineStr">
         <is>
-          <t>https://72films.com</t>
-        </is>
-      </c>
-      <c r="H32" s="15" t="n">
-        <v>24</v>
+          <t>https://www.testingxperts.com</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
       </c>
       <c r="I32" s="15" t="inlineStr">
         <is>
-          <t>10075517</t>
+          <t>10491678</t>
         </is>
       </c>
       <c r="J32" s="16" t="inlineStr">
@@ -6274,17 +6278,17 @@
       </c>
       <c r="L32" s="15" t="inlineStr">
         <is>
-          <t>21/03/2016</t>
+          <t>22/11/2016</t>
         </is>
       </c>
       <c r="M32" s="15" t="inlineStr">
         <is>
-          <t>1St Floor, No.1, Amwell Street, London</t>
+          <t>299A Bethnal Green Road, London</t>
         </is>
       </c>
       <c r="N32" s="15" t="inlineStr">
         <is>
-          <t>EC1R 1UL</t>
+          <t>E2 6AH</t>
         </is>
       </c>
       <c r="O32" s="15" t="inlineStr">
@@ -6294,22 +6298,22 @@
       </c>
       <c r="P32" s="15" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Manish</t>
         </is>
       </c>
       <c r="Q32" s="15" t="inlineStr">
         <is>
-          <t>David Glover</t>
+          <t>Manish Gupta</t>
         </is>
       </c>
       <c r="R32" s="15" t="inlineStr">
         <is>
-          <t>Founder/CEO</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="S32" s="15" t="inlineStr">
         <is>
-          <t>info@72films.com</t>
+          <t>info@testingxperts.com</t>
         </is>
       </c>
       <c r="T32" s="15" t="inlineStr">
@@ -6319,27 +6323,23 @@
       </c>
       <c r="U32" s="16" t="inlineStr">
         <is>
-          <t>https://72films.com/contact/</t>
-        </is>
-      </c>
-      <c r="X32" s="15" t="inlineStr">
-        <is>
-          <t>1st Floor, 1 Amwell Street</t>
-        </is>
-      </c>
+          <t>https://www.testingxperts.com/</t>
+        </is>
+      </c>
+      <c r="X32" s="15" t="n"/>
       <c r="Y32" s="15" t="inlineStr">
         <is>
-          <t>EC1R 1UL</t>
+          <t>E2 6AH</t>
         </is>
       </c>
       <c r="Z32" s="15" t="inlineStr">
         <is>
-          <t>Website (1st Floor, 1 Amwell Street)</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="AA32" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AB32" s="15" t="n">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="AC32" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AD32" s="15" t="inlineStr">
         <is>
-          <t>Monday 12 October at 18:00</t>
+          <t>Monday 28 September at 17:40</t>
         </is>
       </c>
       <c r="AE32" s="15" t="inlineStr">
@@ -6362,15 +6362,23 @@
       </c>
       <c r="AF32" s="15" t="inlineStr">
         <is>
-          <t>6-a-side</t>
+          <t>5-a-side</t>
         </is>
       </c>
       <c r="AG32" s="17">
         <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
         <v/>
       </c>
-      <c r="AH32" s="15" t="n"/>
-      <c r="AI32" s="15" t="n"/>
+      <c r="AH32" s="15" t="inlineStr">
+        <is>
+          <t>award</t>
+        </is>
+      </c>
+      <c r="AI32" s="16" t="inlineStr">
+        <is>
+          <t>https://www.testingxperts.com/contact-us/</t>
+        </is>
+      </c>
       <c r="AJ32" s="18">
         <f>IF(V32&lt;&gt;"",V32,S32)</f>
         <v/>
@@ -6413,37 +6421,35 @@
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Tech / software</t>
+          <t>Marketing / agency</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>N7</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
         <is>
-          <t>Testingxperts Limited</t>
+          <t>October Films Ltd</t>
         </is>
       </c>
       <c r="F33" s="15" t="inlineStr">
         <is>
-          <t>Testingxperts</t>
+          <t>October Films</t>
         </is>
       </c>
       <c r="G33" s="16" t="inlineStr">
         <is>
-          <t>https://www.testingxperts.com</t>
-        </is>
-      </c>
-      <c r="H33" s="15" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
+          <t>https://octoberfilms.co.uk</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>25</v>
       </c>
       <c r="I33" s="15" t="inlineStr">
         <is>
-          <t>10491678</t>
+          <t>02328023</t>
         </is>
       </c>
       <c r="J33" s="16" t="inlineStr">
@@ -6453,22 +6459,22 @@
       </c>
       <c r="K33" s="15" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="L33" s="15" t="inlineStr">
         <is>
-          <t>22/11/2016</t>
+          <t>13/12/1988</t>
         </is>
       </c>
       <c r="M33" s="15" t="inlineStr">
         <is>
-          <t>299A Bethnal Green Road, London</t>
+          <t>Benwell Studios, 11-13 Benwell Road, London</t>
         </is>
       </c>
       <c r="N33" s="15" t="inlineStr">
         <is>
-          <t>E2 6AH</t>
+          <t>N7 7BL</t>
         </is>
       </c>
       <c r="O33" s="15" t="inlineStr">
@@ -6478,22 +6484,22 @@
       </c>
       <c r="P33" s="15" t="inlineStr">
         <is>
-          <t>Manish</t>
+          <t>Jane</t>
         </is>
       </c>
       <c r="Q33" s="15" t="inlineStr">
         <is>
-          <t>Manish Gupta</t>
+          <t>Jane Manning</t>
         </is>
       </c>
       <c r="R33" s="15" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Chief Operating Officer</t>
         </is>
       </c>
       <c r="S33" s="15" t="inlineStr">
         <is>
-          <t>info@testingxperts.com</t>
+          <t>info@octoberfilms.co.uk</t>
         </is>
       </c>
       <c r="T33" s="15" t="inlineStr">
@@ -6503,36 +6509,40 @@
       </c>
       <c r="U33" s="16" t="inlineStr">
         <is>
-          <t>https://www.testingxperts.com/</t>
-        </is>
-      </c>
-      <c r="X33" s="15" t="n"/>
+          <t>https://octoberfilms.co.uk/contact/</t>
+        </is>
+      </c>
+      <c r="X33" s="15" t="inlineStr">
+        <is>
+          <t>11/13 Benwell Road</t>
+        </is>
+      </c>
       <c r="Y33" s="15" t="inlineStr">
         <is>
-          <t>E2 6AH</t>
+          <t>N7 7BL</t>
         </is>
       </c>
       <c r="Z33" s="15" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Website (11/13 Benwell Road)</t>
         </is>
       </c>
       <c r="AA33" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Market Road</t>
         </is>
       </c>
       <c r="AB33" s="15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC33" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Market Road</t>
         </is>
       </c>
       <c r="AD33" s="15" t="inlineStr">
         <is>
-          <t>Monday 28 September at 17:40</t>
+          <t>Monday 28 September at 18:00</t>
         </is>
       </c>
       <c r="AE33" s="15" t="inlineStr">
@@ -6551,12 +6561,12 @@
       </c>
       <c r="AH33" s="15" t="inlineStr">
         <is>
-          <t>award</t>
+          <t>won over 100 prestige awards including EMMY, BAFTA</t>
         </is>
       </c>
       <c r="AI33" s="16" t="inlineStr">
         <is>
-          <t>https://www.testingxperts.com/contact-us/</t>
+          <t>https://octoberfilms.co.uk/about/</t>
         </is>
       </c>
       <c r="AJ33" s="18">
@@ -6601,35 +6611,37 @@
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>Marketing / agency</t>
+          <t>Tech / software</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>EC2M</t>
         </is>
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>October Films Ltd</t>
+          <t>Fenergo UK Limited</t>
         </is>
       </c>
       <c r="F34" s="15" t="inlineStr">
         <is>
-          <t>October Films</t>
+          <t>Fenergo</t>
         </is>
       </c>
       <c r="G34" s="16" t="inlineStr">
         <is>
-          <t>https://octoberfilms.co.uk</t>
-        </is>
-      </c>
-      <c r="H34" s="15" t="n">
-        <v>25</v>
+          <t>https://www.fenergo.com</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
       </c>
       <c r="I34" s="15" t="inlineStr">
         <is>
-          <t>02328023</t>
+          <t>10267569</t>
         </is>
       </c>
       <c r="J34" s="16" t="inlineStr">
@@ -6644,17 +6656,17 @@
       </c>
       <c r="L34" s="15" t="inlineStr">
         <is>
-          <t>13/12/1988</t>
+          <t>07/07/2016</t>
         </is>
       </c>
       <c r="M34" s="15" t="inlineStr">
         <is>
-          <t>Benwell Studios, 11-13 Benwell Road, London</t>
+          <t>Floor One, 24 King William Street, London</t>
         </is>
       </c>
       <c r="N34" s="15" t="inlineStr">
         <is>
-          <t>N7 7BL</t>
+          <t>EC4R 9AT</t>
         </is>
       </c>
       <c r="O34" s="15" t="inlineStr">
@@ -6664,22 +6676,22 @@
       </c>
       <c r="P34" s="15" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Marc</t>
         </is>
       </c>
       <c r="Q34" s="15" t="inlineStr">
         <is>
-          <t>Jane Manning</t>
+          <t>Marc Murphy</t>
         </is>
       </c>
       <c r="R34" s="15" t="inlineStr">
         <is>
-          <t>Chief Operating Officer</t>
+          <t>CEO &amp; Founder</t>
         </is>
       </c>
       <c r="S34" s="15" t="inlineStr">
         <is>
-          <t>info@octoberfilms.co.uk</t>
+          <t>hello@fenergo.com</t>
         </is>
       </c>
       <c r="T34" s="15" t="inlineStr">
@@ -6689,27 +6701,23 @@
       </c>
       <c r="U34" s="16" t="inlineStr">
         <is>
-          <t>https://octoberfilms.co.uk/contact/</t>
-        </is>
-      </c>
-      <c r="X34" s="15" t="inlineStr">
-        <is>
-          <t>11/13 Benwell Road</t>
-        </is>
-      </c>
+          <t>https://www.fenergo.com/</t>
+        </is>
+      </c>
+      <c r="X34" s="15" t="n"/>
       <c r="Y34" s="15" t="inlineStr">
         <is>
-          <t>N7 7BL</t>
+          <t>EC2M 7LS</t>
         </is>
       </c>
       <c r="Z34" s="15" t="inlineStr">
         <is>
-          <t>Website (11/13 Benwell Road)</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="AA34" s="15" t="inlineStr">
         <is>
-          <t>Market Road</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AB34" s="15" t="n">
@@ -6717,12 +6725,12 @@
       </c>
       <c r="AC34" s="15" t="inlineStr">
         <is>
-          <t>Market Road</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AD34" s="15" t="inlineStr">
         <is>
-          <t>Monday 28 September at 18:00</t>
+          <t>Monday 28 September at 17:40</t>
         </is>
       </c>
       <c r="AE34" s="15" t="inlineStr">
@@ -6739,16 +6747,8 @@
         <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
         <v/>
       </c>
-      <c r="AH34" s="15" t="inlineStr">
-        <is>
-          <t>won over 100 prestige awards including EMMY, BAFTA</t>
-        </is>
-      </c>
-      <c r="AI34" s="16" t="inlineStr">
-        <is>
-          <t>https://octoberfilms.co.uk/about/</t>
-        </is>
-      </c>
+      <c r="AH34" s="15" t="n"/>
+      <c r="AI34" s="15" t="n"/>
       <c r="AJ34" s="18">
         <f>IF(V34&lt;&gt;"",V34,S34)</f>
         <v/>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>Tech / software</t>
+          <t>Consultancy</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
@@ -6801,17 +6801,17 @@
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
-          <t>Fenergo UK Limited</t>
+          <t>Yendall Hunter Limited</t>
         </is>
       </c>
       <c r="F35" s="15" t="inlineStr">
         <is>
-          <t>Fenergo</t>
+          <t>Yendall Hunter</t>
         </is>
       </c>
       <c r="G35" s="16" t="inlineStr">
         <is>
-          <t>https://www.fenergo.com</t>
+          <t>https://www.yendallhunter.com</t>
         </is>
       </c>
       <c r="H35" s="15" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="I35" s="15" t="inlineStr">
         <is>
-          <t>10267569</t>
+          <t>09410777</t>
         </is>
       </c>
       <c r="J35" s="16" t="inlineStr">
@@ -6831,22 +6831,22 @@
       </c>
       <c r="K35" s="15" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L35" s="15" t="inlineStr">
         <is>
-          <t>07/07/2016</t>
+          <t>28/01/2015</t>
         </is>
       </c>
       <c r="M35" s="15" t="inlineStr">
         <is>
-          <t>Floor One, 24 King William Street, London</t>
+          <t>Dashwood House, 69 Old Broad Street, London</t>
         </is>
       </c>
       <c r="N35" s="15" t="inlineStr">
         <is>
-          <t>EC4R 9AT</t>
+          <t>EC2M 1QS</t>
         </is>
       </c>
       <c r="O35" s="15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="P35" s="15" t="inlineStr">
         <is>
-          <t>Marc</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="Q35" s="15" t="inlineStr">
         <is>
-          <t>Marc Murphy</t>
+          <t>Martin Hunter</t>
         </is>
       </c>
       <c r="R35" s="15" t="inlineStr">
         <is>
-          <t>CEO &amp; Founder</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="S35" s="15" t="inlineStr">
         <is>
-          <t>hello@fenergo.com</t>
+          <t>info@yendallhunter.com</t>
         </is>
       </c>
       <c r="T35" s="15" t="inlineStr">
@@ -6881,18 +6881,22 @@
       </c>
       <c r="U35" s="16" t="inlineStr">
         <is>
-          <t>https://www.fenergo.com/</t>
-        </is>
-      </c>
-      <c r="X35" s="15" t="n"/>
+          <t>https://www.yendallhunter.com/</t>
+        </is>
+      </c>
+      <c r="X35" s="15" t="inlineStr">
+        <is>
+          <t>69 Old Broad Street</t>
+        </is>
+      </c>
       <c r="Y35" s="15" t="inlineStr">
         <is>
-          <t>EC2M 7LS</t>
+          <t>EC2M 1QS</t>
         </is>
       </c>
       <c r="Z35" s="15" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Website (69 Old Broad Street)</t>
         </is>
       </c>
       <c r="AA35" s="15" t="inlineStr">
@@ -6971,27 +6975,27 @@
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>Consultancy</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>EC2M</t>
+          <t>EC1R</t>
         </is>
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>Yendall Hunter Limited</t>
+          <t>Fluence Energy UK Limited</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
-          <t>Yendall Hunter</t>
+          <t>Fluence Energy</t>
         </is>
       </c>
       <c r="G36" s="16" t="inlineStr">
         <is>
-          <t>https://www.yendallhunter.com</t>
+          <t>https://fluenceenergy.com</t>
         </is>
       </c>
       <c r="H36" s="15" t="inlineStr">
@@ -7001,7 +7005,7 @@
       </c>
       <c r="I36" s="15" t="inlineStr">
         <is>
-          <t>09410777</t>
+          <t>14401806</t>
         </is>
       </c>
       <c r="J36" s="16" t="inlineStr">
@@ -7011,22 +7015,22 @@
       </c>
       <c r="K36" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="L36" s="15" t="inlineStr">
         <is>
-          <t>28/01/2015</t>
+          <t>06/10/2022</t>
         </is>
       </c>
       <c r="M36" s="15" t="inlineStr">
         <is>
-          <t>Dashwood House, 69 Old Broad Street, London</t>
+          <t>Unit 180, 3Rd Floor Exmouth House 3/11 Pine Street, Farringdon, London</t>
         </is>
       </c>
       <c r="N36" s="15" t="inlineStr">
         <is>
-          <t>EC2M 1QS</t>
+          <t>EC1R 0JH</t>
         </is>
       </c>
       <c r="O36" s="15" t="inlineStr">
@@ -7036,22 +7040,22 @@
       </c>
       <c r="P36" s="15" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Julian</t>
         </is>
       </c>
       <c r="Q36" s="15" t="inlineStr">
         <is>
-          <t>Martin Hunter</t>
+          <t>Julian Nebreda</t>
         </is>
       </c>
       <c r="R36" s="15" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="S36" s="15" t="inlineStr">
         <is>
-          <t>info@yendallhunter.com</t>
+          <t>branding@fluenceenergy.com</t>
         </is>
       </c>
       <c r="T36" s="15" t="inlineStr">
@@ -7061,27 +7065,27 @@
       </c>
       <c r="U36" s="16" t="inlineStr">
         <is>
-          <t>https://www.yendallhunter.com/</t>
+          <t>https://fluenceenergy.com/about/media-room/</t>
         </is>
       </c>
       <c r="X36" s="15" t="inlineStr">
         <is>
-          <t>69 Old Broad Street</t>
+          <t>Unit 180, 3rd Floor Exmouth House 3/11 Pine Street</t>
         </is>
       </c>
       <c r="Y36" s="15" t="inlineStr">
         <is>
-          <t>EC2M 1QS</t>
+          <t>EC1R 0JH</t>
         </is>
       </c>
       <c r="Z36" s="15" t="inlineStr">
         <is>
-          <t>Website (69 Old Broad Street)</t>
+          <t>Website (Unit 180, 3rd Floor Exmouth House 3/11 Pine Street)</t>
         </is>
       </c>
       <c r="AA36" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AB36" s="15" t="n">
@@ -7089,12 +7093,12 @@
       </c>
       <c r="AC36" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AD36" s="15" t="inlineStr">
         <is>
-          <t>Monday 28 September at 17:40</t>
+          <t>Monday 12 October at 18:00</t>
         </is>
       </c>
       <c r="AE36" s="15" t="inlineStr">
@@ -7104,7 +7108,7 @@
       </c>
       <c r="AF36" s="15" t="inlineStr">
         <is>
-          <t>5-a-side</t>
+          <t>6-a-side</t>
         </is>
       </c>
       <c r="AG36" s="17">
@@ -7155,27 +7159,27 @@
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Finance / accounting</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>EC1R</t>
+          <t>EC3A</t>
         </is>
       </c>
       <c r="E37" s="15" t="inlineStr">
         <is>
-          <t>Fluence Energy UK Limited</t>
+          <t>Jenoa Limited</t>
         </is>
       </c>
       <c r="F37" s="15" t="inlineStr">
         <is>
-          <t>Fluence Energy</t>
+          <t>Jenoa</t>
         </is>
       </c>
       <c r="G37" s="16" t="inlineStr">
         <is>
-          <t>https://fluenceenergy.com</t>
+          <t>https://jenoa.com:443</t>
         </is>
       </c>
       <c r="H37" s="15" t="inlineStr">
@@ -7185,7 +7189,7 @@
       </c>
       <c r="I37" s="15" t="inlineStr">
         <is>
-          <t>14401806</t>
+          <t>12292684</t>
         </is>
       </c>
       <c r="J37" s="16" t="inlineStr">
@@ -7200,17 +7204,17 @@
       </c>
       <c r="L37" s="15" t="inlineStr">
         <is>
-          <t>06/10/2022</t>
+          <t>31/10/2019</t>
         </is>
       </c>
       <c r="M37" s="15" t="inlineStr">
         <is>
-          <t>Unit 180, 3Rd Floor Exmouth House 3/11 Pine Street, Farringdon, London</t>
+          <t>C/O Clyde &amp; Co Llp, St Botolph Building, 138 Houndsditch, London</t>
         </is>
       </c>
       <c r="N37" s="15" t="inlineStr">
         <is>
-          <t>EC1R 0JH</t>
+          <t>EC3A 7AR</t>
         </is>
       </c>
       <c r="O37" s="15" t="inlineStr">
@@ -7220,12 +7224,12 @@
       </c>
       <c r="P37" s="15" t="inlineStr">
         <is>
-          <t>Julian</t>
+          <t>Mahboob</t>
         </is>
       </c>
       <c r="Q37" s="15" t="inlineStr">
         <is>
-          <t>Julian Nebreda</t>
+          <t>Mahboob Khan</t>
         </is>
       </c>
       <c r="R37" s="15" t="inlineStr">
@@ -7235,7 +7239,7 @@
       </c>
       <c r="S37" s="15" t="inlineStr">
         <is>
-          <t>branding@fluenceenergy.com</t>
+          <t>london@jenoa.com</t>
         </is>
       </c>
       <c r="T37" s="15" t="inlineStr">
@@ -7245,40 +7249,36 @@
       </c>
       <c r="U37" s="16" t="inlineStr">
         <is>
-          <t>https://fluenceenergy.com/about/media-room/</t>
-        </is>
-      </c>
-      <c r="X37" s="15" t="inlineStr">
-        <is>
-          <t>Unit 180, 3rd Floor Exmouth House 3/11 Pine Street</t>
-        </is>
-      </c>
+          <t>https://jenoa.com/en/locations/</t>
+        </is>
+      </c>
+      <c r="X37" s="15" t="n"/>
       <c r="Y37" s="15" t="inlineStr">
         <is>
-          <t>EC1R 0JH</t>
+          <t>EC3A 8BE</t>
         </is>
       </c>
       <c r="Z37" s="15" t="inlineStr">
         <is>
-          <t>Website (Unit 180, 3rd Floor Exmouth House 3/11 Pine Street)</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="AA37" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AB37" s="15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC37" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AD37" s="15" t="inlineStr">
         <is>
-          <t>Monday 12 October at 18:00</t>
+          <t>Monday 28 September at 17:40</t>
         </is>
       </c>
       <c r="AE37" s="15" t="inlineStr">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="AF37" s="15" t="inlineStr">
         <is>
-          <t>6-a-side</t>
+          <t>5-a-side</t>
         </is>
       </c>
       <c r="AG37" s="17">
@@ -7335,31 +7335,31 @@
         <v>36</v>
       </c>
       <c r="B38" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Finance / accounting</t>
+          <t>Tech / software</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>EC3A</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t>Jenoa Limited</t>
+          <t>Vendavo UK Limited</t>
         </is>
       </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
-          <t>Jenoa</t>
+          <t>Vendavo</t>
         </is>
       </c>
       <c r="G38" s="16" t="inlineStr">
         <is>
-          <t>https://jenoa.com:443</t>
+          <t>https://www.vendavo.com</t>
         </is>
       </c>
       <c r="H38" s="15" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="I38" s="15" t="inlineStr">
         <is>
-          <t>12292684</t>
+          <t>05724979</t>
         </is>
       </c>
       <c r="J38" s="16" t="inlineStr">
@@ -7379,22 +7379,22 @@
       </c>
       <c r="K38" s="15" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="L38" s="15" t="inlineStr">
         <is>
-          <t>31/10/2019</t>
+          <t>28/02/2006</t>
         </is>
       </c>
       <c r="M38" s="15" t="inlineStr">
         <is>
-          <t>C/O Clyde &amp; Co Llp, St Botolph Building, 138 Houndsditch, London</t>
+          <t>2Nd Floor, 168 Shoreditch High Street, London</t>
         </is>
       </c>
       <c r="N38" s="15" t="inlineStr">
         <is>
-          <t>EC3A 7AR</t>
+          <t>E1 6RA</t>
         </is>
       </c>
       <c r="O38" s="15" t="inlineStr">
@@ -7402,45 +7402,33 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P38" s="15" t="inlineStr">
-        <is>
-          <t>Mahboob</t>
-        </is>
-      </c>
-      <c r="Q38" s="15" t="inlineStr">
-        <is>
-          <t>Mahboob Khan</t>
-        </is>
-      </c>
-      <c r="R38" s="15" t="inlineStr">
-        <is>
-          <t>Chief Executive Officer</t>
-        </is>
-      </c>
+      <c r="P38" s="15" t="n"/>
+      <c r="Q38" s="15" t="n"/>
+      <c r="R38" s="15" t="n"/>
       <c r="S38" s="15" t="inlineStr">
         <is>
-          <t>london@jenoa.com</t>
+          <t>info@vendavo.com</t>
         </is>
       </c>
       <c r="T38" s="15" t="inlineStr">
         <is>
-          <t>a/b named person via general inbox</t>
+          <t>c general inbox</t>
         </is>
       </c>
       <c r="U38" s="16" t="inlineStr">
         <is>
-          <t>https://jenoa.com/en/locations/</t>
+          <t>https://www.vendavo.com/company/contact/</t>
         </is>
       </c>
       <c r="X38" s="15" t="n"/>
       <c r="Y38" s="15" t="inlineStr">
         <is>
-          <t>EC3A 8BE</t>
+          <t>E1 6RA</t>
         </is>
       </c>
       <c r="Z38" s="15" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Registered office (no address on website)</t>
         </is>
       </c>
       <c r="AA38" s="15" t="inlineStr">
@@ -7449,7 +7437,7 @@
         </is>
       </c>
       <c r="AB38" s="15" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AC38" s="15" t="inlineStr">
         <is>
@@ -7519,7 +7507,7 @@
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>Tech / software</t>
+          <t>Marketing / agency</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
@@ -7529,17 +7517,17 @@
       </c>
       <c r="E39" s="15" t="inlineStr">
         <is>
-          <t>Vendavo UK Limited</t>
+          <t>Whitepaperco Limited</t>
         </is>
       </c>
       <c r="F39" s="15" t="inlineStr">
         <is>
-          <t>Vendavo</t>
+          <t>Whitepaperco</t>
         </is>
       </c>
       <c r="G39" s="16" t="inlineStr">
         <is>
-          <t>https://www.vendavo.com</t>
+          <t>https://www.whitepaperco.com</t>
         </is>
       </c>
       <c r="H39" s="15" t="inlineStr">
@@ -7549,7 +7537,7 @@
       </c>
       <c r="I39" s="15" t="inlineStr">
         <is>
-          <t>05724979</t>
+          <t>09980890</t>
         </is>
       </c>
       <c r="J39" s="16" t="inlineStr">
@@ -7559,22 +7547,22 @@
       </c>
       <c r="K39" s="15" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L39" s="15" t="inlineStr">
         <is>
-          <t>28/02/2006</t>
+          <t>01/02/2016</t>
         </is>
       </c>
       <c r="M39" s="15" t="inlineStr">
         <is>
-          <t>2Nd Floor, 168 Shoreditch High Street, London</t>
+          <t>Elder Studios, 4-6 Elder Street, London</t>
         </is>
       </c>
       <c r="N39" s="15" t="inlineStr">
         <is>
-          <t>E1 6RA</t>
+          <t>E1 6BT</t>
         </is>
       </c>
       <c r="O39" s="15" t="inlineStr">
@@ -7587,7 +7575,7 @@
       <c r="R39" s="15" t="n"/>
       <c r="S39" s="15" t="inlineStr">
         <is>
-          <t>info@vendavo.com</t>
+          <t>hello@whitepaperco.com</t>
         </is>
       </c>
       <c r="T39" s="15" t="inlineStr">
@@ -7597,18 +7585,22 @@
       </c>
       <c r="U39" s="16" t="inlineStr">
         <is>
-          <t>https://www.vendavo.com/company/contact/</t>
-        </is>
-      </c>
-      <c r="X39" s="15" t="n"/>
+          <t>https://www.whitepaperco.com/</t>
+        </is>
+      </c>
+      <c r="X39" s="15" t="inlineStr">
+        <is>
+          <t>Elder Studios, 4-6 Elder Street</t>
+        </is>
+      </c>
       <c r="Y39" s="15" t="inlineStr">
         <is>
-          <t>E1 6RA</t>
+          <t>E1 6BT</t>
         </is>
       </c>
       <c r="Z39" s="15" t="inlineStr">
         <is>
-          <t>Registered office (no address on website)</t>
+          <t>Website (Elder Studios, 4-6 Elder Street)</t>
         </is>
       </c>
       <c r="AA39" s="15" t="inlineStr">
@@ -7617,7 +7609,7 @@
         </is>
       </c>
       <c r="AB39" s="15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC39" s="15" t="inlineStr">
         <is>
@@ -7687,7 +7679,7 @@
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Marketing / agency</t>
+          <t>Tech / software</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
@@ -7697,17 +7689,17 @@
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t>Whitepaperco Limited</t>
+          <t>Made Tech Limited</t>
         </is>
       </c>
       <c r="F40" s="15" t="inlineStr">
         <is>
-          <t>Whitepaperco</t>
+          <t>Made Tech</t>
         </is>
       </c>
       <c r="G40" s="16" t="inlineStr">
         <is>
-          <t>https://www.whitepaperco.com</t>
+          <t>https://made.studio</t>
         </is>
       </c>
       <c r="H40" s="15" t="inlineStr">
@@ -7717,7 +7709,7 @@
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
-          <t>09980890</t>
+          <t>06591591</t>
         </is>
       </c>
       <c r="J40" s="16" t="inlineStr">
@@ -7727,22 +7719,22 @@
       </c>
       <c r="K40" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="L40" s="15" t="inlineStr">
         <is>
-          <t>01/02/2016</t>
+          <t>13/05/2008</t>
         </is>
       </c>
       <c r="M40" s="15" t="inlineStr">
         <is>
-          <t>Elder Studios, 4-6 Elder Street, London</t>
+          <t>Fora, 35-41 Folgate Street, London</t>
         </is>
       </c>
       <c r="N40" s="15" t="inlineStr">
         <is>
-          <t>E1 6BT</t>
+          <t>E1 6BX</t>
         </is>
       </c>
       <c r="O40" s="15" t="inlineStr">
@@ -7755,7 +7747,7 @@
       <c r="R40" s="15" t="n"/>
       <c r="S40" s="15" t="inlineStr">
         <is>
-          <t>hello@whitepaperco.com</t>
+          <t>hello@made.studio</t>
         </is>
       </c>
       <c r="T40" s="15" t="inlineStr">
@@ -7765,22 +7757,22 @@
       </c>
       <c r="U40" s="16" t="inlineStr">
         <is>
-          <t>https://www.whitepaperco.com/</t>
+          <t>https://made.studio/</t>
         </is>
       </c>
       <c r="X40" s="15" t="inlineStr">
         <is>
-          <t>Elder Studios, 4-6 Elder Street</t>
+          <t>FORA, 35-41 FOLGATE STREET</t>
         </is>
       </c>
       <c r="Y40" s="15" t="inlineStr">
         <is>
-          <t>E1 6BT</t>
+          <t>E1 6BX</t>
         </is>
       </c>
       <c r="Z40" s="15" t="inlineStr">
         <is>
-          <t>Website (Elder Studios, 4-6 Elder Street)</t>
+          <t>Website (FORA, 35-41 FOLGATE STREET)</t>
         </is>
       </c>
       <c r="AA40" s="15" t="inlineStr">
@@ -7789,7 +7781,7 @@
         </is>
       </c>
       <c r="AB40" s="15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC40" s="15" t="inlineStr">
         <is>
@@ -7859,27 +7851,27 @@
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>Tech / software</t>
+          <t>Professional services (LLP)</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>EC2A</t>
         </is>
       </c>
       <c r="E41" s="15" t="inlineStr">
         <is>
-          <t>Made Tech Limited</t>
+          <t>Gill Jennings &amp; Every LLP</t>
         </is>
       </c>
       <c r="F41" s="15" t="inlineStr">
         <is>
-          <t>Made Tech</t>
+          <t>Gill Jennings &amp; Every</t>
         </is>
       </c>
       <c r="G41" s="16" t="inlineStr">
         <is>
-          <t>https://made.studio</t>
+          <t>https://www.gje.com</t>
         </is>
       </c>
       <c r="H41" s="15" t="inlineStr">
@@ -7889,7 +7881,7 @@
       </c>
       <c r="I41" s="15" t="inlineStr">
         <is>
-          <t>06591591</t>
+          <t>OC313165</t>
         </is>
       </c>
       <c r="J41" s="16" t="inlineStr">
@@ -7904,17 +7896,17 @@
       </c>
       <c r="L41" s="15" t="inlineStr">
         <is>
-          <t>13/05/2008</t>
+          <t>09/05/2005</t>
         </is>
       </c>
       <c r="M41" s="15" t="inlineStr">
         <is>
-          <t>Fora, 35-41 Folgate Street, London</t>
+          <t>The Broadgate Tower, 20 Primrose Street, London</t>
         </is>
       </c>
       <c r="N41" s="15" t="inlineStr">
         <is>
-          <t>E1 6BX</t>
+          <t>EC2A 2ES</t>
         </is>
       </c>
       <c r="O41" s="15" t="inlineStr">
@@ -7927,7 +7919,7 @@
       <c r="R41" s="15" t="n"/>
       <c r="S41" s="15" t="inlineStr">
         <is>
-          <t>hello@made.studio</t>
+          <t>gje@gje.com</t>
         </is>
       </c>
       <c r="T41" s="15" t="inlineStr">
@@ -7937,22 +7929,18 @@
       </c>
       <c r="U41" s="16" t="inlineStr">
         <is>
-          <t>https://made.studio/</t>
-        </is>
-      </c>
-      <c r="X41" s="15" t="inlineStr">
-        <is>
-          <t>FORA, 35-41 FOLGATE STREET</t>
-        </is>
-      </c>
+          <t>https://www.gje.com/</t>
+        </is>
+      </c>
+      <c r="X41" s="15" t="n"/>
       <c r="Y41" s="15" t="inlineStr">
         <is>
-          <t>E1 6BX</t>
+          <t>EC2A 2ES</t>
         </is>
       </c>
       <c r="Z41" s="15" t="inlineStr">
         <is>
-          <t>Website (FORA, 35-41 FOLGATE STREET)</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="AA41" s="15" t="inlineStr">
@@ -7961,7 +7949,7 @@
         </is>
       </c>
       <c r="AB41" s="15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC41" s="15" t="inlineStr">
         <is>
@@ -8036,22 +8024,22 @@
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>EC2A</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>Gill Jennings &amp; Every LLP</t>
+          <t>Squadron LLP</t>
         </is>
       </c>
       <c r="F42" s="15" t="inlineStr">
         <is>
-          <t>Gill Jennings &amp; Every</t>
+          <t>Squadron</t>
         </is>
       </c>
       <c r="G42" s="16" t="inlineStr">
         <is>
-          <t>https://www.gje.com</t>
+          <t>https://squadron.com</t>
         </is>
       </c>
       <c r="H42" s="15" t="inlineStr">
@@ -8061,7 +8049,7 @@
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
-          <t>OC313165</t>
+          <t>OC449650</t>
         </is>
       </c>
       <c r="J42" s="16" t="inlineStr">
@@ -8076,17 +8064,17 @@
       </c>
       <c r="L42" s="15" t="inlineStr">
         <is>
-          <t>09/05/2005</t>
+          <t>25/10/2023</t>
         </is>
       </c>
       <c r="M42" s="15" t="inlineStr">
         <is>
-          <t>The Broadgate Tower, 20 Primrose Street, London</t>
+          <t>One Bishops Square, London</t>
         </is>
       </c>
       <c r="N42" s="15" t="inlineStr">
         <is>
-          <t>EC2A 2ES</t>
+          <t>E1 6AD</t>
         </is>
       </c>
       <c r="O42" s="15" t="inlineStr">
@@ -8099,7 +8087,7 @@
       <c r="R42" s="15" t="n"/>
       <c r="S42" s="15" t="inlineStr">
         <is>
-          <t>gje@gje.com</t>
+          <t>info@squadron.com</t>
         </is>
       </c>
       <c r="T42" s="15" t="inlineStr">
@@ -8109,18 +8097,18 @@
       </c>
       <c r="U42" s="16" t="inlineStr">
         <is>
-          <t>https://www.gje.com/</t>
+          <t>https://squadron.com/</t>
         </is>
       </c>
       <c r="X42" s="15" t="n"/>
       <c r="Y42" s="15" t="inlineStr">
         <is>
-          <t>EC2A 2ES</t>
+          <t>E1 6AD</t>
         </is>
       </c>
       <c r="Z42" s="15" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Registered office (no address on website)</t>
         </is>
       </c>
       <c r="AA42" s="15" t="inlineStr">
@@ -8204,32 +8192,30 @@
       </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>EC2M</t>
         </is>
       </c>
       <c r="E43" s="15" t="inlineStr">
         <is>
-          <t>Squadron LLP</t>
+          <t>Rbb Economics LLP</t>
         </is>
       </c>
       <c r="F43" s="15" t="inlineStr">
         <is>
-          <t>Squadron</t>
+          <t>Rbb Economics</t>
         </is>
       </c>
       <c r="G43" s="16" t="inlineStr">
         <is>
-          <t>https://squadron.com</t>
-        </is>
-      </c>
-      <c r="H43" s="15" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
+          <t>https://www.rbbecon.com</t>
+        </is>
+      </c>
+      <c r="H43" s="15" t="n">
+        <v>190</v>
       </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
-          <t>OC449650</t>
+          <t>OC315356</t>
         </is>
       </c>
       <c r="J43" s="16" t="inlineStr">
@@ -8239,22 +8225,22 @@
       </c>
       <c r="K43" s="15" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="L43" s="15" t="inlineStr">
         <is>
-          <t>25/10/2023</t>
+          <t>26/09/2005</t>
         </is>
       </c>
       <c r="M43" s="15" t="inlineStr">
         <is>
-          <t>One Bishops Square, London</t>
+          <t>199 Bishopsgate, London</t>
         </is>
       </c>
       <c r="N43" s="15" t="inlineStr">
         <is>
-          <t>E1 6AD</t>
+          <t>EC2M 3TY</t>
         </is>
       </c>
       <c r="O43" s="15" t="inlineStr">
@@ -8267,7 +8253,7 @@
       <c r="R43" s="15" t="n"/>
       <c r="S43" s="15" t="inlineStr">
         <is>
-          <t>info@squadron.com</t>
+          <t>london@rbbecon.com</t>
         </is>
       </c>
       <c r="T43" s="15" t="inlineStr">
@@ -8277,18 +8263,18 @@
       </c>
       <c r="U43" s="16" t="inlineStr">
         <is>
-          <t>https://squadron.com/</t>
+          <t>https://www.rbbecon.com/contact/</t>
         </is>
       </c>
       <c r="X43" s="15" t="n"/>
       <c r="Y43" s="15" t="inlineStr">
         <is>
-          <t>E1 6AD</t>
+          <t>EC2M 3TY</t>
         </is>
       </c>
       <c r="Z43" s="15" t="inlineStr">
         <is>
-          <t>Registered office (no address on website)</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="AA43" s="15" t="inlineStr">
@@ -8297,7 +8283,7 @@
         </is>
       </c>
       <c r="AB43" s="15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC43" s="15" t="inlineStr">
         <is>
@@ -8323,8 +8309,16 @@
         <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
         <v/>
       </c>
-      <c r="AH43" s="15" t="n"/>
-      <c r="AI43" s="15" t="n"/>
+      <c r="AH43" s="15" t="inlineStr">
+        <is>
+          <t>team of 190 economics consultants</t>
+        </is>
+      </c>
+      <c r="AI43" s="16" t="inlineStr">
+        <is>
+          <t>https://www.rbbecon.com/team/</t>
+        </is>
+      </c>
       <c r="AJ43" s="18">
         <f>IF(V43&lt;&gt;"",V43,S43)</f>
         <v/>
@@ -8367,7 +8361,7 @@
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>Professional services (LLP)</t>
+          <t>Tech / software</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
@@ -8377,25 +8371,27 @@
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>Rbb Economics LLP</t>
+          <t>Quantexa Limited</t>
         </is>
       </c>
       <c r="F44" s="15" t="inlineStr">
         <is>
-          <t>Rbb Economics</t>
+          <t>Quantexa</t>
         </is>
       </c>
       <c r="G44" s="16" t="inlineStr">
         <is>
-          <t>https://www.rbbecon.com</t>
-        </is>
-      </c>
-      <c r="H44" s="15" t="n">
-        <v>190</v>
+          <t>https://www.quantexa.com</t>
+        </is>
+      </c>
+      <c r="H44" s="15" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
       </c>
       <c r="I44" s="15" t="inlineStr">
         <is>
-          <t>OC315356</t>
+          <t>10045407</t>
         </is>
       </c>
       <c r="J44" s="16" t="inlineStr">
@@ -8410,17 +8406,17 @@
       </c>
       <c r="L44" s="15" t="inlineStr">
         <is>
-          <t>26/09/2005</t>
+          <t>07/03/2016</t>
         </is>
       </c>
       <c r="M44" s="15" t="inlineStr">
         <is>
-          <t>199 Bishopsgate, London</t>
+          <t>C/O Company Secretarial Department, 280 Bishopsgate, London</t>
         </is>
       </c>
       <c r="N44" s="15" t="inlineStr">
         <is>
-          <t>EC2M 3TY</t>
+          <t>EC2M 4AG</t>
         </is>
       </c>
       <c r="O44" s="15" t="inlineStr">
@@ -8433,7 +8429,7 @@
       <c r="R44" s="15" t="n"/>
       <c r="S44" s="15" t="inlineStr">
         <is>
-          <t>london@rbbecon.com</t>
+          <t>info@quantexa.com</t>
         </is>
       </c>
       <c r="T44" s="15" t="inlineStr">
@@ -8443,18 +8439,18 @@
       </c>
       <c r="U44" s="16" t="inlineStr">
         <is>
-          <t>https://www.rbbecon.com/contact/</t>
+          <t>https://www.quantexa.com/</t>
         </is>
       </c>
       <c r="X44" s="15" t="n"/>
       <c r="Y44" s="15" t="inlineStr">
         <is>
-          <t>EC2M 3TY</t>
+          <t>EC2M 4AG</t>
         </is>
       </c>
       <c r="Z44" s="15" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Website (other page)</t>
         </is>
       </c>
       <c r="AA44" s="15" t="inlineStr">
@@ -8489,16 +8485,8 @@
         <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
         <v/>
       </c>
-      <c r="AH44" s="15" t="inlineStr">
-        <is>
-          <t>team of 190 economics consultants</t>
-        </is>
-      </c>
-      <c r="AI44" s="16" t="inlineStr">
-        <is>
-          <t>https://www.rbbecon.com/team/</t>
-        </is>
-      </c>
+      <c r="AH44" s="15" t="n"/>
+      <c r="AI44" s="15" t="n"/>
       <c r="AJ44" s="18">
         <f>IF(V44&lt;&gt;"",V44,S44)</f>
         <v/>
@@ -8546,22 +8534,22 @@
       </c>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>EC2M</t>
+          <t>EC2A</t>
         </is>
       </c>
       <c r="E45" s="15" t="inlineStr">
         <is>
-          <t>Quantexa Limited</t>
+          <t>Hadean Supercomputing Ltd</t>
         </is>
       </c>
       <c r="F45" s="15" t="inlineStr">
         <is>
-          <t>Quantexa</t>
+          <t>Hadean Supercomputing</t>
         </is>
       </c>
       <c r="G45" s="16" t="inlineStr">
         <is>
-          <t>https://www.quantexa.com</t>
+          <t>https://hadean.com</t>
         </is>
       </c>
       <c r="H45" s="15" t="inlineStr">
@@ -8571,7 +8559,7 @@
       </c>
       <c r="I45" s="15" t="inlineStr">
         <is>
-          <t>10045407</t>
+          <t>09808169</t>
         </is>
       </c>
       <c r="J45" s="16" t="inlineStr">
@@ -8586,17 +8574,17 @@
       </c>
       <c r="L45" s="15" t="inlineStr">
         <is>
-          <t>07/03/2016</t>
+          <t>03/10/2015</t>
         </is>
       </c>
       <c r="M45" s="15" t="inlineStr">
         <is>
-          <t>C/O Company Secretarial Department, 280 Bishopsgate, London</t>
+          <t>9 Appold Street, London</t>
         </is>
       </c>
       <c r="N45" s="15" t="inlineStr">
         <is>
-          <t>EC2M 4AG</t>
+          <t>EC2A 2AP</t>
         </is>
       </c>
       <c r="O45" s="15" t="inlineStr">
@@ -8609,7 +8597,7 @@
       <c r="R45" s="15" t="n"/>
       <c r="S45" s="15" t="inlineStr">
         <is>
-          <t>info@quantexa.com</t>
+          <t>people@hadean.com</t>
         </is>
       </c>
       <c r="T45" s="15" t="inlineStr">
@@ -8619,18 +8607,18 @@
       </c>
       <c r="U45" s="16" t="inlineStr">
         <is>
-          <t>https://www.quantexa.com/</t>
+          <t>https://hadean.com/careers/</t>
         </is>
       </c>
       <c r="X45" s="15" t="n"/>
       <c r="Y45" s="15" t="inlineStr">
         <is>
-          <t>EC2M 4AG</t>
+          <t>EC2A 2AP</t>
         </is>
       </c>
       <c r="Z45" s="15" t="inlineStr">
         <is>
-          <t>Website (other page)</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="AA45" s="15" t="inlineStr">
@@ -8709,37 +8697,35 @@
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Tech / software</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>EC2A</t>
+          <t>EC1V</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>Hadean Supercomputing Ltd</t>
+          <t>Maccreanor Lavington Limited</t>
         </is>
       </c>
       <c r="F46" s="15" t="inlineStr">
         <is>
-          <t>Hadean Supercomputing</t>
+          <t>Maccreanor Lavington</t>
         </is>
       </c>
       <c r="G46" s="16" t="inlineStr">
         <is>
-          <t>https://hadean.com</t>
-        </is>
-      </c>
-      <c r="H46" s="15" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
+          <t>https://www.maccreanorlavington.com</t>
+        </is>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>80</v>
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
-          <t>09808169</t>
+          <t>04944069</t>
         </is>
       </c>
       <c r="J46" s="16" t="inlineStr">
@@ -8754,17 +8740,17 @@
       </c>
       <c r="L46" s="15" t="inlineStr">
         <is>
-          <t>03/10/2015</t>
+          <t>27/10/2003</t>
         </is>
       </c>
       <c r="M46" s="15" t="inlineStr">
         <is>
-          <t>9 Appold Street, London</t>
+          <t>4Th Floor, 63 -71 Gee Street, London</t>
         </is>
       </c>
       <c r="N46" s="15" t="inlineStr">
         <is>
-          <t>EC2A 2AP</t>
+          <t>EC1V 3RS</t>
         </is>
       </c>
       <c r="O46" s="15" t="inlineStr">
@@ -8777,7 +8763,7 @@
       <c r="R46" s="15" t="n"/>
       <c r="S46" s="15" t="inlineStr">
         <is>
-          <t>people@hadean.com</t>
+          <t>nl@maccreanorlavington.com</t>
         </is>
       </c>
       <c r="T46" s="15" t="inlineStr">
@@ -8787,25 +8773,27 @@
       </c>
       <c r="U46" s="16" t="inlineStr">
         <is>
-          <t>https://hadean.com/careers/</t>
-        </is>
-      </c>
-      <c r="X46" s="15" t="n"/>
+          <t>https://www.maccreanorlavington.com/</t>
+        </is>
+      </c>
+      <c r="X46" s="15" t="inlineStr">
+        <is>
+          <t>63 Gee Street</t>
+        </is>
+      </c>
       <c r="Y46" s="15" t="inlineStr">
         <is>
-          <t>EC2A 2AP</t>
+          <t>EC1V 3RS</t>
         </is>
       </c>
       <c r="Z46" s="15" t="inlineStr">
         <is>
-          <t>Website (10 days 
- SCEPTRE 
- Case St)</t>
+          <t>Website (63 Gee Street)</t>
         </is>
       </c>
       <c r="AA46" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AB46" s="15" t="n">
@@ -8813,12 +8801,12 @@
       </c>
       <c r="AC46" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AD46" s="15" t="inlineStr">
         <is>
-          <t>Monday 28 September at 17:40</t>
+          <t>Monday 12 October at 18:00</t>
         </is>
       </c>
       <c r="AE46" s="15" t="inlineStr">
@@ -8828,15 +8816,23 @@
       </c>
       <c r="AF46" s="15" t="inlineStr">
         <is>
-          <t>5-a-side</t>
+          <t>6-a-side</t>
         </is>
       </c>
       <c r="AG46" s="17">
         <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
         <v/>
       </c>
-      <c r="AH46" s="15" t="n"/>
-      <c r="AI46" s="15" t="n"/>
+      <c r="AH46" s="15" t="inlineStr">
+        <is>
+          <t>recognised with many awards including the RIBA Stirling Prize</t>
+        </is>
+      </c>
+      <c r="AI46" s="16" t="inlineStr">
+        <is>
+          <t>https://www.maccreanorlavington.com/practice/about-us/</t>
+        </is>
+      </c>
       <c r="AJ46" s="18">
         <f>IF(V46&lt;&gt;"",V46,S46)</f>
         <v/>
@@ -8879,7 +8875,7 @@
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Tech / software</t>
         </is>
       </c>
       <c r="D47" s="15" t="inlineStr">
@@ -8889,25 +8885,27 @@
       </c>
       <c r="E47" s="15" t="inlineStr">
         <is>
-          <t>Maccreanor Lavington Limited</t>
+          <t>Tvf Limited</t>
         </is>
       </c>
       <c r="F47" s="15" t="inlineStr">
         <is>
-          <t>Maccreanor Lavington</t>
+          <t>Tvf</t>
         </is>
       </c>
       <c r="G47" s="16" t="inlineStr">
         <is>
-          <t>https://www.maccreanorlavington.com</t>
-        </is>
-      </c>
-      <c r="H47" s="15" t="n">
-        <v>80</v>
+          <t>https://tvf.co.uk</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
       </c>
       <c r="I47" s="15" t="inlineStr">
         <is>
-          <t>04944069</t>
+          <t>02830019</t>
         </is>
       </c>
       <c r="J47" s="16" t="inlineStr">
@@ -8917,22 +8915,22 @@
       </c>
       <c r="K47" s="15" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L47" s="15" t="inlineStr">
         <is>
-          <t>27/10/2003</t>
+          <t>24/06/1993</t>
         </is>
       </c>
       <c r="M47" s="15" t="inlineStr">
         <is>
-          <t>4Th Floor, 63 -71 Gee Street, London</t>
+          <t>375 City Road, London</t>
         </is>
       </c>
       <c r="N47" s="15" t="inlineStr">
         <is>
-          <t>EC1V 3RS</t>
+          <t>EC1V 1NB</t>
         </is>
       </c>
       <c r="O47" s="15" t="inlineStr">
@@ -8945,7 +8943,7 @@
       <c r="R47" s="15" t="n"/>
       <c r="S47" s="15" t="inlineStr">
         <is>
-          <t>nl@maccreanorlavington.com</t>
+          <t>cvs@tvf.co.uk</t>
         </is>
       </c>
       <c r="T47" s="15" t="inlineStr">
@@ -8955,22 +8953,22 @@
       </c>
       <c r="U47" s="16" t="inlineStr">
         <is>
-          <t>https://www.maccreanorlavington.com/</t>
+          <t>https://tvf.co.uk/contact</t>
         </is>
       </c>
       <c r="X47" s="15" t="inlineStr">
         <is>
-          <t>63 Gee Street</t>
+          <t>375 City Road</t>
         </is>
       </c>
       <c r="Y47" s="15" t="inlineStr">
         <is>
-          <t>EC1V 3RS</t>
+          <t>EC1V 1NB</t>
         </is>
       </c>
       <c r="Z47" s="15" t="inlineStr">
         <is>
-          <t>Website (63 Gee Street)</t>
+          <t>Website (375 City Road)</t>
         </is>
       </c>
       <c r="AA47" s="15" t="inlineStr">
@@ -8979,7 +8977,7 @@
         </is>
       </c>
       <c r="AB47" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC47" s="15" t="inlineStr">
         <is>
@@ -9007,12 +9005,12 @@
       </c>
       <c r="AH47" s="15" t="inlineStr">
         <is>
-          <t>recognised with many awards including the RIBA Stirling Prize</t>
+          <t>award-winning media company with TV and software divisions</t>
         </is>
       </c>
       <c r="AI47" s="16" t="inlineStr">
         <is>
-          <t>https://www.maccreanorlavington.com/practice/about-us/</t>
+          <t>https://tvf.co.uk/</t>
         </is>
       </c>
       <c r="AJ47" s="18">
@@ -9057,27 +9055,27 @@
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Tech / software</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>EC1V</t>
+          <t>EC2A</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>Tvf Limited</t>
+          <t>Montash Limited</t>
         </is>
       </c>
       <c r="F48" s="15" t="inlineStr">
         <is>
-          <t>Tvf</t>
+          <t>Montash</t>
         </is>
       </c>
       <c r="G48" s="16" t="inlineStr">
         <is>
-          <t>https://tvf.co.uk</t>
+          <t>https://montash.com</t>
         </is>
       </c>
       <c r="H48" s="15" t="inlineStr">
@@ -9087,7 +9085,7 @@
       </c>
       <c r="I48" s="15" t="inlineStr">
         <is>
-          <t>02830019</t>
+          <t>05195273</t>
         </is>
       </c>
       <c r="J48" s="16" t="inlineStr">
@@ -9097,22 +9095,22 @@
       </c>
       <c r="K48" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="L48" s="15" t="inlineStr">
         <is>
-          <t>24/06/1993</t>
+          <t>02/08/2004</t>
         </is>
       </c>
       <c r="M48" s="15" t="inlineStr">
         <is>
-          <t>375 City Road, London</t>
+          <t>100 Clifton Street, London</t>
         </is>
       </c>
       <c r="N48" s="15" t="inlineStr">
         <is>
-          <t>EC1V 1NB</t>
+          <t>EC2A 4TP</t>
         </is>
       </c>
       <c r="O48" s="15" t="inlineStr">
@@ -9125,7 +9123,7 @@
       <c r="R48" s="15" t="n"/>
       <c r="S48" s="15" t="inlineStr">
         <is>
-          <t>cvs@tvf.co.uk</t>
+          <t>info@montash.com</t>
         </is>
       </c>
       <c r="T48" s="15" t="inlineStr">
@@ -9135,27 +9133,27 @@
       </c>
       <c r="U48" s="16" t="inlineStr">
         <is>
-          <t>https://tvf.co.uk/contact</t>
+          <t>https://montash.com/</t>
         </is>
       </c>
       <c r="X48" s="15" t="inlineStr">
         <is>
-          <t>375 City Road</t>
+          <t>100 Clifton Street</t>
         </is>
       </c>
       <c r="Y48" s="15" t="inlineStr">
         <is>
-          <t>EC1V 1NB</t>
+          <t>EC2A 4TP</t>
         </is>
       </c>
       <c r="Z48" s="15" t="inlineStr">
         <is>
-          <t>Website (375 City Road)</t>
+          <t>Website (100 Clifton Street)</t>
         </is>
       </c>
       <c r="AA48" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AB48" s="15" t="n">
@@ -9163,12 +9161,12 @@
       </c>
       <c r="AC48" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AD48" s="15" t="inlineStr">
         <is>
-          <t>Monday 12 October at 18:00</t>
+          <t>Monday 28 September at 17:40</t>
         </is>
       </c>
       <c r="AE48" s="15" t="inlineStr">
@@ -9178,23 +9176,15 @@
       </c>
       <c r="AF48" s="15" t="inlineStr">
         <is>
-          <t>6-a-side</t>
+          <t>5-a-side</t>
         </is>
       </c>
       <c r="AG48" s="17">
         <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
         <v/>
       </c>
-      <c r="AH48" s="15" t="inlineStr">
-        <is>
-          <t>award-winning media company with TV and software divisions</t>
-        </is>
-      </c>
-      <c r="AI48" s="16" t="inlineStr">
-        <is>
-          <t>https://tvf.co.uk/</t>
-        </is>
-      </c>
+      <c r="AH48" s="15" t="n"/>
+      <c r="AI48" s="15" t="n"/>
       <c r="AJ48" s="18">
         <f>IF(V48&lt;&gt;"",V48,S48)</f>
         <v/>
@@ -9237,27 +9227,27 @@
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Professional services (LLP)</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>EC2A</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="E49" s="15" t="inlineStr">
         <is>
-          <t>Montash Limited</t>
+          <t>Valeo Foods (Group) UK LLP</t>
         </is>
       </c>
       <c r="F49" s="15" t="inlineStr">
         <is>
-          <t>Montash</t>
+          <t>Valeo Foods</t>
         </is>
       </c>
       <c r="G49" s="16" t="inlineStr">
         <is>
-          <t>https://montash.com</t>
+          <t>https://www.valeofoods.co.uk</t>
         </is>
       </c>
       <c r="H49" s="15" t="inlineStr">
@@ -9267,7 +9257,7 @@
       </c>
       <c r="I49" s="15" t="inlineStr">
         <is>
-          <t>05195273</t>
+          <t>OC391111</t>
         </is>
       </c>
       <c r="J49" s="16" t="inlineStr">
@@ -9277,22 +9267,22 @@
       </c>
       <c r="K49" s="15" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="L49" s="15" t="inlineStr">
         <is>
-          <t>02/08/2004</t>
+          <t>13/02/2014</t>
         </is>
       </c>
       <c r="M49" s="15" t="inlineStr">
         <is>
-          <t>100 Clifton Street, London</t>
+          <t>9 Perseverance Works, Kingsland Road, London</t>
         </is>
       </c>
       <c r="N49" s="15" t="inlineStr">
         <is>
-          <t>EC2A 4TP</t>
+          <t>E2 8DD</t>
         </is>
       </c>
       <c r="O49" s="15" t="inlineStr">
@@ -9305,7 +9295,7 @@
       <c r="R49" s="15" t="n"/>
       <c r="S49" s="15" t="inlineStr">
         <is>
-          <t>info@montash.com</t>
+          <t>consumers@valeofoods.co.uk</t>
         </is>
       </c>
       <c r="T49" s="15" t="inlineStr">
@@ -9315,22 +9305,22 @@
       </c>
       <c r="U49" s="16" t="inlineStr">
         <is>
-          <t>https://montash.com/</t>
+          <t>https://www.valeofoods.co.uk/contact</t>
         </is>
       </c>
       <c r="X49" s="15" t="inlineStr">
         <is>
-          <t>100 Clifton Street</t>
+          <t>9 Perseverance Works, Kingsland Road, London</t>
         </is>
       </c>
       <c r="Y49" s="15" t="inlineStr">
         <is>
-          <t>EC2A 4TP</t>
+          <t>E2 8DD</t>
         </is>
       </c>
       <c r="Z49" s="15" t="inlineStr">
         <is>
-          <t>Website (100 Clifton Street)</t>
+          <t>Website (9 Perseverance Works, Kingsland Road, London)</t>
         </is>
       </c>
       <c r="AA49" s="15" t="inlineStr">
@@ -9339,7 +9329,7 @@
         </is>
       </c>
       <c r="AB49" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC49" s="15" t="inlineStr">
         <is>
@@ -9409,7 +9399,7 @@
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Professional services (LLP)</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
@@ -9419,17 +9409,17 @@
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>Valeo Foods (Group) UK LLP</t>
+          <t>Atelier Ten Ltd</t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
         <is>
-          <t>Valeo Foods</t>
+          <t>Atelier Ten</t>
         </is>
       </c>
       <c r="G50" s="16" t="inlineStr">
         <is>
-          <t>https://www.valeofoods.co.uk</t>
+          <t>https://www.atelierten.com</t>
         </is>
       </c>
       <c r="H50" s="15" t="inlineStr">
@@ -9439,7 +9429,7 @@
       </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
-          <t>OC391111</t>
+          <t>02552224</t>
         </is>
       </c>
       <c r="J50" s="16" t="inlineStr">
@@ -9449,17 +9439,17 @@
       </c>
       <c r="K50" s="15" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="L50" s="15" t="inlineStr">
         <is>
-          <t>13/02/2014</t>
+          <t>25/10/1990</t>
         </is>
       </c>
       <c r="M50" s="15" t="inlineStr">
         <is>
-          <t>9 Perseverance Works, Kingsland Road, London</t>
+          <t>19 Perseverance Works, 38 Kingsland Road, London</t>
         </is>
       </c>
       <c r="N50" s="15" t="inlineStr">
@@ -9477,7 +9467,7 @@
       <c r="R50" s="15" t="n"/>
       <c r="S50" s="15" t="inlineStr">
         <is>
-          <t>consumers@valeofoods.co.uk</t>
+          <t>london@atelierten.com</t>
         </is>
       </c>
       <c r="T50" s="15" t="inlineStr">
@@ -9487,12 +9477,12 @@
       </c>
       <c r="U50" s="16" t="inlineStr">
         <is>
-          <t>https://www.valeofoods.co.uk/contact</t>
+          <t>https://www.atelierten.com/offices/london/</t>
         </is>
       </c>
       <c r="X50" s="15" t="inlineStr">
         <is>
-          <t>9 Perseverance Works, Kingsland Road, London</t>
+          <t>London</t>
         </is>
       </c>
       <c r="Y50" s="15" t="inlineStr">
@@ -9502,7 +9492,7 @@
       </c>
       <c r="Z50" s="15" t="inlineStr">
         <is>
-          <t>Website (9 Perseverance Works, Kingsland Road, London)</t>
+          <t>Website (London)</t>
         </is>
       </c>
       <c r="AA50" s="15" t="inlineStr">
@@ -9581,37 +9571,35 @@
       </c>
       <c r="C51" s="15" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Tech / software</t>
         </is>
       </c>
       <c r="D51" s="15" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>EC1V</t>
         </is>
       </c>
       <c r="E51" s="15" t="inlineStr">
         <is>
-          <t>Atelier Ten Ltd</t>
+          <t>Aptem Ltd</t>
         </is>
       </c>
       <c r="F51" s="15" t="inlineStr">
         <is>
-          <t>Atelier Ten</t>
+          <t>Aptem</t>
         </is>
       </c>
       <c r="G51" s="16" t="inlineStr">
         <is>
-          <t>https://www.atelierten.com</t>
-        </is>
-      </c>
-      <c r="H51" s="15" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
+          <t>https://www.aptem.co.uk</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>100</v>
       </c>
       <c r="I51" s="15" t="inlineStr">
         <is>
-          <t>02552224</t>
+          <t>06824227</t>
         </is>
       </c>
       <c r="J51" s="16" t="inlineStr">
@@ -9621,22 +9609,22 @@
       </c>
       <c r="K51" s="15" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="L51" s="15" t="inlineStr">
         <is>
-          <t>25/10/1990</t>
+          <t>19/02/2009</t>
         </is>
       </c>
       <c r="M51" s="15" t="inlineStr">
         <is>
-          <t>19 Perseverance Works, 38 Kingsland Road, London</t>
+          <t>Eagle House, 167 City Road, London</t>
         </is>
       </c>
       <c r="N51" s="15" t="inlineStr">
         <is>
-          <t>E2 8DD</t>
+          <t>EC1V 1NR</t>
         </is>
       </c>
       <c r="O51" s="15" t="inlineStr">
@@ -9649,7 +9637,7 @@
       <c r="R51" s="15" t="n"/>
       <c r="S51" s="15" t="inlineStr">
         <is>
-          <t>london@atelierten.com</t>
+          <t>info@aptem.co.uk</t>
         </is>
       </c>
       <c r="T51" s="15" t="inlineStr">
@@ -9659,27 +9647,27 @@
       </c>
       <c r="U51" s="16" t="inlineStr">
         <is>
-          <t>https://www.atelierten.com/offices/london/</t>
+          <t>https://www.aptem.co.uk/contact-us/</t>
         </is>
       </c>
       <c r="X51" s="15" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Eagle House, 167 City Road, London</t>
         </is>
       </c>
       <c r="Y51" s="15" t="inlineStr">
         <is>
-          <t>E2 8DD</t>
+          <t>EC1V 1NR</t>
         </is>
       </c>
       <c r="Z51" s="15" t="inlineStr">
         <is>
-          <t>Website (London)</t>
+          <t>Website (Eagle House, 167 City Road, London)</t>
         </is>
       </c>
       <c r="AA51" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AB51" s="15" t="n">
@@ -9687,12 +9675,12 @@
       </c>
       <c r="AC51" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AD51" s="15" t="inlineStr">
         <is>
-          <t>Monday 28 September at 17:40</t>
+          <t>Monday 12 October at 18:00</t>
         </is>
       </c>
       <c r="AE51" s="15" t="inlineStr">
@@ -9702,7 +9690,7 @@
       </c>
       <c r="AF51" s="15" t="inlineStr">
         <is>
-          <t>5-a-side</t>
+          <t>6-a-side</t>
         </is>
       </c>
       <c r="AG51" s="17">
@@ -9758,30 +9746,32 @@
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>EC1V</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>Aptem Ltd</t>
+          <t>Vivacity Labs Limited</t>
         </is>
       </c>
       <c r="F52" s="15" t="inlineStr">
         <is>
-          <t>Aptem</t>
+          <t>Vivacity Labs</t>
         </is>
       </c>
       <c r="G52" s="16" t="inlineStr">
         <is>
-          <t>https://www.aptem.co.uk</t>
-        </is>
-      </c>
-      <c r="H52" s="15" t="n">
-        <v>100</v>
+          <t>https://vivacitylabs.com</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
       </c>
       <c r="I52" s="15" t="inlineStr">
         <is>
-          <t>06824227</t>
+          <t>09924516</t>
         </is>
       </c>
       <c r="J52" s="16" t="inlineStr">
@@ -9791,22 +9781,22 @@
       </c>
       <c r="K52" s="15" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="L52" s="15" t="inlineStr">
         <is>
-          <t>19/02/2009</t>
+          <t>21/12/2015</t>
         </is>
       </c>
       <c r="M52" s="15" t="inlineStr">
         <is>
-          <t>Eagle House, 167 City Road, London</t>
+          <t>3 Haberdasher Street, London</t>
         </is>
       </c>
       <c r="N52" s="15" t="inlineStr">
         <is>
-          <t>EC1V 1NR</t>
+          <t>N1 6ED</t>
         </is>
       </c>
       <c r="O52" s="15" t="inlineStr">
@@ -9819,7 +9809,7 @@
       <c r="R52" s="15" t="n"/>
       <c r="S52" s="15" t="inlineStr">
         <is>
-          <t>info@aptem.co.uk</t>
+          <t>contact@vivacitylabs.com</t>
         </is>
       </c>
       <c r="T52" s="15" t="inlineStr">
@@ -9829,27 +9819,27 @@
       </c>
       <c r="U52" s="16" t="inlineStr">
         <is>
-          <t>https://www.aptem.co.uk/contact-us/</t>
+          <t>https://vivacitylabs.com/north-america/about-us/contact/</t>
         </is>
       </c>
       <c r="X52" s="15" t="inlineStr">
         <is>
-          <t>Eagle House, 167 City Road, London</t>
+          <t>3 HABERDASHER STREET, LONDON</t>
         </is>
       </c>
       <c r="Y52" s="15" t="inlineStr">
         <is>
-          <t>EC1V 1NR</t>
+          <t>N1 6ED</t>
         </is>
       </c>
       <c r="Z52" s="15" t="inlineStr">
         <is>
-          <t>Website (Eagle House, 167 City Road, London)</t>
+          <t>Website (3 HABERDASHER STREET, LONDON)</t>
         </is>
       </c>
       <c r="AA52" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Shoreditch Rooftop</t>
         </is>
       </c>
       <c r="AB52" s="15" t="n">
@@ -9857,12 +9847,12 @@
       </c>
       <c r="AC52" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Shoreditch Rooftop</t>
         </is>
       </c>
       <c r="AD52" s="15" t="inlineStr">
         <is>
-          <t>Monday 12 October at 18:00</t>
+          <t>Monday 28 September at 18:00</t>
         </is>
       </c>
       <c r="AE52" s="15" t="inlineStr">
@@ -9872,15 +9862,23 @@
       </c>
       <c r="AF52" s="15" t="inlineStr">
         <is>
-          <t>6-a-side</t>
+          <t>5-a-side</t>
         </is>
       </c>
       <c r="AG52" s="17">
         <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
         <v/>
       </c>
-      <c r="AH52" s="15" t="n"/>
-      <c r="AI52" s="15" t="n"/>
+      <c r="AH52" s="15" t="inlineStr">
+        <is>
+          <t>expanding globally with current growth trajectory</t>
+        </is>
+      </c>
+      <c r="AI52" s="16" t="inlineStr">
+        <is>
+          <t>https://vivacitylabs.com/north-america/about-us/contact/</t>
+        </is>
+      </c>
       <c r="AJ52" s="18">
         <f>IF(V52&lt;&gt;"",V52,S52)</f>
         <v/>
@@ -9923,27 +9921,27 @@
       </c>
       <c r="C53" s="15" t="inlineStr">
         <is>
-          <t>Tech / software</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>EC1V</t>
         </is>
       </c>
       <c r="E53" s="15" t="inlineStr">
         <is>
-          <t>Vivacity Labs Limited</t>
+          <t>Allford Hall Monaghan Morris Limited</t>
         </is>
       </c>
       <c r="F53" s="15" t="inlineStr">
         <is>
-          <t>Vivacity Labs</t>
+          <t>Allford Hall Monaghan Morris</t>
         </is>
       </c>
       <c r="G53" s="16" t="inlineStr">
         <is>
-          <t>https://vivacitylabs.com</t>
+          <t>https://www.ahmm.co.uk</t>
         </is>
       </c>
       <c r="H53" s="15" t="inlineStr">
@@ -9953,7 +9951,7 @@
       </c>
       <c r="I53" s="15" t="inlineStr">
         <is>
-          <t>09924516</t>
+          <t>07155322</t>
         </is>
       </c>
       <c r="J53" s="16" t="inlineStr">
@@ -9968,17 +9966,17 @@
       </c>
       <c r="L53" s="15" t="inlineStr">
         <is>
-          <t>21/12/2015</t>
+          <t>11/02/2010</t>
         </is>
       </c>
       <c r="M53" s="15" t="inlineStr">
         <is>
-          <t>3 Haberdasher Street, London</t>
+          <t>Morelands, 5 - 23 Old Street, London</t>
         </is>
       </c>
       <c r="N53" s="15" t="inlineStr">
         <is>
-          <t>N1 6ED</t>
+          <t>EC1V 9HL</t>
         </is>
       </c>
       <c r="O53" s="15" t="inlineStr">
@@ -9991,7 +9989,7 @@
       <c r="R53" s="15" t="n"/>
       <c r="S53" s="15" t="inlineStr">
         <is>
-          <t>contact@vivacitylabs.com</t>
+          <t>info@ahmm.co.uk</t>
         </is>
       </c>
       <c r="T53" s="15" t="inlineStr">
@@ -10001,40 +9999,40 @@
       </c>
       <c r="U53" s="16" t="inlineStr">
         <is>
-          <t>https://vivacitylabs.com/north-america/about-us/contact/</t>
+          <t>https://www.ahmm.co.uk/contact/</t>
         </is>
       </c>
       <c r="X53" s="15" t="inlineStr">
         <is>
-          <t>3 HABERDASHER STREET, LONDON</t>
+          <t>5-23 Old Street</t>
         </is>
       </c>
       <c r="Y53" s="15" t="inlineStr">
         <is>
-          <t>N1 6ED</t>
+          <t>EC1V 9HL</t>
         </is>
       </c>
       <c r="Z53" s="15" t="inlineStr">
         <is>
-          <t>Website (3 HABERDASHER STREET, LONDON)</t>
+          <t>Website (5-23 Old Street)</t>
         </is>
       </c>
       <c r="AA53" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Rooftop</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AB53" s="15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC53" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Rooftop</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AD53" s="15" t="inlineStr">
         <is>
-          <t>Monday 28 September at 18:00</t>
+          <t>Monday 12 October at 18:00</t>
         </is>
       </c>
       <c r="AE53" s="15" t="inlineStr">
@@ -10044,7 +10042,7 @@
       </c>
       <c r="AF53" s="15" t="inlineStr">
         <is>
-          <t>5-a-side</t>
+          <t>6-a-side</t>
         </is>
       </c>
       <c r="AG53" s="17">
@@ -10095,7 +10093,7 @@
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Marketing / agency</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
@@ -10105,27 +10103,25 @@
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t>Allford Hall Monaghan Morris Limited</t>
+          <t>Censuswide Limited</t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
         <is>
-          <t>Allford Hall Monaghan Morris</t>
+          <t>Censuswide</t>
         </is>
       </c>
       <c r="G54" s="16" t="inlineStr">
         <is>
-          <t>https://www.ahmm.co.uk</t>
-        </is>
-      </c>
-      <c r="H54" s="15" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
+          <t>https://censuswide.com</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>29</v>
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
-          <t>07155322</t>
+          <t>07924059</t>
         </is>
       </c>
       <c r="J54" s="16" t="inlineStr">
@@ -10135,22 +10131,22 @@
       </c>
       <c r="K54" s="15" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="L54" s="15" t="inlineStr">
         <is>
-          <t>11/02/2010</t>
+          <t>25/01/2012</t>
         </is>
       </c>
       <c r="M54" s="15" t="inlineStr">
         <is>
-          <t>Morelands, 5 - 23 Old Street, London</t>
+          <t>12-14 Berry Street, London</t>
         </is>
       </c>
       <c r="N54" s="15" t="inlineStr">
         <is>
-          <t>EC1V 9HL</t>
+          <t>EC1V 0AU</t>
         </is>
       </c>
       <c r="O54" s="15" t="inlineStr">
@@ -10163,7 +10159,7 @@
       <c r="R54" s="15" t="n"/>
       <c r="S54" s="15" t="inlineStr">
         <is>
-          <t>info@ahmm.co.uk</t>
+          <t>info@censuswide.com</t>
         </is>
       </c>
       <c r="T54" s="15" t="inlineStr">
@@ -10173,22 +10169,22 @@
       </c>
       <c r="U54" s="16" t="inlineStr">
         <is>
-          <t>https://www.ahmm.co.uk/contact/</t>
+          <t>https://censuswide.com/</t>
         </is>
       </c>
       <c r="X54" s="15" t="inlineStr">
         <is>
-          <t>5-23 Old Street</t>
+          <t>12-14 Berry Street, London</t>
         </is>
       </c>
       <c r="Y54" s="15" t="inlineStr">
         <is>
-          <t>EC1V 9HL</t>
+          <t>EC1V 0AU</t>
         </is>
       </c>
       <c r="Z54" s="15" t="inlineStr">
         <is>
-          <t>Website (5-23 Old Street)</t>
+          <t>Website (12-14 Berry Street, London)</t>
         </is>
       </c>
       <c r="AA54" s="15" t="inlineStr">
@@ -10267,35 +10263,35 @@
       </c>
       <c r="C55" s="15" t="inlineStr">
         <is>
-          <t>Marketing / agency</t>
+          <t>Tech / software</t>
         </is>
       </c>
       <c r="D55" s="15" t="inlineStr">
         <is>
-          <t>EC1V</t>
+          <t>EC2A</t>
         </is>
       </c>
       <c r="E55" s="15" t="inlineStr">
         <is>
-          <t>Censuswide Limited</t>
+          <t>Elsewhen Ltd</t>
         </is>
       </c>
       <c r="F55" s="15" t="inlineStr">
         <is>
-          <t>Censuswide</t>
+          <t>Elsewhen</t>
         </is>
       </c>
       <c r="G55" s="16" t="inlineStr">
         <is>
-          <t>https://censuswide.com</t>
+          <t>https://www.elsewhen.com</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="I55" s="15" t="inlineStr">
         <is>
-          <t>07924059</t>
+          <t>07608360</t>
         </is>
       </c>
       <c r="J55" s="16" t="inlineStr">
@@ -10310,17 +10306,17 @@
       </c>
       <c r="L55" s="15" t="inlineStr">
         <is>
-          <t>25/01/2012</t>
+          <t>19/04/2011</t>
         </is>
       </c>
       <c r="M55" s="15" t="inlineStr">
         <is>
-          <t>12-14 Berry Street, London</t>
+          <t>86-90 Paul Street, London</t>
         </is>
       </c>
       <c r="N55" s="15" t="inlineStr">
         <is>
-          <t>EC1V 0AU</t>
+          <t>EC2A 4NE</t>
         </is>
       </c>
       <c r="O55" s="15" t="inlineStr">
@@ -10333,7 +10329,7 @@
       <c r="R55" s="15" t="n"/>
       <c r="S55" s="15" t="inlineStr">
         <is>
-          <t>info@censuswide.com</t>
+          <t>hello@elsewhen.com</t>
         </is>
       </c>
       <c r="T55" s="15" t="inlineStr">
@@ -10343,27 +10339,27 @@
       </c>
       <c r="U55" s="16" t="inlineStr">
         <is>
-          <t>https://censuswide.com/</t>
+          <t>https://www.elsewhen.com/</t>
         </is>
       </c>
       <c r="X55" s="15" t="inlineStr">
         <is>
-          <t>12-14 Berry Street, London</t>
+          <t>1 St Peter's Sq,</t>
         </is>
       </c>
       <c r="Y55" s="15" t="inlineStr">
         <is>
-          <t>EC1V 0AU</t>
+          <t>EC2A 4NE</t>
         </is>
       </c>
       <c r="Z55" s="15" t="inlineStr">
         <is>
-          <t>Website (12-14 Berry Street, London)</t>
+          <t>Website (1 St Peter's Sq,)</t>
         </is>
       </c>
       <c r="AA55" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AB55" s="15" t="n">
@@ -10371,12 +10367,12 @@
       </c>
       <c r="AC55" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AD55" s="15" t="inlineStr">
         <is>
-          <t>Monday 12 October at 18:00</t>
+          <t>Monday 28 September at 17:40</t>
         </is>
       </c>
       <c r="AE55" s="15" t="inlineStr">
@@ -10386,15 +10382,23 @@
       </c>
       <c r="AF55" s="15" t="inlineStr">
         <is>
-          <t>6-a-side</t>
+          <t>5-a-side</t>
         </is>
       </c>
       <c r="AG55" s="17">
         <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
         <v/>
       </c>
-      <c r="AH55" s="15" t="n"/>
-      <c r="AI55" s="15" t="n"/>
+      <c r="AH55" s="15" t="inlineStr">
+        <is>
+          <t>team of 100+ professionals</t>
+        </is>
+      </c>
+      <c r="AI55" s="16" t="inlineStr">
+        <is>
+          <t>https://www.elsewhen.com/about/</t>
+        </is>
+      </c>
       <c r="AJ55" s="18">
         <f>IF(V55&lt;&gt;"",V55,S55)</f>
         <v/>
@@ -10447,25 +10451,27 @@
       </c>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t>Elsewhen Ltd</t>
+          <t>Clover Technology Ltd</t>
         </is>
       </c>
       <c r="F56" s="15" t="inlineStr">
         <is>
-          <t>Elsewhen</t>
+          <t>Clover Technology</t>
         </is>
       </c>
       <c r="G56" s="16" t="inlineStr">
         <is>
-          <t>https://www.elsewhen.com</t>
-        </is>
-      </c>
-      <c r="H56" s="15" t="n">
-        <v>100</v>
+          <t>https://www.clovertechnology.co.uk</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
-          <t>07608360</t>
+          <t>13206820</t>
         </is>
       </c>
       <c r="J56" s="16" t="inlineStr">
@@ -10480,7 +10486,7 @@
       </c>
       <c r="L56" s="15" t="inlineStr">
         <is>
-          <t>19/04/2011</t>
+          <t>17/02/2021</t>
         </is>
       </c>
       <c r="M56" s="15" t="inlineStr">
@@ -10503,7 +10509,7 @@
       <c r="R56" s="15" t="n"/>
       <c r="S56" s="15" t="inlineStr">
         <is>
-          <t>hello@elsewhen.com</t>
+          <t>info@clovertechnology.co.uk</t>
         </is>
       </c>
       <c r="T56" s="15" t="inlineStr">
@@ -10513,12 +10519,12 @@
       </c>
       <c r="U56" s="16" t="inlineStr">
         <is>
-          <t>https://www.elsewhen.com/</t>
+          <t>https://www.clovertechnology.co.uk/</t>
         </is>
       </c>
       <c r="X56" s="15" t="inlineStr">
         <is>
-          <t>1 St Peter's Sq,</t>
+          <t>86-90 Paul Street</t>
         </is>
       </c>
       <c r="Y56" s="15" t="inlineStr">
@@ -10528,7 +10534,7 @@
       </c>
       <c r="Z56" s="15" t="inlineStr">
         <is>
-          <t>Website (1 St Peter's Sq,)</t>
+          <t>Website (86-90 Paul Street)</t>
         </is>
       </c>
       <c r="AA56" s="15" t="inlineStr">
@@ -10563,16 +10569,8 @@
         <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
         <v/>
       </c>
-      <c r="AH56" s="15" t="inlineStr">
-        <is>
-          <t>team of 100+ professionals</t>
-        </is>
-      </c>
-      <c r="AI56" s="16" t="inlineStr">
-        <is>
-          <t>https://www.elsewhen.com/about/</t>
-        </is>
-      </c>
+      <c r="AH56" s="15" t="n"/>
+      <c r="AI56" s="15" t="n"/>
       <c r="AJ56" s="18">
         <f>IF(V56&lt;&gt;"",V56,S56)</f>
         <v/>
@@ -10615,7 +10613,7 @@
       </c>
       <c r="C57" s="15" t="inlineStr">
         <is>
-          <t>Tech / software</t>
+          <t>Marketing / agency</t>
         </is>
       </c>
       <c r="D57" s="15" t="inlineStr">
@@ -10625,17 +10623,17 @@
       </c>
       <c r="E57" s="15" t="inlineStr">
         <is>
-          <t>Clover Technology Ltd</t>
+          <t>Louder Productions Limited</t>
         </is>
       </c>
       <c r="F57" s="15" t="inlineStr">
         <is>
-          <t>Clover Technology</t>
+          <t>Louder Productions</t>
         </is>
       </c>
       <c r="G57" s="16" t="inlineStr">
         <is>
-          <t>https://www.clovertechnology.co.uk</t>
+          <t>https://www.louderproductions.com</t>
         </is>
       </c>
       <c r="H57" s="15" t="inlineStr">
@@ -10645,7 +10643,7 @@
       </c>
       <c r="I57" s="15" t="inlineStr">
         <is>
-          <t>13206820</t>
+          <t>06459817</t>
         </is>
       </c>
       <c r="J57" s="16" t="inlineStr">
@@ -10655,22 +10653,22 @@
       </c>
       <c r="K57" s="15" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="L57" s="15" t="inlineStr">
         <is>
-          <t>17/02/2021</t>
+          <t>27/12/2007</t>
         </is>
       </c>
       <c r="M57" s="15" t="inlineStr">
         <is>
-          <t>86-90 Paul Street, London</t>
+          <t>27 Paul Street, London</t>
         </is>
       </c>
       <c r="N57" s="15" t="inlineStr">
         <is>
-          <t>EC2A 4NE</t>
+          <t>EC2A 4JU</t>
         </is>
       </c>
       <c r="O57" s="15" t="inlineStr">
@@ -10683,7 +10681,7 @@
       <c r="R57" s="15" t="n"/>
       <c r="S57" s="15" t="inlineStr">
         <is>
-          <t>info@clovertechnology.co.uk</t>
+          <t>info@louderproductions.com</t>
         </is>
       </c>
       <c r="T57" s="15" t="inlineStr">
@@ -10693,22 +10691,18 @@
       </c>
       <c r="U57" s="16" t="inlineStr">
         <is>
-          <t>https://www.clovertechnology.co.uk/</t>
-        </is>
-      </c>
-      <c r="X57" s="15" t="inlineStr">
-        <is>
-          <t>86-90 Paul Street</t>
-        </is>
-      </c>
+          <t>https://louderproductions.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="X57" s="15" t="n"/>
       <c r="Y57" s="15" t="inlineStr">
         <is>
-          <t>EC2A 4NE</t>
+          <t>EC2A 4JU</t>
         </is>
       </c>
       <c r="Z57" s="15" t="inlineStr">
         <is>
-          <t>Website (86-90 Paul Street)</t>
+          <t>Registered office (no address on website)</t>
         </is>
       </c>
       <c r="AA57" s="15" t="inlineStr">
@@ -10787,7 +10781,7 @@
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>Marketing / agency</t>
+          <t>Tech / software</t>
         </is>
       </c>
       <c r="D58" s="15" t="inlineStr">
@@ -10797,17 +10791,17 @@
       </c>
       <c r="E58" s="15" t="inlineStr">
         <is>
-          <t>Louder Productions Limited</t>
+          <t>Arcontech Group PLC</t>
         </is>
       </c>
       <c r="F58" s="15" t="inlineStr">
         <is>
-          <t>Louder Productions</t>
+          <t>Arcontech</t>
         </is>
       </c>
       <c r="G58" s="16" t="inlineStr">
         <is>
-          <t>https://www.louderproductions.com</t>
+          <t>https://www.arcontech.com</t>
         </is>
       </c>
       <c r="H58" s="15" t="inlineStr">
@@ -10817,7 +10811,7 @@
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
-          <t>06459817</t>
+          <t>04062416</t>
         </is>
       </c>
       <c r="J58" s="16" t="inlineStr">
@@ -10832,12 +10826,12 @@
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
-          <t>27/12/2007</t>
+          <t>24/08/2000</t>
         </is>
       </c>
       <c r="M58" s="15" t="inlineStr">
         <is>
-          <t>27 Paul Street, London</t>
+          <t>1St Floor, 11-21 Paul Street, London</t>
         </is>
       </c>
       <c r="N58" s="15" t="inlineStr">
@@ -10855,7 +10849,7 @@
       <c r="R58" s="15" t="n"/>
       <c r="S58" s="15" t="inlineStr">
         <is>
-          <t>info@louderproductions.com</t>
+          <t>mail@arcontech.com</t>
         </is>
       </c>
       <c r="T58" s="15" t="inlineStr">
@@ -10865,10 +10859,14 @@
       </c>
       <c r="U58" s="16" t="inlineStr">
         <is>
-          <t>https://louderproductions.com/contact-us/</t>
-        </is>
-      </c>
-      <c r="X58" s="15" t="n"/>
+          <t>https://www.arcontech.com/</t>
+        </is>
+      </c>
+      <c r="X58" s="15" t="inlineStr">
+        <is>
+          <t>1st Floor, 11-21 Paul Street</t>
+        </is>
+      </c>
       <c r="Y58" s="15" t="inlineStr">
         <is>
           <t>EC2A 4JU</t>
@@ -10876,7 +10874,7 @@
       </c>
       <c r="Z58" s="15" t="inlineStr">
         <is>
-          <t>Registered office (no address on website)</t>
+          <t>Website (1st Floor, 11-21 Paul Street)</t>
         </is>
       </c>
       <c r="AA58" s="15" t="inlineStr">
@@ -10965,27 +10963,25 @@
       </c>
       <c r="E59" s="15" t="inlineStr">
         <is>
-          <t>Arcontech Group PLC</t>
+          <t>Veed Limited</t>
         </is>
       </c>
       <c r="F59" s="15" t="inlineStr">
         <is>
-          <t>Arcontech</t>
+          <t>Veed</t>
         </is>
       </c>
       <c r="G59" s="16" t="inlineStr">
         <is>
-          <t>https://www.arcontech.com</t>
-        </is>
-      </c>
-      <c r="H59" s="15" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
+          <t>https://www.veed.io</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="n">
+        <v>150</v>
       </c>
       <c r="I59" s="15" t="inlineStr">
         <is>
-          <t>04062416</t>
+          <t>11264311</t>
         </is>
       </c>
       <c r="J59" s="16" t="inlineStr">
@@ -11000,17 +10996,17 @@
       </c>
       <c r="L59" s="15" t="inlineStr">
         <is>
-          <t>24/08/2000</t>
+          <t>20/03/2018</t>
         </is>
       </c>
       <c r="M59" s="15" t="inlineStr">
         <is>
-          <t>1St Floor, 11-21 Paul Street, London</t>
+          <t>17-18 Clere Street, London</t>
         </is>
       </c>
       <c r="N59" s="15" t="inlineStr">
         <is>
-          <t>EC2A 4JU</t>
+          <t>EC2A 4LJ</t>
         </is>
       </c>
       <c r="O59" s="15" t="inlineStr">
@@ -11023,7 +11019,7 @@
       <c r="R59" s="15" t="n"/>
       <c r="S59" s="15" t="inlineStr">
         <is>
-          <t>mail@arcontech.com</t>
+          <t>hello@veed.io</t>
         </is>
       </c>
       <c r="T59" s="15" t="inlineStr">
@@ -11033,22 +11029,22 @@
       </c>
       <c r="U59" s="16" t="inlineStr">
         <is>
-          <t>https://www.arcontech.com/</t>
+          <t>https://www.veed.io/</t>
         </is>
       </c>
       <c r="X59" s="15" t="inlineStr">
         <is>
-          <t>1st Floor, 11-21 Paul Street</t>
+          <t>17-18 CLERE STREET</t>
         </is>
       </c>
       <c r="Y59" s="15" t="inlineStr">
         <is>
-          <t>EC2A 4JU</t>
+          <t>EC2A 4LJ</t>
         </is>
       </c>
       <c r="Z59" s="15" t="inlineStr">
         <is>
-          <t>Website (1st Floor, 11-21 Paul Street)</t>
+          <t>Website (17-18 CLERE STREET)</t>
         </is>
       </c>
       <c r="AA59" s="15" t="inlineStr">
@@ -11137,17 +11133,17 @@
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>Veed Limited</t>
+          <t>Atech Support Limited</t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
         <is>
-          <t>Veed</t>
+          <t>Atech Support</t>
         </is>
       </c>
       <c r="G60" s="16" t="inlineStr">
         <is>
-          <t>https://www.veed.io</t>
+          <t>https://www.atech.co.uk</t>
         </is>
       </c>
       <c r="H60" s="15" t="inlineStr">
@@ -11157,7 +11153,7 @@
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
-          <t>11264311</t>
+          <t>06021756</t>
         </is>
       </c>
       <c r="J60" s="16" t="inlineStr">
@@ -11167,22 +11163,22 @@
       </c>
       <c r="K60" s="15" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
-          <t>20/03/2018</t>
+          <t>07/12/2006</t>
         </is>
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>17-18 Clere Street, London</t>
+          <t>11-21 Paul Street, Shoreditch, London</t>
         </is>
       </c>
       <c r="N60" s="15" t="inlineStr">
         <is>
-          <t>EC2A 4LJ</t>
+          <t>EC2A 4JU</t>
         </is>
       </c>
       <c r="O60" s="15" t="inlineStr">
@@ -11195,7 +11191,7 @@
       <c r="R60" s="15" t="n"/>
       <c r="S60" s="15" t="inlineStr">
         <is>
-          <t>hello@veed.io</t>
+          <t>enquiries@atech.co.uk</t>
         </is>
       </c>
       <c r="T60" s="15" t="inlineStr">
@@ -11205,22 +11201,18 @@
       </c>
       <c r="U60" s="16" t="inlineStr">
         <is>
-          <t>https://www.veed.io/</t>
-        </is>
-      </c>
-      <c r="X60" s="15" t="inlineStr">
-        <is>
-          <t>17-18 CLERE STREET</t>
-        </is>
-      </c>
+          <t>https://www.atech.co.uk/</t>
+        </is>
+      </c>
+      <c r="X60" s="15" t="n"/>
       <c r="Y60" s="15" t="inlineStr">
         <is>
-          <t>EC2A 4LJ</t>
+          <t>EC2A 4JU</t>
         </is>
       </c>
       <c r="Z60" s="15" t="inlineStr">
         <is>
-          <t>Website (17-18 CLERE STREET)</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="AA60" s="15" t="inlineStr">
@@ -11299,27 +11291,27 @@
       </c>
       <c r="C61" s="15" t="inlineStr">
         <is>
-          <t>Tech / software</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="D61" s="15" t="inlineStr">
         <is>
-          <t>EC2A</t>
+          <t>N7</t>
         </is>
       </c>
       <c r="E61" s="15" t="inlineStr">
         <is>
-          <t>Atech Support Limited</t>
+          <t>Dasa Cis Limited</t>
         </is>
       </c>
       <c r="F61" s="15" t="inlineStr">
         <is>
-          <t>Atech Support</t>
+          <t>Dasa Cis</t>
         </is>
       </c>
       <c r="G61" s="16" t="inlineStr">
         <is>
-          <t>https://www.atech.co.uk</t>
+          <t>https://dasacis.co.uk</t>
         </is>
       </c>
       <c r="H61" s="15" t="inlineStr">
@@ -11329,7 +11321,7 @@
       </c>
       <c r="I61" s="15" t="inlineStr">
         <is>
-          <t>06021756</t>
+          <t>08576888</t>
         </is>
       </c>
       <c r="J61" s="16" t="inlineStr">
@@ -11339,22 +11331,22 @@
       </c>
       <c r="K61" s="15" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L61" s="15" t="inlineStr">
         <is>
-          <t>07/12/2006</t>
+          <t>20/06/2013</t>
         </is>
       </c>
       <c r="M61" s="15" t="inlineStr">
         <is>
-          <t>11-21 Paul Street, Shoreditch, London</t>
+          <t>Studio 6, 6 Hornsey Street, London</t>
         </is>
       </c>
       <c r="N61" s="15" t="inlineStr">
         <is>
-          <t>EC2A 4JU</t>
+          <t>N7 8GR</t>
         </is>
       </c>
       <c r="O61" s="15" t="inlineStr">
@@ -11367,7 +11359,7 @@
       <c r="R61" s="15" t="n"/>
       <c r="S61" s="15" t="inlineStr">
         <is>
-          <t>enquiries@atech.co.uk</t>
+          <t>info@dasacis.co.uk</t>
         </is>
       </c>
       <c r="T61" s="15" t="inlineStr">
@@ -11377,23 +11369,27 @@
       </c>
       <c r="U61" s="16" t="inlineStr">
         <is>
-          <t>https://www.atech.co.uk/</t>
-        </is>
-      </c>
-      <c r="X61" s="15" t="n"/>
+          <t>https://dasacis.co.uk/</t>
+        </is>
+      </c>
+      <c r="X61" s="15" t="inlineStr">
+        <is>
+          <t>58 High Street</t>
+        </is>
+      </c>
       <c r="Y61" s="15" t="inlineStr">
         <is>
-          <t>EC2A 4JU</t>
+          <t>N7 8GR</t>
         </is>
       </c>
       <c r="Z61" s="15" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Website (58 High Street)</t>
         </is>
       </c>
       <c r="AA61" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Market Road</t>
         </is>
       </c>
       <c r="AB61" s="15" t="n">
@@ -11401,12 +11397,12 @@
       </c>
       <c r="AC61" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Market Road</t>
         </is>
       </c>
       <c r="AD61" s="15" t="inlineStr">
         <is>
-          <t>Monday 28 September at 17:40</t>
+          <t>Monday 28 September at 18:00</t>
         </is>
       </c>
       <c r="AE61" s="15" t="inlineStr">
@@ -11423,7 +11419,11 @@
         <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
         <v/>
       </c>
-      <c r="AH61" s="15" t="n"/>
+      <c r="AH61" s="15" t="inlineStr">
+        <is>
+          <t>office at 58 High Street</t>
+        </is>
+      </c>
       <c r="AI61" s="15" t="n"/>
       <c r="AJ61" s="18">
         <f>IF(V61&lt;&gt;"",V61,S61)</f>
@@ -11467,37 +11467,35 @@
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Tech / software</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>EC2A</t>
         </is>
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>Dasa Cis Limited</t>
+          <t>Tryzens Global Limited</t>
         </is>
       </c>
       <c r="F62" s="15" t="inlineStr">
         <is>
-          <t>Dasa Cis</t>
+          <t>Tryzens</t>
         </is>
       </c>
       <c r="G62" s="16" t="inlineStr">
         <is>
-          <t>https://dasacis.co.uk</t>
-        </is>
-      </c>
-      <c r="H62" s="15" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
+          <t>https://tryzens.com</t>
+        </is>
+      </c>
+      <c r="H62" s="15" t="n">
+        <v>350</v>
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
-          <t>08576888</t>
+          <t>08624932</t>
         </is>
       </c>
       <c r="J62" s="16" t="inlineStr">
@@ -11507,22 +11505,22 @@
       </c>
       <c r="K62" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="L62" s="15" t="inlineStr">
         <is>
-          <t>20/06/2013</t>
+          <t>25/07/2013</t>
         </is>
       </c>
       <c r="M62" s="15" t="inlineStr">
         <is>
-          <t>Studio 6, 6 Hornsey Street, London</t>
+          <t>4Th Floor, 20 Appold Street, London</t>
         </is>
       </c>
       <c r="N62" s="15" t="inlineStr">
         <is>
-          <t>N7 8GR</t>
+          <t>EC2A 2AS</t>
         </is>
       </c>
       <c r="O62" s="15" t="inlineStr">
@@ -11535,7 +11533,7 @@
       <c r="R62" s="15" t="n"/>
       <c r="S62" s="15" t="inlineStr">
         <is>
-          <t>info@dasacis.co.uk</t>
+          <t>hello@tryzens.com</t>
         </is>
       </c>
       <c r="T62" s="15" t="inlineStr">
@@ -11545,27 +11543,27 @@
       </c>
       <c r="U62" s="16" t="inlineStr">
         <is>
-          <t>https://dasacis.co.uk/</t>
+          <t>https://tryzens.com/contact-us/</t>
         </is>
       </c>
       <c r="X62" s="15" t="inlineStr">
         <is>
-          <t>58 High Street</t>
+          <t>4th Floor, 20 Appold Street</t>
         </is>
       </c>
       <c r="Y62" s="15" t="inlineStr">
         <is>
-          <t>N7 8GR</t>
+          <t>EC2A 2AS</t>
         </is>
       </c>
       <c r="Z62" s="15" t="inlineStr">
         <is>
-          <t>Website (58 High Street)</t>
+          <t>Website (4th Floor, 20 Appold Street)</t>
         </is>
       </c>
       <c r="AA62" s="15" t="inlineStr">
         <is>
-          <t>Market Road</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AB62" s="15" t="n">
@@ -11573,12 +11571,12 @@
       </c>
       <c r="AC62" s="15" t="inlineStr">
         <is>
-          <t>Market Road</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AD62" s="15" t="inlineStr">
         <is>
-          <t>Monday 28 September at 18:00</t>
+          <t>Monday 28 September at 17:40</t>
         </is>
       </c>
       <c r="AE62" s="15" t="inlineStr">
@@ -11595,11 +11593,7 @@
         <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
         <v/>
       </c>
-      <c r="AH62" s="15" t="inlineStr">
-        <is>
-          <t>office at 58 High Street</t>
-        </is>
-      </c>
+      <c r="AH62" s="15" t="n"/>
       <c r="AI62" s="15" t="n"/>
       <c r="AJ62" s="18">
         <f>IF(V62&lt;&gt;"",V62,S62)</f>
@@ -11643,35 +11637,37 @@
       </c>
       <c r="C63" s="15" t="inlineStr">
         <is>
-          <t>Tech / software</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="D63" s="15" t="inlineStr">
         <is>
-          <t>EC2A</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="E63" s="15" t="inlineStr">
         <is>
-          <t>Tryzens Global Limited</t>
+          <t>Karakusevic Carson Architects Limited</t>
         </is>
       </c>
       <c r="F63" s="15" t="inlineStr">
         <is>
-          <t>Tryzens</t>
+          <t>Karakusevic Carson Architects</t>
         </is>
       </c>
       <c r="G63" s="16" t="inlineStr">
         <is>
-          <t>https://tryzens.com</t>
-        </is>
-      </c>
-      <c r="H63" s="15" t="n">
-        <v>350</v>
+          <t>https://www.karakusevic-carson.com</t>
+        </is>
+      </c>
+      <c r="H63" s="15" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
       </c>
       <c r="I63" s="15" t="inlineStr">
         <is>
-          <t>08624932</t>
+          <t>08720267</t>
         </is>
       </c>
       <c r="J63" s="16" t="inlineStr">
@@ -11686,17 +11682,17 @@
       </c>
       <c r="L63" s="15" t="inlineStr">
         <is>
-          <t>25/07/2013</t>
+          <t>07/10/2013</t>
         </is>
       </c>
       <c r="M63" s="15" t="inlineStr">
         <is>
-          <t>4Th Floor, 20 Appold Street, London</t>
+          <t>Studio 501 37 Cremer Street, Hackney, London</t>
         </is>
       </c>
       <c r="N63" s="15" t="inlineStr">
         <is>
-          <t>EC2A 2AS</t>
+          <t>E2 8HD</t>
         </is>
       </c>
       <c r="O63" s="15" t="inlineStr">
@@ -11709,7 +11705,7 @@
       <c r="R63" s="15" t="n"/>
       <c r="S63" s="15" t="inlineStr">
         <is>
-          <t>hello@tryzens.com</t>
+          <t>mail@karakusevic-carson.com</t>
         </is>
       </c>
       <c r="T63" s="15" t="inlineStr">
@@ -11719,40 +11715,40 @@
       </c>
       <c r="U63" s="16" t="inlineStr">
         <is>
-          <t>https://tryzens.com/contact-us/</t>
+          <t>https://www.karakusevic-carson.com/</t>
         </is>
       </c>
       <c r="X63" s="15" t="inlineStr">
         <is>
-          <t>4th Floor, 20 Appold Street</t>
+          <t>37 Cremer St</t>
         </is>
       </c>
       <c r="Y63" s="15" t="inlineStr">
         <is>
-          <t>EC2A 2AS</t>
+          <t>E2 8HD</t>
         </is>
       </c>
       <c r="Z63" s="15" t="inlineStr">
         <is>
-          <t>Website (4th Floor, 20 Appold Street)</t>
+          <t>Website (37 Cremer St)</t>
         </is>
       </c>
       <c r="AA63" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Shoreditch Rooftop</t>
         </is>
       </c>
       <c r="AB63" s="15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AC63" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Shoreditch Rooftop</t>
         </is>
       </c>
       <c r="AD63" s="15" t="inlineStr">
         <is>
-          <t>Monday 28 September at 17:40</t>
+          <t>Monday 28 September at 18:00</t>
         </is>
       </c>
       <c r="AE63" s="15" t="inlineStr">
@@ -11813,27 +11809,27 @@
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>EC2A</t>
         </is>
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>Karakusevic Carson Architects Limited</t>
+          <t>Your World Recruitment Limited</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
-          <t>Karakusevic Carson Architects</t>
+          <t>Your World Recruitment</t>
         </is>
       </c>
       <c r="G64" s="16" t="inlineStr">
         <is>
-          <t>https://www.karakusevic-carson.com</t>
+          <t>https://www.yourworld.com</t>
         </is>
       </c>
       <c r="H64" s="15" t="inlineStr">
@@ -11843,7 +11839,7 @@
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t>08720267</t>
+          <t>05460751</t>
         </is>
       </c>
       <c r="J64" s="16" t="inlineStr">
@@ -11853,22 +11849,22 @@
       </c>
       <c r="K64" s="15" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>07/10/2013</t>
+          <t>23/05/2005</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>Studio 501 37 Cremer Street, Hackney, London</t>
+          <t>4Th Floor, 69 Wilson Street, London</t>
         </is>
       </c>
       <c r="N64" s="15" t="inlineStr">
         <is>
-          <t>E2 8HD</t>
+          <t>EC2A 2BB</t>
         </is>
       </c>
       <c r="O64" s="15" t="inlineStr">
@@ -11881,7 +11877,7 @@
       <c r="R64" s="15" t="n"/>
       <c r="S64" s="15" t="inlineStr">
         <is>
-          <t>mail@karakusevic-carson.com</t>
+          <t>info@yourworld.com</t>
         </is>
       </c>
       <c r="T64" s="15" t="inlineStr">
@@ -11891,27 +11887,27 @@
       </c>
       <c r="U64" s="16" t="inlineStr">
         <is>
-          <t>https://www.karakusevic-carson.com/</t>
+          <t>https://www.yourworld.com/uk/contact</t>
         </is>
       </c>
       <c r="X64" s="15" t="inlineStr">
         <is>
-          <t>37 Cremer St</t>
+          <t>4th Floor, 69 Wilson Street</t>
         </is>
       </c>
       <c r="Y64" s="15" t="inlineStr">
         <is>
-          <t>E2 8HD</t>
+          <t>EC2A 2BB</t>
         </is>
       </c>
       <c r="Z64" s="15" t="inlineStr">
         <is>
-          <t>Website (37 Cremer St)</t>
+          <t>Website (4th Floor, 69 Wilson Street)</t>
         </is>
       </c>
       <c r="AA64" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Rooftop</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AB64" s="15" t="n">
@@ -11919,12 +11915,12 @@
       </c>
       <c r="AC64" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Rooftop</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AD64" s="15" t="inlineStr">
         <is>
-          <t>Monday 28 September at 18:00</t>
+          <t>Monday 28 September at 17:40</t>
         </is>
       </c>
       <c r="AE64" s="15" t="inlineStr">
@@ -11985,7 +11981,7 @@
       </c>
       <c r="C65" s="15" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Tech / software</t>
         </is>
       </c>
       <c r="D65" s="15" t="inlineStr">
@@ -11995,27 +11991,25 @@
       </c>
       <c r="E65" s="15" t="inlineStr">
         <is>
-          <t>Your World Recruitment Limited</t>
+          <t>Datasite UK Ltd.</t>
         </is>
       </c>
       <c r="F65" s="15" t="inlineStr">
         <is>
-          <t>Your World Recruitment</t>
+          <t>Datasite</t>
         </is>
       </c>
       <c r="G65" s="16" t="inlineStr">
         <is>
-          <t>https://www.yourworld.com</t>
-        </is>
-      </c>
-      <c r="H65" s="15" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
+          <t>https://www.datasite.com</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="n">
+        <v>44</v>
       </c>
       <c r="I65" s="15" t="inlineStr">
         <is>
-          <t>05460751</t>
+          <t>03829230</t>
         </is>
       </c>
       <c r="J65" s="16" t="inlineStr">
@@ -12030,17 +12024,17 @@
       </c>
       <c r="L65" s="15" t="inlineStr">
         <is>
-          <t>23/05/2005</t>
+          <t>17/08/1999</t>
         </is>
       </c>
       <c r="M65" s="15" t="inlineStr">
         <is>
-          <t>4Th Floor, 69 Wilson Street, London</t>
+          <t>15 Bonhill Street, London</t>
         </is>
       </c>
       <c r="N65" s="15" t="inlineStr">
         <is>
-          <t>EC2A 2BB</t>
+          <t>EC2A 4DN</t>
         </is>
       </c>
       <c r="O65" s="15" t="inlineStr">
@@ -12053,7 +12047,7 @@
       <c r="R65" s="15" t="n"/>
       <c r="S65" s="15" t="inlineStr">
         <is>
-          <t>info@yourworld.com</t>
+          <t>hr@datasite.com</t>
         </is>
       </c>
       <c r="T65" s="15" t="inlineStr">
@@ -12063,22 +12057,18 @@
       </c>
       <c r="U65" s="16" t="inlineStr">
         <is>
-          <t>https://www.yourworld.com/uk/contact</t>
-        </is>
-      </c>
-      <c r="X65" s="15" t="inlineStr">
-        <is>
-          <t>4th Floor, 69 Wilson Street</t>
-        </is>
-      </c>
+          <t>https://www.datasite.com/en/company/careers</t>
+        </is>
+      </c>
+      <c r="X65" s="15" t="n"/>
       <c r="Y65" s="15" t="inlineStr">
         <is>
-          <t>EC2A 2BB</t>
+          <t>EC2A 4DN</t>
         </is>
       </c>
       <c r="Z65" s="15" t="inlineStr">
         <is>
-          <t>Website (4th Floor, 69 Wilson Street)</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="AA65" s="15" t="inlineStr">
@@ -12113,8 +12103,16 @@
         <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
         <v/>
       </c>
-      <c r="AH65" s="15" t="n"/>
-      <c r="AI65" s="15" t="n"/>
+      <c r="AH65" s="15" t="inlineStr">
+        <is>
+          <t>team of 44 people</t>
+        </is>
+      </c>
+      <c r="AI65" s="16" t="inlineStr">
+        <is>
+          <t>https://www.datasite.com/en/company/about</t>
+        </is>
+      </c>
       <c r="AJ65" s="18">
         <f>IF(V65&lt;&gt;"",V65,S65)</f>
         <v/>
@@ -12157,35 +12155,37 @@
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Tech / software</t>
+          <t>Consultancy</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>EC2A</t>
+          <t>EC1V</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>Datasite UK Ltd.</t>
+          <t>Beeline.Com Limited</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
-          <t>Datasite</t>
+          <t>Beeline.Com</t>
         </is>
       </c>
       <c r="G66" s="16" t="inlineStr">
         <is>
-          <t>https://www.datasite.com</t>
-        </is>
-      </c>
-      <c r="H66" s="15" t="n">
-        <v>44</v>
+          <t>https://www.beeline.com</t>
+        </is>
+      </c>
+      <c r="H66" s="15" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
-          <t>03829230</t>
+          <t>04993515</t>
         </is>
       </c>
       <c r="J66" s="16" t="inlineStr">
@@ -12195,22 +12195,22 @@
       </c>
       <c r="K66" s="15" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
-          <t>17/08/1999</t>
+          <t>12/12/2003</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>15 Bonhill Street, London</t>
+          <t>124 City Road, London</t>
         </is>
       </c>
       <c r="N66" s="15" t="inlineStr">
         <is>
-          <t>EC2A 4DN</t>
+          <t>EC1V 2NX</t>
         </is>
       </c>
       <c r="O66" s="15" t="inlineStr">
@@ -12223,7 +12223,7 @@
       <c r="R66" s="15" t="n"/>
       <c r="S66" s="15" t="inlineStr">
         <is>
-          <t>hr@datasite.com</t>
+          <t>beelinecommunity@beeline.com</t>
         </is>
       </c>
       <c r="T66" s="15" t="inlineStr">
@@ -12233,23 +12233,27 @@
       </c>
       <c r="U66" s="16" t="inlineStr">
         <is>
-          <t>https://www.datasite.com/en/company/careers</t>
-        </is>
-      </c>
-      <c r="X66" s="15" t="n"/>
+          <t>https://www.beeline.com/contact/support</t>
+        </is>
+      </c>
+      <c r="X66" s="15" t="inlineStr">
+        <is>
+          <t>124 City Road</t>
+        </is>
+      </c>
       <c r="Y66" s="15" t="inlineStr">
         <is>
-          <t>EC2A 4DN</t>
+          <t>EC1V 2NX</t>
         </is>
       </c>
       <c r="Z66" s="15" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Website (124 City Road)</t>
         </is>
       </c>
       <c r="AA66" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AB66" s="15" t="n">
@@ -12257,12 +12261,12 @@
       </c>
       <c r="AC66" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AD66" s="15" t="inlineStr">
         <is>
-          <t>Monday 28 September at 17:40</t>
+          <t>Monday 12 October at 18:00</t>
         </is>
       </c>
       <c r="AE66" s="15" t="inlineStr">
@@ -12272,23 +12276,15 @@
       </c>
       <c r="AF66" s="15" t="inlineStr">
         <is>
-          <t>5-a-side</t>
+          <t>6-a-side</t>
         </is>
       </c>
       <c r="AG66" s="17">
         <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
         <v/>
       </c>
-      <c r="AH66" s="15" t="inlineStr">
-        <is>
-          <t>team of 44 people</t>
-        </is>
-      </c>
-      <c r="AI66" s="16" t="inlineStr">
-        <is>
-          <t>https://www.datasite.com/en/company/about</t>
-        </is>
-      </c>
+      <c r="AH66" s="15" t="n"/>
+      <c r="AI66" s="15" t="n"/>
       <c r="AJ66" s="18">
         <f>IF(V66&lt;&gt;"",V66,S66)</f>
         <v/>
@@ -12331,27 +12327,27 @@
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
-          <t>Consultancy</t>
+          <t>Tech / software</t>
         </is>
       </c>
       <c r="D67" s="15" t="inlineStr">
         <is>
-          <t>EC1V</t>
+          <t>EC1M</t>
         </is>
       </c>
       <c r="E67" s="15" t="inlineStr">
         <is>
-          <t>Beeline.Com Limited</t>
+          <t>Permutive Limited</t>
         </is>
       </c>
       <c r="F67" s="15" t="inlineStr">
         <is>
-          <t>Beeline.Com</t>
+          <t>Permutive</t>
         </is>
       </c>
       <c r="G67" s="16" t="inlineStr">
         <is>
-          <t>https://www.beeline.com</t>
+          <t>https://permutive.com</t>
         </is>
       </c>
       <c r="H67" s="15" t="inlineStr">
@@ -12361,7 +12357,7 @@
       </c>
       <c r="I67" s="15" t="inlineStr">
         <is>
-          <t>04993515</t>
+          <t>08738815</t>
         </is>
       </c>
       <c r="J67" s="16" t="inlineStr">
@@ -12371,22 +12367,22 @@
       </c>
       <c r="K67" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="L67" s="15" t="inlineStr">
         <is>
-          <t>12/12/2003</t>
+          <t>18/10/2013</t>
         </is>
       </c>
       <c r="M67" s="15" t="inlineStr">
         <is>
-          <t>124 City Road, London</t>
+          <t>Floor 2, 8-10 Charterhouse Buildings, Goswell Road, London</t>
         </is>
       </c>
       <c r="N67" s="15" t="inlineStr">
         <is>
-          <t>EC1V 2NX</t>
+          <t>EC1M 7AN</t>
         </is>
       </c>
       <c r="O67" s="15" t="inlineStr">
@@ -12399,7 +12395,7 @@
       <c r="R67" s="15" t="n"/>
       <c r="S67" s="15" t="inlineStr">
         <is>
-          <t>beelinecommunity@beeline.com</t>
+          <t>hello@permutive.com</t>
         </is>
       </c>
       <c r="T67" s="15" t="inlineStr">
@@ -12409,22 +12405,22 @@
       </c>
       <c r="U67" s="16" t="inlineStr">
         <is>
-          <t>https://www.beeline.com/contact/support</t>
+          <t>https://permutive.com/</t>
         </is>
       </c>
       <c r="X67" s="15" t="inlineStr">
         <is>
-          <t>124 City Road</t>
+          <t>FLOOR 2</t>
         </is>
       </c>
       <c r="Y67" s="15" t="inlineStr">
         <is>
-          <t>EC1V 2NX</t>
+          <t>EC1M 7AN</t>
         </is>
       </c>
       <c r="Z67" s="15" t="inlineStr">
         <is>
-          <t>Website (124 City Road)</t>
+          <t>Website (FLOOR 2)</t>
         </is>
       </c>
       <c r="AA67" s="15" t="inlineStr">
@@ -12508,22 +12504,22 @@
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>EC1M</t>
+          <t>EC2A</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>Permutive Limited</t>
+          <t>Optimove UK Limited</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>Permutive</t>
+          <t>Optimove</t>
         </is>
       </c>
       <c r="G68" s="16" t="inlineStr">
         <is>
-          <t>https://permutive.com</t>
+          <t>https://www.optimove.com</t>
         </is>
       </c>
       <c r="H68" s="15" t="inlineStr">
@@ -12533,7 +12529,7 @@
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
-          <t>08738815</t>
+          <t>10443820</t>
         </is>
       </c>
       <c r="J68" s="16" t="inlineStr">
@@ -12548,17 +12544,17 @@
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>18/10/2013</t>
+          <t>25/10/2016</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>Floor 2, 8-10 Charterhouse Buildings, Goswell Road, London</t>
+          <t>14 Bonhill Street, London</t>
         </is>
       </c>
       <c r="N68" s="15" t="inlineStr">
         <is>
-          <t>EC1M 7AN</t>
+          <t>EC2A 4BX</t>
         </is>
       </c>
       <c r="O68" s="15" t="inlineStr">
@@ -12571,7 +12567,7 @@
       <c r="R68" s="15" t="n"/>
       <c r="S68" s="15" t="inlineStr">
         <is>
-          <t>hello@permutive.com</t>
+          <t>info@optimove.com</t>
         </is>
       </c>
       <c r="T68" s="15" t="inlineStr">
@@ -12581,27 +12577,27 @@
       </c>
       <c r="U68" s="16" t="inlineStr">
         <is>
-          <t>https://permutive.com/</t>
+          <t>https://www.optimove.com/contact</t>
         </is>
       </c>
       <c r="X68" s="15" t="inlineStr">
         <is>
-          <t>FLOOR 2</t>
+          <t>14 Bonhill Street</t>
         </is>
       </c>
       <c r="Y68" s="15" t="inlineStr">
         <is>
-          <t>EC1M 7AN</t>
+          <t>EC2A 4BX</t>
         </is>
       </c>
       <c r="Z68" s="15" t="inlineStr">
         <is>
-          <t>Website (FLOOR 2)</t>
+          <t>Website (14 Bonhill Street)</t>
         </is>
       </c>
       <c r="AA68" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AB68" s="15" t="n">
@@ -12609,12 +12605,12 @@
       </c>
       <c r="AC68" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AD68" s="15" t="inlineStr">
         <is>
-          <t>Monday 12 October at 18:00</t>
+          <t>Monday 28 September at 17:40</t>
         </is>
       </c>
       <c r="AE68" s="15" t="inlineStr">
@@ -12624,7 +12620,7 @@
       </c>
       <c r="AF68" s="15" t="inlineStr">
         <is>
-          <t>6-a-side</t>
+          <t>5-a-side</t>
         </is>
       </c>
       <c r="AG68" s="17">
@@ -12680,22 +12676,22 @@
       </c>
       <c r="D69" s="15" t="inlineStr">
         <is>
-          <t>EC2A</t>
+          <t>EC1V</t>
         </is>
       </c>
       <c r="E69" s="15" t="inlineStr">
         <is>
-          <t>Optimove UK Limited</t>
+          <t>Northdoor PLC</t>
         </is>
       </c>
       <c r="F69" s="15" t="inlineStr">
         <is>
-          <t>Optimove</t>
+          <t>Northdoor</t>
         </is>
       </c>
       <c r="G69" s="16" t="inlineStr">
         <is>
-          <t>https://www.optimove.com</t>
+          <t>https://northdoor.co</t>
         </is>
       </c>
       <c r="H69" s="15" t="inlineStr">
@@ -12705,7 +12701,7 @@
       </c>
       <c r="I69" s="15" t="inlineStr">
         <is>
-          <t>10443820</t>
+          <t>02192480</t>
         </is>
       </c>
       <c r="J69" s="16" t="inlineStr">
@@ -12715,22 +12711,22 @@
       </c>
       <c r="K69" s="15" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="L69" s="15" t="inlineStr">
         <is>
-          <t>25/10/2016</t>
+          <t>11/11/1987</t>
         </is>
       </c>
       <c r="M69" s="15" t="inlineStr">
         <is>
-          <t>14 Bonhill Street, London</t>
+          <t>Third Floor, Bentima House, 168-172 Old Street, London</t>
         </is>
       </c>
       <c r="N69" s="15" t="inlineStr">
         <is>
-          <t>EC2A 4BX</t>
+          <t>EC1V 9BP</t>
         </is>
       </c>
       <c r="O69" s="15" t="inlineStr">
@@ -12743,7 +12739,7 @@
       <c r="R69" s="15" t="n"/>
       <c r="S69" s="15" t="inlineStr">
         <is>
-          <t>info@optimove.com</t>
+          <t>eli@northdoor.co</t>
         </is>
       </c>
       <c r="T69" s="15" t="inlineStr">
@@ -12753,27 +12749,27 @@
       </c>
       <c r="U69" s="16" t="inlineStr">
         <is>
-          <t>https://www.optimove.com/contact</t>
+          <t>https://northdoor.co/</t>
         </is>
       </c>
       <c r="X69" s="15" t="inlineStr">
         <is>
-          <t>14 Bonhill Street</t>
+          <t>Third Floor, Bentima House, 168-172 Old Street</t>
         </is>
       </c>
       <c r="Y69" s="15" t="inlineStr">
         <is>
-          <t>EC2A 4BX</t>
+          <t>EC1V 9BP</t>
         </is>
       </c>
       <c r="Z69" s="15" t="inlineStr">
         <is>
-          <t>Website (14 Bonhill Street)</t>
+          <t>Website (Third Floor, Bentima House, 168-172 Old Street)</t>
         </is>
       </c>
       <c r="AA69" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AB69" s="15" t="n">
@@ -12781,12 +12777,12 @@
       </c>
       <c r="AC69" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AD69" s="15" t="inlineStr">
         <is>
-          <t>Monday 28 September at 17:40</t>
+          <t>Monday 12 October at 18:00</t>
         </is>
       </c>
       <c r="AE69" s="15" t="inlineStr">
@@ -12796,7 +12792,7 @@
       </c>
       <c r="AF69" s="15" t="inlineStr">
         <is>
-          <t>5-a-side</t>
+          <t>6-a-side</t>
         </is>
       </c>
       <c r="AG69" s="17">
@@ -12847,27 +12843,27 @@
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Tech / software</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>EC1V</t>
+          <t>EC1Y</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>Northdoor PLC</t>
+          <t>Eric Parry Architects Ltd</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>Northdoor</t>
+          <t>Eric Parry Architects</t>
         </is>
       </c>
       <c r="G70" s="16" t="inlineStr">
         <is>
-          <t>https://northdoor.co</t>
+          <t>https://ericparryarchitects.co.uk</t>
         </is>
       </c>
       <c r="H70" s="15" t="inlineStr">
@@ -12877,7 +12873,7 @@
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
-          <t>02192480</t>
+          <t>02522093</t>
         </is>
       </c>
       <c r="J70" s="16" t="inlineStr">
@@ -12892,17 +12888,17 @@
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>11/11/1987</t>
+          <t>13/07/1990</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>Third Floor, Bentima House, 168-172 Old Street, London</t>
+          <t>28-42 Banner Street, London</t>
         </is>
       </c>
       <c r="N70" s="15" t="inlineStr">
         <is>
-          <t>EC1V 9BP</t>
+          <t>EC1Y 8QE</t>
         </is>
       </c>
       <c r="O70" s="15" t="inlineStr">
@@ -12915,7 +12911,7 @@
       <c r="R70" s="15" t="n"/>
       <c r="S70" s="15" t="inlineStr">
         <is>
-          <t>eli@northdoor.co</t>
+          <t>epa@ericparryarchitects.co.uk</t>
         </is>
       </c>
       <c r="T70" s="15" t="inlineStr">
@@ -12925,22 +12921,22 @@
       </c>
       <c r="U70" s="16" t="inlineStr">
         <is>
-          <t>https://northdoor.co/</t>
+          <t>https://ericparryarchitects.co.uk/</t>
         </is>
       </c>
       <c r="X70" s="15" t="inlineStr">
         <is>
-          <t>Third Floor, Bentima House, 168-172 Old Street</t>
+          <t>28-42 Banner Street</t>
         </is>
       </c>
       <c r="Y70" s="15" t="inlineStr">
         <is>
-          <t>EC1V 9BP</t>
+          <t>EC1Y 8QE</t>
         </is>
       </c>
       <c r="Z70" s="15" t="inlineStr">
         <is>
-          <t>Website (Third Floor, Bentima House, 168-172 Old Street)</t>
+          <t>Website (28-42 Banner Street)</t>
         </is>
       </c>
       <c r="AA70" s="15" t="inlineStr">
@@ -13024,22 +13020,22 @@
       </c>
       <c r="D71" s="15" t="inlineStr">
         <is>
-          <t>EC1Y</t>
+          <t>EC2A</t>
         </is>
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>Eric Parry Architects Ltd</t>
+          <t>McBains Ltd</t>
         </is>
       </c>
       <c r="F71" s="15" t="inlineStr">
         <is>
-          <t>Eric Parry Architects</t>
+          <t>McBains</t>
         </is>
       </c>
       <c r="G71" s="16" t="inlineStr">
         <is>
-          <t>https://ericparryarchitects.co.uk</t>
+          <t>https://mcbains.co.uk</t>
         </is>
       </c>
       <c r="H71" s="15" t="inlineStr">
@@ -13049,7 +13045,7 @@
       </c>
       <c r="I71" s="15" t="inlineStr">
         <is>
-          <t>02522093</t>
+          <t>03094139</t>
         </is>
       </c>
       <c r="J71" s="16" t="inlineStr">
@@ -13059,22 +13055,22 @@
       </c>
       <c r="K71" s="15" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="L71" s="15" t="inlineStr">
         <is>
-          <t>13/07/1990</t>
+          <t>23/08/1995</t>
         </is>
       </c>
       <c r="M71" s="15" t="inlineStr">
         <is>
-          <t>28-42 Banner Street, London</t>
+          <t>5Th Floor, 26 Finsbury Square, London</t>
         </is>
       </c>
       <c r="N71" s="15" t="inlineStr">
         <is>
-          <t>EC1Y 8QE</t>
+          <t>EC2A 1DS</t>
         </is>
       </c>
       <c r="O71" s="15" t="inlineStr">
@@ -13087,7 +13083,7 @@
       <c r="R71" s="15" t="n"/>
       <c r="S71" s="15" t="inlineStr">
         <is>
-          <t>epa@ericparryarchitects.co.uk</t>
+          <t>info@mcbains.co.uk</t>
         </is>
       </c>
       <c r="T71" s="15" t="inlineStr">
@@ -13097,27 +13093,23 @@
       </c>
       <c r="U71" s="16" t="inlineStr">
         <is>
-          <t>https://ericparryarchitects.co.uk/</t>
-        </is>
-      </c>
-      <c r="X71" s="15" t="inlineStr">
-        <is>
-          <t>28-42 Banner Street</t>
-        </is>
-      </c>
+          <t>https://mcbains.co.uk/</t>
+        </is>
+      </c>
+      <c r="X71" s="15" t="n"/>
       <c r="Y71" s="15" t="inlineStr">
         <is>
-          <t>EC1Y 8QE</t>
+          <t>EC2A 1DS</t>
         </is>
       </c>
       <c r="Z71" s="15" t="inlineStr">
         <is>
-          <t>Website (28-42 Banner Street)</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="AA71" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AB71" s="15" t="n">
@@ -13125,12 +13117,12 @@
       </c>
       <c r="AC71" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AD71" s="15" t="inlineStr">
         <is>
-          <t>Monday 12 October at 18:00</t>
+          <t>Monday 28 September at 17:40</t>
         </is>
       </c>
       <c r="AE71" s="15" t="inlineStr">
@@ -13140,7 +13132,7 @@
       </c>
       <c r="AF71" s="15" t="inlineStr">
         <is>
-          <t>6-a-side</t>
+          <t>5-a-side</t>
         </is>
       </c>
       <c r="AG71" s="17">
@@ -13191,27 +13183,27 @@
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Marketing / agency</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>EC2A</t>
+          <t>EC1R</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>McBains Ltd</t>
+          <t>Lightbox Media Limited</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>McBains</t>
+          <t>Lightbox Media</t>
         </is>
       </c>
       <c r="G72" s="16" t="inlineStr">
         <is>
-          <t>https://mcbains.co.uk</t>
+          <t>https://lightboxmedia.co</t>
         </is>
       </c>
       <c r="H72" s="15" t="inlineStr">
@@ -13221,7 +13213,7 @@
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
-          <t>03094139</t>
+          <t>08768677</t>
         </is>
       </c>
       <c r="J72" s="16" t="inlineStr">
@@ -13231,22 +13223,22 @@
       </c>
       <c r="K72" s="15" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>23/08/1995</t>
+          <t>11/11/2013</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>5Th Floor, 26 Finsbury Square, London</t>
+          <t>10 Amwell Street, London</t>
         </is>
       </c>
       <c r="N72" s="15" t="inlineStr">
         <is>
-          <t>EC2A 1DS</t>
+          <t>EC1R 1UQ</t>
         </is>
       </c>
       <c r="O72" s="15" t="inlineStr">
@@ -13259,7 +13251,7 @@
       <c r="R72" s="15" t="n"/>
       <c r="S72" s="15" t="inlineStr">
         <is>
-          <t>info@mcbains.co.uk</t>
+          <t>studio@lightboxmedia.co</t>
         </is>
       </c>
       <c r="T72" s="15" t="inlineStr">
@@ -13269,36 +13261,40 @@
       </c>
       <c r="U72" s="16" t="inlineStr">
         <is>
-          <t>https://mcbains.co.uk/</t>
-        </is>
-      </c>
-      <c r="X72" s="15" t="n"/>
+          <t>https://lightboxmedia.co/</t>
+        </is>
+      </c>
+      <c r="X72" s="15" t="inlineStr">
+        <is>
+          <t>10 AMWELL STREET</t>
+        </is>
+      </c>
       <c r="Y72" s="15" t="inlineStr">
         <is>
-          <t>EC2A 1DS</t>
+          <t>EC1R 1UQ</t>
         </is>
       </c>
       <c r="Z72" s="15" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Website (10 AMWELL STREET)</t>
         </is>
       </c>
       <c r="AA72" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AB72" s="15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC72" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AD72" s="15" t="inlineStr">
         <is>
-          <t>Monday 28 September at 17:40</t>
+          <t>Monday 12 October at 18:00</t>
         </is>
       </c>
       <c r="AE72" s="15" t="inlineStr">
@@ -13308,7 +13304,7 @@
       </c>
       <c r="AF72" s="15" t="inlineStr">
         <is>
-          <t>5-a-side</t>
+          <t>6-a-side</t>
         </is>
       </c>
       <c r="AG72" s="17">
@@ -13364,22 +13360,22 @@
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>EC1R</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>Lightbox Media Limited</t>
+          <t>Blue Square Marketing Limited</t>
         </is>
       </c>
       <c r="F73" s="15" t="inlineStr">
         <is>
-          <t>Lightbox Media</t>
+          <t>Blue Square Marketing</t>
         </is>
       </c>
       <c r="G73" s="16" t="inlineStr">
         <is>
-          <t>https://lightboxmedia.co</t>
+          <t>https://bluesquare.io</t>
         </is>
       </c>
       <c r="H73" s="15" t="inlineStr">
@@ -13389,7 +13385,7 @@
       </c>
       <c r="I73" s="15" t="inlineStr">
         <is>
-          <t>08768677</t>
+          <t>06797461</t>
         </is>
       </c>
       <c r="J73" s="16" t="inlineStr">
@@ -13399,22 +13395,22 @@
       </c>
       <c r="K73" s="15" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L73" s="15" t="inlineStr">
         <is>
-          <t>11/11/2013</t>
+          <t>21/01/2009</t>
         </is>
       </c>
       <c r="M73" s="15" t="inlineStr">
         <is>
-          <t>10 Amwell Street, London</t>
+          <t>10 East Road, London</t>
         </is>
       </c>
       <c r="N73" s="15" t="inlineStr">
         <is>
-          <t>EC1R 1UQ</t>
+          <t>N1 6AD</t>
         </is>
       </c>
       <c r="O73" s="15" t="inlineStr">
@@ -13427,7 +13423,7 @@
       <c r="R73" s="15" t="n"/>
       <c r="S73" s="15" t="inlineStr">
         <is>
-          <t>studio@lightboxmedia.co</t>
+          <t>contact@bluesquare.io</t>
         </is>
       </c>
       <c r="T73" s="15" t="inlineStr">
@@ -13437,22 +13433,18 @@
       </c>
       <c r="U73" s="16" t="inlineStr">
         <is>
-          <t>https://lightboxmedia.co/</t>
-        </is>
-      </c>
-      <c r="X73" s="15" t="inlineStr">
-        <is>
-          <t>10 AMWELL STREET</t>
-        </is>
-      </c>
+          <t>https://bluesquare.io/</t>
+        </is>
+      </c>
+      <c r="X73" s="15" t="n"/>
       <c r="Y73" s="15" t="inlineStr">
         <is>
-          <t>EC1R 1UQ</t>
+          <t>N1 6AD</t>
         </is>
       </c>
       <c r="Z73" s="15" t="inlineStr">
         <is>
-          <t>Website (10 AMWELL STREET)</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="AA73" s="15" t="inlineStr">
@@ -13531,7 +13523,7 @@
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Marketing / agency</t>
+          <t>Tech / software</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
@@ -13541,17 +13533,17 @@
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>Blue Square Marketing Limited</t>
+          <t>Push Gaming Limited</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>Blue Square Marketing</t>
+          <t>Push Gaming</t>
         </is>
       </c>
       <c r="G74" s="16" t="inlineStr">
         <is>
-          <t>https://bluesquare.io</t>
+          <t>https://www.pushgaming.com</t>
         </is>
       </c>
       <c r="H74" s="15" t="inlineStr">
@@ -13561,7 +13553,7 @@
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
-          <t>06797461</t>
+          <t>07395813</t>
         </is>
       </c>
       <c r="J74" s="16" t="inlineStr">
@@ -13576,12 +13568,12 @@
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>21/01/2009</t>
+          <t>04/10/2010</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>10 East Road, London</t>
+          <t>10Th Floor, 10, East Road, London</t>
         </is>
       </c>
       <c r="N74" s="15" t="inlineStr">
@@ -13599,7 +13591,7 @@
       <c r="R74" s="15" t="n"/>
       <c r="S74" s="15" t="inlineStr">
         <is>
-          <t>contact@bluesquare.io</t>
+          <t>info@pushgaming.com</t>
         </is>
       </c>
       <c r="T74" s="15" t="inlineStr">
@@ -13609,10 +13601,14 @@
       </c>
       <c r="U74" s="16" t="inlineStr">
         <is>
-          <t>https://bluesquare.io/</t>
-        </is>
-      </c>
-      <c r="X74" s="15" t="n"/>
+          <t>https://www.pushgaming.com/</t>
+        </is>
+      </c>
+      <c r="X74" s="15" t="inlineStr">
+        <is>
+          <t>10th Floor, 10 East Road</t>
+        </is>
+      </c>
       <c r="Y74" s="15" t="inlineStr">
         <is>
           <t>N1 6AD</t>
@@ -13620,7 +13616,7 @@
       </c>
       <c r="Z74" s="15" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Website (10th Floor, 10 East Road)</t>
         </is>
       </c>
       <c r="AA74" s="15" t="inlineStr">
@@ -13699,7 +13695,7 @@
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>Tech / software</t>
+          <t>Marketing / agency</t>
         </is>
       </c>
       <c r="D75" s="15" t="inlineStr">
@@ -13709,17 +13705,17 @@
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>Push Gaming Limited</t>
+          <t>Creative Monster Limited</t>
         </is>
       </c>
       <c r="F75" s="15" t="inlineStr">
         <is>
-          <t>Push Gaming</t>
+          <t>Creative Monster</t>
         </is>
       </c>
       <c r="G75" s="16" t="inlineStr">
         <is>
-          <t>https://www.pushgaming.com</t>
+          <t>https://www.creativemonster.com</t>
         </is>
       </c>
       <c r="H75" s="15" t="inlineStr">
@@ -13729,7 +13725,7 @@
       </c>
       <c r="I75" s="15" t="inlineStr">
         <is>
-          <t>07395813</t>
+          <t>10806730</t>
         </is>
       </c>
       <c r="J75" s="16" t="inlineStr">
@@ -13744,12 +13740,12 @@
       </c>
       <c r="L75" s="15" t="inlineStr">
         <is>
-          <t>04/10/2010</t>
+          <t>07/06/2017</t>
         </is>
       </c>
       <c r="M75" s="15" t="inlineStr">
         <is>
-          <t>10Th Floor, 10, East Road, London</t>
+          <t>10 East Road, London</t>
         </is>
       </c>
       <c r="N75" s="15" t="inlineStr">
@@ -13767,7 +13763,7 @@
       <c r="R75" s="15" t="n"/>
       <c r="S75" s="15" t="inlineStr">
         <is>
-          <t>info@pushgaming.com</t>
+          <t>info@creativemonster.com</t>
         </is>
       </c>
       <c r="T75" s="15" t="inlineStr">
@@ -13777,14 +13773,10 @@
       </c>
       <c r="U75" s="16" t="inlineStr">
         <is>
-          <t>https://www.pushgaming.com/</t>
-        </is>
-      </c>
-      <c r="X75" s="15" t="inlineStr">
-        <is>
-          <t>10th Floor, 10 East Road</t>
-        </is>
-      </c>
+          <t>https://www.creativemonster.com/</t>
+        </is>
+      </c>
+      <c r="X75" s="15" t="n"/>
       <c r="Y75" s="15" t="inlineStr">
         <is>
           <t>N1 6AD</t>
@@ -13792,7 +13784,7 @@
       </c>
       <c r="Z75" s="15" t="inlineStr">
         <is>
-          <t>Website (10th Floor, 10 East Road)</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="AA75" s="15" t="inlineStr">
@@ -13871,27 +13863,27 @@
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Marketing / agency</t>
+          <t>Tech / software</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>EC2M</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>Creative Monster Limited</t>
+          <t>Ipc Information Systems</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>Creative Monster</t>
+          <t>Ipc Information Systems</t>
         </is>
       </c>
       <c r="G76" s="16" t="inlineStr">
         <is>
-          <t>https://www.creativemonster.com</t>
+          <t>https://www.ipc.com</t>
         </is>
       </c>
       <c r="H76" s="15" t="inlineStr">
@@ -13901,7 +13893,7 @@
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t>10806730</t>
+          <t>01823833</t>
         </is>
       </c>
       <c r="J76" s="16" t="inlineStr">
@@ -13911,22 +13903,22 @@
       </c>
       <c r="K76" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>07/06/2017</t>
+          <t>12/06/1984</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>10 East Road, London</t>
+          <t>Devonshire Square, 1St Floor, 7 Devonshire Square, London</t>
         </is>
       </c>
       <c r="N76" s="15" t="inlineStr">
         <is>
-          <t>N1 6AD</t>
+          <t>EC2M 4YH</t>
         </is>
       </c>
       <c r="O76" s="15" t="inlineStr">
@@ -13939,7 +13931,7 @@
       <c r="R76" s="15" t="n"/>
       <c r="S76" s="15" t="inlineStr">
         <is>
-          <t>info@creativemonster.com</t>
+          <t>hr@ipc.com</t>
         </is>
       </c>
       <c r="T76" s="15" t="inlineStr">
@@ -13949,23 +13941,27 @@
       </c>
       <c r="U76" s="16" t="inlineStr">
         <is>
-          <t>https://www.creativemonster.com/</t>
-        </is>
-      </c>
-      <c r="X76" s="15" t="n"/>
+          <t>https://www.ipc.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="X76" s="15" t="inlineStr">
+        <is>
+          <t>DEVONSHIRE SQUARE</t>
+        </is>
+      </c>
       <c r="Y76" s="15" t="inlineStr">
         <is>
-          <t>N1 6AD</t>
+          <t>EC2M 4YH</t>
         </is>
       </c>
       <c r="Z76" s="15" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Website (DEVONSHIRE SQUARE)</t>
         </is>
       </c>
       <c r="AA76" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AB76" s="15" t="n">
@@ -13973,12 +13969,12 @@
       </c>
       <c r="AC76" s="15" t="inlineStr">
         <is>
-          <t>Old St - Moreland Primary School</t>
+          <t>Shoreditch Powerleague</t>
         </is>
       </c>
       <c r="AD76" s="15" t="inlineStr">
         <is>
-          <t>Monday 12 October at 18:00</t>
+          <t>Monday 28 September at 17:40</t>
         </is>
       </c>
       <c r="AE76" s="15" t="inlineStr">
@@ -13988,7 +13984,7 @@
       </c>
       <c r="AF76" s="15" t="inlineStr">
         <is>
-          <t>6-a-side</t>
+          <t>5-a-side</t>
         </is>
       </c>
       <c r="AG76" s="17">
@@ -14039,7 +14035,7 @@
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>Tech / software</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="D77" s="15" t="inlineStr">
@@ -14049,17 +14045,17 @@
       </c>
       <c r="E77" s="15" t="inlineStr">
         <is>
-          <t>Ipc Information Systems</t>
+          <t>Oliver Bernard Limited</t>
         </is>
       </c>
       <c r="F77" s="15" t="inlineStr">
         <is>
-          <t>Ipc Information Systems</t>
+          <t>Oliver Bernard</t>
         </is>
       </c>
       <c r="G77" s="16" t="inlineStr">
         <is>
-          <t>https://www.ipc.com</t>
+          <t>https://www.oliverbernard.com</t>
         </is>
       </c>
       <c r="H77" s="15" t="inlineStr">
@@ -14069,7 +14065,7 @@
       </c>
       <c r="I77" s="15" t="inlineStr">
         <is>
-          <t>01823833</t>
+          <t>07128139</t>
         </is>
       </c>
       <c r="J77" s="16" t="inlineStr">
@@ -14084,17 +14080,17 @@
       </c>
       <c r="L77" s="15" t="inlineStr">
         <is>
-          <t>12/06/1984</t>
+          <t>18/01/2010</t>
         </is>
       </c>
       <c r="M77" s="15" t="inlineStr">
         <is>
-          <t>Devonshire Square, 1St Floor, 7 Devonshire Square, London</t>
+          <t>1 Finsbury Avenue, Wilson Street, London</t>
         </is>
       </c>
       <c r="N77" s="15" t="inlineStr">
         <is>
-          <t>EC2M 4YH</t>
+          <t>EC2M 2PF</t>
         </is>
       </c>
       <c r="O77" s="15" t="inlineStr">
@@ -14107,7 +14103,7 @@
       <c r="R77" s="15" t="n"/>
       <c r="S77" s="15" t="inlineStr">
         <is>
-          <t>hr@ipc.com</t>
+          <t>info@oliverbernard.com</t>
         </is>
       </c>
       <c r="T77" s="15" t="inlineStr">
@@ -14117,22 +14113,22 @@
       </c>
       <c r="U77" s="16" t="inlineStr">
         <is>
-          <t>https://www.ipc.com/contact-us/</t>
+          <t>https://www.oliverbernard.com/contact</t>
         </is>
       </c>
       <c r="X77" s="15" t="inlineStr">
         <is>
-          <t>DEVONSHIRE SQUARE</t>
+          <t>0207 952 5720 Our London office in Finsbury Avenue</t>
         </is>
       </c>
       <c r="Y77" s="15" t="inlineStr">
         <is>
-          <t>EC2M 4YH</t>
+          <t>EC2M 2PF</t>
         </is>
       </c>
       <c r="Z77" s="15" t="inlineStr">
         <is>
-          <t>Website (DEVONSHIRE SQUARE)</t>
+          <t>Website (0207 952 5720 Our London office in Finsbury Avenue)</t>
         </is>
       </c>
       <c r="AA77" s="15" t="inlineStr">
@@ -14141,7 +14137,7 @@
         </is>
       </c>
       <c r="AB77" s="15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC77" s="15" t="inlineStr">
         <is>
@@ -14211,27 +14207,27 @@
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Tech / software</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>EC2M</t>
+          <t>EC1M</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>Oliver Bernard Limited</t>
+          <t>Container Solutions Software Group Ltd</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
         <is>
-          <t>Oliver Bernard</t>
+          <t>Container Solutions Software</t>
         </is>
       </c>
       <c r="G78" s="16" t="inlineStr">
         <is>
-          <t>https://www.oliverbernard.com</t>
+          <t>https://www.container-solutions.com</t>
         </is>
       </c>
       <c r="H78" s="15" t="inlineStr">
@@ -14241,7 +14237,7 @@
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>07128139</t>
+          <t>14061734</t>
         </is>
       </c>
       <c r="J78" s="16" t="inlineStr">
@@ -14256,17 +14252,17 @@
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>18/01/2010</t>
+          <t>22/04/2022</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>1 Finsbury Avenue, Wilson Street, London</t>
+          <t>29 Clerkenwell Road, London</t>
         </is>
       </c>
       <c r="N78" s="15" t="inlineStr">
         <is>
-          <t>EC2M 2PF</t>
+          <t>EC1M 5RN</t>
         </is>
       </c>
       <c r="O78" s="15" t="inlineStr">
@@ -14279,7 +14275,7 @@
       <c r="R78" s="15" t="n"/>
       <c r="S78" s="15" t="inlineStr">
         <is>
-          <t>info@oliverbernard.com</t>
+          <t>info@container-solutions.com</t>
         </is>
       </c>
       <c r="T78" s="15" t="inlineStr">
@@ -14289,27 +14285,27 @@
       </c>
       <c r="U78" s="16" t="inlineStr">
         <is>
-          <t>https://www.oliverbernard.com/contact</t>
+          <t>https://www.container-solutions.com/</t>
         </is>
       </c>
       <c r="X78" s="15" t="inlineStr">
         <is>
-          <t>0207 952 5720 Our London office in Finsbury Avenue</t>
+          <t>29 CLERKENWELL ROAD</t>
         </is>
       </c>
       <c r="Y78" s="15" t="inlineStr">
         <is>
-          <t>EC2M 2PF</t>
+          <t>EC1M 5RN</t>
         </is>
       </c>
       <c r="Z78" s="15" t="inlineStr">
         <is>
-          <t>Website (0207 952 5720 Our London office in Finsbury Avenue)</t>
+          <t>Website (29 CLERKENWELL ROAD)</t>
         </is>
       </c>
       <c r="AA78" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AB78" s="15" t="n">
@@ -14317,12 +14313,12 @@
       </c>
       <c r="AC78" s="15" t="inlineStr">
         <is>
-          <t>Shoreditch Powerleague</t>
+          <t>Old St - Moreland Primary School</t>
         </is>
       </c>
       <c r="AD78" s="15" t="inlineStr">
         <is>
-          <t>Monday 28 September at 17:40</t>
+          <t>Monday 12 October at 18:00</t>
         </is>
       </c>
       <c r="AE78" s="15" t="inlineStr">
@@ -14332,7 +14328,7 @@
       </c>
       <c r="AF78" s="15" t="inlineStr">
         <is>
-          <t>5-a-side</t>
+          <t>6-a-side</t>
         </is>
       </c>
       <c r="AG78" s="17">
@@ -15476,10 +15472,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U17" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U18" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI18" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI17" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U18" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U19" r:id="rId56"/>
@@ -15510,10 +15506,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U28" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U29" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI29" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI28" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U29" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U30" r:id="rId90"/>
@@ -15523,14 +15519,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U32" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U33" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI33" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U34" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI34" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI32" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U33" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI33" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U34" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId105"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U35" r:id="rId107"/>
@@ -15558,24 +15554,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U43" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U44" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI44" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI43" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U44" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId137"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U45" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U46" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U47" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI47" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U48" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI48" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI46" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U47" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI47" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U48" r:id="rId149"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId151"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U49" r:id="rId152"/>
@@ -15588,105 +15584,106 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId159"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U52" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U53" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U54" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U55" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U56" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI56" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U57" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U58" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U59" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U60" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U61" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U62" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U63" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U64" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U65" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U66" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI66" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U67" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U68" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J69" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U69" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U70" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U71" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J72" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U72" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J73" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U73" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U74" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J75" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U75" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U76" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U77" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U78" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U79" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI79" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U80" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U81" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U82" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J83" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U83" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J84" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U84" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI52" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U53" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U54" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U55" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI55" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U56" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U57" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U58" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U59" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U60" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U61" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U62" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U63" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U64" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U65" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI65" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U66" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U67" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U68" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J69" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U69" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U70" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U71" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J72" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U72" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J73" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U73" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U74" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J75" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U75" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U76" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U77" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U78" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U79" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI79" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U80" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U81" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U82" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J83" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U83" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J84" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U84" r:id="rId261"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/corporates/FC_Urban_London_after_work_leads.xlsx
+++ b/corporates/FC_Urban_London_after_work_leads.xlsx
@@ -1186,7 +1186,8 @@
           <t>Hi Leadscale team,
 Following up on Monday 12 October at 18:00 (or 19:00) at Moreland School, a 9-minute walk from Owen Street. Still {PRICE} a player, we handle the pitch, sign-ups and payments. Shall I hold a slot for the team?
 Best,
-Brian</t>
+Brian
+FC Urban</t>
         </is>
       </c>
       <c r="AQ3" s="20">
@@ -1405,7 +1406,8 @@
           <t>Hi Martin,
 Following up on Monday 12 October at 18:00 (or 19:00) at Moreland School, a 10-minute walk from Old Street. Still {PRICE} a player, we sort the pitch, sign-ups and payments. Want me to hold a slot for the Exigere team?
 Best,
-Brian</t>
+Brian
+FC Urban</t>
         </is>
       </c>
       <c r="AQ4" s="20">
@@ -7092,7 +7094,8 @@
         <is>
           <t>Following up on the Monday 12 October slot at Moreland School (6-a-side, 18:00 or 19:00) — still open, an 11-minute walk from Banner Street. It's {PRICE} a player, and we handle the pitch booking and payments end to end. Let me know if you'd like it as your weekly game.
 Best,
-Brian</t>
+Brian
+FC Urban</t>
         </is>
       </c>
       <c r="AQ30" s="20">
@@ -7307,7 +7310,8 @@
         <is>
           <t>Following up on Monday 12 October — the 6-a-side slot at Moreland School (18:00 or 19:00) is still free, 12 minutes from East Road. It's {PRICE} a player, and we handle the pitch booking and payments. Would this work as your weekly game?
 Best,
-Brian</t>
+Brian
+FC Urban</t>
         </is>
       </c>
       <c r="AQ31" s="20">
@@ -7522,7 +7526,8 @@
         <is>
           <t>Checking in on Monday 28 September — the 5-a-side slot at Powerleague Shoreditch (17:40 or 19:40) is still open, or Thursday 1 October at 18:20. It's {PRICE} a player, and we handle booking and payments. Keen to get the team a regular weekly game.
 Best,
-Brian</t>
+Brian
+FC Urban</t>
         </is>
       </c>
       <c r="AQ32" s="20">
@@ -7735,7 +7740,8 @@
           <t>Hi Wellcom London team,
 Following up on Monday 12 October at 18:00 (or 19:00) at Moreland School — a 5-minute walk from Berry Place. Still {PRICE} a player, we handle the pitch, sign-ups and payments. Would you like me to hold a slot for the team's first game?
 Best,
-Brian</t>
+Brian
+FC Urban</t>
         </is>
       </c>
       <c r="AQ33" s="20">
@@ -7944,7 +7950,8 @@
           <t>Hi Mention Me team,
 Following up on Monday 12 October at 18:00 (or 19:00) at Moreland School, 6 minutes from your office. Still {PRICE} a player, we handle the pitch, sign-ups and payments. Shall I hold a slot for the Mentioneers?
 Best,
-Brian</t>
+Brian
+FC Urban</t>
         </is>
       </c>
       <c r="AQ34" s="20">
@@ -8169,7 +8176,8 @@
           <t>Hi Simon,
 Following up on Monday 28 September at 17:40 (or 19:40) at Powerleague Shoreditch — 7 minutes from Primrose Street. Still {PRICE} a player, we sort the pitch, sign-ups and payments. Want me to hold a slot for the Oakleaf team?
 Best,
-Brian</t>
+Brian
+FC Urban</t>
         </is>
       </c>
       <c r="AQ35" s="20">
@@ -8390,7 +8398,8 @@
           <t>Hi Tyler,
 Following up on Monday 28 September at 17:40 (or 19:40) at Powerleague Shoreditch, 10 minutes from Paul Street. Still {PRICE} a player, we handle the pitch, sign-ups and payments. Shall I hold a slot for the team?
 Best,
-Brian</t>
+Brian
+FC Urban</t>
         </is>
       </c>
       <c r="AQ36" s="20">
@@ -11634,7 +11643,8 @@
         <is>
           <t>Just checking — the Monday 28 September 5-a-side slot at Powerleague Shoreditch is still open, or Thursday 1 October at 18:20 if that's easier. It's {PRICE} a player, and we handle the booking and payments. Keen to get McBains a regular weekly game.
 Best,
-Brian</t>
+Brian
+FC Urban</t>
         </is>
       </c>
       <c r="AQ51" s="20">
@@ -13518,7 +13528,8 @@
         <is>
           <t>Following up on Monday 12 October — the 6-a-side slot at Moreland School (18:00 or 19:00) is still free, 12 minutes from your N1 office. It's {PRICE} a player, and we handle the pitch booking and payments end to end. Would this suit as a weekly game?
 Best,
-Brian</t>
+Brian
+FC Urban</t>
         </is>
       </c>
       <c r="AQ60" s="20">
@@ -15452,7 +15463,8 @@
           <t>Hi Ivan,
 Following up on Monday 12 October at 18:00 (or 19:00) at Moreland School, 6 minutes from Wenlock Road. Still {PRICE} a player, we handle the pitch, sign-ups and payments. Shall I hold a slot for the MoonPay team?
 Best,
-Brian</t>
+Brian
+FC Urban</t>
         </is>
       </c>
       <c r="AQ69" s="20">
@@ -16093,7 +16105,8 @@
           <t>Hi Side team,
 Following up on Monday 28 September at 18:00 at Market Road Pitches, 6 minutes from Blundell Street. Still {PRICE} a player, we handle the pitch, sign-ups and payments. Shall I hold the slot for you?
 Best,
-Brian</t>
+Brian
+FC Urban</t>
         </is>
       </c>
       <c r="AQ72" s="20">
@@ -16958,7 +16971,8 @@
         <is>
           <t>Following up on Monday 12 October — the 6-a-side slot at Moreland School (18:00 or 19:00) is still free, an 11-minute walk from your office. It's {PRICE} a player, and we handle the pitch booking and payments end to end. Keen to get Northdoor a regular weekly game.
 Best,
-Brian</t>
+Brian
+FC Urban</t>
         </is>
       </c>
       <c r="AQ76" s="20">
@@ -17168,7 +17182,8 @@
         <is>
           <t>Following up on Monday 12 October — the 6-a-side slot at Moreland School (18:00 or 19:00) is still free, 12 minutes from Amwell Street. It's {PRICE} a player, and we handle the pitch booking and payments end to end. Would this work as your weekly game?
 Best,
-Brian</t>
+Brian
+FC Urban</t>
         </is>
       </c>
       <c r="AQ77" s="20">
@@ -17374,7 +17389,8 @@
         <is>
           <t>Following up on Monday 12 October — the 6-a-side slot at Moreland School (18:00 or 19:00) is still free, 12 minutes from your N1 office. It's {PRICE} a player, and we handle the pitch booking and payments end to end. Would this suit as a weekly game?
 Best,
-Brian</t>
+Brian
+FC Urban</t>
         </is>
       </c>
       <c r="AQ78" s="20">

--- a/corporates/FC_Urban_London_after_work_leads.xlsx
+++ b/corporates/FC_Urban_London_after_work_leads.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Read me" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Outreach'!$A$2:$BE$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Outreach'!$A$2:$BC$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -138,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -164,16 +164,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -276,7 +273,7 @@
         <t>Website = address from the firm's own site. "Registered office (no address on website)" = the site shows no address, so the Companies House address was used.</t>
       </text>
     </comment>
-    <comment ref="AT2" authorId="0" shapeId="0">
+    <comment ref="AR2" authorId="0" shapeId="0">
       <text>
         <t>The domain has a mail (MX) record. Mailbox-level SMTP checks could not run from the research environment (port 25 blocked) — run a verifier before sending.</t>
       </text>
@@ -574,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE79"/>
+  <dimension ref="A1:BC79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -619,21 +616,19 @@
     <col width="40" customWidth="1" min="40" max="40"/>
     <col width="60" customWidth="1" min="41" max="41"/>
     <col width="45" customWidth="1" min="42" max="42"/>
-    <col width="60" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
-    <col width="10" customWidth="1" min="45" max="45"/>
-    <col width="9" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
-    <col width="30" customWidth="1" min="48" max="48"/>
-    <col width="8" customWidth="1" min="49" max="49"/>
-    <col width="11" customWidth="1" min="50" max="50"/>
-    <col width="11" customWidth="1" min="51" max="51"/>
+    <col width="10" customWidth="1" min="43" max="43"/>
+    <col width="9" customWidth="1" min="44" max="44"/>
+    <col width="24" customWidth="1" min="45" max="45"/>
+    <col width="30" customWidth="1" min="46" max="46"/>
+    <col width="8" customWidth="1" min="47" max="47"/>
+    <col width="11" customWidth="1" min="48" max="48"/>
+    <col width="11" customWidth="1" min="49" max="49"/>
+    <col width="8" customWidth="1" min="50" max="50"/>
+    <col width="14" customWidth="1" min="51" max="51"/>
     <col width="8" customWidth="1" min="52" max="52"/>
-    <col width="14" customWidth="1" min="53" max="53"/>
+    <col width="8" customWidth="1" min="53" max="53"/>
     <col width="8" customWidth="1" min="54" max="54"/>
-    <col width="8" customWidth="1" min="55" max="55"/>
-    <col width="8" customWidth="1" min="56" max="56"/>
-    <col width="28" customWidth="1" min="57" max="57"/>
+    <col width="28" customWidth="1" min="55" max="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -695,29 +690,27 @@
       <c r="AN1" s="8" t="n"/>
       <c r="AO1" s="8" t="n"/>
       <c r="AP1" s="8" t="n"/>
-      <c r="AQ1" s="8" t="n"/>
-      <c r="AR1" s="8" t="n"/>
-      <c r="AS1" s="9" t="inlineStr">
+      <c r="AQ1" s="9" t="inlineStr">
         <is>
           <t>Checks</t>
         </is>
       </c>
+      <c r="AR1" s="10" t="n"/>
+      <c r="AS1" s="10" t="n"/>
       <c r="AT1" s="10" t="n"/>
-      <c r="AU1" s="10" t="n"/>
-      <c r="AV1" s="10" t="n"/>
-      <c r="AW1" s="11" t="inlineStr">
+      <c r="AU1" s="11" t="inlineStr">
         <is>
           <t>Tracking — fill in</t>
         </is>
       </c>
+      <c r="AV1" s="12" t="n"/>
+      <c r="AW1" s="12" t="n"/>
       <c r="AX1" s="12" t="n"/>
       <c r="AY1" s="12" t="n"/>
       <c r="AZ1" s="12" t="n"/>
       <c r="BA1" s="12" t="n"/>
       <c r="BB1" s="12" t="n"/>
       <c r="BC1" s="12" t="n"/>
-      <c r="BD1" s="12" t="n"/>
-      <c r="BE1" s="12" t="n"/>
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
@@ -922,85 +915,75 @@
       </c>
       <c r="AO2" s="13" t="inlineStr">
         <is>
-          <t>Personalised email (price pending)</t>
+          <t>Email draft</t>
         </is>
       </c>
       <c r="AP2" s="13" t="inlineStr">
         <is>
-          <t>Personalised follow-up (price pending)</t>
+          <t>Follow-up email (day 5)</t>
         </is>
       </c>
       <c r="AQ2" s="13" t="inlineStr">
         <is>
-          <t>Email draft</t>
+          <t>Suppression check</t>
         </is>
       </c>
       <c r="AR2" s="13" t="inlineStr">
         <is>
-          <t>Follow-up email (day 4)</t>
+          <t>MX check</t>
         </is>
       </c>
       <c r="AS2" s="13" t="inlineStr">
         <is>
-          <t>Suppression check</t>
+          <t>Hold (check first)</t>
         </is>
       </c>
       <c r="AT2" s="13" t="inlineStr">
         <is>
-          <t>MX check</t>
-        </is>
-      </c>
-      <c r="AU2" s="13" t="inlineStr">
-        <is>
-          <t>Hold (check first)</t>
-        </is>
-      </c>
-      <c r="AV2" s="13" t="inlineStr">
-        <is>
           <t>Draftable</t>
         </is>
       </c>
+      <c r="AU2" s="14" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="AV2" s="14" t="inlineStr">
+        <is>
+          <t>Contacted on</t>
+        </is>
+      </c>
       <c r="AW2" s="14" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Follow-up sent on</t>
         </is>
       </c>
       <c r="AX2" s="14" t="inlineStr">
         <is>
-          <t>Contacted on</t>
+          <t>Replied</t>
         </is>
       </c>
       <c r="AY2" s="14" t="inlineStr">
         <is>
-          <t>Follow-up sent on</t>
+          <t>Reply category</t>
         </is>
       </c>
       <c r="AZ2" s="14" t="inlineStr">
         <is>
-          <t>Replied</t>
+          <t>Call booked</t>
         </is>
       </c>
       <c r="BA2" s="14" t="inlineStr">
         <is>
-          <t>Reply category</t>
+          <t>Group created</t>
         </is>
       </c>
       <c r="BB2" s="14" t="inlineStr">
         <is>
-          <t>Call booked</t>
+          <t>First game booked</t>
         </is>
       </c>
       <c r="BC2" s="14" t="inlineStr">
-        <is>
-          <t>Group created</t>
-        </is>
-      </c>
-      <c r="BD2" s="14" t="inlineStr">
-        <is>
-          <t>First game booked</t>
-        </is>
-      </c>
-      <c r="BE2" s="14" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1139,9 +1122,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG3" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG3" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH3" s="15" t="inlineStr">
         <is>
@@ -1168,14 +1152,19 @@
         <f>IF(V3&lt;&gt;"",V3,S3)</f>
         <v/>
       </c>
-      <c r="AN3" s="18">
-        <f>IF(AG3="","","9 min from Owen Street: a weekly team game")</f>
-        <v/>
+      <c r="AN3" s="15" t="inlineStr">
+        <is>
+          <t>Weekly football for the Leadscale team</t>
+        </is>
       </c>
       <c r="AO3" s="19" t="inlineStr">
         <is>
           <t>Hi Leadscale team,
-You describe Team Leadscale as growing and close-knit, valuing circles of knowledge over hierarchy — that's exactly the kind of team that plays well together. We've got a 6-a-side pitch at Moreland School, Gard Street, a 9-minute walk from Owen Street, with Monday 12 October at 18:00 open (or 19:00), and it's an easy way to make that a regular weekly thing. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Would your team be up for it?
+You describe Team Leadscale as growing and close-knit, valuing circles of knowledge over hierarchy, which sounds like a team that would enjoy playing together.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 9-minute walk from your office on Owen Street.
+We're looking for someone at Leadscale who'd enjoy helping start a regular office kickabout for colleagues; we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
 Best,
 Brian
 FC Urban</t>
@@ -1184,37 +1173,30 @@
       <c r="AP3" s="19" t="inlineStr">
         <is>
           <t>Hi Leadscale team,
-Following up on Monday 12 October at 18:00 (or 19:00) at Moreland School, a 9-minute walk from Owen Street. Still {PRICE} a player, we handle the pitch, sign-ups and payments. Shall I hold a slot for the team?
+Just following up on my note below about setting up a regular football game for colleagues near your office. Would there be any interest, or is there someone else at Leadscale I should be speaking to about staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ3" s="20">
-        <f>IF(OR(AG3="",AO3=""),"",SUBSTITUTE(AO3,"{PRICE}","£"&amp;IF(AG3=INT(AG3),TEXT(AG3,"0"),TEXT(AG3,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR3" s="20">
-        <f>IF(OR(AG3="",AP3=""),"",SUBSTITUTE(AP3,"{PRICE}","£"&amp;IF(AG3=INT(AG3),TEXT(AG3,"0"),TEXT(AG3,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS3" s="15" t="inlineStr">
+      <c r="AQ3" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR3" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS3" s="15" t="n"/>
       <c r="AT3" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU3" s="15" t="n"/>
-      <c r="AV3" s="18">
-        <f>IF(AU3&lt;&gt;"","No – hold: "&amp;AU3,IF(AG3="","No – no confirmed London price per player",IF(AM3="","No – no email",IF(AO3="","No – no personalised email",IF(AS3&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX3" s="21" t="n"/>
-      <c r="AY3" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV3" s="20" t="n"/>
+      <c r="AW3" s="20" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="15" t="n">
@@ -1359,9 +1341,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG4" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG4" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH4" s="15" t="inlineStr">
         <is>
@@ -1388,14 +1371,19 @@
         <f>IF(V4&lt;&gt;"",V4,S4)</f>
         <v/>
       </c>
-      <c r="AN4" s="18">
-        <f>IF(AG4="","","10 min from Old Street: a weekly team game")</f>
-        <v/>
+      <c r="AN4" s="15" t="inlineStr">
+        <is>
+          <t>Football for the Exigere team?</t>
+        </is>
       </c>
       <c r="AO4" s="19" t="inlineStr">
         <is>
           <t>Hi Martin,
-Exigere already gets the whole team together for your annual company conference, so a regular weekly game wouldn't be a stretch. We've got the floodlit 6-a-side pitch at Moreland School, Gard Street, a 10-minute walk from your Old Street office, with Monday 12 October at 18:00 open (or 19:00), and it can become a fixed weekly slot. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Shall I hold Monday for you?
+Exigere's team benefits include an annual company conference and a paid volunteering day, so the team clearly matters to you.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 10-minute walk from your office on Old Street.
+We're looking for someone at Exigere to start a regular after-work kickabout for colleagues; we handle the pitch, extra players if you're short, payments and organisation.
+Would that be of interest to the team? If it's not for you, would you mind pointing me to whoever looks after staff socials or wellbeing?
+FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
 Best,
 Brian
 FC Urban</t>
@@ -1404,37 +1392,30 @@
       <c r="AP4" s="19" t="inlineStr">
         <is>
           <t>Hi Martin,
-Following up on Monday 12 October at 18:00 (or 19:00) at Moreland School, a 10-minute walk from Old Street. Still {PRICE} a player, we sort the pitch, sign-ups and payments. Want me to hold a slot for the Exigere team?
+Just checking back on my note about setting up a regular football game for the Exigere team. Would that be of interest, or is there someone else there I should speak to about staff socials?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ4" s="20">
-        <f>IF(OR(AG4="",AO4=""),"",SUBSTITUTE(AO4,"{PRICE}","£"&amp;IF(AG4=INT(AG4),TEXT(AG4,"0"),TEXT(AG4,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR4" s="20">
-        <f>IF(OR(AG4="",AP4=""),"",SUBSTITUTE(AP4,"{PRICE}","£"&amp;IF(AG4=INT(AG4),TEXT(AG4,"0"),TEXT(AG4,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS4" s="15" t="inlineStr">
+      <c r="AQ4" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR4" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS4" s="15" t="n"/>
       <c r="AT4" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU4" s="15" t="n"/>
-      <c r="AV4" s="18">
-        <f>IF(AU4&lt;&gt;"","No – hold: "&amp;AU4,IF(AG4="","No – no confirmed London price per player",IF(AM4="","No – no email",IF(AO4="","No – no personalised email",IF(AS4&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX4" s="21" t="n"/>
-      <c r="AY4" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV4" s="20" t="n"/>
+      <c r="AW4" s="20" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
@@ -1577,9 +1558,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG5" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG5" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH5" s="15" t="inlineStr">
         <is>
@@ -1606,17 +1588,19 @@
         <f>IF(V5&lt;&gt;"",V5,S5)</f>
         <v/>
       </c>
-      <c r="AN5" s="18">
-        <f>IF(AG5="","","5-a-side near Bonhill Street for Veretec?")</f>
-        <v/>
+      <c r="AN5" s="15" t="inlineStr">
+        <is>
+          <t>A weekly kickabout for Veretec?</t>
+        </is>
       </c>
       <c r="AO5" s="19" t="inlineStr">
         <is>
           <t>Hi Sandra,
-Veretec's careers page describes your studio as vibrant, enthusiastic and collaborative, with a genuinely friendly, social culture. That sounds like a team that would enjoy a regular kickabout.
-We've a 5-a-side pitch at Powerleague Shoreditch, Braithwaite Street, E1 6GJ, a 10-minute walk from 10 Bonhill Street, with slots free Monday 28 September at 17:40 or 19:40. It could easily become your weekly team game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Shall I hold Monday 28 September for you?
+Veretec's careers page describes your studio as vibrant, enthusiastic and collaborative, with a genuinely friendly, social culture, which sounds like a team that would enjoy playing together.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 10-minute walk from your office on Bonhill Street.
+We're looking for someone at Veretec who'd enjoy helping start a regular kickabout for the studio; we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
 Best,
 Brian
 FC Urban</t>
@@ -1625,37 +1609,30 @@
       <c r="AP5" s="19" t="inlineStr">
         <is>
           <t>Hi Sandra,
-Quick follow-up on the 5-a-side at Powerleague Shoreditch. The Monday 28 September slots are still free, or there's Thursday 1 October at 18:20 if that suits better. It's {PRICE} a player, one link for the team, and we handle the rest.
+Just following up on my note about a regular kickabout for the Veretec studio. Would there be any interest, or is there someone else there I should speak to about staff socials?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ5" s="20">
-        <f>IF(OR(AG5="",AO5=""),"",SUBSTITUTE(AO5,"{PRICE}","£"&amp;IF(AG5=INT(AG5),TEXT(AG5,"0"),TEXT(AG5,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR5" s="20">
-        <f>IF(OR(AG5="",AP5=""),"",SUBSTITUTE(AP5,"{PRICE}","£"&amp;IF(AG5=INT(AG5),TEXT(AG5,"0"),TEXT(AG5,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS5" s="15" t="inlineStr">
+      <c r="AQ5" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR5" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS5" s="15" t="n"/>
       <c r="AT5" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU5" s="15" t="n"/>
-      <c r="AV5" s="18">
-        <f>IF(AU5&lt;&gt;"","No – hold: "&amp;AU5,IF(AG5="","No – no confirmed London price per player",IF(AM5="","No – no email",IF(AO5="","No – no personalised email",IF(AS5&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX5" s="21" t="n"/>
-      <c r="AY5" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV5" s="20" t="n"/>
+      <c r="AW5" s="20" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
@@ -1802,9 +1779,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG6" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG6" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH6" s="15" t="inlineStr">
         <is>
@@ -1831,17 +1809,19 @@
         <f>IF(V6&lt;&gt;"",V6,S6)</f>
         <v/>
       </c>
-      <c r="AN6" s="18">
-        <f>IF(AG6="","","6-a-side near Sutton Lane for Codurance?")</f>
-        <v/>
+      <c r="AN6" s="15" t="inlineStr">
+        <is>
+          <t>A Codurance football group?</t>
+        </is>
       </c>
       <c r="AO6" s="19" t="inlineStr">
         <is>
           <t>Hi Robert,
-Codurance's own story page calls your engineers software craftspeople, with roots in the London Software Craftsmanship Community you helped start back in 2010. That close-knit culture usually makes a good five-a-side team too.
-We've a 6-a-side pitch at the floodlit 3G at Moreland School, Gard Street, EC1V 8DW, an 11-minute walk from 3 Sutton Lane, with slots free Monday 12 October at 18:00, 19:00 or 20:00. It could become your regular weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Shall I hold Monday 12 October for you?
+Codurance's own story page calls your engineers software craftspeople, rooted in the London Software Craftsmanship Community you helped start in 2010.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), an 11-minute walk from your office on Sutton Lane.
+We're looking for someone at Codurance to start a regular office kickabout for colleagues; we handle the pitch, extra players if you're short, payments and organisation.
+Would that be of interest to the team? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
 Best,
 Brian
 FC Urban</t>
@@ -1850,37 +1830,30 @@
       <c r="AP6" s="19" t="inlineStr">
         <is>
           <t>Hi Robert,
-Following up on the 6-a-side at Moreland School. Monday 12 October still has slots at 18:00, 19:00 and 20:00. It's {PRICE} a player, one link for the team, and we handle the pitch and payments.
+Just checking back on my note about a regular football group for Codurance. Would that be of interest, or is there someone else there better placed to look at staff socials?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ6" s="20">
-        <f>IF(OR(AG6="",AO6=""),"",SUBSTITUTE(AO6,"{PRICE}","£"&amp;IF(AG6=INT(AG6),TEXT(AG6,"0"),TEXT(AG6,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR6" s="20">
-        <f>IF(OR(AG6="",AP6=""),"",SUBSTITUTE(AP6,"{PRICE}","£"&amp;IF(AG6=INT(AG6),TEXT(AG6,"0"),TEXT(AG6,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS6" s="15" t="inlineStr">
+      <c r="AQ6" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR6" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS6" s="15" t="n"/>
       <c r="AT6" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU6" s="15" t="n"/>
-      <c r="AV6" s="18">
-        <f>IF(AU6&lt;&gt;"","No – hold: "&amp;AU6,IF(AG6="","No – no confirmed London price per player",IF(AM6="","No – no email",IF(AO6="","No – no personalised email",IF(AS6&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX6" s="21" t="n"/>
-      <c r="AY6" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV6" s="20" t="n"/>
+      <c r="AW6" s="20" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">
@@ -2023,9 +1996,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG7" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG7" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH7" s="15" t="inlineStr">
         <is>
@@ -2052,17 +2026,19 @@
         <f>IF(V7&lt;&gt;"",V7,S7)</f>
         <v/>
       </c>
-      <c r="AN7" s="18">
-        <f>IF(AG7="","","5-a-side near Devonshire Square, Precise Consultants?")</f>
-        <v/>
+      <c r="AN7" s="15" t="inlineStr">
+        <is>
+          <t>A team game for Precise Consultants?</t>
+        </is>
       </c>
       <c r="AO7" s="19" t="inlineStr">
         <is>
           <t>Hi Sophie,
-Precise Consultants have just gone a step further than carbon neutral to carbon negative, offsetting 82.66 tonnes of CO2e through verified projects. A team that takes that seriously might enjoy getting outdoors together too.
-We've a 5-a-side pitch at Powerleague Shoreditch, Braithwaite Street, E1 6GJ, a 12-minute walk from 14 Devonshire Square, with slots free Monday 28 September at 17:40 or 19:40. It could become your weekly team game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Would your team be up for it?
+Precise Consultants have gone a step further than carbon neutral to carbon negative, offsetting 82.66 tonnes of CO2e through verified projects.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 12-minute walk from your office on Devonshire Square.
+We're looking for someone at Precise Consultants to start a regular team game, perhaps a friendly against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
 Best,
 Brian
 FC Urban</t>
@@ -2071,37 +2047,30 @@
       <c r="AP7" s="19" t="inlineStr">
         <is>
           <t>Hi Sophie,
-Following up on the 5-a-side at Powerleague Shoreditch. Monday 28 September at 17:40 or 19:40 is still free, or Thursday 1 October at 18:20. It's {PRICE} a player, one link for the team, and we handle the rest.
+Just following up on my note about a regular football game for the Precise Consultants team. Would there be any interest, or is there someone else there I should speak to about staff socials?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ7" s="20">
-        <f>IF(OR(AG7="",AO7=""),"",SUBSTITUTE(AO7,"{PRICE}","£"&amp;IF(AG7=INT(AG7),TEXT(AG7,"0"),TEXT(AG7,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR7" s="20">
-        <f>IF(OR(AG7="",AP7=""),"",SUBSTITUTE(AP7,"{PRICE}","£"&amp;IF(AG7=INT(AG7),TEXT(AG7,"0"),TEXT(AG7,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS7" s="15" t="inlineStr">
+      <c r="AQ7" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR7" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS7" s="15" t="n"/>
       <c r="AT7" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU7" s="15" t="n"/>
-      <c r="AV7" s="18">
-        <f>IF(AU7&lt;&gt;"","No – hold: "&amp;AU7,IF(AG7="","No – no confirmed London price per player",IF(AM7="","No – no email",IF(AO7="","No – no personalised email",IF(AS7&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX7" s="21" t="n"/>
-      <c r="AY7" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV7" s="20" t="n"/>
+      <c r="AW7" s="20" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="n">
@@ -2248,9 +2217,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG8" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG8" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH8" s="15" t="inlineStr">
         <is>
@@ -2277,17 +2247,19 @@
         <f>IF(V8&lt;&gt;"",V8,S8)</f>
         <v/>
       </c>
-      <c r="AN8" s="18">
-        <f>IF(AG8="","","5-a-side near Old Broad Street for Guy Butler?")</f>
-        <v/>
+      <c r="AN8" s="15" t="inlineStr">
+        <is>
+          <t>After-work football for Guy Butler?</t>
+        </is>
       </c>
       <c r="AO8" s="19" t="inlineStr">
         <is>
           <t>Hi Jamie,
-Guy Butler's website says you can trace your roots back over 50 years as an independent bond house in the City, with a team that has worked together for many years. That's exactly the kind of long-standing team that enjoys a regular five-a-side.
-We've a 5-a-side pitch at Powerleague Shoreditch, Braithwaite Street, E1 6GJ, a 14-minute walk from 69 Old Broad Street, with slots free Monday 28 September at 17:40 or 19:40. It could become your weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Shall I hold Monday 28 September for you?
+Guy Butler's website traces your roots back over 50 years as an independent bond house in the City, a team built to last.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), a 14-minute walk from your office on Old Broad Street.
+We're looking for someone at Guy Butler to start a regular after-work social, or perhaps a game against another firm; we handle the pitch, extra players if you're short, payments and organisation.
+Would that interest the team? If it's not for you, could you forward this to whoever looks after staff socials or wellbeing?
+FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
 Best,
 Brian
 FC Urban</t>
@@ -2296,37 +2268,30 @@
       <c r="AP8" s="19" t="inlineStr">
         <is>
           <t>Hi Jamie,
-Following up on the 5-a-side at Powerleague Shoreditch. Monday 28 September at 17:40 or 19:40 is still open, or Thursday 1 October at 18:20. It's {PRICE} a player, one link for the team, and we handle the rest.
+Just checking back on my note about a regular after-work football game for Guy Butler. Would that be of interest, or is there someone else there better placed to look at this?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ8" s="20">
-        <f>IF(OR(AG8="",AO8=""),"",SUBSTITUTE(AO8,"{PRICE}","£"&amp;IF(AG8=INT(AG8),TEXT(AG8,"0"),TEXT(AG8,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR8" s="20">
-        <f>IF(OR(AG8="",AP8=""),"",SUBSTITUTE(AP8,"{PRICE}","£"&amp;IF(AG8=INT(AG8),TEXT(AG8,"0"),TEXT(AG8,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS8" s="15" t="inlineStr">
+      <c r="AQ8" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR8" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS8" s="15" t="n"/>
       <c r="AT8" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU8" s="15" t="n"/>
-      <c r="AV8" s="18">
-        <f>IF(AU8&lt;&gt;"","No – hold: "&amp;AU8,IF(AG8="","No – no confirmed London price per player",IF(AM8="","No – no email",IF(AO8="","No – no personalised email",IF(AS8&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX8" s="21" t="n"/>
-      <c r="AY8" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV8" s="20" t="n"/>
+      <c r="AW8" s="20" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="15" t="n">
@@ -2467,9 +2432,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG9" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG9" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH9" s="15" t="inlineStr">
         <is>
@@ -2500,17 +2466,19 @@
         <f>IF(V9&lt;&gt;"",V9,S9)</f>
         <v/>
       </c>
-      <c r="AN9" s="18">
-        <f>IF(AG9="","","6-a-side near Aldersgate Street for Goodman Masson?")</f>
-        <v/>
+      <c r="AN9" s="15" t="inlineStr">
+        <is>
+          <t>Football for the Goodman Masson team?</t>
+        </is>
       </c>
       <c r="AO9" s="19" t="inlineStr">
         <is>
           <t>Hi Iain,
-Goodman Masson was named the UK's Best Workplace for Wellbeing back in 2023, which says a lot about how you look after the team. A weekly game is an easy way to keep that going.
-We've a 6-a-side pitch at the floodlit 3G at Moreland School, Gard Street, EC1V 8DW, a 14-minute walk from 120 Aldersgate Street, with slots free Monday 12 October at 18:00 or 19:00. It could become your regular fixture.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Shall I hold Monday 12 October for you?
+Goodman Masson was named the UK's Best Workplace for Wellbeing in 2023, reflecting how you look after the team.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), a 14-minute walk from your office on Aldersgate Street.
+We're looking for someone at Goodman Masson to start a regular team game, perhaps a friendly against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
 Best,
 Brian
 FC Urban</t>
@@ -2519,37 +2487,30 @@
       <c r="AP9" s="19" t="inlineStr">
         <is>
           <t>Hi Iain,
-Following up on the 6-a-side at Moreland School. Monday 12 October still has slots at 18:00 and 19:00, or 20:00. It's {PRICE} a player, one link for the team, and we handle the pitch and payments.
+Just following up on my note about a regular football game for the Goodman Masson team. Would there be any interest, or is there someone else there I should speak to about this?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ9" s="20">
-        <f>IF(OR(AG9="",AO9=""),"",SUBSTITUTE(AO9,"{PRICE}","£"&amp;IF(AG9=INT(AG9),TEXT(AG9,"0"),TEXT(AG9,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR9" s="20">
-        <f>IF(OR(AG9="",AP9=""),"",SUBSTITUTE(AP9,"{PRICE}","£"&amp;IF(AG9=INT(AG9),TEXT(AG9,"0"),TEXT(AG9,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS9" s="15" t="inlineStr">
+      <c r="AQ9" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR9" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS9" s="15" t="n"/>
       <c r="AT9" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU9" s="15" t="n"/>
-      <c r="AV9" s="18">
-        <f>IF(AU9&lt;&gt;"","No – hold: "&amp;AU9,IF(AG9="","No – no confirmed London price per player",IF(AM9="","No – no email",IF(AO9="","No – no personalised email",IF(AS9&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX9" s="21" t="n"/>
-      <c r="AY9" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV9" s="20" t="n"/>
+      <c r="AW9" s="20" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="15" t="n">
@@ -2696,9 +2657,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG10" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG10" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH10" s="15" t="inlineStr">
         <is>
@@ -2725,17 +2687,19 @@
         <f>IF(V10&lt;&gt;"",V10,S10)</f>
         <v/>
       </c>
-      <c r="AN10" s="18">
-        <f>IF(AG10="","","Congrats on Embassy -- football on Dallington St?")</f>
-        <v/>
+      <c r="AN10" s="15" t="inlineStr">
+        <is>
+          <t>A weekly game for Turbine Studios?</t>
+        </is>
       </c>
       <c r="AO10" s="19" t="inlineStr">
         <is>
           <t>Hi Tracey,
-Congratulations on Embassy landing at Prime Video -- must be a good week at Turbine.
-We run a floodlit 6-a-side pitch at Moreland School, Gard Street, an 8-minute walk from Dallington Street. There's a slot free Monday 12 October at 18:00, or 19:00, and it could easily become your regular weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Shall I hold Monday for you?
+Congratulations on Embassy, starring Anna Kendrick and J.K. Simmons, landing at Prime Video, must be a good week at Turbine.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), an 8-minute walk from your office on Dallington Street.
+We're looking for someone at Turbine Studios who'd enjoy helping start a regular kickabout for the studio; we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
 Best,
 Brian
 FC Urban</t>
@@ -2744,37 +2708,30 @@
       <c r="AP10" s="19" t="inlineStr">
         <is>
           <t>Hi Tracey,
-Following up on the 6-a-side slot at Moreland School, 8 minutes from Dallington Street. Monday 12 October at 19:00 is still free. It's {PRICE} a player, and we handle the booking and payments, so it's one link for the team. Worth a try?
+Just following up on my note about a regular football game for the Turbine Studios team. Would there be any interest, or is there someone else there I should forward this to?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ10" s="20">
-        <f>IF(OR(AG10="",AO10=""),"",SUBSTITUTE(AO10,"{PRICE}","£"&amp;IF(AG10=INT(AG10),TEXT(AG10,"0"),TEXT(AG10,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR10" s="20">
-        <f>IF(OR(AG10="",AP10=""),"",SUBSTITUTE(AP10,"{PRICE}","£"&amp;IF(AG10=INT(AG10),TEXT(AG10,"0"),TEXT(AG10,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS10" s="15" t="inlineStr">
+      <c r="AQ10" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR10" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS10" s="15" t="n"/>
       <c r="AT10" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU10" s="15" t="n"/>
-      <c r="AV10" s="18">
-        <f>IF(AU10&lt;&gt;"","No – hold: "&amp;AU10,IF(AG10="","No – no confirmed London price per player",IF(AM10="","No – no email",IF(AO10="","No – no personalised email",IF(AS10&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX10" s="21" t="n"/>
-      <c r="AY10" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV10" s="20" t="n"/>
+      <c r="AW10" s="20" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="15" t="n">
@@ -2917,9 +2874,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG11" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG11" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH11" s="15" t="inlineStr">
         <is>
@@ -2946,17 +2904,19 @@
         <f>IF(V11&lt;&gt;"",V11,S11)</f>
         <v/>
       </c>
-      <c r="AN11" s="18">
-        <f>IF(AG11="","","Football near N7 9AA, after a big week for Ori")</f>
-        <v/>
+      <c r="AN11" s="15" t="inlineStr">
+        <is>
+          <t>Football for the Ori Biotech team?</t>
+        </is>
       </c>
       <c r="AO11" s="19" t="inlineStr">
         <is>
           <t>Hi Nick,
-Congratulations on the new 10-year, $120M manufacturing partnership -- a big one to land.
-We run a 5-a-side pitch at Market Road Pitches, Caledonian Road, a 9-minute walk from your office near N7 9AA. There's a slot free Monday 28 September at 18:00, and it could easily become your regular weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Would your team be up for it?
+Congratulations on the new 10-year, $120M manufacturing partnership, quite a deal to land.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Market Road (Caledonian Road) (https://www.fcurban.com/locations/market-road), a 9-minute walk from your office near N7 9AA.
+We're looking for someone at Ori Biotech who'd enjoy helping start a regular office kickabout for colleagues; we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
 Best,
 Brian
 FC Urban</t>
@@ -2965,37 +2925,30 @@
       <c r="AP11" s="19" t="inlineStr">
         <is>
           <t>Hi Nick,
-Still holding the 5-a-side slot at Market Road Pitches on Monday 28 September at 18:00, 9 minutes from your office. It's {PRICE} a player, and we handle the booking and payments, so it's one link for the team. Fancy giving it a go?
+Just following up on my note about a regular football game for the Ori Biotech team. Would there be any interest, or is there someone else there I should forward this to?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ11" s="20">
-        <f>IF(OR(AG11="",AO11=""),"",SUBSTITUTE(AO11,"{PRICE}","£"&amp;IF(AG11=INT(AG11),TEXT(AG11,"0"),TEXT(AG11,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR11" s="20">
-        <f>IF(OR(AG11="",AP11=""),"",SUBSTITUTE(AP11,"{PRICE}","£"&amp;IF(AG11=INT(AG11),TEXT(AG11,"0"),TEXT(AG11,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS11" s="15" t="inlineStr">
+      <c r="AQ11" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR11" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS11" s="15" t="n"/>
       <c r="AT11" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU11" s="15" t="n"/>
-      <c r="AV11" s="18">
-        <f>IF(AU11&lt;&gt;"","No – hold: "&amp;AU11,IF(AG11="","No – no confirmed London price per player",IF(AM11="","No – no email",IF(AO11="","No – no personalised email",IF(AS11&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX11" s="21" t="n"/>
-      <c r="AY11" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV11" s="20" t="n"/>
+      <c r="AW11" s="20" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="15" t="n">
@@ -3142,9 +3095,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG12" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG12" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH12" s="15" t="inlineStr">
         <is>
@@ -3171,17 +3125,19 @@
         <f>IF(V12&lt;&gt;"",V12,S12)</f>
         <v/>
       </c>
-      <c r="AN12" s="18">
-        <f>IF(AG12="","","Football 11 minutes from Hoxton Square")</f>
-        <v/>
+      <c r="AN12" s="15" t="inlineStr">
+        <is>
+          <t>Office football for Human Made Machine?</t>
+        </is>
       </c>
       <c r="AO12" s="19" t="inlineStr">
         <is>
           <t>Hi Sabrina,
-You've built a culture around people first, flexible working and giving back -- a weekly team game fits that pretty well.
-We've a 5-a-side pitch at Powerleague Shoreditch, Braithwaite Street, an 11-minute walk from Hoxton Square. There's a slot free Monday 28 September at 17:40, or 19:40, and it could become your regular weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Would your team be up for it?
+You've built a culture around giving a share of profits to charity, flexible hybrid working and real personal development, which sounds like a team that plays well together.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), an 11-minute walk from your office on Hoxton Square.
+We're looking for someone at Human Made Machine to start a regular office kickabout for colleagues; we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
 Best,
 Brian
 FC Urban</t>
@@ -3190,37 +3146,30 @@
       <c r="AP12" s="19" t="inlineStr">
         <is>
           <t>Hi Sabrina,
-Following up on the five-a-side slot at Powerleague Shoreditch, 11 minutes from Hoxton Square. Thursday 1 October at 18:20 is still open. It's {PRICE} a player, and we handle the booking and payments -- one link for the team. Worth a try?
+Just following up on my note about a regular football game for the Human Made Machine team. Would there be any interest, or is there someone else there I should forward this to?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ12" s="20">
-        <f>IF(OR(AG12="",AO12=""),"",SUBSTITUTE(AO12,"{PRICE}","£"&amp;IF(AG12=INT(AG12),TEXT(AG12,"0"),TEXT(AG12,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR12" s="20">
-        <f>IF(OR(AG12="",AP12=""),"",SUBSTITUTE(AP12,"{PRICE}","£"&amp;IF(AG12=INT(AG12),TEXT(AG12,"0"),TEXT(AG12,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS12" s="15" t="inlineStr">
+      <c r="AQ12" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR12" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS12" s="15" t="n"/>
       <c r="AT12" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU12" s="15" t="n"/>
-      <c r="AV12" s="18">
-        <f>IF(AU12&lt;&gt;"","No – hold: "&amp;AU12,IF(AG12="","No – no confirmed London price per player",IF(AM12="","No – no email",IF(AO12="","No – no personalised email",IF(AS12&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX12" s="21" t="n"/>
-      <c r="AY12" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV12" s="20" t="n"/>
+      <c r="AW12" s="20" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="15" t="n">
@@ -3365,9 +3314,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG13" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG13" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH13" s="15" t="inlineStr">
         <is>
@@ -3394,17 +3344,19 @@
         <f>IF(V13&lt;&gt;"",V13,S13)</f>
         <v/>
       </c>
-      <c r="AN13" s="18">
-        <f>IF(AG13="","","Football near Great Sutton St, for a Best Places team")</f>
-        <v/>
+      <c r="AN13" s="15" t="inlineStr">
+        <is>
+          <t>Football for the Artiq team?</t>
+        </is>
       </c>
       <c r="AO13" s="19" t="inlineStr">
         <is>
           <t>Hi Patrick,
-Going from a team of two to a Sunday Times Best Places to Work winner is quite a run -- worth marking with something the whole team can join in on.
-We run a floodlit 6-a-side pitch at Moreland School, Gard Street, an 11-minute walk from Great Sutton Street. There's a slot free Monday 12 October at 18:00, 19:00, or 20:00, and it could become your regular weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Shall I hold Monday for you?
+Going from a team of two in 2009 to a Sunday Times Best Places to Work winner in 2023 is quite a run.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), an 11-minute walk from your office on Great Sutton Street.
+We're looking for someone at Artiq who'd enjoy helping start a regular office kickabout for colleagues; we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
 Best,
 Brian
 FC Urban</t>
@@ -3413,37 +3365,30 @@
       <c r="AP13" s="19" t="inlineStr">
         <is>
           <t>Hi Patrick,
-Still holding the 6-a-side slot at Moreland School, 11 minutes from Great Sutton Street. Monday 12 October at 19:00 is free. It's {PRICE} a player, and we handle the booking and payments, so it's one link for the team. Fancy giving it a go?
+Just following up on my note about a regular football game for the Artiq team. Would there be any interest, or is there someone else there I should forward this to?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ13" s="20">
-        <f>IF(OR(AG13="",AO13=""),"",SUBSTITUTE(AO13,"{PRICE}","£"&amp;IF(AG13=INT(AG13),TEXT(AG13,"0"),TEXT(AG13,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR13" s="20">
-        <f>IF(OR(AG13="",AP13=""),"",SUBSTITUTE(AP13,"{PRICE}","£"&amp;IF(AG13=INT(AG13),TEXT(AG13,"0"),TEXT(AG13,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS13" s="15" t="inlineStr">
+      <c r="AQ13" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR13" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS13" s="15" t="n"/>
       <c r="AT13" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU13" s="15" t="n"/>
-      <c r="AV13" s="18">
-        <f>IF(AU13&lt;&gt;"","No – hold: "&amp;AU13,IF(AG13="","No – no confirmed London price per player",IF(AM13="","No – no email",IF(AO13="","No – no personalised email",IF(AS13&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX13" s="21" t="n"/>
-      <c r="AY13" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV13" s="20" t="n"/>
+      <c r="AW13" s="20" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="15" t="n">
@@ -3590,9 +3535,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG14" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG14" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH14" s="15" t="inlineStr">
         <is>
@@ -3623,16 +3569,19 @@
         <f>IF(V14&lt;&gt;"",V14,S14)</f>
         <v/>
       </c>
-      <c r="AN14" s="18">
-        <f>IF(AG14="","","5-a-side, 11 minutes from Worship Street")</f>
-        <v/>
+      <c r="AN14" s="15" t="inlineStr">
+        <is>
+          <t>Football for the OSF Digital team?</t>
+        </is>
       </c>
       <c r="AO14" s="19" t="inlineStr">
         <is>
           <t>Hi David,
-Congratulations on becoming CEO last year, and on the ISO 27001 certification and EcoVadis Bronze this year, good momentum to keep going. We've got a 5-a-side pitch at Powerleague Shoreditch, an 11-minute walk from Worship Street, with a slot free Monday 28 September at 17:40, or 19:40 if evenings suit better. It's an easy way to turn that into a regular weekly game for the team.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Would your team be up for it?
+Congratulations on becoming CEO last year, and on the ISO 27001 certification and EcoVadis Bronze this year, good momentum to keep going.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), an 11-minute walk from your office on Worship Street.
+We're looking for someone at OSF Digital who'd enjoy helping start a regular office kickabout for colleagues; we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
 Best,
 Brian
 FC Urban</t>
@@ -3641,37 +3590,30 @@
       <c r="AP14" s="19" t="inlineStr">
         <is>
           <t>Hi David,
-Just checking back on the Shoreditch pitch. Monday 28 September has gone, but Thursday 1 October at 18:20 is open, still an 11-minute walk from Worship Street. It's {PRICE} a player, and we handle booking and payments. Want me to lock it in for OSF?
+Just following up on my note about a regular football game for the OSF Digital team. Would there be any interest, or is there someone else there I should forward this to?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ14" s="20">
-        <f>IF(OR(AG14="",AO14=""),"",SUBSTITUTE(AO14,"{PRICE}","£"&amp;IF(AG14=INT(AG14),TEXT(AG14,"0"),TEXT(AG14,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR14" s="20">
-        <f>IF(OR(AG14="",AP14=""),"",SUBSTITUTE(AP14,"{PRICE}","£"&amp;IF(AG14=INT(AG14),TEXT(AG14,"0"),TEXT(AG14,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS14" s="15" t="inlineStr">
+      <c r="AQ14" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR14" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS14" s="15" t="n"/>
       <c r="AT14" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU14" s="15" t="n"/>
-      <c r="AV14" s="18">
-        <f>IF(AU14&lt;&gt;"","No – hold: "&amp;AU14,IF(AG14="","No – no confirmed London price per player",IF(AM14="","No – no email",IF(AO14="","No – no personalised email",IF(AS14&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX14" s="21" t="n"/>
-      <c r="AY14" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV14" s="20" t="n"/>
+      <c r="AW14" s="20" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="15" t="n">
@@ -3816,9 +3758,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG15" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG15" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH15" s="15" t="inlineStr">
         <is>
@@ -3849,16 +3792,19 @@
         <f>IF(V15&lt;&gt;"",V15,S15)</f>
         <v/>
       </c>
-      <c r="AN15" s="18">
-        <f>IF(AG15="","","Best Places to Work 2026 - and a weekly game?")</f>
-        <v/>
+      <c r="AN15" s="15" t="inlineStr">
+        <is>
+          <t>Football for the Windfall Films team?</t>
+        </is>
       </c>
       <c r="AO15" s="19" t="inlineStr">
         <is>
           <t>Hi Carlo,
-Congratulations on being named Best Places to Work in TV 2026 at the Broadcast Awards, sounds like exactly the kind of team that would enjoy a regular kickabout together. We've got a floodlit 6-a-side pitch at Moreland School, a 13-minute walk from St Peter's Street, with a slot free Monday 12 October at 18:00, or 19:00 if that works better. It could easily become your weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Shall I hold Monday for you?
+Congratulations on being named Best Places to Work in TV 2026 at the Broadcast Awards, a great sign for the team.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), a 13-minute walk from your office on St Peter's Street.
+We're looking for someone at Windfall Films who'd enjoy helping start a regular office kickabout for colleagues; we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
 Best,
 Brian
 FC Urban</t>
@@ -3867,37 +3813,30 @@
       <c r="AP15" s="19" t="inlineStr">
         <is>
           <t>Hi Carlo,
-Following up on the pitch near St Peter's Street. Monday 12 October at 18:00 is still free, or 19:00 works too. It's {PRICE} a player, and we handle the booking and payments. Fits nicely for a team that just won Best Places to Work. Worth a try?
+Just following up on my note about a regular football game for the Windfall Films team. Would there be any interest, or is there someone else there I should forward this to?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ15" s="20">
-        <f>IF(OR(AG15="",AO15=""),"",SUBSTITUTE(AO15,"{PRICE}","£"&amp;IF(AG15=INT(AG15),TEXT(AG15,"0"),TEXT(AG15,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR15" s="20">
-        <f>IF(OR(AG15="",AP15=""),"",SUBSTITUTE(AP15,"{PRICE}","£"&amp;IF(AG15=INT(AG15),TEXT(AG15,"0"),TEXT(AG15,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS15" s="15" t="inlineStr">
+      <c r="AQ15" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR15" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS15" s="15" t="n"/>
       <c r="AT15" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU15" s="15" t="n"/>
-      <c r="AV15" s="18">
-        <f>IF(AU15&lt;&gt;"","No – hold: "&amp;AU15,IF(AG15="","No – no confirmed London price per player",IF(AM15="","No – no email",IF(AO15="","No – no personalised email",IF(AS15&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX15" s="21" t="n"/>
-      <c r="AY15" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV15" s="20" t="n"/>
+      <c r="AW15" s="20" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="15" t="n">
@@ -4042,9 +3981,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG16" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG16" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH16" s="15" t="inlineStr">
         <is>
@@ -4075,16 +4015,19 @@
         <f>IF(V16&lt;&gt;"",V16,S16)</f>
         <v/>
       </c>
-      <c r="AN16" s="18">
-        <f>IF(AG16="","","72 Films, ranked #2 - fancy a weekly game?")</f>
-        <v/>
+      <c r="AN16" s="15" t="inlineStr">
+        <is>
+          <t>Football for the 72 Films team?</t>
+        </is>
       </c>
       <c r="AO16" s="19" t="inlineStr">
         <is>
           <t>Hi David,
-Congratulations on being ranked the UK's number two independent production company in Broadcast's 2026 Annual Peer Poll, quite a year for the team. We've got a floodlit 6-a-side pitch at Moreland School, a 13-minute walk from Amwell Street, with a slot free Monday 12 October at 18:00, or 19:00 if that suits better. It's a good excuse to make it a regular weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Shall I hold Monday for you?
+Congratulations on being ranked the UK's number two independent production company in Broadcast's 2026 Annual Peer Poll, quite a year for the team.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), a 13-minute walk from your office on Amwell Street.
+We're looking for someone at 72 Films who'd enjoy helping start a regular office kickabout for colleagues; we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
 Best,
 Brian
 FC Urban</t>
@@ -4093,37 +4036,30 @@
       <c r="AP16" s="19" t="inlineStr">
         <is>
           <t>Hi David,
-Just checking back on the pitch near Amwell Street. Monday 12 October at 18:00 is still open, or 19:00 works too. It's {PRICE} a player, and we handle booking and payments. Good way to celebrate that #2 ranking with the team. Shall I hold it?
+Just following up on my note about a regular football game for the 72 Films team. Would there be any interest, or is there someone else there I should forward this to?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ16" s="20">
-        <f>IF(OR(AG16="",AO16=""),"",SUBSTITUTE(AO16,"{PRICE}","£"&amp;IF(AG16=INT(AG16),TEXT(AG16,"0"),TEXT(AG16,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR16" s="20">
-        <f>IF(OR(AG16="",AP16=""),"",SUBSTITUTE(AP16,"{PRICE}","£"&amp;IF(AG16=INT(AG16),TEXT(AG16,"0"),TEXT(AG16,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS16" s="15" t="inlineStr">
+      <c r="AQ16" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR16" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS16" s="15" t="n"/>
       <c r="AT16" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU16" s="15" t="n"/>
-      <c r="AV16" s="18">
-        <f>IF(AU16&lt;&gt;"","No – hold: "&amp;AU16,IF(AG16="","No – no confirmed London price per player",IF(AM16="","No – no email",IF(AO16="","No – no personalised email",IF(AS16&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX16" s="21" t="n"/>
-      <c r="AY16" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV16" s="20" t="n"/>
+      <c r="AW16" s="20" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="15" t="n">
@@ -4268,9 +4204,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG17" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG17" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH17" s="15" t="inlineStr">
         <is>
@@ -4301,16 +4238,19 @@
         <f>IF(V17&lt;&gt;"",V17,S17)</f>
         <v/>
       </c>
-      <c r="AN17" s="18">
-        <f>IF(AG17="","","A 5-a-side pitch near Benwell Road for October Films")</f>
-        <v/>
+      <c r="AN17" s="15" t="inlineStr">
+        <is>
+          <t>Football for the October Films team?</t>
+        </is>
       </c>
       <c r="AO17" s="19" t="inlineStr">
         <is>
           <t>Hi Jane,
-October Films has been turning out award-winning documentaries from Benwell Road since 1989, picking up over 100 prizes along the way, including EMMY, Prix Italia and BAFTA, quite a team to be proud of. We've got a 5-a-side pitch at Market Road, a 14-minute walk away, free Monday 28 September at 18:00. It could easily become your regular weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Shall I hold Monday for you?
+October Films has been turning out award-winning documentaries from Benwell Road since 1989, picking up over 100 prizes including EMMY, Prix Italia and BAFTA.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Market Road (Caledonian Road) (https://www.fcurban.com/locations/market-road), a 14-minute walk from your office on Benwell Road.
+We're looking for someone at October Films who'd enjoy helping start a regular office kickabout for colleagues; we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
 Best,
 Brian
 FC Urban</t>
@@ -4319,37 +4259,30 @@
       <c r="AP17" s="19" t="inlineStr">
         <is>
           <t>Hi Jane,
-Circling back on the 5-a-side pitch near Benwell Road. If Monday's slot has gone, let me know a day and time that suits the team and I'll check what's free at Market Road. It's {PRICE} a player, and we handle booking and payments end to end. Worth a go?
+Just following up on my note about a regular football game for the October Films team. Would there be any interest, or is there someone else there I should forward this to?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ17" s="20">
-        <f>IF(OR(AG17="",AO17=""),"",SUBSTITUTE(AO17,"{PRICE}","£"&amp;IF(AG17=INT(AG17),TEXT(AG17,"0"),TEXT(AG17,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR17" s="20">
-        <f>IF(OR(AG17="",AP17=""),"",SUBSTITUTE(AP17,"{PRICE}","£"&amp;IF(AG17=INT(AG17),TEXT(AG17,"0"),TEXT(AG17,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS17" s="15" t="inlineStr">
+      <c r="AQ17" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR17" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS17" s="15" t="n"/>
       <c r="AT17" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU17" s="15" t="n"/>
-      <c r="AV17" s="18">
-        <f>IF(AU17&lt;&gt;"","No – hold: "&amp;AU17,IF(AG17="","No – no confirmed London price per player",IF(AM17="","No – no email",IF(AO17="","No – no personalised email",IF(AS17&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX17" s="21" t="n"/>
-      <c r="AY17" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV17" s="20" t="n"/>
+      <c r="AW17" s="20" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="n">
@@ -4496,9 +4429,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG18" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG18" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH18" s="15" t="inlineStr">
         <is>
@@ -4529,16 +4463,19 @@
         <f>IF(V18&lt;&gt;"",V18,S18)</f>
         <v/>
       </c>
-      <c r="AN18" s="18">
-        <f>IF(AG18="","","A 5-a-side pitch near Dashwood House, Old Broad St")</f>
-        <v/>
+      <c r="AN18" s="15" t="inlineStr">
+        <is>
+          <t>After-work football for Yendall Hunter?</t>
+        </is>
       </c>
       <c r="AO18" s="19" t="inlineStr">
         <is>
           <t>Hi Martin,
-Since the move to Dashwood House on Old Broad Street, it's a great excuse to get the team out together. We've got a 5-a-side pitch at Powerleague Shoreditch, a 14-minute walk away, with a slot free Monday 28 September at 17:40, or 19:40 if evenings suit better. It could easily become your regular weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Shall I hold Monday for you?
+Since your move to Dashwood House on Old Broad Street in 2024, it's a good moment to get the team out together.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), a 14-minute walk from your office.
+We're looking for someone at Yendall Hunter to start a regular after-work social, or perhaps a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
+Would that be of interest to the team? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
 Best,
 Brian
 FC Urban</t>
@@ -4547,37 +4484,30 @@
       <c r="AP18" s="19" t="inlineStr">
         <is>
           <t>Hi Martin,
-Just checking back on the pitch near Dashwood House. Monday's slot has gone, but Thursday 1 October at 18:20 is still free. It's {PRICE} a player, and we handle booking and payments. Good way to get the team together after the move. Shall I hold it?
+Just following up on my note about a regular after-work football game for Yendall Hunter. Would that be of interest, or is there someone else there I should forward this to?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ18" s="20">
-        <f>IF(OR(AG18="",AO18=""),"",SUBSTITUTE(AO18,"{PRICE}","£"&amp;IF(AG18=INT(AG18),TEXT(AG18,"0"),TEXT(AG18,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR18" s="20">
-        <f>IF(OR(AG18="",AP18=""),"",SUBSTITUTE(AP18,"{PRICE}","£"&amp;IF(AG18=INT(AG18),TEXT(AG18,"0"),TEXT(AG18,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS18" s="15" t="inlineStr">
+      <c r="AQ18" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR18" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS18" s="15" t="n"/>
       <c r="AT18" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU18" s="15" t="n"/>
-      <c r="AV18" s="18">
-        <f>IF(AU18&lt;&gt;"","No – hold: "&amp;AU18,IF(AG18="","No – no confirmed London price per player",IF(AM18="","No – no email",IF(AO18="","No – no personalised email",IF(AS18&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX18" s="21" t="n"/>
-      <c r="AY18" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV18" s="20" t="n"/>
+      <c r="AW18" s="20" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="n">
@@ -4720,9 +4650,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG19" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG19" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH19" s="15" t="inlineStr">
         <is>
@@ -4753,14 +4684,19 @@
         <f>IF(V19&lt;&gt;"",V19,S19)</f>
         <v/>
       </c>
-      <c r="AN19" s="18">
-        <f>IF(AG19="","","A weekly 5-a-side, 15 min from St Mary Axe")</f>
-        <v/>
+      <c r="AN19" s="15" t="inlineStr">
+        <is>
+          <t>Football for the JENOA team?</t>
+        </is>
       </c>
       <c r="AO19" s="19" t="inlineStr">
         <is>
           <t>Hi Mahboob,
-JENOA launched in 2020 as a digital-first broker, backed by Abdul Latif Jameel's 80-year heritage — sounds like a team that could do with a regular game together. We've got a 5-a-side pitch at Powerleague Shoreditch, Braithwaite Street, E1 6GJ, about a 15-minute walk from St Mary Axe. There's a slot open Monday 28 September at 17:40, or 19:40 if evenings suit better, and it could become your weekly fixture. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Shall I hold Monday for you?
+JENOA launched in 2020 as a digital-first broker, backed by Abdul Latif Jameel's 80-year heritage, sounds like a team worth bringing together.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 15-minute walk from your office at St Mary Axe.
+We're looking for someone at JENOA who'd enjoy helping start a regular team social or after-work game for colleagues; we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
 Best,
 Brian
 FC Urban</t>
@@ -4769,37 +4705,30 @@
       <c r="AP19" s="19" t="inlineStr">
         <is>
           <t>Hi Mahboob,
-Following up on that 5-a-side slot at Powerleague Shoreditch — Monday 28 September at 17:40 is still open, or Thursday 1 October at 18:20 if that's easier. It's {PRICE} a player; we handle the booking and payments, so it's simple to start. Let me know if you'd like it held.
+Just following up on my note about a regular football game for the JENOA team. Would there be any interest, or is there someone else there I should forward this to?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ19" s="20">
-        <f>IF(OR(AG19="",AO19=""),"",SUBSTITUTE(AO19,"{PRICE}","£"&amp;IF(AG19=INT(AG19),TEXT(AG19,"0"),TEXT(AG19,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR19" s="20">
-        <f>IF(OR(AG19="",AP19=""),"",SUBSTITUTE(AP19,"{PRICE}","£"&amp;IF(AG19=INT(AG19),TEXT(AG19,"0"),TEXT(AG19,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS19" s="15" t="inlineStr">
+      <c r="AQ19" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR19" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS19" s="15" t="n"/>
       <c r="AT19" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU19" s="15" t="n"/>
-      <c r="AV19" s="18">
-        <f>IF(AU19&lt;&gt;"","No – hold: "&amp;AU19,IF(AG19="","No – no confirmed London price per player",IF(AM19="","No – no email",IF(AO19="","No – no personalised email",IF(AS19&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX19" s="21" t="n"/>
-      <c r="AY19" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV19" s="20" t="n"/>
+      <c r="AW19" s="20" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="n">
@@ -4930,9 +4859,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG20" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG20" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH20" s="15" t="inlineStr">
         <is>
@@ -4963,14 +4893,19 @@
         <f>IF(V20&lt;&gt;"",V20,S20)</f>
         <v/>
       </c>
-      <c r="AN20" s="18">
-        <f>IF(AG20="","","6 minutes from Broadgate Tower: weekly 5-a-side")</f>
-        <v/>
+      <c r="AN20" s="15" t="inlineStr">
+        <is>
+          <t>A weekly game for Gill Jennings &amp; Every?</t>
+        </is>
       </c>
       <c r="AO20" s="19" t="inlineStr">
         <is>
           <t>Hi Gill Jennings &amp; Every team,
-With around 125 of you in Broadgate Tower, and a habit of getting together socially in the area, a regular five-a-side game sounds right up your street. We've got a pitch at Powerleague Shoreditch, Braithwaite Street, E1 6GJ, about a 6-minute walk from your office. There's a slot open Monday 28 September at 17:40, or 19:40 if that suits better, and it could become your weekly fixture. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Shall I hold Monday for you?
+With around 125 of you in Broadgate Tower, and a habit of getting together socially, a regular game sounds like a natural fit.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 6-minute walk from your office.
+We're looking for someone at Gill Jennings &amp; Every to start a regular team social or after-work game for colleagues; we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, could you forward this to whoever looks after staff socials or wellbeing?
+FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
 Best,
 Brian
 FC Urban</t>
@@ -4979,37 +4914,30 @@
       <c r="AP20" s="19" t="inlineStr">
         <is>
           <t>Hi Gill Jennings &amp; Every team,
-Following up on the 5-a-side slot at Powerleague Shoreditch, a short walk from Broadgate Tower — Monday 28 September at 17:40 is still open, or Thursday 1 October at 18:20. It's {PRICE} a player; we handle the booking and payments. Let me know if you'd like it held.
+Just following up on my note about a regular football game for the team. Would there be any interest, or is there someone else I should forward this to about staff socials?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ20" s="20">
-        <f>IF(OR(AG20="",AO20=""),"",SUBSTITUTE(AO20,"{PRICE}","£"&amp;IF(AG20=INT(AG20),TEXT(AG20,"0"),TEXT(AG20,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR20" s="20">
-        <f>IF(OR(AG20="",AP20=""),"",SUBSTITUTE(AP20,"{PRICE}","£"&amp;IF(AG20=INT(AG20),TEXT(AG20,"0"),TEXT(AG20,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS20" s="15" t="inlineStr">
+      <c r="AQ20" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR20" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS20" s="15" t="n"/>
       <c r="AT20" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU20" s="15" t="n"/>
-      <c r="AV20" s="18">
-        <f>IF(AU20&lt;&gt;"","No – hold: "&amp;AU20,IF(AG20="","No – no confirmed London price per player",IF(AM20="","No – no email",IF(AO20="","No – no personalised email",IF(AS20&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX20" s="21" t="n"/>
-      <c r="AY20" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV20" s="20" t="n"/>
+      <c r="AW20" s="20" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="15" t="n">
@@ -5138,9 +5066,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG21" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG21" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH21" s="15" t="inlineStr">
         <is>
@@ -5171,14 +5100,19 @@
         <f>IF(V21&lt;&gt;"",V21,S21)</f>
         <v/>
       </c>
-      <c r="AN21" s="18">
-        <f>IF(AG21="","","7 minutes from Bishopsgate: weekly 5-a-side")</f>
-        <v/>
+      <c r="AN21" s="15" t="inlineStr">
+        <is>
+          <t>Football for the RBB Economics team?</t>
+        </is>
       </c>
       <c r="AO21" s="19" t="inlineStr">
         <is>
-          <t>Hi Rbb Economics team,
-RBB grew from just 16 founding staff to over 300 economists across 18 offices — sounds like a team worth bringing together for a regular game. We've got a 5-a-side pitch at Powerleague Shoreditch, Braithwaite Street, E1 6GJ, about a 7-minute walk from your Bishopsgate office. There's a slot open Monday 28 September at 17:40, or 19:40 if that's easier, and it could become your weekly fixture. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Shall I hold Monday for you?
+          <t>Hi RBB Economics team,
+RBB grew from 16 founding staff in 2002 to over 300 economists across 18 offices, quite a team to bring together.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 7-minute walk from your office.
+We're looking for someone at RBB Economics to start a regular team social, or perhaps a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
 Best,
 Brian
 FC Urban</t>
@@ -5186,38 +5120,31 @@
       </c>
       <c r="AP21" s="19" t="inlineStr">
         <is>
-          <t>Hi Rbb Economics team,
-Following up on the 5-a-side slot at Powerleague Shoreditch, a short walk from Bishopsgate — Monday 28 September at 17:40 is still open, or Thursday 1 October at 18:20. It's {PRICE} a player; we handle the booking and payments. Let me know if you'd like it held.
+          <t>Hi RBB Economics team,
+Just following up on my note about a regular football game for the team. Would there be any interest, or is there someone else I should forward this to about staff socials?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ21" s="20">
-        <f>IF(OR(AG21="",AO21=""),"",SUBSTITUTE(AO21,"{PRICE}","£"&amp;IF(AG21=INT(AG21),TEXT(AG21,"0"),TEXT(AG21,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR21" s="20">
-        <f>IF(OR(AG21="",AP21=""),"",SUBSTITUTE(AP21,"{PRICE}","£"&amp;IF(AG21=INT(AG21),TEXT(AG21,"0"),TEXT(AG21,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS21" s="15" t="inlineStr">
+      <c r="AQ21" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR21" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS21" s="15" t="n"/>
       <c r="AT21" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU21" s="15" t="n"/>
-      <c r="AV21" s="18">
-        <f>IF(AU21&lt;&gt;"","No – hold: "&amp;AU21,IF(AG21="","No – no confirmed London price per player",IF(AM21="","No – no email",IF(AO21="","No – no personalised email",IF(AS21&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX21" s="21" t="n"/>
-      <c r="AY21" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV21" s="20" t="n"/>
+      <c r="AW21" s="20" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="15" t="n">
@@ -5352,9 +5279,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG22" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG22" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH22" s="15" t="inlineStr">
         <is>
@@ -5381,14 +5309,19 @@
         <f>IF(V22&lt;&gt;"",V22,S22)</f>
         <v/>
       </c>
-      <c r="AN22" s="18">
-        <f>IF(AG22="","","A 5-a-side pitch near your Shoreditch office")</f>
-        <v/>
+      <c r="AN22" s="15" t="inlineStr">
+        <is>
+          <t>Football for the Montash team?</t>
+        </is>
       </c>
       <c r="AO22" s="19" t="inlineStr">
         <is>
           <t>Hi Montash team,
-Between the seasonal socials and wellbeing days you already run from your Shoreditch office, a regular match sounds like a natural fit for the team. We have a 5-a-side pitch at Powerleague Shoreditch, on Braithwaite Street, an 8-minute walk from 100 Clifton Street. There's a slot free Monday 28 September at 17:40, or 19:40, and it could easily become your weekly fixture. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Shall I hold the 17:40 slot for you?
+Between the seasonal socials and wellbeing days you already run, a regular match sounds like a natural fit for the team.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), an 8-minute walk from your office on Clifton Street.
+We're looking for someone at Montash to start a regular team game, perhaps a friendly against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
 Best,
 Brian
 FC Urban</t>
@@ -5397,37 +5330,30 @@
       <c r="AP22" s="19" t="inlineStr">
         <is>
           <t>Hi Montash team,
-Just checking back on a weekly 5-a-side near 100 Clifton Street. Monday 28 September at 19:40 at Powerleague Shoreditch is still free. It's {PRICE} a player, and we handle the pitch, sign-ups and payments end to end. Let me know if you'd like it held.
+Just following up on my note about a regular football game for the Montash team. Would there be any interest, or is there someone else there I should forward this to?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ22" s="20">
-        <f>IF(OR(AG22="",AO22=""),"",SUBSTITUTE(AO22,"{PRICE}","£"&amp;IF(AG22=INT(AG22),TEXT(AG22,"0"),TEXT(AG22,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR22" s="20">
-        <f>IF(OR(AG22="",AP22=""),"",SUBSTITUTE(AP22,"{PRICE}","£"&amp;IF(AG22=INT(AG22),TEXT(AG22,"0"),TEXT(AG22,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS22" s="15" t="inlineStr">
+      <c r="AQ22" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR22" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS22" s="15" t="n"/>
       <c r="AT22" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU22" s="15" t="n"/>
-      <c r="AV22" s="18">
-        <f>IF(AU22&lt;&gt;"","No – hold: "&amp;AU22,IF(AG22="","No – no confirmed London price per player",IF(AM22="","No – no email",IF(AO22="","No – no personalised email",IF(AS22&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX22" s="21" t="n"/>
-      <c r="AY22" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV22" s="20" t="n"/>
+      <c r="AW22" s="20" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="15" t="n">
@@ -5562,9 +5488,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG23" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG23" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH23" s="15" t="inlineStr">
         <is>
@@ -5595,14 +5522,18 @@
         <f>IF(V23&lt;&gt;"",V23,S23)</f>
         <v/>
       </c>
-      <c r="AN23" s="18">
-        <f>IF(AG23="","","A 5-a-side pitch near Perseverance Works")</f>
-        <v/>
+      <c r="AN23" s="15" t="inlineStr">
+        <is>
+          <t>A weekly kickabout for Atelier Ten?</t>
+        </is>
       </c>
       <c r="AO23" s="19" t="inlineStr">
         <is>
           <t>Hi Atelier Ten team,
-Congratulations on the 2026 Best of Practice Award from The Architect's Newspaper, a nice moment to mark with the team. We have a 5-a-side pitch at Powerleague Shoreditch, on Braithwaite Street, a 9-minute walk from your Perseverance Works office. There's a slot free Monday 28 September at 17:40, or 19:40, and it could become your standing weekly game. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Would your team be up for it?
+Congratulations on winning the 2026 Best of Practice Award from The Architect's Newspaper, a great moment for the studio.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 9-minute walk from your office at E2 8DD.
+We're looking for someone at Atelier Ten who enjoys football and could help start a weekly kickabout for the studio. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -5611,37 +5542,30 @@
       <c r="AP23" s="19" t="inlineStr">
         <is>
           <t>Hi Atelier Ten team,
-Just checking back on a weekly 5-a-side near Perseverance Works. Monday 28 September at 19:40 at Powerleague Shoreditch is still free. It's {PRICE} a player, and we handle the pitch, sign-ups and payments end to end. Let me know if you'd like it held.
+Just following up on my note below about a weekly football game near your office. Would there be any interest, or could you point me to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ23" s="20">
-        <f>IF(OR(AG23="",AO23=""),"",SUBSTITUTE(AO23,"{PRICE}","£"&amp;IF(AG23=INT(AG23),TEXT(AG23,"0"),TEXT(AG23,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR23" s="20">
-        <f>IF(OR(AG23="",AP23=""),"",SUBSTITUTE(AP23,"{PRICE}","£"&amp;IF(AG23=INT(AG23),TEXT(AG23,"0"),TEXT(AG23,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS23" s="15" t="inlineStr">
+      <c r="AQ23" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR23" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS23" s="15" t="n"/>
       <c r="AT23" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU23" s="15" t="n"/>
-      <c r="AV23" s="18">
-        <f>IF(AU23&lt;&gt;"","No – hold: "&amp;AU23,IF(AG23="","No – no confirmed London price per player",IF(AM23="","No – no email",IF(AO23="","No – no personalised email",IF(AS23&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX23" s="21" t="n"/>
-      <c r="AY23" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV23" s="20" t="n"/>
+      <c r="AW23" s="20" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="15" t="n">
@@ -5774,9 +5698,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG24" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG24" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH24" s="15" t="inlineStr">
         <is>
@@ -5803,14 +5728,18 @@
         <f>IF(V24&lt;&gt;"",V24,S24)</f>
         <v/>
       </c>
-      <c r="AN24" s="18">
-        <f>IF(AG24="","","Aptem's award - and a 6-a-side near City Road")</f>
-        <v/>
+      <c r="AN24" s="15" t="inlineStr">
+        <is>
+          <t>A weekly kickabout for the Aptem team</t>
+        </is>
       </c>
       <c r="AO24" s="19" t="inlineStr">
         <is>
           <t>Hi Aptem team,
-Congratulations on being named Learning Technologies Organisation of the Year, a great way to mark the growth of your 100-strong team. We have a floodlit 6-a-side 3G pitch at Moreland School, Gard Street, just off Old Street, a 9-minute walk from Eagle House on City Road. There's a slot free Monday 12 October at 18:00, or 19:00, and it could easily become your weekly fixture. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Shall I hold the 18:00 slot for you?
+Congratulations on being named Learning Technologies Organisation of the Year.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 9-minute walk from Eagle House on City Road.
+We're looking for someone at Aptem who enjoys football and could help start a weekly office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
+Would that be of interest to the team? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -5819,37 +5748,30 @@
       <c r="AP24" s="19" t="inlineStr">
         <is>
           <t>Hi Aptem team,
-Following up on a weekly 6-a-side near Eagle House. Monday 12 October at 19:00 at Moreland School is still open. It's {PRICE} a player, and we handle the pitch, sign-ups and payments end to end. Let me know if that works.
+Just following up on my note below about a weekly kickabout near Eagle House. Would that be of interest to the team, or could you point me to whoever looks after staff socials?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ24" s="20">
-        <f>IF(OR(AG24="",AO24=""),"",SUBSTITUTE(AO24,"{PRICE}","£"&amp;IF(AG24=INT(AG24),TEXT(AG24,"0"),TEXT(AG24,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR24" s="20">
-        <f>IF(OR(AG24="",AP24=""),"",SUBSTITUTE(AP24,"{PRICE}","£"&amp;IF(AG24=INT(AG24),TEXT(AG24,"0"),TEXT(AG24,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS24" s="15" t="inlineStr">
+      <c r="AQ24" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR24" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS24" s="15" t="n"/>
       <c r="AT24" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU24" s="15" t="n"/>
-      <c r="AV24" s="18">
-        <f>IF(AU24&lt;&gt;"","No – hold: "&amp;AU24,IF(AG24="","No – no confirmed London price per player",IF(AM24="","No – no email",IF(AO24="","No – no personalised email",IF(AS24&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX24" s="21" t="n"/>
-      <c r="AY24" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV24" s="20" t="n"/>
+      <c r="AW24" s="20" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="15" t="n">
@@ -5982,9 +5904,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG25" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG25" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH25" s="15" t="inlineStr">
         <is>
@@ -6011,14 +5934,18 @@
         <f>IF(V25&lt;&gt;"",V25,S25)</f>
         <v/>
       </c>
-      <c r="AN25" s="18">
-        <f>IF(AG25="","","A weekly 5-a-side for Elsewhen, 10 min walk")</f>
-        <v/>
+      <c r="AN25" s="15" t="inlineStr">
+        <is>
+          <t>Office football for the Elsewhen team</t>
+        </is>
       </c>
       <c r="AO25" s="19" t="inlineStr">
         <is>
           <t>Hi Elsewhen team,
-With a team of over 100 strategists, designers and engineers across 11 nationalities, you've got more than enough for a regular five-a-side. We have a 5-a-side pitch at Powerleague Shoreditch, Braithwaite Street, E1 6GJ, a 10-minute walk from St Peter's Sq, with Monday 28 September at 17:40 open, or 19:40 if that's easier — it can become your weekly game. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Shall I hold Monday for you?
+With more than 100 strategists, designers and engineers across 11 nationalities, you've got plenty of people for a five-a-side.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 10-minute walk from your office on St Peter's Square.
+We're looking for someone at Elsewhen who enjoys football and could help start a weekly office kickabout for the studio. We handle the pitch, extra players if you're short, payments and organisation.
+Would that be of interest to the team? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -6026,38 +5953,31 @@
       </c>
       <c r="AP25" s="19" t="inlineStr">
         <is>
-          <t>Hi again,
-Just checking whether a weekly 5-a-side works for Elsewhen. Monday 28 September at 19:40 is still open at Powerleague Shoreditch, 10 minutes from St Peter's Sq, or Thursday 1 October at 18:20 if that's better. It's {PRICE} a player, and we handle the pitch, sign-ups and payments. Happy to hold one.
+          <t>Hi Elsewhen team,
+Just following up on my note below about a weekly office kickabout near St Peter's Square. Would that be of interest, or could you point me to whoever looks after staff socials?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ25" s="20">
-        <f>IF(OR(AG25="",AO25=""),"",SUBSTITUTE(AO25,"{PRICE}","£"&amp;IF(AG25=INT(AG25),TEXT(AG25,"0"),TEXT(AG25,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR25" s="20">
-        <f>IF(OR(AG25="",AP25=""),"",SUBSTITUTE(AP25,"{PRICE}","£"&amp;IF(AG25=INT(AG25),TEXT(AG25,"0"),TEXT(AG25,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS25" s="15" t="inlineStr">
+      <c r="AQ25" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR25" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS25" s="15" t="n"/>
       <c r="AT25" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU25" s="15" t="n"/>
-      <c r="AV25" s="18">
-        <f>IF(AU25&lt;&gt;"","No – hold: "&amp;AU25,IF(AG25="","No – no confirmed London price per player",IF(AM25="","No – no email",IF(AO25="","No – no personalised email",IF(AS25&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX25" s="21" t="n"/>
-      <c r="AY25" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV25" s="20" t="n"/>
+      <c r="AW25" s="20" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="15" t="n">
@@ -6190,9 +6110,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG26" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG26" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH26" s="15" t="inlineStr">
         <is>
@@ -6219,14 +6140,18 @@
         <f>IF(V26&lt;&gt;"",V26,S26)</f>
         <v/>
       </c>
-      <c r="AN26" s="18">
-        <f>IF(AG26="","","A weekly 5-a-side, 10 min from Clere Street")</f>
-        <v/>
+      <c r="AN26" s="15" t="inlineStr">
+        <is>
+          <t>Weekly football for the Veed team</t>
+        </is>
       </c>
       <c r="AO26" s="19" t="inlineStr">
         <is>
           <t>Hi Veed team,
-Loved reading that the VEED team danced to 'Mamma Mia' at their last offsite — sounds like a group that would enjoy a regular five-a-side too. We have a 5-a-side pitch at Powerleague Shoreditch, Braithwaite Street, E1 6GJ, a 10-minute walk from Clere Street, with Monday 28 September at 17:40 open, or 19:40 if that's easier — it can become your weekly game. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Shall I hold Monday for you?
+Loved hearing that the VEED team danced to 'Mamma Mia' at your last offsite, sounds like a group that knows how to have fun together.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 10-minute walk from your office on Clere Street.
+We're looking for someone at Veed who enjoys football and could help start a weekly office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
+Would that be of interest to the team? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -6234,38 +6159,31 @@
       </c>
       <c r="AP26" s="19" t="inlineStr">
         <is>
-          <t>Hi again,
-Just checking whether a weekly 5-a-side appeals to the VEED team. Monday 28 September at 19:40 is still open at Powerleague Shoreditch, 10 minutes from Clere Street, or Thursday 1 October at 18:20 if that's better. It's {PRICE} a player — we handle the rest.
+          <t>Hi Veed team,
+Just following up on my note below about a weekly kickabout near Clere Street. Would that be of interest to the team, or could you point me to whoever looks after staff socials?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ26" s="20">
-        <f>IF(OR(AG26="",AO26=""),"",SUBSTITUTE(AO26,"{PRICE}","£"&amp;IF(AG26=INT(AG26),TEXT(AG26,"0"),TEXT(AG26,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR26" s="20">
-        <f>IF(OR(AG26="",AP26=""),"",SUBSTITUTE(AP26,"{PRICE}","£"&amp;IF(AG26=INT(AG26),TEXT(AG26,"0"),TEXT(AG26,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS26" s="15" t="inlineStr">
+      <c r="AQ26" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR26" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS26" s="15" t="n"/>
       <c r="AT26" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU26" s="15" t="n"/>
-      <c r="AV26" s="18">
-        <f>IF(AU26&lt;&gt;"","No – hold: "&amp;AU26,IF(AG26="","No – no confirmed London price per player",IF(AM26="","No – no email",IF(AO26="","No – no personalised email",IF(AS26&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX26" s="21" t="n"/>
-      <c r="AY26" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV26" s="20" t="n"/>
+      <c r="AW26" s="20" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="15" t="n">
@@ -6398,9 +6316,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG27" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG27" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH27" s="15" t="inlineStr">
         <is>
@@ -6427,17 +6346,18 @@
         <f>IF(V27&lt;&gt;"",V27,S27)</f>
         <v/>
       </c>
-      <c r="AN27" s="18">
-        <f>IF(AG27="","","A weekly game for Tryzens, 10 min from Appold St")</f>
-        <v/>
+      <c r="AN27" s="15" t="inlineStr">
+        <is>
+          <t>A football group for the Tryzens team?</t>
+        </is>
       </c>
       <c r="AO27" s="19" t="inlineStr">
         <is>
           <t>Hi Tryzens team,
-Congratulations on Phil Hoggarth stepping in as CEO this year - with 350+ Tryzenauts across the business, it feels like the right moment to get the London team out together on a Monday evening.
-We run 5-a-side at Powerleague Shoreditch, Braithwaite Street, a 10-minute walk from your office on Appold Street. Monday 28 September at 17:40 is open, or 19:40 the same evening, and it can become your regular weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Shall I hold Monday for you?
+Congratulations to Phil Hoggarth on stepping in as CEO, leading Tryzens' 350-plus team into a new chapter.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 10-minute walk from your office on Appold Street.
+We're looking for someone at Tryzens who enjoys football and could help start a weekly office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
+Would that be of interest to the team? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -6446,37 +6366,30 @@
       <c r="AP27" s="19" t="inlineStr">
         <is>
           <t>Hi Tryzens team,
-Following up on the Monday 28 September slot at Powerleague Shoreditch (17:40 or 19:40), or Thursday 1 October at 18:20. It's {PRICE} a player, and we handle sign-ups and payments, so it's just one link for the team.
+Just following up on my note below about a weekly kickabout near Appold Street. Would that be of interest to the team, or could you point me to whoever looks after staff socials?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ27" s="20">
-        <f>IF(OR(AG27="",AO27=""),"",SUBSTITUTE(AO27,"{PRICE}","£"&amp;IF(AG27=INT(AG27),TEXT(AG27,"0"),TEXT(AG27,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR27" s="20">
-        <f>IF(OR(AG27="",AP27=""),"",SUBSTITUTE(AP27,"{PRICE}","£"&amp;IF(AG27=INT(AG27),TEXT(AG27,"0"),TEXT(AG27,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS27" s="15" t="inlineStr">
+      <c r="AQ27" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR27" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS27" s="15" t="n"/>
       <c r="AT27" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU27" s="15" t="n"/>
-      <c r="AV27" s="18">
-        <f>IF(AU27&lt;&gt;"","No – hold: "&amp;AU27,IF(AG27="","No – no confirmed London price per player",IF(AM27="","No – no email",IF(AO27="","No – no personalised email",IF(AS27&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX27" s="21" t="n"/>
-      <c r="AY27" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV27" s="20" t="n"/>
+      <c r="AW27" s="20" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="n">
@@ -6611,9 +6524,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG28" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG28" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH28" s="15" t="inlineStr">
         <is>
@@ -6640,17 +6554,18 @@
         <f>IF(V28&lt;&gt;"",V28,S28)</f>
         <v/>
       </c>
-      <c r="AN28" s="18">
-        <f>IF(AG28="","","A rooftop pitch 11 minutes from Cremer St")</f>
-        <v/>
+      <c r="AN28" s="15" t="inlineStr">
+        <is>
+          <t>Football for the Karakusevic Carson studio</t>
+        </is>
       </c>
       <c r="AO28" s="19" t="inlineStr">
         <is>
           <t>Hi Karakusevic Carson Architects team,
-Congratulations to Abigail Batchelor on joining the judging panel for the Inspire Future Generations Awards 2026 - good excuse for the studio to get outside together.
-We've got a rooftop 5-a-side pitch at Britannia Leisure Centre, Pitfield Street, an 11-minute walk from Cremer Street. Monday 28 September at 18:00 is open, and it could become your regular weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Shall I hold Monday for you?
+Congratulations to Abigail Batchelor on joining the judging panel for the Inspire Future Generations Awards 2026.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch Rooftop (Britannia Leisure Centre, Pitfield Street) (https://www.fcurban.com/locations/shoreditch-rooftop), about an 11-minute walk from your office on Cremer Street.
+We're looking for someone at Karakusevic Carson Architects who enjoys football and could help start a weekly kickabout for the studio. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -6659,37 +6574,30 @@
       <c r="AP28" s="19" t="inlineStr">
         <is>
           <t>Hi Karakusevic Carson Architects team,
-Following up on the rooftop pitch at Britannia Leisure Centre - Monday 28 September at 18:00 is still open. It's {PRICE} a player, and we handle sign-ups and payments, so it's one link for the studio.
+Just following up on my note below about a weekly kickabout near Cremer Street. Would there be any interest, or could you point me to whoever looks after staff socials?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ28" s="20">
-        <f>IF(OR(AG28="",AO28=""),"",SUBSTITUTE(AO28,"{PRICE}","£"&amp;IF(AG28=INT(AG28),TEXT(AG28,"0"),TEXT(AG28,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR28" s="20">
-        <f>IF(OR(AG28="",AP28=""),"",SUBSTITUTE(AP28,"{PRICE}","£"&amp;IF(AG28=INT(AG28),TEXT(AG28,"0"),TEXT(AG28,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS28" s="15" t="inlineStr">
+      <c r="AQ28" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR28" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS28" s="15" t="n"/>
       <c r="AT28" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU28" s="15" t="n"/>
-      <c r="AV28" s="18">
-        <f>IF(AU28&lt;&gt;"","No – hold: "&amp;AU28,IF(AG28="","No – no confirmed London price per player",IF(AM28="","No – no email",IF(AO28="","No – no personalised email",IF(AS28&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX28" s="21" t="n"/>
-      <c r="AY28" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV28" s="20" t="n"/>
+      <c r="AW28" s="20" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="15" t="n">
@@ -6824,9 +6732,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG29" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG29" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH29" s="15" t="inlineStr">
         <is>
@@ -6857,17 +6766,18 @@
         <f>IF(V29&lt;&gt;"",V29,S29)</f>
         <v/>
       </c>
-      <c r="AN29" s="18">
-        <f>IF(AG29="","","A growing team, a weekly game 11 min from EC1M")</f>
-        <v/>
+      <c r="AN29" s="15" t="inlineStr">
+        <is>
+          <t>Weekly football near Old Street?</t>
+        </is>
       </c>
       <c r="AO29" s="19" t="inlineStr">
         <is>
           <t>Hi Permutive team,
-Your 120-plus team already meets in person every week and holds a yearly offsite to celebrate together - sounds like a group that would enjoy a regular match too.
-We've got a floodlit 6-a-side pitch at Moreland School, Gard Street, an 11-minute walk from your office near Old Street. Monday 12 October at 18:00 is open, or 19:00 the same evening, and it can become your regular weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Shall I hold Monday for you?
+With your 120-plus team already meeting in London every week and celebrating together at a yearly offsite, a regular match feels like a natural fit.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about an 11-minute walk from your office near Old Street.
+We're looking for someone at Permutive who enjoys football and could help start a weekly office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
+Would that be of interest to the team? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -6876,37 +6786,30 @@
       <c r="AP29" s="19" t="inlineStr">
         <is>
           <t>Hi Permutive team,
-Following up on the 6-a-side pitch at Moreland School - Monday 12 October at 18:00, 19:00, or 20:00. It's {PRICE} a player, and we handle sign-ups and payments, so it's one link for the team.
+Just following up on my note below about a weekly kickabout near Old Street. Would that be of interest to the team, or could you point me to whoever looks after staff socials?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ29" s="20">
-        <f>IF(OR(AG29="",AO29=""),"",SUBSTITUTE(AO29,"{PRICE}","£"&amp;IF(AG29=INT(AG29),TEXT(AG29,"0"),TEXT(AG29,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR29" s="20">
-        <f>IF(OR(AG29="",AP29=""),"",SUBSTITUTE(AP29,"{PRICE}","£"&amp;IF(AG29=INT(AG29),TEXT(AG29,"0"),TEXT(AG29,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS29" s="15" t="inlineStr">
+      <c r="AQ29" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR29" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS29" s="15" t="n"/>
       <c r="AT29" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU29" s="15" t="n"/>
-      <c r="AV29" s="18">
-        <f>IF(AU29&lt;&gt;"","No – hold: "&amp;AU29,IF(AG29="","No – no confirmed London price per player",IF(AM29="","No – no email",IF(AO29="","No – no personalised email",IF(AS29&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX29" s="21" t="n"/>
-      <c r="AY29" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV29" s="20" t="n"/>
+      <c r="AW29" s="20" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="15" t="n">
@@ -7041,9 +6944,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG30" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG30" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH30" s="15" t="inlineStr">
         <is>
@@ -7074,17 +6978,18 @@
         <f>IF(V30&lt;&gt;"",V30,S30)</f>
         <v/>
       </c>
-      <c r="AN30" s="18">
-        <f>IF(AG30="","","A weekly 6-a-side game, 11 minutes from Banner Street")</f>
-        <v/>
+      <c r="AN30" s="15" t="inlineStr">
+        <is>
+          <t>Football for the Eric Parry studio?</t>
+        </is>
       </c>
       <c r="AO30" s="19" t="inlineStr">
         <is>
           <t>Hi Eric Parry Architects team,
-Congratulations on One Liverpool Street reaching practical completion this July, after nearly fifteen years on the project — quite a milestone for the studio.
-We've got a floodlit 3G pitch at Moreland School, just off Old Street, an 11-minute walk from Banner Street. There's a 6-a-side slot free on Monday 12 October at 18:00, or 19:00, and it could become your regular weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Shall I hold Monday 12 October for you?
+Congratulations on One Liverpool Street reaching practical completion this July, after nearly fifteen years on the project.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about an 11-minute walk from your office on Banner Street.
+We're looking for someone at Eric Parry Architects who enjoys football and could help start a weekly kickabout for the studio. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -7092,37 +6997,31 @@
       </c>
       <c r="AP30" s="19" t="inlineStr">
         <is>
-          <t>Following up on the Monday 12 October slot at Moreland School (6-a-side, 18:00 or 19:00) — still open, an 11-minute walk from Banner Street. It's {PRICE} a player, and we handle the pitch booking and payments end to end. Let me know if you'd like it as your weekly game.
+          <t>Hi Eric Parry Architects team,
+Just following up on my note below about a weekly kickabout near Banner Street. Would there be any interest, or could you point me to whoever looks after staff socials?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ30" s="20">
-        <f>IF(OR(AG30="",AO30=""),"",SUBSTITUTE(AO30,"{PRICE}","£"&amp;IF(AG30=INT(AG30),TEXT(AG30,"0"),TEXT(AG30,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR30" s="20">
-        <f>IF(OR(AG30="",AP30=""),"",SUBSTITUTE(AP30,"{PRICE}","£"&amp;IF(AG30=INT(AG30),TEXT(AG30,"0"),TEXT(AG30,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS30" s="15" t="inlineStr">
+      <c r="AQ30" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR30" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS30" s="15" t="n"/>
       <c r="AT30" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU30" s="15" t="n"/>
-      <c r="AV30" s="18">
-        <f>IF(AU30&lt;&gt;"","No – hold: "&amp;AU30,IF(AG30="","No – no confirmed London price per player",IF(AM30="","No – no email",IF(AO30="","No – no personalised email",IF(AS30&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX30" s="21" t="n"/>
-      <c r="AY30" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV30" s="20" t="n"/>
+      <c r="AW30" s="20" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="n">
@@ -7257,9 +7156,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG31" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG31" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH31" s="15" t="inlineStr">
         <is>
@@ -7290,17 +7190,18 @@
         <f>IF(V31&lt;&gt;"",V31,S31)</f>
         <v/>
       </c>
-      <c r="AN31" s="18">
-        <f>IF(AG31="","","A weekly 6-a-side pitch, 12 minutes from East Road")</f>
-        <v/>
+      <c r="AN31" s="15" t="inlineStr">
+        <is>
+          <t>Office football for the Push Gaming team</t>
+        </is>
       </c>
       <c r="AO31" s="19" t="inlineStr">
         <is>
           <t>Hi Push Gaming team,
-Congratulations on launching in the Alberta market this July — good momentum as the team keeps growing.
-We've a floodlit 3G pitch at Moreland School, just off Old Street, a 12-minute walk from East Road. There's a 6-a-side slot free on Monday 12 October at 18:00, or 19:00, and it can become your regular weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Shall I hold Monday for you?
+Congratulations on launching in the Alberta market this July, good momentum for the team.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 12-minute walk from your office on East Road.
+We're looking for someone at Push Gaming who enjoys football and could help start a weekly office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
+Would that be of interest to the team? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -7308,37 +7209,31 @@
       </c>
       <c r="AP31" s="19" t="inlineStr">
         <is>
-          <t>Following up on Monday 12 October — the 6-a-side slot at Moreland School (18:00 or 19:00) is still free, 12 minutes from East Road. It's {PRICE} a player, and we handle the pitch booking and payments. Would this work as your weekly game?
+          <t>Hi Push Gaming team,
+Just following up on my note below about a weekly kickabout near East Road. Would that be of interest to the team, or could you point me to whoever looks after staff socials?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ31" s="20">
-        <f>IF(OR(AG31="",AO31=""),"",SUBSTITUTE(AO31,"{PRICE}","£"&amp;IF(AG31=INT(AG31),TEXT(AG31,"0"),TEXT(AG31,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR31" s="20">
-        <f>IF(OR(AG31="",AP31=""),"",SUBSTITUTE(AP31,"{PRICE}","£"&amp;IF(AG31=INT(AG31),TEXT(AG31,"0"),TEXT(AG31,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS31" s="15" t="inlineStr">
+      <c r="AQ31" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR31" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS31" s="15" t="n"/>
       <c r="AT31" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU31" s="15" t="n"/>
-      <c r="AV31" s="18">
-        <f>IF(AU31&lt;&gt;"","No – hold: "&amp;AU31,IF(AG31="","No – no confirmed London price per player",IF(AM31="","No – no email",IF(AO31="","No – no personalised email",IF(AS31&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX31" s="21" t="n"/>
-      <c r="AY31" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV31" s="20" t="n"/>
+      <c r="AW31" s="20" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="n">
@@ -7473,9 +7368,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG32" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG32" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH32" s="15" t="inlineStr">
         <is>
@@ -7506,17 +7402,18 @@
         <f>IF(V32&lt;&gt;"",V32,S32)</f>
         <v/>
       </c>
-      <c r="AN32" s="18">
-        <f>IF(AG32="","","A weekly 5-a-side game, 13 minutes from Finsbury Ave")</f>
-        <v/>
+      <c r="AN32" s="15" t="inlineStr">
+        <is>
+          <t>A football game for the Oliver Bernard team?</t>
+        </is>
       </c>
       <c r="AO32" s="19" t="inlineStr">
         <is>
           <t>Hi Oliver Bernard team,
-Forty-five of you running regular meetups and roundtables for the tech community — sounds like a group that likes getting together.
-We've a 5-a-side pitch at Powerleague Shoreditch, a 13-minute walk from Finsbury Avenue. There's a slot free on Monday 28 September at 17:40, or 19:40, and it can become your regular weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Shall I hold Monday for you?
+With 45 of you running regular tech meetups and roundtables, it sounds like a team that enjoys getting together.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 13-minute walk from your office on Finsbury Avenue.
+We're looking for someone at Oliver Bernard who'd enjoy helping start a regular team game, or even a friendly competition against other firms. We handle the pitch, extra players if you're short, payments and organisation.
+Would that be of interest to the team? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -7524,37 +7421,31 @@
       </c>
       <c r="AP32" s="19" t="inlineStr">
         <is>
-          <t>Checking in on Monday 28 September — the 5-a-side slot at Powerleague Shoreditch (17:40 or 19:40) is still open, or Thursday 1 October at 18:20. It's {PRICE} a player, and we handle booking and payments. Keen to get the team a regular weekly game.
+          <t>Hi Oliver Bernard team,
+Just following up on my note below about a regular team game near Finsbury Avenue. Would that be of interest, or could you point me to whoever looks after staff socials?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ32" s="20">
-        <f>IF(OR(AG32="",AO32=""),"",SUBSTITUTE(AO32,"{PRICE}","£"&amp;IF(AG32=INT(AG32),TEXT(AG32,"0"),TEXT(AG32,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR32" s="20">
-        <f>IF(OR(AG32="",AP32=""),"",SUBSTITUTE(AP32,"{PRICE}","£"&amp;IF(AG32=INT(AG32),TEXT(AG32,"0"),TEXT(AG32,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS32" s="15" t="inlineStr">
+      <c r="AQ32" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR32" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS32" s="15" t="n"/>
       <c r="AT32" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU32" s="15" t="n"/>
-      <c r="AV32" s="18">
-        <f>IF(AU32&lt;&gt;"","No – hold: "&amp;AU32,IF(AG32="","No – no confirmed London price per player",IF(AM32="","No – no email",IF(AO32="","No – no personalised email",IF(AS32&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX32" s="21" t="n"/>
-      <c r="AY32" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV32" s="20" t="n"/>
+      <c r="AW32" s="20" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="15" t="n">
@@ -7689,9 +7580,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG33" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG33" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH33" s="15" t="inlineStr">
         <is>
@@ -7722,14 +7614,18 @@
         <f>IF(V33&lt;&gt;"",V33,S33)</f>
         <v/>
       </c>
-      <c r="AN33" s="18">
-        <f>IF(AG33="","","5 min from Berry Place: a weekly team game")</f>
-        <v/>
+      <c r="AN33" s="15" t="inlineStr">
+        <is>
+          <t>A football game for the Wellcom studio?</t>
+        </is>
       </c>
       <c r="AO33" s="19" t="inlineStr">
         <is>
           <t>Hi Wellcom London team,
-Your Clerkenwell studio has been the set for Ben &amp; Jerry's shoots since 2022 — proof the team knows how to turn a shared space into something fun. We've got a floodlit 3G pitch at Moreland School, Gard Street, just a 5-minute walk from Berry Place, with Monday 12 October at 18:00 open (or 19:00), and it can easily become your regular weekly slot. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Shall I hold Monday for you?
+Your Clerkenwell studio has been the set for Ben &amp; Jerry's shoots since 2022, proof the team knows how to turn a shared space into something fun.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 5-minute walk from your office on Berry Place.
+We're looking for someone at Wellcom London who enjoys football and could help start a weekly kickabout for the studio. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest, or could you point us to whoever's best placed to look into it?
 Best,
 Brian
 FC Urban</t>
@@ -7738,37 +7634,30 @@
       <c r="AP33" s="19" t="inlineStr">
         <is>
           <t>Hi Wellcom London team,
-Following up on Monday 12 October at 18:00 (or 19:00) at Moreland School — a 5-minute walk from Berry Place. Still {PRICE} a player, we handle the pitch, sign-ups and payments. Would you like me to hold a slot for the team's first game?
+Just following up on my note below about a weekly kickabout near Berry Place. Would there be any interest, or could you point us to whoever's best placed to look into it?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ33" s="20">
-        <f>IF(OR(AG33="",AO33=""),"",SUBSTITUTE(AO33,"{PRICE}","£"&amp;IF(AG33=INT(AG33),TEXT(AG33,"0"),TEXT(AG33,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR33" s="20">
-        <f>IF(OR(AG33="",AP33=""),"",SUBSTITUTE(AP33,"{PRICE}","£"&amp;IF(AG33=INT(AG33),TEXT(AG33,"0"),TEXT(AG33,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS33" s="15" t="inlineStr">
+      <c r="AQ33" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR33" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS33" s="15" t="n"/>
       <c r="AT33" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU33" s="15" t="n"/>
-      <c r="AV33" s="18">
-        <f>IF(AU33&lt;&gt;"","No – hold: "&amp;AU33,IF(AG33="","No – no confirmed London price per player",IF(AM33="","No – no email",IF(AO33="","No – no personalised email",IF(AS33&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX33" s="21" t="n"/>
-      <c r="AY33" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV33" s="20" t="n"/>
+      <c r="AW33" s="20" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="15" t="n">
@@ -7899,9 +7788,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG34" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG34" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH34" s="15" t="inlineStr">
         <is>
@@ -7932,14 +7822,18 @@
         <f>IF(V34&lt;&gt;"",V34,S34)</f>
         <v/>
       </c>
-      <c r="AN34" s="18">
-        <f>IF(AG34="","","A new club for the Mentioneers: football")</f>
-        <v/>
+      <c r="AN34" s="15" t="inlineStr">
+        <is>
+          <t>A football group for the Mentioneers?</t>
+        </is>
       </c>
       <c r="AO34" s="19" t="inlineStr">
         <is>
           <t>Hi Mention Me team,
-You've already got running and poker clubs for the Mentioneers, so a weekly five-a-side felt like an easy addition. We've got the floodlit 3G pitch at Moreland School, Gard Street, a 6-minute walk from your office, with Monday 12 October at 18:00 open (or 19:00), and it can become your regular slot. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Would your team be up for it?
+Mentioneers already run their own clubs, from running to poker and board games, plus quarterly socials and monthly pub drinks, sounds like a team that would enjoy a regular match too.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 6-minute walk from your office.
+We're looking for someone at Mention Me who enjoys football and could help start a weekly office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest, or could you point us to whoever's best placed to look into it?
 Best,
 Brian
 FC Urban</t>
@@ -7948,37 +7842,30 @@
       <c r="AP34" s="19" t="inlineStr">
         <is>
           <t>Hi Mention Me team,
-Following up on Monday 12 October at 18:00 (or 19:00) at Moreland School, 6 minutes from your office. Still {PRICE} a player, we handle the pitch, sign-ups and payments. Shall I hold a slot for the Mentioneers?
+Just following up on my note below about a weekly kickabout for the Mentioneers. Would there be any interest, or could you point us to whoever's best placed to look into it?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ34" s="20">
-        <f>IF(OR(AG34="",AO34=""),"",SUBSTITUTE(AO34,"{PRICE}","£"&amp;IF(AG34=INT(AG34),TEXT(AG34,"0"),TEXT(AG34,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR34" s="20">
-        <f>IF(OR(AG34="",AP34=""),"",SUBSTITUTE(AP34,"{PRICE}","£"&amp;IF(AG34=INT(AG34),TEXT(AG34,"0"),TEXT(AG34,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS34" s="15" t="inlineStr">
+      <c r="AQ34" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR34" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS34" s="15" t="n"/>
       <c r="AT34" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU34" s="15" t="n"/>
-      <c r="AV34" s="18">
-        <f>IF(AU34&lt;&gt;"","No – hold: "&amp;AU34,IF(AG34="","No – no confirmed London price per player",IF(AM34="","No – no email",IF(AO34="","No – no personalised email",IF(AS34&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX34" s="21" t="n"/>
-      <c r="AY34" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV34" s="20" t="n"/>
+      <c r="AW34" s="20" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="15" t="n">
@@ -8125,9 +8012,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG35" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG35" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH35" s="15" t="inlineStr">
         <is>
@@ -8158,14 +8046,18 @@
         <f>IF(V35&lt;&gt;"",V35,S35)</f>
         <v/>
       </c>
-      <c r="AN35" s="18">
-        <f>IF(AG35="","","7 min from Primrose Street: a weekly 5-a-side")</f>
-        <v/>
+      <c r="AN35" s="15" t="inlineStr">
+        <is>
+          <t>A regular football game for Oakleaf?</t>
+        </is>
       </c>
       <c r="AO35" s="19" t="inlineStr">
         <is>
           <t>Hi Simon,
-Oakleaf's been placing people internationally since 2005 — 21 years of building teams across 80+ firms, so you know what a good team looks like. We've got a 5-a-side pitch at Powerleague Shoreditch, a 7-minute walk from Primrose Street, with Monday 28 September at 17:40 open (or 19:40), and it can turn into your regular weekly slot. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Shall I hold Monday for you?
+Oakleaf has been building teams internationally since 2005, with 1,400-plus placements across 80-plus firms in 16 countries.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 7-minute walk from your office on Primrose Street.
+We're looking for someone at Oakleaf who'd enjoy helping start a regular after-work game for colleagues, or perhaps a friendly against another firm nearby. We handle the pitch, extra players if you're short, payments and organisation.
+Would you be up for it, or is there someone else better placed to run with it? Either way, feel free to forward this on to whoever looks after socials for the team.
 Best,
 Brian
 FC Urban</t>
@@ -8174,37 +8066,30 @@
       <c r="AP35" s="19" t="inlineStr">
         <is>
           <t>Hi Simon,
-Following up on Monday 28 September at 17:40 (or 19:40) at Powerleague Shoreditch — 7 minutes from Primrose Street. Still {PRICE} a player, we sort the pitch, sign-ups and payments. Want me to hold a slot for the Oakleaf team?
+Just following up on my note below about a regular after-work game for the Oakleaf team. Would you be up for it, or is there someone else better placed to run with it?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ35" s="20">
-        <f>IF(OR(AG35="",AO35=""),"",SUBSTITUTE(AO35,"{PRICE}","£"&amp;IF(AG35=INT(AG35),TEXT(AG35,"0"),TEXT(AG35,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR35" s="20">
-        <f>IF(OR(AG35="",AP35=""),"",SUBSTITUTE(AP35,"{PRICE}","£"&amp;IF(AG35=INT(AG35),TEXT(AG35,"0"),TEXT(AG35,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS35" s="15" t="inlineStr">
+      <c r="AQ35" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR35" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS35" s="15" t="n"/>
       <c r="AT35" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU35" s="15" t="n"/>
-      <c r="AV35" s="18">
-        <f>IF(AU35&lt;&gt;"","No – hold: "&amp;AU35,IF(AG35="","No – no confirmed London price per player",IF(AM35="","No – no email",IF(AO35="","No – no personalised email",IF(AS35&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX35" s="21" t="n"/>
-      <c r="AY35" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV35" s="20" t="n"/>
+      <c r="AW35" s="20" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="15" t="n">
@@ -8347,9 +8232,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG36" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG36" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH36" s="15" t="inlineStr">
         <is>
@@ -8380,14 +8266,18 @@
         <f>IF(V36&lt;&gt;"",V36,S36)</f>
         <v/>
       </c>
-      <c r="AN36" s="18">
-        <f>IF(AG36="","","10 min from Paul Street: a weekly five-a-side")</f>
-        <v/>
+      <c r="AN36" s="15" t="inlineStr">
+        <is>
+          <t>A football group for the Hoptroff team?</t>
+        </is>
       </c>
       <c r="AO36" s="19" t="inlineStr">
         <is>
           <t>Hi Tyler,
-Since the LSEG partnership landed in December, it sounds like the Hoptroff team has had plenty to celebrate — a five-a-side might be a good excuse for another one. We've got a pitch at Powerleague Shoreditch, a 10-minute walk from Paul Street, with Monday 28 September at 17:40 open (or 19:40), and it can turn into your regular weekly game. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Would your team be up for it?
+Since the LSEG partnership landed in December, it sounds like the Hoptroff team has had plenty to celebrate.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 10-minute walk from your office on Paul Street.
+We're looking for someone at Hoptroff who enjoys football and could help start a weekly office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
+Would you be up for it, or is there someone else better placed to run with it? Either way, feel free to forward this on to whoever looks after socials for the team.
 Best,
 Brian
 FC Urban</t>
@@ -8396,37 +8286,30 @@
       <c r="AP36" s="19" t="inlineStr">
         <is>
           <t>Hi Tyler,
-Following up on Monday 28 September at 17:40 (or 19:40) at Powerleague Shoreditch, 10 minutes from Paul Street. Still {PRICE} a player, we handle the pitch, sign-ups and payments. Shall I hold a slot for the team?
+Just following up on my note below about a weekly kickabout for the Hoptroff team. Would you be up for it, or is there someone else better placed to look into it?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ36" s="20">
-        <f>IF(OR(AG36="",AO36=""),"",SUBSTITUTE(AO36,"{PRICE}","£"&amp;IF(AG36=INT(AG36),TEXT(AG36,"0"),TEXT(AG36,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR36" s="20">
-        <f>IF(OR(AG36="",AP36=""),"",SUBSTITUTE(AP36,"{PRICE}","£"&amp;IF(AG36=INT(AG36),TEXT(AG36,"0"),TEXT(AG36,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS36" s="15" t="inlineStr">
+      <c r="AQ36" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR36" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS36" s="15" t="n"/>
       <c r="AT36" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU36" s="15" t="n"/>
-      <c r="AV36" s="18">
-        <f>IF(AU36&lt;&gt;"","No – hold: "&amp;AU36,IF(AG36="","No – no confirmed London price per player",IF(AM36="","No – no email",IF(AO36="","No – no personalised email",IF(AS36&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX36" s="21" t="n"/>
-      <c r="AY36" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV36" s="20" t="n"/>
+      <c r="AW36" s="20" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="15" t="n">
@@ -8567,9 +8450,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG37" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG37" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH37" s="15" t="inlineStr">
         <is>
@@ -8600,17 +8484,18 @@
         <f>IF(V37&lt;&gt;"",V37,S37)</f>
         <v/>
       </c>
-      <c r="AN37" s="18">
-        <f>IF(AG37="","","A weekly 5-a-side near Christopher Street?")</f>
-        <v/>
+      <c r="AN37" s="15" t="inlineStr">
+        <is>
+          <t>A regular football game for Stanton House?</t>
+        </is>
       </c>
       <c r="AO37" s="19" t="inlineStr">
         <is>
           <t>Hi Melanie,
-Stanton House's team has grown past 50 professionals since you started the consultancy in 2010, which is a good size for a weekly game.
-We've a 5-a-side pitch at Powerleague Shoreditch, Braithwaite Street, E1 6GJ, a 10-minute walk from your Christopher Street office, with slots free Monday 28 September at 17:40 or 19:40. It could become your regular weekly fixture.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Would your team be up for it?
+Stanton House's team has grown past 50 professionals since you started the consultancy in 2010.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 10-minute walk from your office on Christopher Street.
+We're looking for someone at Stanton House who'd enjoy helping start a regular team game, or even a friendly against another firm. We handle the pitch, extra players if you're short, payments and organisation.
+Would you be up for it, or is there someone else better placed to run with it? Either way, feel free to forward this on to whoever looks after socials for the team.
 Best,
 Brian
 FC Urban</t>
@@ -8619,37 +8504,30 @@
       <c r="AP37" s="19" t="inlineStr">
         <is>
           <t>Hi Melanie,
-Following up on the 5-a-side at Powerleague Shoreditch. Monday 28 September at 17:40 or 19:40 is still open, or Thursday 1 October at 18:20. It's {PRICE} a player, one link for the team, and we sort the rest.
+Just following up on my note below about a regular team game for Stanton House. Would you be up for it, or is there someone else better placed to run with it?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ37" s="20">
-        <f>IF(OR(AG37="",AO37=""),"",SUBSTITUTE(AO37,"{PRICE}","£"&amp;IF(AG37=INT(AG37),TEXT(AG37,"0"),TEXT(AG37,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR37" s="20">
-        <f>IF(OR(AG37="",AP37=""),"",SUBSTITUTE(AP37,"{PRICE}","£"&amp;IF(AG37=INT(AG37),TEXT(AG37,"0"),TEXT(AG37,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS37" s="15" t="inlineStr">
+      <c r="AQ37" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR37" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS37" s="15" t="n"/>
       <c r="AT37" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU37" s="15" t="n"/>
-      <c r="AV37" s="18">
-        <f>IF(AU37&lt;&gt;"","No – hold: "&amp;AU37,IF(AG37="","No – no confirmed London price per player",IF(AM37="","No – no email",IF(AO37="","No – no personalised email",IF(AS37&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX37" s="21" t="n"/>
-      <c r="AY37" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV37" s="20" t="n"/>
+      <c r="AW37" s="20" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="15" t="n">
@@ -8784,9 +8662,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG38" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG38" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH38" s="15" t="inlineStr">
         <is>
@@ -8817,17 +8696,18 @@
         <f>IF(V38&lt;&gt;"",V38,S38)</f>
         <v/>
       </c>
-      <c r="AN38" s="18">
-        <f>IF(AG38="","","5-a-side near St Mary Axe for Travelfusion?")</f>
-        <v/>
+      <c r="AN38" s="15" t="inlineStr">
+        <is>
+          <t>Office football for the Travelfusion team</t>
+        </is>
       </c>
       <c r="AO38" s="19" t="inlineStr">
         <is>
           <t>Hi Travelfusion team,
-Your careers page promises a comfortable, friendly work environment with flexible hours, which sounds like a team that would enjoy playing together after work.
-We've a 5-a-side pitch at Powerleague Shoreditch, Braithwaite Street, E1 6GJ, a 15-minute walk from 70 St Mary Axe, with slots free Monday 28 September at 17:40 or 19:40. It could become your regular weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Would your team be up for it?
+Your careers page promises a comfortable, friendly work environment with flexible hours, sounds like a team that would enjoy playing together after work.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 15-minute walk from your office on St Mary Axe.
+We're looking for someone at Travelfusion who enjoys football and could help start a weekly office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -8836,37 +8716,30 @@
       <c r="AP38" s="19" t="inlineStr">
         <is>
           <t>Hi Travelfusion team,
-Following up on the 5-a-side at Powerleague Shoreditch. Monday 28 September at 17:40 or 19:40 is still open, or Thursday 1 October at 18:20. It's {PRICE} a player, one link for the team, and we handle the rest.
+Just following up on my note below about a weekly kickabout near St Mary Axe. Would there be any interest, or could you point me to whoever looks after staff socials?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ38" s="20">
-        <f>IF(OR(AG38="",AO38=""),"",SUBSTITUTE(AO38,"{PRICE}","£"&amp;IF(AG38=INT(AG38),TEXT(AG38,"0"),TEXT(AG38,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR38" s="20">
-        <f>IF(OR(AG38="",AP38=""),"",SUBSTITUTE(AP38,"{PRICE}","£"&amp;IF(AG38=INT(AG38),TEXT(AG38,"0"),TEXT(AG38,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS38" s="15" t="inlineStr">
+      <c r="AQ38" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR38" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS38" s="15" t="n"/>
       <c r="AT38" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU38" s="15" t="n"/>
-      <c r="AV38" s="18">
-        <f>IF(AU38&lt;&gt;"","No – hold: "&amp;AU38,IF(AG38="","No – no confirmed London price per player",IF(AM38="","No – no email",IF(AO38="","No – no personalised email",IF(AS38&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX38" s="21" t="n"/>
-      <c r="AY38" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV38" s="20" t="n"/>
+      <c r="AW38" s="20" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="15" t="n">
@@ -9013,9 +8886,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG39" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG39" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH39" s="15" t="inlineStr">
         <is>
@@ -9042,17 +8916,18 @@
         <f>IF(V39&lt;&gt;"",V39,S39)</f>
         <v/>
       </c>
-      <c r="AN39" s="18">
-        <f>IF(AG39="","","Weekly football, 10 minutes from Paul Street")</f>
-        <v/>
+      <c r="AN39" s="15" t="inlineStr">
+        <is>
+          <t>A team game for Simply Education?</t>
+        </is>
       </c>
       <c r="AO39" s="19" t="inlineStr">
         <is>
           <t>Hi Hollie,
-Running recruitment across 18 counties from 6 offices takes a lot of running around -- a weekly game near base might be a nice change of pace.
-We've a 5-a-side pitch at Powerleague Shoreditch, Braithwaite Street, a 10-minute walk from Paul Street. There's a slot free Monday 28 September at 17:40, or 19:40, and it could become your regular weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Would your team be up for it?
+Running recruitment across 18 counties from six offices takes a lot of running around, a regular game closer to base might be a nice change of pace.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 10-minute walk from your office on Paul Street.
+We're looking for someone at Simply Education who'd enjoy helping start a regular team game, or even a friendly against another firm. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -9061,37 +8936,30 @@
       <c r="AP39" s="19" t="inlineStr">
         <is>
           <t>Hi Hollie,
-Following up on the five-a-side slot at Powerleague Shoreditch, 10 minutes from Paul Street. Thursday 1 October at 18:20 is still open. It's {PRICE} a player, and we handle the booking and payments, so it's one link for the team. Worth a try?
+Just following up on my note below about a regular team game near Paul Street. Would there be any interest, or could you point me to whoever looks after staff socials?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ39" s="20">
-        <f>IF(OR(AG39="",AO39=""),"",SUBSTITUTE(AO39,"{PRICE}","£"&amp;IF(AG39=INT(AG39),TEXT(AG39,"0"),TEXT(AG39,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR39" s="20">
-        <f>IF(OR(AG39="",AP39=""),"",SUBSTITUTE(AP39,"{PRICE}","£"&amp;IF(AG39=INT(AG39),TEXT(AG39,"0"),TEXT(AG39,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS39" s="15" t="inlineStr">
+      <c r="AQ39" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR39" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS39" s="15" t="n"/>
       <c r="AT39" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU39" s="15" t="n"/>
-      <c r="AV39" s="18">
-        <f>IF(AU39&lt;&gt;"","No – hold: "&amp;AU39,IF(AG39="","No – no confirmed London price per player",IF(AM39="","No – no email",IF(AO39="","No – no personalised email",IF(AS39&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX39" s="21" t="n"/>
-      <c r="AY39" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV39" s="20" t="n"/>
+      <c r="AW39" s="20" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="15" t="n">
@@ -9238,9 +9106,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG40" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG40" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH40" s="15" t="inlineStr">
         <is>
@@ -9267,17 +9136,18 @@
         <f>IF(V40&lt;&gt;"",V40,S40)</f>
         <v/>
       </c>
-      <c r="AN40" s="18">
-        <f>IF(AG40="","","Football 10 minutes from Bonhill Street")</f>
-        <v/>
+      <c r="AN40" s="15" t="inlineStr">
+        <is>
+          <t>A football group for the Ecodriver team?</t>
+        </is>
       </c>
       <c r="AO40" s="19" t="inlineStr">
         <is>
           <t>Hi Jamie,
-You've spent years helping organisations cut their carbon output, since building the first ecoDriver in 2007. A weekly game is a much simpler way to cut down on screen time.
-We've a 5-a-side pitch at Powerleague Shoreditch, Braithwaite Street, a 10-minute walk from Bonhill Street. There's a slot free Monday 28 September at 17:40, or 19:40, and it could become your regular weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Shall I hold Monday for you?
+You built the first version of ecoDriver back in 2007 and won a Microsoft award for it, quite a foundation to have built the business on.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 10-minute walk from your office on Bonhill Street.
+We're looking for someone at Ecodriver who enjoys football and could help start a weekly office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -9286,37 +9156,30 @@
       <c r="AP40" s="19" t="inlineStr">
         <is>
           <t>Hi Jamie,
-Still holding the five-a-side slot at Powerleague Shoreditch, 10 minutes from Bonhill Street. Thursday 1 October at 18:20 is free. It's {PRICE} a player, and we handle the booking and payments, so it's one link for the team. Worth a go?
+Just following up on my note below about a weekly kickabout near Bonhill Street. Would there be any interest, or could you point me to whoever looks after staff socials?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ40" s="20">
-        <f>IF(OR(AG40="",AO40=""),"",SUBSTITUTE(AO40,"{PRICE}","£"&amp;IF(AG40=INT(AG40),TEXT(AG40,"0"),TEXT(AG40,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR40" s="20">
-        <f>IF(OR(AG40="",AP40=""),"",SUBSTITUTE(AP40,"{PRICE}","£"&amp;IF(AG40=INT(AG40),TEXT(AG40,"0"),TEXT(AG40,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS40" s="15" t="inlineStr">
+      <c r="AQ40" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR40" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS40" s="15" t="n"/>
       <c r="AT40" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU40" s="15" t="n"/>
-      <c r="AV40" s="18">
-        <f>IF(AU40&lt;&gt;"","No – hold: "&amp;AU40,IF(AG40="","No – no confirmed London price per player",IF(AM40="","No – no email",IF(AO40="","No – no personalised email",IF(AS40&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX40" s="21" t="n"/>
-      <c r="AY40" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV40" s="20" t="n"/>
+      <c r="AW40" s="20" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="15" t="n">
@@ -9459,9 +9322,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG41" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG41" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH41" s="15" t="inlineStr">
         <is>
@@ -9492,16 +9356,18 @@
         <f>IF(V41&lt;&gt;"",V41,S41)</f>
         <v/>
       </c>
-      <c r="AN41" s="18">
-        <f>IF(AG41="","","5-a-side near E2 6AH, good for team wellbeing")</f>
-        <v/>
+      <c r="AN41" s="15" t="inlineStr">
+        <is>
+          <t>A football group for the TestingXperts team?</t>
+        </is>
       </c>
       <c r="AO41" s="19" t="inlineStr">
         <is>
           <t>Hi Manish,
-We noticed TestingXperts runs customised wellness programmes for the team, a weekly game is a nice way to put that into practice together. We've got a 5-a-side pitch at Powerleague Shoreditch, a 13-minute walk from your E2 6AH office, with a slot free Monday 28 September at 17:40, or 19:40 if evenings suit better. It could easily become a regular weekly fixture.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Would your team be up for it?
+It's great to see TestingXperts running customised wellness programmes, with staff wellbeing clearly core to how the team works.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 13-minute walk from your office in E2 6AH.
+We're looking for someone at TestingXperts who enjoys football and could help start a weekly office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -9510,37 +9376,30 @@
       <c r="AP41" s="19" t="inlineStr">
         <is>
           <t>Hi Manish,
-Following up on the Shoreditch pitch. Monday's slot has gone, but Thursday 1 October at 18:20 is still open, 13 minutes from your E2 6AH office. It's {PRICE} a player, and we handle booking and payments. Good fit alongside your wellness programmes, shall I hold it?
+Just following up on my note below about a weekly kickabout for the TestingXperts team. Would there be any interest, or could you point me to whoever looks after staff socials?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ41" s="20">
-        <f>IF(OR(AG41="",AO41=""),"",SUBSTITUTE(AO41,"{PRICE}","£"&amp;IF(AG41=INT(AG41),TEXT(AG41,"0"),TEXT(AG41,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR41" s="20">
-        <f>IF(OR(AG41="",AP41=""),"",SUBSTITUTE(AP41,"{PRICE}","£"&amp;IF(AG41=INT(AG41),TEXT(AG41,"0"),TEXT(AG41,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS41" s="15" t="inlineStr">
+      <c r="AQ41" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR41" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS41" s="15" t="n"/>
       <c r="AT41" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU41" s="15" t="n"/>
-      <c r="AV41" s="18">
-        <f>IF(AU41&lt;&gt;"","No – hold: "&amp;AU41,IF(AG41="","No – no confirmed London price per player",IF(AM41="","No – no email",IF(AO41="","No – no personalised email",IF(AS41&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX41" s="21" t="n"/>
-      <c r="AY41" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV41" s="20" t="n"/>
+      <c r="AW41" s="20" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="15" t="n">
@@ -9683,9 +9542,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG42" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG42" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH42" s="15" t="inlineStr">
         <is>
@@ -9716,16 +9576,18 @@
         <f>IF(V42&lt;&gt;"",V42,S42)</f>
         <v/>
       </c>
-      <c r="AN42" s="18">
-        <f>IF(AG42="","","Fenergo's RiskTech100 win, and a 5-a-side pitch")</f>
-        <v/>
+      <c r="AN42" s="15" t="inlineStr">
+        <is>
+          <t>A football group for the Fenergo team?</t>
+        </is>
       </c>
       <c r="AO42" s="19" t="inlineStr">
         <is>
           <t>Hi Marc,
-Congratulations on the three category wins in the Chartis RiskTech100 2027 rankings, good moment to get the team together. We've got a 5-a-side pitch at Powerleague Shoreditch, a 14-minute walk from your EC2M 7LS office, with a slot free Monday 28 September at 17:40, or 19:40 if evenings suit better. It could become a regular weekly fixture for Fenergo.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Would your team be up for it?
+Congratulations on Fenergo's three category wins in the Chartis RiskTech100 2027 rankings, a great moment for the team.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 14-minute walk from your office in EC2M 7LS.
+We're looking for someone at Fenergo who enjoys football and could help start a weekly office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -9734,37 +9596,30 @@
       <c r="AP42" s="19" t="inlineStr">
         <is>
           <t>Hi Marc,
-Following up on the Shoreditch pitch. Monday's slot has gone, but Thursday 1 October at 18:20 is still free, 14 minutes from EC2M 7LS. It's {PRICE} a player, and we handle booking and payments. Good way to celebrate the RiskTech100 wins, shall I hold it?
+Just following up on my note below about a weekly kickabout for the Fenergo team. Would there be any interest, or could you point me to whoever looks after staff socials?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ42" s="20">
-        <f>IF(OR(AG42="",AO42=""),"",SUBSTITUTE(AO42,"{PRICE}","£"&amp;IF(AG42=INT(AG42),TEXT(AG42,"0"),TEXT(AG42,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR42" s="20">
-        <f>IF(OR(AG42="",AP42=""),"",SUBSTITUTE(AP42,"{PRICE}","£"&amp;IF(AG42=INT(AG42),TEXT(AG42,"0"),TEXT(AG42,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS42" s="15" t="inlineStr">
+      <c r="AQ42" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR42" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS42" s="15" t="n"/>
       <c r="AT42" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU42" s="15" t="n"/>
-      <c r="AV42" s="18">
-        <f>IF(AU42&lt;&gt;"","No – hold: "&amp;AU42,IF(AG42="","No – no confirmed London price per player",IF(AM42="","No – no email",IF(AO42="","No – no personalised email",IF(AS42&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX42" s="21" t="n"/>
-      <c r="AY42" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV42" s="20" t="n"/>
+      <c r="AW42" s="20" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="15" t="n">
@@ -9911,9 +9766,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG43" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG43" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH43" s="15" t="inlineStr">
         <is>
@@ -9944,14 +9800,18 @@
         <f>IF(V43&lt;&gt;"",V43,S43)</f>
         <v/>
       </c>
-      <c r="AN43" s="18">
-        <f>IF(AG43="","","A weekly 6-a-side, 14 min from Pine Street")</f>
-        <v/>
+      <c r="AN43" s="15" t="inlineStr">
+        <is>
+          <t>Football for the Fluence Energy team</t>
+        </is>
       </c>
       <c r="AO43" s="19" t="inlineStr">
         <is>
           <t>Hi Julian,
-Building the battery storage technology that's helping power the clean energy transition is demanding work — the kind of team that could use a regular outlet together. We've got a floodlit 3G pitch at Moreland School, Gard Street, EC1V 8DW, about a 14-minute walk from your Pine Street office. There's a slot open Monday 12 October at 18:00 (6-a-side), or 19:00 if that suits better, and it could easily become your weekly game. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Shall I hold the Monday slot for you?
+Building the battery storage technology that's helping power the clean energy transition sounds like demanding work, and a regular game can be a good outlet for the team.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 14-minute walk from your office on Pine Street.
+We're looking for someone at Fluence Energy who'd enjoy starting a regular office kickabout for colleagues - we handle the pitch, extra players if short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -9960,37 +9820,30 @@
       <c r="AP43" s="19" t="inlineStr">
         <is>
           <t>Hi Julian,
-Just following up on the 6-a-side slot at Moreland School — Monday 12 October at 18:00 is still open, or 19:00 works too. It's {PRICE} a player and easy to set up as a regular fixture; we handle the booking and payments. Let me know if you'd like it held.
+Just following up on my note about setting up a regular football game for the Fluence Energy team near your Pine Street office. No pressure at all - if it's of interest, or if there's someone better placed to ask, let me know.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ43" s="20">
-        <f>IF(OR(AG43="",AO43=""),"",SUBSTITUTE(AO43,"{PRICE}","£"&amp;IF(AG43=INT(AG43),TEXT(AG43,"0"),TEXT(AG43,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR43" s="20">
-        <f>IF(OR(AG43="",AP43=""),"",SUBSTITUTE(AP43,"{PRICE}","£"&amp;IF(AG43=INT(AG43),TEXT(AG43,"0"),TEXT(AG43,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS43" s="15" t="inlineStr">
+      <c r="AQ43" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR43" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS43" s="15" t="n"/>
       <c r="AT43" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU43" s="15" t="n"/>
-      <c r="AV43" s="18">
-        <f>IF(AU43&lt;&gt;"","No – hold: "&amp;AU43,IF(AG43="","No – no confirmed London price per player",IF(AM43="","No – no email",IF(AO43="","No – no personalised email",IF(AS43&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX43" s="21" t="n"/>
-      <c r="AY43" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV43" s="20" t="n"/>
+      <c r="AW43" s="20" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="15" t="n">
@@ -10121,9 +9974,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG44" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG44" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH44" s="15" t="inlineStr">
         <is>
@@ -10154,14 +10008,18 @@
         <f>IF(V44&lt;&gt;"",V44,S44)</f>
         <v/>
       </c>
-      <c r="AN44" s="18">
-        <f>IF(AG44="","","3 minutes from your office: weekly 5-a-side")</f>
-        <v/>
+      <c r="AN44" s="15" t="inlineStr">
+        <is>
+          <t>Football 3 minutes from Vendavo's office</t>
+        </is>
       </c>
       <c r="AO44" s="19" t="inlineStr">
         <is>
           <t>Hi Vendavo team,
-Saw the news about Vendavo's July acquisition of Model N's high-tech business unit — sounds like a busy stretch, and a regular game could be a good way for the team to unwind. We've got a 5-a-side pitch at Powerleague Shoreditch, Braithwaite Street, E1 6GJ, just a 3-minute walk from your office. There's a slot open Monday 28 September at 17:40, or 19:40 if that's easier, and it could become your weekly fixture. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Would your team be up for it?
+Congratulations on the July acquisition of Model N's high-tech business unit - sounds like a busy stretch, and a regular game can be a good way for everyone to unwind together.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), just a 3-minute walk from your office.
+We're looking for someone at Vendavo who'd enjoy helping start a regular office kickabout for the team - we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -10170,37 +10028,30 @@
       <c r="AP44" s="19" t="inlineStr">
         <is>
           <t>Hi Vendavo team,
-Following up on the 5-a-side slot at Powerleague Shoreditch, just round the corner from you — Monday 28 September at 17:40 is still open, or Thursday 1 October at 18:20. It's {PRICE} a player; we handle the booking and payments. Let me know if you'd like it held.
+Just checking back on my note about a regular football game for the team, a few minutes' walk from your office. No pressure - if there's interest, or someone else better placed to ask, just let me know or forward it on.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ44" s="20">
-        <f>IF(OR(AG44="",AO44=""),"",SUBSTITUTE(AO44,"{PRICE}","£"&amp;IF(AG44=INT(AG44),TEXT(AG44,"0"),TEXT(AG44,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR44" s="20">
-        <f>IF(OR(AG44="",AP44=""),"",SUBSTITUTE(AP44,"{PRICE}","£"&amp;IF(AG44=INT(AG44),TEXT(AG44,"0"),TEXT(AG44,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS44" s="15" t="inlineStr">
+      <c r="AQ44" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR44" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS44" s="15" t="n"/>
       <c r="AT44" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU44" s="15" t="n"/>
-      <c r="AV44" s="18">
-        <f>IF(AU44&lt;&gt;"","No – hold: "&amp;AU44,IF(AG44="","No – no confirmed London price per player",IF(AM44="","No – no email",IF(AO44="","No – no personalised email",IF(AS44&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX44" s="21" t="n"/>
-      <c r="AY44" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV44" s="20" t="n"/>
+      <c r="AW44" s="20" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="15" t="n">
@@ -10335,9 +10186,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG45" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG45" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH45" s="15" t="inlineStr">
         <is>
@@ -10368,14 +10220,18 @@
         <f>IF(V45&lt;&gt;"",V45,S45)</f>
         <v/>
       </c>
-      <c r="AN45" s="18">
-        <f>IF(AG45="","","4 minutes from Elder Street: weekly 5-a-side")</f>
-        <v/>
+      <c r="AN45" s="15" t="inlineStr">
+        <is>
+          <t>Office football near Elder Street</t>
+        </is>
       </c>
       <c r="AO45" s="19" t="inlineStr">
         <is>
           <t>Hi Whitepaperco team,
-Between projects like the Scalpel and Fusion Group, your team clearly knows how to deliver under pressure — a weekly game could be a good release. We've got a 5-a-side pitch at Powerleague Shoreditch, Braithwaite Street, E1 6GJ, just a 4-minute walk from Elder Street. There's a slot open Monday 28 September at 17:40, or 19:40 if that's easier, and it could become your regular weekly fixture. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Would your team be up for it?
+Good to see the studio's recent projects across London, including the Scalpel and Fusion Group - a regular game could be a good way to switch off together.
+I'm Brian from FC Urban. We organise social football across London, and already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 4-minute walk from your office on Elder Street.
+We're looking for someone at Whitepaperco who'd enjoy starting a regular office kickabout for the team - we handle the pitch, extra players if short, payments and organisation.
+Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -10384,37 +10240,30 @@
       <c r="AP45" s="19" t="inlineStr">
         <is>
           <t>Hi Whitepaperco team,
-Following up on the 5-a-side slot at Powerleague Shoreditch, just down the road from Elder Street — Monday 28 September at 17:40 is still open, or Thursday 1 October at 18:20. It's {PRICE} a player; we handle the booking and payments. Let me know if you'd like it held.
+Just following up on my note about a regular football game a few minutes from your Elder Street office. No pressure - if there's interest, or someone else looks after staff socials, feel free to forward this on to them.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ45" s="20">
-        <f>IF(OR(AG45="",AO45=""),"",SUBSTITUTE(AO45,"{PRICE}","£"&amp;IF(AG45=INT(AG45),TEXT(AG45,"0"),TEXT(AG45,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR45" s="20">
-        <f>IF(OR(AG45="",AP45=""),"",SUBSTITUTE(AP45,"{PRICE}","£"&amp;IF(AG45=INT(AG45),TEXT(AG45,"0"),TEXT(AG45,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS45" s="15" t="inlineStr">
+      <c r="AQ45" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR45" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS45" s="15" t="n"/>
       <c r="AT45" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU45" s="15" t="n"/>
-      <c r="AV45" s="18">
-        <f>IF(AU45&lt;&gt;"","No – hold: "&amp;AU45,IF(AG45="","No – no confirmed London price per player",IF(AM45="","No – no email",IF(AO45="","No – no personalised email",IF(AS45&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX45" s="21" t="n"/>
-      <c r="AY45" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV45" s="20" t="n"/>
+      <c r="AW45" s="20" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="15" t="n">
@@ -10545,9 +10394,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG46" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG46" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH46" s="15" t="inlineStr">
         <is>
@@ -10578,14 +10428,18 @@
         <f>IF(V46&lt;&gt;"",V46,S46)</f>
         <v/>
       </c>
-      <c r="AN46" s="18">
-        <f>IF(AG46="","","A 5-a-side pitch 7 minutes from EC2A 2AP")</f>
-        <v/>
+      <c r="AN46" s="15" t="inlineStr">
+        <is>
+          <t>Football for the Hadean team?</t>
+        </is>
       </c>
       <c r="AO46" s="19" t="inlineStr">
         <is>
           <t>Hi Hadean Supercomputing team,
-Good to see Hadean's recent funding round, backing the push to become the UK's next defence tech unicorn. Teams growing that fast tend to need a regular way to switch off together. We have a 5-a-side pitch at Powerleague Shoreditch, on Braithwaite Street, a 7-minute walk from your EC2A 2AP office. There's a slot free Monday 28 September at 17:40, or 19:40, and it could become your standing weekly game. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Would your team be up for it?
+Good to see the funding Hadean secured in March, backing the push to become the UK's next defence tech unicorn - fast-growing teams can do with a regular way to switch off.
+I'm Brian from FC Urban. We organise social football across London, and already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 7-minute walk from your office.
+We're looking for someone at Hadean who'd enjoy starting a regular office kickabout for the team - we handle the pitch, extra players if short, payments and organisation.
+Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -10594,37 +10448,30 @@
       <c r="AP46" s="19" t="inlineStr">
         <is>
           <t>Hi Hadean Supercomputing team,
-Circling back on a weekly 5-a-side near your EC2A 2AP office. Monday 28 September at 19:40 at Powerleague Shoreditch is still open. It's {PRICE} a player, and we handle the pitch, sign-ups and payments end to end. Let me know if that suits.
+Just following up on my note about a regular football game for the team, a short walk from your office. No pressure at all - if it's of interest, or someone else handles staff socials, do forward it their way.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ46" s="20">
-        <f>IF(OR(AG46="",AO46=""),"",SUBSTITUTE(AO46,"{PRICE}","£"&amp;IF(AG46=INT(AG46),TEXT(AG46,"0"),TEXT(AG46,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR46" s="20">
-        <f>IF(OR(AG46="",AP46=""),"",SUBSTITUTE(AP46,"{PRICE}","£"&amp;IF(AG46=INT(AG46),TEXT(AG46,"0"),TEXT(AG46,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS46" s="15" t="inlineStr">
+      <c r="AQ46" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR46" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS46" s="15" t="n"/>
       <c r="AT46" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU46" s="15" t="n"/>
-      <c r="AV46" s="18">
-        <f>IF(AU46&lt;&gt;"","No – hold: "&amp;AU46,IF(AG46="","No – no confirmed London price per player",IF(AM46="","No – no email",IF(AO46="","No – no personalised email",IF(AS46&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX46" s="21" t="n"/>
-      <c r="AY46" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV46" s="20" t="n"/>
+      <c r="AW46" s="20" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="15" t="n">
@@ -10759,9 +10606,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG47" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG47" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH47" s="15" t="inlineStr">
         <is>
@@ -10792,14 +10640,18 @@
         <f>IF(V47&lt;&gt;"",V47,S47)</f>
         <v/>
       </c>
-      <c r="AN47" s="18">
-        <f>IF(AG47="","","A weekly 5-a-side, 9 min from Haberdasher St")</f>
-        <v/>
+      <c r="AN47" s="15" t="inlineStr">
+        <is>
+          <t>Rooftop football near Haberdasher Street</t>
+        </is>
       </c>
       <c r="AO47" s="19" t="inlineStr">
         <is>
           <t>Hi Vivacity Labs team,
-Vivacity is on an upward growth trajectory, expanding internationally and adding new people all the time, and a weekly game is a good way to get new starters mixing outside the office. We have a 5-a-side game at the rooftop pitch at Britannia Leisure Centre, Pitfield Street, N1 5FT, a 9-minute walk from Haberdasher Street, with Monday 28 September at 18:00 open — it can become your regular weekly slot. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Shall I hold Monday for you?
+Good to see Vivacity on such an upward trajectory, expanding internationally and doubling headcount - a regular game is a good way to get new starters mixing.
+I'm Brian from FC Urban. We organise social football across London, and already run games at Shoreditch Rooftop (Britannia Leisure Centre, Pitfield Street) (https://www.fcurban.com/locations/shoreditch-rooftop), about a 9-minute walk from Haberdasher Street.
+We're looking for someone at Vivacity Labs who'd enjoy starting a regular office kickabout for the team - we handle the pitch, extra players if short, payments and organisation.
+Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -10807,38 +10659,31 @@
       </c>
       <c r="AP47" s="19" t="inlineStr">
         <is>
-          <t>Hi again,
-Just checking whether a weekly 5-a-side still appeals. Monday 28 September at 18:00 is still open at Britannia Leisure Centre, N1 5FT, 9 minutes from Haberdasher Street. It's {PRICE} a player, and we handle the pitch, sign-ups and payments — someone just shares one link. Happy to hold it if useful.
+          <t>Hi Vivacity Labs team,
+Just following up on my note about setting up a regular football game near your Haberdasher Street office. No pressure - if there's interest, or someone else looks after staff socials, happy for this to be forwarded on.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ47" s="20">
-        <f>IF(OR(AG47="",AO47=""),"",SUBSTITUTE(AO47,"{PRICE}","£"&amp;IF(AG47=INT(AG47),TEXT(AG47,"0"),TEXT(AG47,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR47" s="20">
-        <f>IF(OR(AG47="",AP47=""),"",SUBSTITUTE(AP47,"{PRICE}","£"&amp;IF(AG47=INT(AG47),TEXT(AG47,"0"),TEXT(AG47,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS47" s="15" t="inlineStr">
+      <c r="AQ47" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR47" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS47" s="15" t="n"/>
       <c r="AT47" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU47" s="15" t="n"/>
-      <c r="AV47" s="18">
-        <f>IF(AU47&lt;&gt;"","No – hold: "&amp;AU47,IF(AG47="","No – no confirmed London price per player",IF(AM47="","No – no email",IF(AO47="","No – no personalised email",IF(AS47&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX47" s="21" t="n"/>
-      <c r="AY47" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV47" s="20" t="n"/>
+      <c r="AW47" s="20" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="15" t="n">
@@ -10973,9 +10818,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG48" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG48" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH48" s="15" t="inlineStr">
         <is>
@@ -11006,14 +10852,18 @@
         <f>IF(V48&lt;&gt;"",V48,S48)</f>
         <v/>
       </c>
-      <c r="AN48" s="18">
-        <f>IF(AG48="","","AHMM's own office, Old Street — a weekly 6-a-side?")</f>
-        <v/>
+      <c r="AN48" s="15" t="inlineStr">
+        <is>
+          <t>A weekly kickabout at Morelands?</t>
+        </is>
       </c>
       <c r="AO48" s="19" t="inlineStr">
         <is>
           <t>Hi Allford Hall Monaghan Morris team,
-Morelands, your own office on Old Street, is actually one of AHMM's own projects — nice to design the building you then work in. We have a 6-a-side pitch at the floodlit 3G pitch at Moreland School, Gard Street, EC1V 8DW, a 10-minute walk from Old Street, with Monday 12 October at 18:00 open, or 19:00 if that suits better — it can become your regular weekly game. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Would your team be up for it?
+Morelands, your office on Old Street, is actually one of AHMM's own projects - nice to design the building you then work in.
+I'm Brian from FC Urban. We organise social football across London, and already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 10-minute walk from your office.
+We're looking for someone at AHMM who'd enjoy starting a regular kickabout for the studio - we handle the pitch, extra players if short, payments and organisation.
+Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -11021,38 +10871,31 @@
       </c>
       <c r="AP48" s="19" t="inlineStr">
         <is>
-          <t>Hi again,
-Following up on a weekly game for the AHMM team. Monday 12 October at 19:00 is still open at Moreland School, 10 minutes from Old Street, or 18:00 if easier. It's {PRICE} a player, and we handle the pitch, sign-ups and payments — one link for the team. Let me know if you'd like it held.
+          <t>Hi Allford Hall Monaghan Morris team,
+Just following up on my note about a regular football game a short walk from Morelands. No pressure - if there's interest, or someone else at the studio looks after socials, feel free to forward this on.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ48" s="20">
-        <f>IF(OR(AG48="",AO48=""),"",SUBSTITUTE(AO48,"{PRICE}","£"&amp;IF(AG48=INT(AG48),TEXT(AG48,"0"),TEXT(AG48,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR48" s="20">
-        <f>IF(OR(AG48="",AP48=""),"",SUBSTITUTE(AP48,"{PRICE}","£"&amp;IF(AG48=INT(AG48),TEXT(AG48,"0"),TEXT(AG48,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS48" s="15" t="inlineStr">
+      <c r="AQ48" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR48" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS48" s="15" t="n"/>
       <c r="AT48" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU48" s="15" t="n"/>
-      <c r="AV48" s="18">
-        <f>IF(AU48&lt;&gt;"","No – hold: "&amp;AU48,IF(AG48="","No – no confirmed London price per player",IF(AM48="","No – no email",IF(AO48="","No – no personalised email",IF(AS48&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX48" s="21" t="n"/>
-      <c r="AY48" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV48" s="20" t="n"/>
+      <c r="AW48" s="20" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="15" t="n">
@@ -11185,9 +11028,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG49" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG49" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH49" s="15" t="inlineStr">
         <is>
@@ -11218,14 +11062,18 @@
         <f>IF(V49&lt;&gt;"",V49,S49)</f>
         <v/>
       </c>
-      <c r="AN49" s="18">
-        <f>IF(AG49="","","A weekly 6-a-side, 10 min from Berry Street")</f>
-        <v/>
+      <c r="AN49" s="15" t="inlineStr">
+        <is>
+          <t>Football near Berry Street</t>
+        </is>
       </c>
       <c r="AO49" s="19" t="inlineStr">
         <is>
           <t>Hi Censuswide team,
-Your research for the Mayor of London's 'Have A Word' campaign ended up on billboards in Piccadilly Circus — good proof research travels, and a weekly game is an easy way to get the office out together too. We have a 6-a-side pitch at the floodlit 3G pitch at Moreland School, Gard Street, EC1V 8DW, a 10-minute walk from Berry Street, with Monday 12 October at 18:00 open, or 20:00 if that's easier — it can become your regular weekly slot. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Shall I hold Monday for you?
+Good to see your research for the Mayor of London's "Have A Word" campaign on billboards in Piccadilly Circus - proof it travels, and a game is a good way to get the office out.
+I'm Brian from FC Urban. We organise social football across London, and already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 10-minute walk from Berry Street.
+We're looking for someone at Censuswide who'd enjoy starting a regular office kickabout for the team - we handle the pitch, extra players, payments and organisation.
+Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -11233,38 +11081,31 @@
       </c>
       <c r="AP49" s="19" t="inlineStr">
         <is>
-          <t>Hi again,
-Just checking on a weekly game for Censuswide. Monday 12 October at 18:00 is still open at Moreland School, 10 minutes from Berry Street, or 20:00 works too. It's {PRICE} a player, and we handle the pitch, sign-ups and payments — one link for the team. Happy to hold a slot.
+          <t>Hi Censuswide team,
+Just following up on my note about a regular football game near your Berry Street office. No pressure - if there's interest, or someone else looks after staff socials, do forward this on to them.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ49" s="20">
-        <f>IF(OR(AG49="",AO49=""),"",SUBSTITUTE(AO49,"{PRICE}","£"&amp;IF(AG49=INT(AG49),TEXT(AG49,"0"),TEXT(AG49,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR49" s="20">
-        <f>IF(OR(AG49="",AP49=""),"",SUBSTITUTE(AP49,"{PRICE}","£"&amp;IF(AG49=INT(AG49),TEXT(AG49,"0"),TEXT(AG49,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS49" s="15" t="inlineStr">
+      <c r="AQ49" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR49" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS49" s="15" t="n"/>
       <c r="AT49" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU49" s="15" t="n"/>
-      <c r="AV49" s="18">
-        <f>IF(AU49&lt;&gt;"","No – hold: "&amp;AU49,IF(AG49="","No – no confirmed London price per player",IF(AM49="","No – no email",IF(AO49="","No – no personalised email",IF(AS49&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX49" s="21" t="n"/>
-      <c r="AY49" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV49" s="20" t="n"/>
+      <c r="AW49" s="20" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="15" t="n">
@@ -11395,9 +11236,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG50" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG50" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH50" s="15" t="n"/>
       <c r="AI50" s="15" t="n"/>
@@ -11420,16 +11262,17 @@
         <f>IF(V50&lt;&gt;"",V50,S50)</f>
         <v/>
       </c>
-      <c r="AN50" s="18">
-        <f>IF(AG50="","","5-a-side, 10 minutes from your EC2A office")</f>
-        <v/>
+      <c r="AN50" s="15" t="inlineStr">
+        <is>
+          <t>Weekly football for Atech Support</t>
+        </is>
       </c>
       <c r="AO50" s="19" t="inlineStr">
         <is>
           <t>Hi Atech Support team,
-We run 5-a-side football at Powerleague Shoreditch, Braithwaite Street, a 10-minute walk from your office. Monday 28 September at 17:40 is open, or 19:40 the same evening, and it can easily become a weekly fixture for your team.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Would your team be up for it?
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 10-minute walk from your office.
+We're looking for someone at Atech Support who'd enjoy helping start a regular office kickabout for the team, nothing fancy, just an excuse to get out from behind the desk - we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -11438,37 +11281,30 @@
       <c r="AP50" s="19" t="inlineStr">
         <is>
           <t>Hi Atech Support team,
-Following up on the 5-a-side slot at Powerleague Shoreditch - Monday 28 September at 17:40, or Thursday 1 October at 18:20 if that suits better. It's {PRICE} a player, and we handle sign-ups and payments so it's one link for the team.
+Just checking back on my note about setting up a regular football game near your office. No pressure at all - if it's of interest, or someone else looks after staff socials, happy for this to be forwarded on.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ50" s="20">
-        <f>IF(OR(AG50="",AO50=""),"",SUBSTITUTE(AO50,"{PRICE}","£"&amp;IF(AG50=INT(AG50),TEXT(AG50,"0"),TEXT(AG50,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR50" s="20">
-        <f>IF(OR(AG50="",AP50=""),"",SUBSTITUTE(AP50,"{PRICE}","£"&amp;IF(AG50=INT(AG50),TEXT(AG50,"0"),TEXT(AG50,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS50" s="15" t="inlineStr">
+      <c r="AQ50" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR50" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS50" s="15" t="n"/>
       <c r="AT50" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU50" s="15" t="n"/>
-      <c r="AV50" s="18">
-        <f>IF(AU50&lt;&gt;"","No – hold: "&amp;AU50,IF(AG50="","No – no confirmed London price per player",IF(AM50="","No – no email",IF(AO50="","No – no personalised email",IF(AS50&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX50" s="21" t="n"/>
-      <c r="AY50" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV50" s="20" t="n"/>
+      <c r="AW50" s="20" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="15" t="n">
@@ -11599,9 +11435,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG51" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG51" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH51" s="15" t="n"/>
       <c r="AI51" s="15" t="n"/>
@@ -11624,16 +11461,17 @@
         <f>IF(V51&lt;&gt;"",V51,S51)</f>
         <v/>
       </c>
-      <c r="AN51" s="18">
-        <f>IF(AG51="","","A weekly 5-a-side pitch 11 minutes from your EC2A office")</f>
-        <v/>
+      <c r="AN51" s="15" t="inlineStr">
+        <is>
+          <t>Weekly football for the McBains team</t>
+        </is>
       </c>
       <c r="AO51" s="19" t="inlineStr">
         <is>
           <t>Hi McBains team,
-We've a 5-a-side pitch at Powerleague Shoreditch, an 11-minute walk from your EC2A office. There's a slot free on Monday 28 September at 17:40, or 19:40 if evenings suit better, and it can become a regular weekly fixture for the team.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Shall I hold the Monday slot for you?
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about an 11-minute walk from your office.
+We're looking for someone at McBains who'd enjoy helping start a regular kickabout for the studio, an easy way to get colleagues together outside the office - we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -11641,37 +11479,31 @@
       </c>
       <c r="AP51" s="19" t="inlineStr">
         <is>
-          <t>Just checking — the Monday 28 September 5-a-side slot at Powerleague Shoreditch is still open, or Thursday 1 October at 18:20 if that's easier. It's {PRICE} a player, and we handle the booking and payments. Keen to get McBains a regular weekly game.
+          <t>Hi McBains team,
+Just following up on my note about a regular football game a short walk from your office. No pressure - if there's interest, or someone else at the studio looks after socials, feel free to forward this on.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ51" s="20">
-        <f>IF(OR(AG51="",AO51=""),"",SUBSTITUTE(AO51,"{PRICE}","£"&amp;IF(AG51=INT(AG51),TEXT(AG51,"0"),TEXT(AG51,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR51" s="20">
-        <f>IF(OR(AG51="",AP51=""),"",SUBSTITUTE(AP51,"{PRICE}","£"&amp;IF(AG51=INT(AG51),TEXT(AG51,"0"),TEXT(AG51,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS51" s="15" t="inlineStr">
+      <c r="AQ51" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR51" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS51" s="15" t="n"/>
       <c r="AT51" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU51" s="15" t="n"/>
-      <c r="AV51" s="18">
-        <f>IF(AU51&lt;&gt;"","No – hold: "&amp;AU51,IF(AG51="","No – no confirmed London price per player",IF(AM51="","No – no email",IF(AO51="","No – no personalised email",IF(AS51&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX51" s="21" t="n"/>
-      <c r="AY51" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV51" s="20" t="n"/>
+      <c r="AW51" s="20" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="15" t="n">
@@ -11800,9 +11632,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG52" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG52" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH52" s="15" t="inlineStr">
         <is>
@@ -11833,14 +11666,18 @@
         <f>IF(V52&lt;&gt;"",V52,S52)</f>
         <v/>
       </c>
-      <c r="AN52" s="18">
-        <f>IF(AG52="","","A weekly 5-a-side for Fincore's 24-person team")</f>
-        <v/>
+      <c r="AN52" s="15" t="inlineStr">
+        <is>
+          <t>Weekly football for the Fincore team</t>
+        </is>
       </c>
       <c r="AO52" s="19" t="inlineStr">
         <is>
           <t>Hi Fincore team,
-With a team of 24, you've got more than enough for a proper weekly five-a-side. We have a pitch at Powerleague Shoreditch, Braithwaite Street, a 14-minute walk from your EC2M office. There's a slot on Monday 28 September at 17:40, or 19:40 if that's easier, and it can become your regular weekly game. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Shall I hold Monday for you?
+With a 24-person team built by a CFO-turned-founder, you've easily got the numbers for a proper weekly kickabout.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 14-minute walk from your office.
+We're looking for someone at Fincore who'd enjoy helping start a regular office kickabout for the team - we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -11848,37 +11685,31 @@
       </c>
       <c r="AP52" s="19" t="inlineStr">
         <is>
-          <t>Hi again, still keen to get Fincore's weekly five-a-side going? Powerleague Shoreditch has a slot free on Thursday 1 October at 18:20, 14 minutes from your office. It's {PRICE} a player, we handle the booking, one link for the team. Worth a go?
+          <t>Hi Fincore team,
+Just following up on my note about a regular football game for the team, a walk from your office. No pressure - if there's interest, or someone else looks after staff socials, feel free to forward this on to them.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ52" s="20">
-        <f>IF(OR(AG52="",AO52=""),"",SUBSTITUTE(AO52,"{PRICE}","£"&amp;IF(AG52=INT(AG52),TEXT(AG52,"0"),TEXT(AG52,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR52" s="20">
-        <f>IF(OR(AG52="",AP52=""),"",SUBSTITUTE(AP52,"{PRICE}","£"&amp;IF(AG52=INT(AG52),TEXT(AG52,"0"),TEXT(AG52,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS52" s="15" t="inlineStr">
+      <c r="AQ52" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR52" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS52" s="15" t="n"/>
       <c r="AT52" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU52" s="15" t="n"/>
-      <c r="AV52" s="18">
-        <f>IF(AU52&lt;&gt;"","No – hold: "&amp;AU52,IF(AG52="","No – no confirmed London price per player",IF(AM52="","No – no email",IF(AO52="","No – no personalised email",IF(AS52&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX52" s="21" t="n"/>
-      <c r="AY52" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV52" s="20" t="n"/>
+      <c r="AW52" s="20" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="15" t="n">
@@ -12013,9 +11844,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG53" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG53" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH53" s="15" t="inlineStr">
         <is>
@@ -12046,14 +11878,18 @@
         <f>IF(V53&lt;&gt;"",V53,S53)</f>
         <v/>
       </c>
-      <c r="AN53" s="18">
-        <f>IF(AG53="","","GTN's 7th Best Firm to Work For win, a weekly game?")</f>
-        <v/>
+      <c r="AN53" s="15" t="inlineStr">
+        <is>
+          <t>Football for the GTN team</t>
+        </is>
       </c>
       <c r="AO53" s="19" t="inlineStr">
         <is>
-          <t>Hi Gtn Europe Financial team,
-Congratulations on GTN being named a Best Accounting Firm to Work For for the seventh year running. Sounds like a team worth getting together outside the office. We have a floodlit 6-a-side pitch at Moreland School, Gard Street, a 14-minute walk from Charterhouse Mews. There's a slot free on Monday 12 October at 18:00, or 19:00 if that suits, and it can become your regular weekly game. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Shall I hold Monday for you?
+          <t>Hi GTN team,
+Congratulations on GTN being named a Best Accounting Firm to Work For, seventh year running - a good excuse to get the team together outside the office too.
+I'm Brian from FC Urban. We organise social football across London, and already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 14-minute walk from Charterhouse Mews.
+We're looking for someone at GTN who'd enjoy starting a regular after-work game for colleagues, or a game against another firm nearby - we handle the pitch, extra players, payments and organisation.
+Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -12061,37 +11897,31 @@
       </c>
       <c r="AP53" s="19" t="inlineStr">
         <is>
-          <t>Hi again, following up on a weekly six-a-side for the GTN team near Charterhouse Mews. Moreland School still has Monday 12 October at 19:00 or 20:00 free. It's {PRICE} a player, we handle the booking, one link for everyone. Would that work?
+          <t>Hi GTN team,
+Just following up on my note about a regular after-work football game for the team. No pressure - if there's interest, or someone else looks after staff socials, do forward this on to them.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ53" s="20">
-        <f>IF(OR(AG53="",AO53=""),"",SUBSTITUTE(AO53,"{PRICE}","£"&amp;IF(AG53=INT(AG53),TEXT(AG53,"0"),TEXT(AG53,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR53" s="20">
-        <f>IF(OR(AG53="",AP53=""),"",SUBSTITUTE(AP53,"{PRICE}","£"&amp;IF(AG53=INT(AG53),TEXT(AG53,"0"),TEXT(AG53,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS53" s="15" t="inlineStr">
+      <c r="AQ53" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR53" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS53" s="15" t="n"/>
       <c r="AT53" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU53" s="15" t="n"/>
-      <c r="AV53" s="18">
-        <f>IF(AU53&lt;&gt;"","No – hold: "&amp;AU53,IF(AG53="","No – no confirmed London price per player",IF(AM53="","No – no email",IF(AO53="","No – no personalised email",IF(AS53&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX53" s="21" t="n"/>
-      <c r="AY53" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV53" s="20" t="n"/>
+      <c r="AW53" s="20" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="15" t="n">
@@ -12234,9 +12064,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG54" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG54" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH54" s="15" t="n"/>
       <c r="AI54" s="15" t="n"/>
@@ -12259,16 +12090,17 @@
         <f>IF(V54&lt;&gt;"",V54,S54)</f>
         <v/>
       </c>
-      <c r="AN54" s="18">
-        <f>IF(AG54="","","A weekly 6-a-side near Mallow Street for Yu Life?")</f>
-        <v/>
+      <c r="AN54" s="15" t="inlineStr">
+        <is>
+          <t>A regular football game for YuLife?</t>
+        </is>
       </c>
       <c r="AO54" s="19" t="inlineStr">
         <is>
           <t>Hi Esme,
-We've a 6-a-side pitch at the floodlit 3G pitch at Moreland School, Gard Street, EC1V 8DW, a 13-minute walk from 12 Mallow Street, with slots free Monday 12 October at 18:00 or 19:00.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. It could easily become your regular weekly game, a good excuse to get the team outside after work.
-Would your team be up for it?
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 13-minute walk from your office on Mallow Street.
+We're looking for someone at YuLife who'd enjoy helping start a regular office kickabout for the team - we handle the pitch, extra players if you're short, payments and organisation.
+Would you be up for it, or is there someone else at YuLife who'd be better placed to look at this?
 Best,
 Brian
 FC Urban</t>
@@ -12277,37 +12109,30 @@
       <c r="AP54" s="19" t="inlineStr">
         <is>
           <t>Hi Esme,
-Following up on the 6-a-side near Mallow Street. Monday 12 October still has slots at 18:00 and 19:00, or 20:00 if that's easier. It's {PRICE} a player, one link for the team, and we sort the rest.
+Just following up on my note about setting up a regular football game for the YuLife team near Mallow Street. No pressure at all - if it's of interest, or there's someone better placed to ask, do let me know.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ54" s="20">
-        <f>IF(OR(AG54="",AO54=""),"",SUBSTITUTE(AO54,"{PRICE}","£"&amp;IF(AG54=INT(AG54),TEXT(AG54,"0"),TEXT(AG54,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR54" s="20">
-        <f>IF(OR(AG54="",AP54=""),"",SUBSTITUTE(AP54,"{PRICE}","£"&amp;IF(AG54=INT(AG54),TEXT(AG54,"0"),TEXT(AG54,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS54" s="15" t="inlineStr">
+      <c r="AQ54" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR54" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS54" s="15" t="n"/>
       <c r="AT54" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU54" s="15" t="n"/>
-      <c r="AV54" s="18">
-        <f>IF(AU54&lt;&gt;"","No – hold: "&amp;AU54,IF(AG54="","No – no confirmed London price per player",IF(AM54="","No – no email",IF(AO54="","No – no personalised email",IF(AS54&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX54" s="21" t="n"/>
-      <c r="AY54" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV54" s="20" t="n"/>
+      <c r="AW54" s="20" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="15" t="n">
@@ -12452,9 +12277,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG55" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG55" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH55" s="15" t="inlineStr">
         <is>
@@ -12485,16 +12311,17 @@
         <f>IF(V55&lt;&gt;"",V55,S55)</f>
         <v/>
       </c>
-      <c r="AN55" s="18">
-        <f>IF(AG55="","","6-a-side, 11 minutes from Kemp House")</f>
-        <v/>
+      <c r="AN55" s="15" t="inlineStr">
+        <is>
+          <t>A regular game for the Creditex team?</t>
+        </is>
       </c>
       <c r="AO55" s="19" t="inlineStr">
         <is>
           <t>Hi Emma,
-We've got a floodlit 6-a-side pitch at Moreland School, just off Old Street, an 11-minute walk from Kemp House. There's a slot free Monday 12 October at 18:00, or 19:00 if that suits better, and it could become your team's regular weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Shall I hold Monday for you?
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about an 11-minute walk from your office on City Road.
+We're looking for someone at Creditex Brokerage who'd enjoy helping start a regular after-work game for colleagues, or even a game against another firm nearby - we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -12503,37 +12330,30 @@
       <c r="AP55" s="19" t="inlineStr">
         <is>
           <t>Hi Emma,
-Following up on the 6-a-side slot near Kemp House. Monday 12 October at 18:00 is still open, or 19:00 works too. It's {PRICE} a player, and we handle the booking and payments end to end. Keen to get your team on the pitch?
+Just following up on my note about a regular football game a short walk from your City Road office. No pressure - if there's interest, or someone else looks after staff socials, feel free to forward this on.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ55" s="20">
-        <f>IF(OR(AG55="",AO55=""),"",SUBSTITUTE(AO55,"{PRICE}","£"&amp;IF(AG55=INT(AG55),TEXT(AG55,"0"),TEXT(AG55,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR55" s="20">
-        <f>IF(OR(AG55="",AP55=""),"",SUBSTITUTE(AP55,"{PRICE}","£"&amp;IF(AG55=INT(AG55),TEXT(AG55,"0"),TEXT(AG55,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS55" s="15" t="inlineStr">
+      <c r="AQ55" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR55" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS55" s="15" t="n"/>
       <c r="AT55" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU55" s="15" t="n"/>
-      <c r="AV55" s="18">
-        <f>IF(AU55&lt;&gt;"","No – hold: "&amp;AU55,IF(AG55="","No – no confirmed London price per player",IF(AM55="","No – no email",IF(AO55="","No – no personalised email",IF(AS55&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX55" s="21" t="n"/>
-      <c r="AY55" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV55" s="20" t="n"/>
+      <c r="AW55" s="20" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="15" t="n">
@@ -12668,9 +12488,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG56" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG56" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH56" s="15" t="n"/>
       <c r="AI56" s="15" t="n"/>
@@ -12693,14 +12514,17 @@
         <f>IF(V56&lt;&gt;"",V56,S56)</f>
         <v/>
       </c>
-      <c r="AN56" s="18">
-        <f>IF(AG56="","","5 minutes from Folgate Street: weekly 5-a-side")</f>
-        <v/>
+      <c r="AN56" s="15" t="inlineStr">
+        <is>
+          <t>Football near Folgate Street</t>
+        </is>
       </c>
       <c r="AO56" s="19" t="inlineStr">
         <is>
           <t>Hi Made Tech team,
-We've got a 5-a-side pitch at Powerleague Shoreditch, Braithwaite Street, E1 6GJ, just a 5-minute walk from your Folgate Street office. There's a slot open Monday 28 September at 17:40, or 19:40 if that's easier, and it could become your weekly game. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Would your team be up for it?
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 5-minute walk from your office on Folgate Street.
+We're looking for someone at Made Tech who'd enjoy helping start a regular office kickabout for the team - we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -12709,37 +12533,30 @@
       <c r="AP56" s="19" t="inlineStr">
         <is>
           <t>Hi Made Tech team,
-Following up on the 5-a-side slot at Powerleague Shoreditch, a short walk from Folgate Street — Monday 28 September at 17:40 is still open, or Thursday 1 October at 18:20. It's {PRICE} a player; we handle the booking and payments. Let me know if you'd like it held.
+Just following up on my note about a regular football game a short walk from your Folgate Street office. No pressure - if there's interest, or someone else looks after staff socials, feel free to forward this on.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ56" s="20">
-        <f>IF(OR(AG56="",AO56=""),"",SUBSTITUTE(AO56,"{PRICE}","£"&amp;IF(AG56=INT(AG56),TEXT(AG56,"0"),TEXT(AG56,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR56" s="20">
-        <f>IF(OR(AG56="",AP56=""),"",SUBSTITUTE(AP56,"{PRICE}","£"&amp;IF(AG56=INT(AG56),TEXT(AG56,"0"),TEXT(AG56,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS56" s="15" t="inlineStr">
+      <c r="AQ56" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR56" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS56" s="15" t="n"/>
       <c r="AT56" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU56" s="15" t="n"/>
-      <c r="AV56" s="18">
-        <f>IF(AU56&lt;&gt;"","No – hold: "&amp;AU56,IF(AG56="","No – no confirmed London price per player",IF(AM56="","No – no email",IF(AO56="","No – no personalised email",IF(AS56&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX56" s="21" t="n"/>
-      <c r="AY56" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV56" s="20" t="n"/>
+      <c r="AW56" s="20" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="15" t="n">
@@ -12874,9 +12691,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG57" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG57" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH57" s="15" t="n"/>
       <c r="AI57" s="15" t="n"/>
@@ -12899,14 +12717,17 @@
         <f>IF(V57&lt;&gt;"",V57,S57)</f>
         <v/>
       </c>
-      <c r="AN57" s="18">
-        <f>IF(AG57="","","A weekly 5-a-side, 10 min from Paul Street")</f>
-        <v/>
+      <c r="AN57" s="15" t="inlineStr">
+        <is>
+          <t>Weekly football for Clover Technology</t>
+        </is>
       </c>
       <c r="AO57" s="19" t="inlineStr">
         <is>
           <t>Hi Clover Technology team,
-We have a 5-a-side pitch at Powerleague Shoreditch, Braithwaite Street, E1 6GJ, a 10-minute walk from Paul Street, with Monday 28 September at 17:40 open, or 19:40 if that's easier — it can become your regular weekly game. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Would your team be up for it?
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 10-minute walk from your office on Paul Street.
+We're looking for someone at Clover Technology who'd enjoy helping start a regular office kickabout for the team - we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -12914,38 +12735,31 @@
       </c>
       <c r="AP57" s="19" t="inlineStr">
         <is>
-          <t>Hi again,
-Just checking whether a weekly 5-a-side would suit Clover Technology. Monday 28 September at 19:40 is still open at Powerleague Shoreditch, 10 minutes from Paul Street, or Thursday 1 October at 18:20 if better. It's {PRICE} a player, and we handle the pitch, sign-ups and payments. Let me know.
+          <t>Hi Clover Technology team,
+Just following up on my note about a regular football game near your Paul Street office. No pressure - if there's interest, or someone else looks after staff socials, feel free to forward this on to them.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ57" s="20">
-        <f>IF(OR(AG57="",AO57=""),"",SUBSTITUTE(AO57,"{PRICE}","£"&amp;IF(AG57=INT(AG57),TEXT(AG57,"0"),TEXT(AG57,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR57" s="20">
-        <f>IF(OR(AG57="",AP57=""),"",SUBSTITUTE(AP57,"{PRICE}","£"&amp;IF(AG57=INT(AG57),TEXT(AG57,"0"),TEXT(AG57,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS57" s="15" t="inlineStr">
+      <c r="AQ57" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR57" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS57" s="15" t="n"/>
       <c r="AT57" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU57" s="15" t="n"/>
-      <c r="AV57" s="18">
-        <f>IF(AU57&lt;&gt;"","No – hold: "&amp;AU57,IF(AG57="","No – no confirmed London price per player",IF(AM57="","No – no email",IF(AO57="","No – no personalised email",IF(AS57&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX57" s="21" t="n"/>
-      <c r="AY57" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV57" s="20" t="n"/>
+      <c r="AW57" s="20" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="15" t="n">
@@ -13076,9 +12890,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG58" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG58" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH58" s="15" t="n"/>
       <c r="AI58" s="15" t="n"/>
@@ -13101,14 +12916,17 @@
         <f>IF(V58&lt;&gt;"",V58,S58)</f>
         <v/>
       </c>
-      <c r="AN58" s="18">
-        <f>IF(AG58="","","A weekly 5-a-side, 10 min from your EC2A office")</f>
-        <v/>
+      <c r="AN58" s="15" t="inlineStr">
+        <is>
+          <t>Weekly football for Louder Productions</t>
+        </is>
       </c>
       <c r="AO58" s="19" t="inlineStr">
         <is>
           <t>Hi Louder Productions team,
-We have a 5-a-side pitch at Powerleague Shoreditch, Braithwaite Street, E1 6GJ, a 10-minute walk from your EC2A 4JU office, with Monday 28 September at 17:40 open, or 19:40 if that's easier — it can become your regular weekly game. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Would your team be up for it?
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 10-minute walk from your office.
+We're looking for someone at Louder Productions who'd enjoy helping start a regular office kickabout for the team - we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -13116,38 +12934,31 @@
       </c>
       <c r="AP58" s="19" t="inlineStr">
         <is>
-          <t>Hi again,
-Just checking whether a weekly 5-a-side would suit the Louder Productions team. Monday 28 September at 19:40 is still open at Powerleague Shoreditch, 10 minutes from your office, or Thursday 1 October at 18:20 works too. It's {PRICE} a player, and we handle everything else.
+          <t>Hi Louder Productions team,
+Just following up on my note about a regular football game near your office. No pressure at all - if there's interest, or someone else looks after staff socials, feel free to forward this on to them.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ58" s="20">
-        <f>IF(OR(AG58="",AO58=""),"",SUBSTITUTE(AO58,"{PRICE}","£"&amp;IF(AG58=INT(AG58),TEXT(AG58,"0"),TEXT(AG58,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR58" s="20">
-        <f>IF(OR(AG58="",AP58=""),"",SUBSTITUTE(AP58,"{PRICE}","£"&amp;IF(AG58=INT(AG58),TEXT(AG58,"0"),TEXT(AG58,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS58" s="15" t="inlineStr">
+      <c r="AQ58" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR58" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS58" s="15" t="n"/>
       <c r="AT58" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU58" s="15" t="n"/>
-      <c r="AV58" s="18">
-        <f>IF(AU58&lt;&gt;"","No – hold: "&amp;AU58,IF(AG58="","No – no confirmed London price per player",IF(AM58="","No – no email",IF(AO58="","No – no personalised email",IF(AS58&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX58" s="21" t="n"/>
-      <c r="AY58" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV58" s="20" t="n"/>
+      <c r="AW58" s="20" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="15" t="n">
@@ -13282,9 +13093,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG59" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG59" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH59" s="15" t="n"/>
       <c r="AI59" s="15" t="n"/>
@@ -13307,14 +13119,17 @@
         <f>IF(V59&lt;&gt;"",V59,S59)</f>
         <v/>
       </c>
-      <c r="AN59" s="18">
-        <f>IF(AG59="","","A weekly 5-a-side, 10 min from Paul Street")</f>
-        <v/>
+      <c r="AN59" s="15" t="inlineStr">
+        <is>
+          <t>Football near your Paul Street office</t>
+        </is>
       </c>
       <c r="AO59" s="19" t="inlineStr">
         <is>
           <t>Hi Arcontech team,
-We have a 5-a-side pitch at Powerleague Shoreditch, Braithwaite Street, E1 6GJ, a 10-minute walk from Paul Street, with Monday 28 September at 17:40 open, or 19:40 if that's easier — it can become your regular weekly game. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Would your team be up for it?
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 10-minute walk from your office on Paul Street.
+We're looking for someone at Arcontech who'd enjoy helping start a regular office kickabout for the team - we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -13322,38 +13137,31 @@
       </c>
       <c r="AP59" s="19" t="inlineStr">
         <is>
-          <t>Hi again,
-Just checking whether a weekly 5-a-side would suit Arcontech. Monday 28 September at 19:40 is still open at Powerleague Shoreditch, 10 minutes from Paul Street, or Thursday 1 October at 18:20 if better. It's {PRICE} a player, and we handle the pitch, sign-ups and payments. Let me know.
+          <t>Hi Arcontech team,
+Just following up on my note about a regular football game near your Paul Street office. No pressure - if there's interest, or someone else looks after staff socials, feel free to forward this on to them.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ59" s="20">
-        <f>IF(OR(AG59="",AO59=""),"",SUBSTITUTE(AO59,"{PRICE}","£"&amp;IF(AG59=INT(AG59),TEXT(AG59,"0"),TEXT(AG59,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR59" s="20">
-        <f>IF(OR(AG59="",AP59=""),"",SUBSTITUTE(AP59,"{PRICE}","£"&amp;IF(AG59=INT(AG59),TEXT(AG59,"0"),TEXT(AG59,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS59" s="15" t="inlineStr">
+      <c r="AQ59" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR59" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS59" s="15" t="n"/>
       <c r="AT59" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU59" s="15" t="n"/>
-      <c r="AV59" s="18">
-        <f>IF(AU59&lt;&gt;"","No – hold: "&amp;AU59,IF(AG59="","No – no confirmed London price per player",IF(AM59="","No – no email",IF(AO59="","No – no personalised email",IF(AS59&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX59" s="21" t="n"/>
-      <c r="AY59" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV59" s="20" t="n"/>
+      <c r="AW59" s="20" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="15" t="n">
@@ -13484,9 +13292,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG60" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG60" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH60" s="15" t="n"/>
       <c r="AI60" s="15" t="n"/>
@@ -13509,16 +13318,17 @@
         <f>IF(V60&lt;&gt;"",V60,S60)</f>
         <v/>
       </c>
-      <c r="AN60" s="18">
-        <f>IF(AG60="","","A weekly 6-a-side pitch, 12 minutes from your N1 office")</f>
-        <v/>
+      <c r="AN60" s="15" t="inlineStr">
+        <is>
+          <t>Weekly football for Blue Square</t>
+        </is>
       </c>
       <c r="AO60" s="19" t="inlineStr">
         <is>
           <t>Hi Blue Square Marketing team,
-We've a floodlit 3G pitch at Moreland School, just off Old Street, a 12-minute walk from your N1 office. There's a 6-a-side slot free on Monday 12 October at 18:00, or 19:00 if that suits better, and it can easily become a weekly fixture for the team.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Would your team be up for it?
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 12-minute walk from your office.
+We're looking for someone at Blue Square Marketing who'd enjoy helping start a regular office kickabout for the team - we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -13526,37 +13336,31 @@
       </c>
       <c r="AP60" s="19" t="inlineStr">
         <is>
-          <t>Following up on Monday 12 October — the 6-a-side slot at Moreland School (18:00 or 19:00) is still free, 12 minutes from your N1 office. It's {PRICE} a player, and we handle the pitch booking and payments end to end. Would this suit as a weekly game?
+          <t>Hi Blue Square Marketing team,
+Just following up on my note about a regular football game near your office. No pressure at all - if there's interest, or someone else looks after staff socials, feel free to forward this on to them.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ60" s="20">
-        <f>IF(OR(AG60="",AO60=""),"",SUBSTITUTE(AO60,"{PRICE}","£"&amp;IF(AG60=INT(AG60),TEXT(AG60,"0"),TEXT(AG60,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR60" s="20">
-        <f>IF(OR(AG60="",AP60=""),"",SUBSTITUTE(AP60,"{PRICE}","£"&amp;IF(AG60=INT(AG60),TEXT(AG60,"0"),TEXT(AG60,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS60" s="15" t="inlineStr">
+      <c r="AQ60" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR60" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS60" s="15" t="n"/>
       <c r="AT60" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU60" s="15" t="n"/>
-      <c r="AV60" s="18">
-        <f>IF(AU60&lt;&gt;"","No – hold: "&amp;AU60,IF(AG60="","No – no confirmed London price per player",IF(AM60="","No – no email",IF(AO60="","No – no personalised email",IF(AS60&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX60" s="21" t="n"/>
-      <c r="AY60" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV60" s="20" t="n"/>
+      <c r="AW60" s="20" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="15" t="n">
@@ -13691,9 +13495,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG61" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG61" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH61" s="15" t="n"/>
       <c r="AI61" s="15" t="n"/>
@@ -13716,14 +13521,17 @@
         <f>IF(V61&lt;&gt;"",V61,S61)</f>
         <v/>
       </c>
-      <c r="AN61" s="18">
-        <f>IF(AG61="","","Weekly 6-a-side, 13 min from Clerkenwell Road")</f>
-        <v/>
+      <c r="AN61" s="15" t="inlineStr">
+        <is>
+          <t>Football near Clerkenwell Road</t>
+        </is>
       </c>
       <c r="AO61" s="19" t="inlineStr">
         <is>
-          <t>Hi Container Solutions Software team,
-We have a floodlit 6-a-side pitch at Moreland School, Gard Street, just off Old Street, a 13-minute walk from Clerkenwell Road. There's an open slot on Monday 12 October at 18:00, or 19:00 if that suits better, and it could easily become your regular weekly game. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Shall I hold Monday for you?
+          <t>Hi Container Solutions team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 13-minute walk from your office on Clerkenwell Road.
+We're looking for someone at Container Solutions who'd enjoy helping start a regular office kickabout for the team - we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -13731,37 +13539,31 @@
       </c>
       <c r="AP61" s="19" t="inlineStr">
         <is>
-          <t>Hi again, just checking whether Monday 12 October still works for a game at Moreland School, 13 minutes from Clerkenwell Road. The 18:00 or 19:00 slot is still open. It's {PRICE} a player, and we handle the booking and sign-ups, so it's one link for your team. Worth a try?
+          <t>Hi Container Solutions team,
+Just following up on my note about a regular football game near your Clerkenwell Road office. No pressure - if there's interest, or someone else looks after staff socials, feel free to forward this on.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ61" s="20">
-        <f>IF(OR(AG61="",AO61=""),"",SUBSTITUTE(AO61,"{PRICE}","£"&amp;IF(AG61=INT(AG61),TEXT(AG61,"0"),TEXT(AG61,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR61" s="20">
-        <f>IF(OR(AG61="",AP61=""),"",SUBSTITUTE(AP61,"{PRICE}","£"&amp;IF(AG61=INT(AG61),TEXT(AG61,"0"),TEXT(AG61,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS61" s="15" t="inlineStr">
+      <c r="AQ61" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR61" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS61" s="15" t="n"/>
       <c r="AT61" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU61" s="15" t="n"/>
-      <c r="AV61" s="18">
-        <f>IF(AU61&lt;&gt;"","No – hold: "&amp;AU61,IF(AG61="","No – no confirmed London price per player",IF(AM61="","No – no email",IF(AO61="","No – no personalised email",IF(AS61&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX61" s="21" t="n"/>
-      <c r="AY61" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV61" s="20" t="n"/>
+      <c r="AW61" s="20" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="15" t="n">
@@ -13896,9 +13698,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG62" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG62" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH62" s="15" t="n"/>
       <c r="AI62" s="15" t="n"/>
@@ -13921,14 +13724,17 @@
         <f>IF(V62&lt;&gt;"",V62,S62)</f>
         <v/>
       </c>
-      <c r="AN62" s="18">
-        <f>IF(AG62="","","Weekly 5-a-side, 15 min from Finsbury Circus")</f>
-        <v/>
+      <c r="AN62" s="15" t="inlineStr">
+        <is>
+          <t>Weekly football for the Parseq team</t>
+        </is>
       </c>
       <c r="AO62" s="19" t="inlineStr">
         <is>
           <t>Hi Parseq team,
-We have a five-a-side pitch at Powerleague Shoreditch, Braithwaite Street, a 15-minute walk from Finsbury Circus. There's an open slot on Monday 28 September at 17:40, or 19:40 if that works better, and it can easily become your regular weekly game. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Shall I hold Monday for you?
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 15-minute walk from your office on Finsbury Circus.
+We're looking for someone at Parseq who'd enjoy helping start a regular office kickabout for the team - we handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -13936,37 +13742,31 @@
       </c>
       <c r="AP62" s="19" t="inlineStr">
         <is>
-          <t>Hi again, checking whether a weekly five-a-side still appeals to the Parseq team. Powerleague Shoreditch has Thursday 1 October at 18:20 open, 15 minutes from Finsbury Circus. It's {PRICE} a player, we handle the booking and sign-ups, one link for the team. Worth a try?
+          <t>Hi Parseq team,
+Just following up on my note about a regular football game near your Finsbury Circus office. No pressure - if there's interest, or someone else looks after staff socials, feel free to forward this on to them.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ62" s="20">
-        <f>IF(OR(AG62="",AO62=""),"",SUBSTITUTE(AO62,"{PRICE}","£"&amp;IF(AG62=INT(AG62),TEXT(AG62,"0"),TEXT(AG62,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR62" s="20">
-        <f>IF(OR(AG62="",AP62=""),"",SUBSTITUTE(AP62,"{PRICE}","£"&amp;IF(AG62=INT(AG62),TEXT(AG62,"0"),TEXT(AG62,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AS62" s="15" t="inlineStr">
+      <c r="AQ62" s="15" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
+      <c r="AR62" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
+      </c>
+      <c r="AS62" s="15" t="n"/>
       <c r="AT62" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU62" s="15" t="n"/>
-      <c r="AV62" s="18">
-        <f>IF(AU62&lt;&gt;"","No – hold: "&amp;AU62,IF(AG62="","No – no confirmed London price per player",IF(AM62="","No – no email",IF(AO62="","No – no personalised email",IF(AS62&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX62" s="21" t="n"/>
-      <c r="AY62" s="21" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AV62" s="20" t="n"/>
+      <c r="AW62" s="20" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="15" t="n">
@@ -14097,9 +13897,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG63" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG63" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH63" s="15" t="inlineStr">
         <is>
@@ -14130,14 +13931,19 @@
         <f>IF(V63&lt;&gt;"",V63,S63)</f>
         <v/>
       </c>
-      <c r="AN63" s="18">
-        <f>IF(AG63="","","Ten years in - fancy a weekly 5-a-side?")</f>
-        <v/>
+      <c r="AN63" s="15" t="inlineStr">
+        <is>
+          <t>Office football for the Quantexa team</t>
+        </is>
       </c>
       <c r="AO63" s="19" t="inlineStr">
         <is>
           <t>Hi Quantexa team,
-Congratulations on ten years in business, especially with a new office just opening in Malaga. A growing team like yours is exactly the sort that ends up loving a regular game. We have a 5-a-side pitch at Powerleague Shoreditch, on Braithwaite Street, a 7-minute walk from your EC2M 4AG office. There's a slot free Monday 28 September at 17:40, or 19:40, and it could easily become your weekly fixture. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Shall I hold the 17:40 slot for you?
+Congratulations on ten years in business, especially with a new office just opening in Malaga.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 7-minute walk from your office on EC2M 4AG.
+We're looking for someone at Quantexa who'd enjoy helping start a regular office kickabout for colleagues after work. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+More on how it works: FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates).
 Best,
 Brian
 FC Urban</t>
@@ -14146,41 +13952,34 @@
       <c r="AP63" s="19" t="inlineStr">
         <is>
           <t>Hi Quantexa team,
-Just following up on a weekly 5-a-side near your EC2M 4AG office. Monday 28 September at 19:40 at Powerleague Shoreditch is still free. It's {PRICE} a player, and we handle the pitch, sign-ups and payments end to end. Let me know if you'd like it held.
+Just following up on my note below about setting up a regular football game for the team near your EC2M 4AG office. No pressure at all - if it's of interest, or you know who'd be best placed to look at it, I'd love to hear.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ63" s="20">
-        <f>IF(OR(AG63="",AO63=""),"",SUBSTITUTE(AO63,"{PRICE}","£"&amp;IF(AG63=INT(AG63),TEXT(AG63,"0"),TEXT(AG63,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR63" s="20">
-        <f>IF(OR(AG63="",AP63=""),"",SUBSTITUTE(AP63,"{PRICE}","£"&amp;IF(AG63=INT(AG63),TEXT(AG63,"0"),TEXT(AG63,"0.00"))))</f>
-        <v/>
+      <c r="AQ63" s="15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="AR63" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
       </c>
       <c r="AS63" s="15" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>check headcount (likely over 500)</t>
         </is>
       </c>
       <c r="AT63" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU63" s="15" t="inlineStr">
-        <is>
-          <t>check headcount (likely over 500)</t>
-        </is>
-      </c>
-      <c r="AV63" s="18">
-        <f>IF(AU63&lt;&gt;"","No – hold: "&amp;AU63,IF(AG63="","No – no confirmed London price per player",IF(AM63="","No – no email",IF(AO63="","No – no personalised email",IF(AS63&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX63" s="21" t="n"/>
-      <c r="AY63" s="21" t="n"/>
+          <t>No – hold: check headcount (likely over 500)</t>
+        </is>
+      </c>
+      <c r="AV63" s="20" t="n"/>
+      <c r="AW63" s="20" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="15" t="n">
@@ -14313,9 +14112,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG64" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG64" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH64" s="15" t="inlineStr">
         <is>
@@ -14346,14 +14146,18 @@
         <f>IF(V64&lt;&gt;"",V64,S64)</f>
         <v/>
       </c>
-      <c r="AN64" s="18">
-        <f>IF(AG64="","","A 6-a-side pitch 7 minutes from Gee Street")</f>
-        <v/>
+      <c r="AN64" s="15" t="inlineStr">
+        <is>
+          <t>Office football near Gee Street?</t>
+        </is>
       </c>
       <c r="AO64" s="19" t="inlineStr">
         <is>
           <t>Hi Maccreanor Lavington team,
-Congratulations on the RIBA Stirling Prize recognition, quite the achievement for a practice of around 80 people. A close-knit team like yours often takes well to a regular match together. We have a floodlit 6-a-side 3G pitch at Moreland School, Gard Street, just off Old Street, a 7-minute walk from Gee Street. There's a slot free Monday 12 October at 18:00, or 19:00, and it could easily become your weekly fixture. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Shall I hold the 18:00 slot for you?
+Congratulations on the RIBA Stirling Prize recognition, quite the achievement for a practice of around 80 people.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 7-minute walk from your office on Gee Street.
+We're looking for someone at Maccreanor Lavington who'd enjoy helping start a regular office kickabout for the studio. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -14362,41 +14166,34 @@
       <c r="AP64" s="19" t="inlineStr">
         <is>
           <t>Hi Maccreanor Lavington team,
-Just checking back on a weekly 6-a-side near Gee Street. Monday 12 October at 19:00 at Moreland School is still free. It's {PRICE} a player, and we handle the pitch, sign-ups and payments end to end. Let me know if you'd like it held.
+Just following up on my note about a regular football game for the studio near Gee Street. No pressure - if there's interest, or you can point me to whoever looks after socials, that would be great.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ64" s="20">
-        <f>IF(OR(AG64="",AO64=""),"",SUBSTITUTE(AO64,"{PRICE}","£"&amp;IF(AG64=INT(AG64),TEXT(AG64,"0"),TEXT(AG64,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR64" s="20">
-        <f>IF(OR(AG64="",AP64=""),"",SUBSTITUTE(AP64,"{PRICE}","£"&amp;IF(AG64=INT(AG64),TEXT(AG64,"0"),TEXT(AG64,"0.00"))))</f>
-        <v/>
+      <c r="AQ64" s="15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="AR64" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
       </c>
       <c r="AS64" s="15" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>inbox is another country or CV/careers inbox</t>
         </is>
       </c>
       <c r="AT64" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU64" s="15" t="inlineStr">
-        <is>
-          <t>inbox is another country or CV/careers inbox</t>
-        </is>
-      </c>
-      <c r="AV64" s="18">
-        <f>IF(AU64&lt;&gt;"","No – hold: "&amp;AU64,IF(AG64="","No – no confirmed London price per player",IF(AM64="","No – no email",IF(AO64="","No – no personalised email",IF(AS64&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX64" s="21" t="n"/>
-      <c r="AY64" s="21" t="n"/>
+          <t>No – hold: inbox is another country or CV/careers inbox</t>
+        </is>
+      </c>
+      <c r="AV64" s="20" t="n"/>
+      <c r="AW64" s="20" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="15" t="n">
@@ -14531,9 +14328,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG65" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG65" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH65" s="15" t="inlineStr">
         <is>
@@ -14564,14 +14362,18 @@
         <f>IF(V65&lt;&gt;"",V65,S65)</f>
         <v/>
       </c>
-      <c r="AN65" s="18">
-        <f>IF(AG65="","","KETTLE Chips sponsor cricket - fancy football?")</f>
-        <v/>
+      <c r="AN65" s="15" t="inlineStr">
+        <is>
+          <t>Football near Perseverance Works?</t>
+        </is>
       </c>
       <c r="AO65" s="19" t="inlineStr">
         <is>
           <t>Hi Valeo Foods team,
-Great to see your KETTLE Chips brand named Official Partner of the ICC Women's T20 World Cup 2026, proof the team backs sport as much as snacks. In that spirit, we have a 5-a-side pitch at Powerleague Shoreditch, on Braithwaite Street, a 9-minute walk from your Perseverance Works office. There's a slot free Monday 28 September at 17:40, or 19:40, and it could become your regular weekly game. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Shall I hold the 17:40 slot for you?
+Great to see your KETTLE Chips brand named Official Partner of the ICC Women's T20 World Cup 2026.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 9-minute walk from your office on Perseverance Works.
+We're looking for someone at Valeo Foods who'd enjoy helping start a regular after-work game for colleagues, maybe even a friendly against another firm nearby. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -14580,41 +14382,34 @@
       <c r="AP65" s="19" t="inlineStr">
         <is>
           <t>Hi Valeo Foods team,
-Following up on a weekly 5-a-side near Perseverance Works. Monday 28 September at 19:40 at Powerleague Shoreditch is still open. It's {PRICE} a player, and we handle the pitch, sign-ups and payments end to end. Let me know if that suits.
+Just checking back on my note about starting a regular after-work football game for the team near Kingsland Road. If it's of interest, or you know who best to point me to, I'd love to hear.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ65" s="20">
-        <f>IF(OR(AG65="",AO65=""),"",SUBSTITUTE(AO65,"{PRICE}","£"&amp;IF(AG65=INT(AG65),TEXT(AG65,"0"),TEXT(AG65,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR65" s="20">
-        <f>IF(OR(AG65="",AP65=""),"",SUBSTITUTE(AP65,"{PRICE}","£"&amp;IF(AG65=INT(AG65),TEXT(AG65,"0"),TEXT(AG65,"0.00"))))</f>
-        <v/>
+      <c r="AQ65" s="15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="AR65" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
       </c>
       <c r="AS65" s="15" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>check headcount (likely over 500)</t>
         </is>
       </c>
       <c r="AT65" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU65" s="15" t="inlineStr">
-        <is>
-          <t>check headcount (likely over 500)</t>
-        </is>
-      </c>
-      <c r="AV65" s="18">
-        <f>IF(AU65&lt;&gt;"","No – hold: "&amp;AU65,IF(AG65="","No – no confirmed London price per player",IF(AM65="","No – no email",IF(AO65="","No – no personalised email",IF(AS65&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX65" s="21" t="n"/>
-      <c r="AY65" s="21" t="n"/>
+          <t>No – hold: check headcount (likely over 500)</t>
+        </is>
+      </c>
+      <c r="AV65" s="20" t="n"/>
+      <c r="AW65" s="20" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="15" t="n">
@@ -14749,9 +14544,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG66" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG66" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH66" s="15" t="inlineStr">
         <is>
@@ -14778,17 +14574,18 @@
         <f>IF(V66&lt;&gt;"",V66,S66)</f>
         <v/>
       </c>
-      <c r="AN66" s="18">
-        <f>IF(AG66="","","A weekly game 11 minutes from Wilson Street")</f>
-        <v/>
+      <c r="AN66" s="15" t="inlineStr">
+        <is>
+          <t>Weekly football near Wilson Street</t>
+        </is>
       </c>
       <c r="AO66" s="19" t="inlineStr">
         <is>
           <t>Hi Your World Recruitment team,
-Great to see Your World supplied 5,565 staff to healthcare providers and worked with 770 organisations in 2025 - quite a year for the team.
-We run 5-a-side at Powerleague Shoreditch, Braithwaite Street, an 11-minute walk from your office on Wilson Street. Monday 28 September at 17:40 is open, or 19:40 the same evening, and it can become your regular weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Would your team be up for it?
+Great to see you supplied 5,565 staff to healthcare providers and worked with 770 organisations in 2025.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about an 11-minute walk from your office on Wilson Street.
+We're looking for someone at Your World Recruitment who'd enjoy helping start a regular team game, perhaps a friendly against other firms. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -14797,41 +14594,34 @@
       <c r="AP66" s="19" t="inlineStr">
         <is>
           <t>Hi Your World Recruitment team,
-Following up on the 5-a-side slot at Powerleague Shoreditch - Monday 28 September at 17:40, or Thursday 1 October at 18:20 if easier. It's {PRICE} a player, and we handle sign-ups and payments, so it's one link for the team.
+Just following up on my note about setting up a regular football game for the team near Wilson Street, perhaps even a friendly against another firm. If it's of interest, or you know who to point me to, I'd love to hear.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ66" s="20">
-        <f>IF(OR(AG66="",AO66=""),"",SUBSTITUTE(AO66,"{PRICE}","£"&amp;IF(AG66=INT(AG66),TEXT(AG66,"0"),TEXT(AG66,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR66" s="20">
-        <f>IF(OR(AG66="",AP66=""),"",SUBSTITUTE(AP66,"{PRICE}","£"&amp;IF(AG66=INT(AG66),TEXT(AG66,"0"),TEXT(AG66,"0.00"))))</f>
-        <v/>
+      <c r="AQ66" s="15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="AR66" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
       </c>
       <c r="AS66" s="15" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>check headcount (likely over 500)</t>
         </is>
       </c>
       <c r="AT66" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU66" s="15" t="inlineStr">
-        <is>
-          <t>check headcount (likely over 500)</t>
-        </is>
-      </c>
-      <c r="AV66" s="18">
-        <f>IF(AU66&lt;&gt;"","No – hold: "&amp;AU66,IF(AG66="","No – no confirmed London price per player",IF(AM66="","No – no email",IF(AO66="","No – no personalised email",IF(AS66&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX66" s="21" t="n"/>
-      <c r="AY66" s="21" t="n"/>
+          <t>No – hold: check headcount (likely over 500)</t>
+        </is>
+      </c>
+      <c r="AV66" s="20" t="n"/>
+      <c r="AW66" s="20" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="15" t="n">
@@ -14966,9 +14756,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG67" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG67" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH67" s="15" t="inlineStr">
         <is>
@@ -14995,17 +14786,18 @@
         <f>IF(V67&lt;&gt;"",V67,S67)</f>
         <v/>
       </c>
-      <c r="AN67" s="18">
-        <f>IF(AG67="","","25 years in, a weekly game 11 min from City Rd")</f>
-        <v/>
+      <c r="AN67" s="15" t="inlineStr">
+        <is>
+          <t>Football near City Road for Beeline?</t>
+        </is>
       </c>
       <c r="AO67" s="19" t="inlineStr">
         <is>
-          <t>Hi Beeline.Com team,
-Congratulations on 25 years of leading the extended workforce industry - a good year to get the team together on the pitch.
-We've got a floodlit 6-a-side pitch at Moreland School, Gard Street, an 11-minute walk from your office on City Road. Monday 12 October at 18:00 is open, or 19:00 the same evening, and it can become your regular weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Shall I hold Monday for you?
+          <t>Hi Beeline team,
+Congratulations on 25 years of leading the extended workforce industry, a good year to get the team together.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about an 11-minute walk from your office on City Road.
+We're looking for someone at Beeline who'd enjoy helping start a regular after-work game for colleagues, maybe even a friendly against another firm nearby. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -15013,42 +14805,35 @@
       </c>
       <c r="AP67" s="19" t="inlineStr">
         <is>
-          <t>Hi Beeline.Com team,
-Following up on the 6-a-side pitch at Moreland School - Monday 12 October at 18:00, 19:00, or 20:00, whichever suits. It's {PRICE} a player, and we handle sign-ups and payments, so it's one link for the team.
+          <t>Hi Beeline team,
+Just following up on my note about a regular after-work football game for the team near City Road. No pressure - if there's interest, or you can point me to whoever runs socials, that would be great.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ67" s="20">
-        <f>IF(OR(AG67="",AO67=""),"",SUBSTITUTE(AO67,"{PRICE}","£"&amp;IF(AG67=INT(AG67),TEXT(AG67,"0"),TEXT(AG67,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR67" s="20">
-        <f>IF(OR(AG67="",AP67=""),"",SUBSTITUTE(AP67,"{PRICE}","£"&amp;IF(AG67=INT(AG67),TEXT(AG67,"0"),TEXT(AG67,"0.00"))))</f>
-        <v/>
+      <c r="AQ67" s="15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="AR67" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
       </c>
       <c r="AS67" s="15" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>check headcount (likely over 500)</t>
         </is>
       </c>
       <c r="AT67" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU67" s="15" t="inlineStr">
-        <is>
-          <t>check headcount (likely over 500)</t>
-        </is>
-      </c>
-      <c r="AV67" s="18">
-        <f>IF(AU67&lt;&gt;"","No – hold: "&amp;AU67,IF(AG67="","No – no confirmed London price per player",IF(AM67="","No – no email",IF(AO67="","No – no personalised email",IF(AS67&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX67" s="21" t="n"/>
-      <c r="AY67" s="21" t="n"/>
+          <t>No – hold: check headcount (likely over 500)</t>
+        </is>
+      </c>
+      <c r="AV67" s="20" t="n"/>
+      <c r="AW67" s="20" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="15" t="n">
@@ -15183,9 +14968,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG68" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG68" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH68" s="15" t="inlineStr">
         <is>
@@ -15212,17 +14998,18 @@
         <f>IF(V68&lt;&gt;"",V68,S68)</f>
         <v/>
       </c>
-      <c r="AN68" s="18">
-        <f>IF(AG68="","","5-a-side + Comradery, 11 min from Bonhill St")</f>
-        <v/>
+      <c r="AN68" s="15" t="inlineStr">
+        <is>
+          <t>Office football near Bonhill Street?</t>
+        </is>
       </c>
       <c r="AO68" s="19" t="inlineStr">
         <is>
           <t>Hi Optimove team,
-Comradery is one of your core values, and wellness and team events are built into life at Optimove - a five-a-side game would fit right in.
-We run 5-a-side at Powerleague Shoreditch, Braithwaite Street, an 11-minute walk from your office on Bonhill Street. Monday 28 September at 17:40 is open, or 19:40 the same evening, and it can become your regular weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Would your team be up for it?
+Comradery is one of your core values, with wellness and team events built into life at Optimove, and a five-a-side game would fit right in.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about an 11-minute walk from your office on Bonhill Street.
+We're looking for someone at Optimove who'd enjoy helping start a regular office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -15231,41 +15018,34 @@
       <c r="AP68" s="19" t="inlineStr">
         <is>
           <t>Hi Optimove team,
-Following up on the 5-a-side slot at Powerleague Shoreditch - Monday 28 September at 17:40, or Thursday 1 October at 18:20. It's {PRICE} a player, and we handle sign-ups and payments, so it's one link for the team.
+Just following up on my note about a regular office football game for the team near Bonhill Street. If there's interest, or you can point me to whoever looks after socials or wellbeing, I'd love to hear.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ68" s="20">
-        <f>IF(OR(AG68="",AO68=""),"",SUBSTITUTE(AO68,"{PRICE}","£"&amp;IF(AG68=INT(AG68),TEXT(AG68,"0"),TEXT(AG68,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR68" s="20">
-        <f>IF(OR(AG68="",AP68=""),"",SUBSTITUTE(AP68,"{PRICE}","£"&amp;IF(AG68=INT(AG68),TEXT(AG68,"0"),TEXT(AG68,"0.00"))))</f>
-        <v/>
+      <c r="AQ68" s="15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="AR68" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
       </c>
       <c r="AS68" s="15" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>check headcount (likely over 500)</t>
         </is>
       </c>
       <c r="AT68" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU68" s="15" t="inlineStr">
-        <is>
-          <t>check headcount (likely over 500)</t>
-        </is>
-      </c>
-      <c r="AV68" s="18">
-        <f>IF(AU68&lt;&gt;"","No – hold: "&amp;AU68,IF(AG68="","No – no confirmed London price per player",IF(AM68="","No – no email",IF(AO68="","No – no personalised email",IF(AS68&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX68" s="21" t="n"/>
-      <c r="AY68" s="21" t="n"/>
+          <t>No – hold: check headcount (likely over 500)</t>
+        </is>
+      </c>
+      <c r="AV68" s="20" t="n"/>
+      <c r="AW68" s="20" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="15" t="n">
@@ -15412,9 +15192,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG69" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG69" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH69" s="15" t="inlineStr">
         <is>
@@ -15445,14 +15226,18 @@
         <f>IF(V69&lt;&gt;"",V69,S69)</f>
         <v/>
       </c>
-      <c r="AN69" s="18">
-        <f>IF(AG69="","","After the North Capital news — a weekly game?")</f>
-        <v/>
+      <c r="AN69" s="15" t="inlineStr">
+        <is>
+          <t>Football near Wenlock Road, Ivan?</t>
+        </is>
       </c>
       <c r="AO69" s="19" t="inlineStr">
         <is>
           <t>Hi Ivan,
-With MoonPay announcing the North Capital acquisition this week, it feels like a good moment for the team to blow off some steam together. We've got a 6-a-side pitch at Moreland School, Gard Street, a 6-minute walk from Wenlock Road, with Monday 12 October at 18:00 open (or 19:00), and it can become your regular weekly game. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Shall I hold Monday for you?
+Congratulations on this week's North Capital acquisition, a big step into onchain capital markets, and a good moment for the team to blow off some steam together.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 6-minute walk from your office on Wenlock Road.
+We're looking for someone at Moonpay who'd enjoy helping start a regular office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
+Would you be up for it, or is there someone else on the team better placed to look at this?
 Best,
 Brian
 FC Urban</t>
@@ -15461,41 +15246,34 @@
       <c r="AP69" s="19" t="inlineStr">
         <is>
           <t>Hi Ivan,
-Following up on Monday 12 October at 18:00 (or 19:00) at Moreland School, 6 minutes from Wenlock Road. Still {PRICE} a player, we handle the pitch, sign-ups and payments. Shall I hold a slot for the MoonPay team?
+Just following up on my note about starting a regular office football game for the Moonpay team near Wenlock Road. Would you be up for it, or is there someone else I should speak to?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ69" s="20">
-        <f>IF(OR(AG69="",AO69=""),"",SUBSTITUTE(AO69,"{PRICE}","£"&amp;IF(AG69=INT(AG69),TEXT(AG69,"0"),TEXT(AG69,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR69" s="20">
-        <f>IF(OR(AG69="",AP69=""),"",SUBSTITUTE(AP69,"{PRICE}","£"&amp;IF(AG69=INT(AG69),TEXT(AG69,"0"),TEXT(AG69,"0.00"))))</f>
-        <v/>
+      <c r="AQ69" s="15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="AR69" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
       </c>
       <c r="AS69" s="15" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>check headcount (likely over 500)</t>
         </is>
       </c>
       <c r="AT69" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU69" s="15" t="inlineStr">
-        <is>
-          <t>check headcount (likely over 500)</t>
-        </is>
-      </c>
-      <c r="AV69" s="18">
-        <f>IF(AU69&lt;&gt;"","No – hold: "&amp;AU69,IF(AG69="","No – no confirmed London price per player",IF(AM69="","No – no email",IF(AO69="","No – no personalised email",IF(AS69&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX69" s="21" t="n"/>
-      <c r="AY69" s="21" t="n"/>
+          <t>No – hold: check headcount (likely over 500)</t>
+        </is>
+      </c>
+      <c r="AV69" s="20" t="n"/>
+      <c r="AW69" s="20" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="15" t="n">
@@ -15630,9 +15408,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG70" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG70" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH70" s="15" t="inlineStr">
         <is>
@@ -15663,14 +15442,18 @@
         <f>IF(V70&lt;&gt;"",V70,S70)</f>
         <v/>
       </c>
-      <c r="AN70" s="18">
-        <f>IF(AG70="","","A 6-a-side pitch near 375 City Road")</f>
-        <v/>
+      <c r="AN70" s="15" t="inlineStr">
+        <is>
+          <t>Office football near City Road for TVF?</t>
+        </is>
       </c>
       <c r="AO70" s="19" t="inlineStr">
         <is>
-          <t>Hi Tvf team,
-Your TVF Communications team has spent over 30 years helping pharma and biotech clients explain complex science clearly, which takes a good team spirit to sustain. That's exactly what a regular match builds. We have a floodlit 6-a-side 3G pitch at Moreland School, Gard Street, just off Old Street, an 8-minute walk from 375 City Road. There's a slot free Monday 12 October at 18:00, or 19:00, and it could become your standing weekly game. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Would your team be up for it?
+          <t>Hi TVF team,
+Your TVF Communications team has spent over 30 years helping pharma and biotech clients explain complex science clearly, which takes real team spirit to sustain.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about an 8-minute walk from your office on 375 City Road.
+We're looking for someone at TVF who'd enjoy helping start a regular office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -15678,42 +15461,35 @@
       </c>
       <c r="AP70" s="19" t="inlineStr">
         <is>
-          <t>Hi Tvf team,
-Following up on a weekly 6-a-side near 375 City Road. Monday 12 October at 19:00 at Moreland School is still open. It's {PRICE} a player, and we handle the pitch, sign-ups and payments end to end. Let me know if that works.
+          <t>Hi TVF team,
+Just following up on my note about a regular office football game for the team near City Road. If there's interest, or you know who best to forward this to, I'd love to hear.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ70" s="20">
-        <f>IF(OR(AG70="",AO70=""),"",SUBSTITUTE(AO70,"{PRICE}","£"&amp;IF(AG70=INT(AG70),TEXT(AG70,"0"),TEXT(AG70,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR70" s="20">
-        <f>IF(OR(AG70="",AP70=""),"",SUBSTITUTE(AP70,"{PRICE}","£"&amp;IF(AG70=INT(AG70),TEXT(AG70,"0"),TEXT(AG70,"0.00"))))</f>
-        <v/>
+      <c r="AQ70" s="15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="AR70" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
       </c>
       <c r="AS70" s="15" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>inbox is another country or CV/careers inbox</t>
         </is>
       </c>
       <c r="AT70" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU70" s="15" t="inlineStr">
-        <is>
-          <t>inbox is another country or CV/careers inbox</t>
-        </is>
-      </c>
-      <c r="AV70" s="18">
-        <f>IF(AU70&lt;&gt;"","No – hold: "&amp;AU70,IF(AG70="","No – no confirmed London price per player",IF(AM70="","No – no email",IF(AO70="","No – no personalised email",IF(AS70&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX70" s="21" t="n"/>
-      <c r="AY70" s="21" t="n"/>
+          <t>No – hold: inbox is another country or CV/careers inbox</t>
+        </is>
+      </c>
+      <c r="AV70" s="20" t="n"/>
+      <c r="AW70" s="20" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="15" t="n">
@@ -15842,9 +15618,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG71" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG71" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH71" s="15" t="inlineStr">
         <is>
@@ -15875,16 +15652,18 @@
         <f>IF(V71&lt;&gt;"",V71,S71)</f>
         <v/>
       </c>
-      <c r="AN71" s="18">
-        <f>IF(AG71="","","5-a-side, 11 minutes from Bonhill Street")</f>
-        <v/>
+      <c r="AN71" s="15" t="inlineStr">
+        <is>
+          <t>Office football for the Datasite team?</t>
+        </is>
       </c>
       <c r="AO71" s="19" t="inlineStr">
         <is>
           <t>Hi Datasite team,
-We run 5-a-side at Powerleague Shoreditch, Braithwaite Street, an 11-minute walk from your office on Bonhill Street. Monday 28 September at 17:40 is open, or 19:40 the same evening, and it can become a regular weekly fixture for your team of 44.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Would your team be up for it?
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about an 11-minute walk from your office at EC2A 4DN.
+We're looking for someone at Datasite who'd enjoy helping start a regular office kickabout for colleagues, something that could easily become a standing weekly fixture. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+More on how it works: FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates).
 Best,
 Brian
 FC Urban</t>
@@ -15893,41 +15672,34 @@
       <c r="AP71" s="19" t="inlineStr">
         <is>
           <t>Hi Datasite team,
-Following up on the 5-a-side slot at Powerleague Shoreditch - Monday 28 September at 17:40, or Thursday 1 October at 18:20. It's {PRICE} a player, and we handle sign-ups and payments, so it's one link for the team.
+Just following up on my note about starting a regular office football game for the team near EC2A 4DN. If there's interest, or you can point me to whoever looks after socials, I'd love to hear.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ71" s="20">
-        <f>IF(OR(AG71="",AO71=""),"",SUBSTITUTE(AO71,"{PRICE}","£"&amp;IF(AG71=INT(AG71),TEXT(AG71,"0"),TEXT(AG71,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR71" s="20">
-        <f>IF(OR(AG71="",AP71=""),"",SUBSTITUTE(AP71,"{PRICE}","£"&amp;IF(AG71=INT(AG71),TEXT(AG71,"0"),TEXT(AG71,"0.00"))))</f>
-        <v/>
+      <c r="AQ71" s="15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="AR71" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
       </c>
       <c r="AS71" s="15" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>check headcount (likely over 500)</t>
         </is>
       </c>
       <c r="AT71" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU71" s="15" t="inlineStr">
-        <is>
-          <t>check headcount (likely over 500)</t>
-        </is>
-      </c>
-      <c r="AV71" s="18">
-        <f>IF(AU71&lt;&gt;"","No – hold: "&amp;AU71,IF(AG71="","No – no confirmed London price per player",IF(AM71="","No – no email",IF(AO71="","No – no personalised email",IF(AS71&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX71" s="21" t="n"/>
-      <c r="AY71" s="21" t="n"/>
+          <t>No – hold: check headcount (likely over 500)</t>
+        </is>
+      </c>
+      <c r="AV71" s="20" t="n"/>
+      <c r="AW71" s="20" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="15" t="n">
@@ -16062,9 +15834,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG72" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG72" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH72" s="15" t="n"/>
       <c r="AI72" s="15" t="n"/>
@@ -16087,14 +15860,18 @@
         <f>IF(V72&lt;&gt;"",V72,S72)</f>
         <v/>
       </c>
-      <c r="AN72" s="18">
-        <f>IF(AG72="","","6 min from Blundell Street — a weekly game")</f>
-        <v/>
+      <c r="AN72" s="15" t="inlineStr">
+        <is>
+          <t>Office football near Blundell Street?</t>
+        </is>
       </c>
       <c r="AO72" s="19" t="inlineStr">
         <is>
-          <t>Hi Side team,
-We've got a 5-a-side pitch at Market Road Pitches, Market Road, a 6-minute walk from Blundell Street, with Monday 28 September at 18:00 open, and it's an easy way to start a regular weekly game for the team. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with everyone. Would your team be up for it?
+          <t>Hi there,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Market Road (Caledonian Road) (https://www.fcurban.com/locations/market-road), about a 6-minute walk from your office on Blundell Street.
+We're looking for someone at Side who'd enjoy helping start a regular office kickabout for the team, something that could easily become a standing weekly game. We handle the pitch, extra players if you're short, payments and organisation.
+Would you be up for it, or is there someone else on the team better placed to look at this?
+More on how it works: FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates).
 Best,
 Brian
 FC Urban</t>
@@ -16102,42 +15879,35 @@
       </c>
       <c r="AP72" s="19" t="inlineStr">
         <is>
-          <t>Hi Side team,
-Following up on Monday 28 September at 18:00 at Market Road Pitches, 6 minutes from Blundell Street. Still {PRICE} a player, we handle the pitch, sign-ups and payments. Shall I hold the slot for you?
+          <t>Hi there,
+Just following up on my note about starting a regular office football game for the Side team near Blundell Street. Would you be up for it, or is there someone else I should speak to?
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ72" s="20">
-        <f>IF(OR(AG72="",AO72=""),"",SUBSTITUTE(AO72,"{PRICE}","£"&amp;IF(AG72=INT(AG72),TEXT(AG72,"0"),TEXT(AG72,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR72" s="20">
-        <f>IF(OR(AG72="",AP72=""),"",SUBSTITUTE(AP72,"{PRICE}","£"&amp;IF(AG72=INT(AG72),TEXT(AG72,"0"),TEXT(AG72,"0.00"))))</f>
-        <v/>
+      <c r="AQ72" s="15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="AR72" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
       </c>
       <c r="AS72" s="15" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>website may be a different company</t>
         </is>
       </c>
       <c r="AT72" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU72" s="15" t="inlineStr">
-        <is>
-          <t>website may be a different company</t>
-        </is>
-      </c>
-      <c r="AV72" s="18">
-        <f>IF(AU72&lt;&gt;"","No – hold: "&amp;AU72,IF(AG72="","No – no confirmed London price per player",IF(AM72="","No – no email",IF(AO72="","No – no personalised email",IF(AS72&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX72" s="21" t="n"/>
-      <c r="AY72" s="21" t="n"/>
+          <t>No – hold: website may be a different company</t>
+        </is>
+      </c>
+      <c r="AV72" s="20" t="n"/>
+      <c r="AW72" s="20" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="15" t="n">
@@ -16280,9 +16050,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG73" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG73" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH73" s="15" t="n"/>
       <c r="AI73" s="15" t="n"/>
@@ -16305,16 +16076,18 @@
         <f>IF(V73&lt;&gt;"",V73,S73)</f>
         <v/>
       </c>
-      <c r="AN73" s="18">
-        <f>IF(AG73="","","A 2-minute pitch from Redchurch Street")</f>
-        <v/>
+      <c r="AN73" s="15" t="inlineStr">
+        <is>
+          <t>Football 2 minutes from Redchurch Street</t>
+        </is>
       </c>
       <c r="AO73" s="19" t="inlineStr">
         <is>
           <t>Hi Mother London team,
-We run a 5-a-side pitch at Powerleague Shoreditch, Braithwaite Street, a 2-minute walk from Redchurch Street. There's a slot free Monday 28 September at 17:40, or Monday 28 September at 19:40, and it could easily become your regular weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Would your team be up for it?
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), just a 2-minute walk from your office on Redchurch Street.
+We're looking for someone at Mother London who'd enjoy helping start a regular office kickabout for the studio, something that could easily become a standing weekly game. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+More on how it works: FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates).
 Best,
 Brian
 FC Urban</t>
@@ -16322,42 +16095,35 @@
       </c>
       <c r="AP73" s="19" t="inlineStr">
         <is>
-          <t>Hi again,
-Still holding that 5-a-side slot at Powerleague Shoreditch on Monday 28 September at 17:40, 2 minutes from Redchurch Street. It's {PRICE} a player, and we handle the booking and payments, so it's one link for the team. Worth a go?
+          <t>Hi Mother London team,
+Just following up on my note about a regular office football game for the studio, just two minutes from Redchurch Street. If there's interest, or you can point me to whoever looks after socials, I'd love to hear.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ73" s="20">
-        <f>IF(OR(AG73="",AO73=""),"",SUBSTITUTE(AO73,"{PRICE}","£"&amp;IF(AG73=INT(AG73),TEXT(AG73,"0"),TEXT(AG73,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR73" s="20">
-        <f>IF(OR(AG73="",AP73=""),"",SUBSTITUTE(AP73,"{PRICE}","£"&amp;IF(AG73=INT(AG73),TEXT(AG73,"0"),TEXT(AG73,"0.00"))))</f>
-        <v/>
+      <c r="AQ73" s="15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="AR73" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
       </c>
       <c r="AS73" s="15" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>website may be a different company</t>
         </is>
       </c>
       <c r="AT73" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU73" s="15" t="inlineStr">
-        <is>
-          <t>website may be a different company</t>
-        </is>
-      </c>
-      <c r="AV73" s="18">
-        <f>IF(AU73&lt;&gt;"","No – hold: "&amp;AU73,IF(AG73="","No – no confirmed London price per player",IF(AM73="","No – no email",IF(AO73="","No – no personalised email",IF(AS73&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX73" s="21" t="n"/>
-      <c r="AY73" s="21" t="n"/>
+          <t>No – hold: website may be a different company</t>
+        </is>
+      </c>
+      <c r="AV73" s="20" t="n"/>
+      <c r="AW73" s="20" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="15" t="n">
@@ -16500,9 +16266,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG74" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG74" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH74" s="15" t="inlineStr">
         <is>
@@ -16533,17 +16300,18 @@
         <f>IF(V74&lt;&gt;"",V74,S74)</f>
         <v/>
       </c>
-      <c r="AN74" s="18">
-        <f>IF(AG74="","","Five-a-side, 7 minutes from your office")</f>
-        <v/>
+      <c r="AN74" s="15" t="inlineStr">
+        <is>
+          <t>Weekly football for the Paloma team?</t>
+        </is>
       </c>
       <c r="AO74" s="19" t="inlineStr">
         <is>
           <t>Hi Donald,
-You spend your days backing fund managers with the infrastructure to perform. A weekly five-a-side could do the same for your own team.
-We've a 5-a-side pitch at Powerleague Shoreditch, Braithwaite Street, a 7-minute walk from your office. There's a slot free Monday 28 September at 17:40, or Thursday 1 October at 18:20, and it could become your regular weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Shall I hold Monday for you?
+You spend your days backing fund managers with the capital and infrastructure to focus on performance. A weekly five-a-side could do something similar for your own team.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 7-minute walk from your office at EC2A 2DA.
+We're looking for someone at Paloma who'd enjoy helping start a regular after-work game for the team. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -16552,41 +16320,34 @@
       <c r="AP74" s="19" t="inlineStr">
         <is>
           <t>Hi Donald,
-Following up on the five-a-side slot at Powerleague Shoreditch, 7 minutes from your office. Thursday 1 October at 18:20 is still open. It's {PRICE} a player, and we handle the booking and payments, so it's one link for the team. Worth trying?
+Just following up on my note about a regular after-work football game for the Paloma team. If it's of interest, or you know who'd be best placed to look at it, I'd love to hear.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ74" s="20">
-        <f>IF(OR(AG74="",AO74=""),"",SUBSTITUTE(AO74,"{PRICE}","£"&amp;IF(AG74=INT(AG74),TEXT(AG74,"0"),TEXT(AG74,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR74" s="20">
-        <f>IF(OR(AG74="",AP74=""),"",SUBSTITUTE(AP74,"{PRICE}","£"&amp;IF(AG74=INT(AG74),TEXT(AG74,"0"),TEXT(AG74,"0.00"))))</f>
-        <v/>
+      <c r="AQ74" s="15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="AR74" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
       </c>
       <c r="AS74" s="15" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>website may be a different company</t>
         </is>
       </c>
       <c r="AT74" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU74" s="15" t="inlineStr">
-        <is>
-          <t>website may be a different company</t>
-        </is>
-      </c>
-      <c r="AV74" s="18">
-        <f>IF(AU74&lt;&gt;"","No – hold: "&amp;AU74,IF(AG74="","No – no confirmed London price per player",IF(AM74="","No – no email",IF(AO74="","No – no personalised email",IF(AS74&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX74" s="21" t="n"/>
-      <c r="AY74" s="21" t="n"/>
+          <t>No – hold: website may be a different company</t>
+        </is>
+      </c>
+      <c r="AV74" s="20" t="n"/>
+      <c r="AW74" s="20" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="15" t="n">
@@ -16717,9 +16478,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG75" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG75" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH75" s="15" t="n"/>
       <c r="AI75" s="15" t="n"/>
@@ -16742,14 +16504,18 @@
         <f>IF(V75&lt;&gt;"",V75,S75)</f>
         <v/>
       </c>
-      <c r="AN75" s="18">
-        <f>IF(AG75="","","6 minutes from your office: weekly 5-a-side")</f>
-        <v/>
+      <c r="AN75" s="15" t="inlineStr">
+        <is>
+          <t>Weekly football for the Squadron team?</t>
+        </is>
       </c>
       <c r="AO75" s="19" t="inlineStr">
         <is>
           <t>Hi Squadron team,
-We've got a 5-a-side pitch at Powerleague Shoreditch, Braithwaite Street, E1 6GJ, about a 6-minute walk from your office. There's a slot open Monday 28 September at 17:40, or 19:40 if that's easier, and it could become your weekly game. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Would your team be up for it?
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 6-minute walk from your office at E1 6AD.
+We're looking for someone at Squadron who'd enjoy helping start a regular after-work game for the team, maybe even a friendly against another firm nearby. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+More on how it works: FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates).
 Best,
 Brian
 FC Urban</t>
@@ -16758,41 +16524,34 @@
       <c r="AP75" s="19" t="inlineStr">
         <is>
           <t>Hi Squadron team,
-Following up on the 5-a-side slot at Powerleague Shoreditch, a short walk from your office — Monday 28 September at 17:40 is still open, or Thursday 1 October at 18:20. It's {PRICE} a player; we handle the booking and payments. Let me know if you'd like it held.
+Just following up on my note about a regular after-work football game for the team near E1 6AD. If there's interest, or you can point me to whoever looks after socials, I'd love to hear.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ75" s="20">
-        <f>IF(OR(AG75="",AO75=""),"",SUBSTITUTE(AO75,"{PRICE}","£"&amp;IF(AG75=INT(AG75),TEXT(AG75,"0"),TEXT(AG75,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR75" s="20">
-        <f>IF(OR(AG75="",AP75=""),"",SUBSTITUTE(AP75,"{PRICE}","£"&amp;IF(AG75=INT(AG75),TEXT(AG75,"0"),TEXT(AG75,"0.00"))))</f>
-        <v/>
+      <c r="AQ75" s="15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="AR75" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
       </c>
       <c r="AS75" s="15" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>website may be a different company</t>
         </is>
       </c>
       <c r="AT75" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU75" s="15" t="inlineStr">
-        <is>
-          <t>website may be a different company</t>
-        </is>
-      </c>
-      <c r="AV75" s="18">
-        <f>IF(AU75&lt;&gt;"","No – hold: "&amp;AU75,IF(AG75="","No – no confirmed London price per player",IF(AM75="","No – no email",IF(AO75="","No – no personalised email",IF(AS75&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX75" s="21" t="n"/>
-      <c r="AY75" s="21" t="n"/>
+          <t>No – hold: website may be a different company</t>
+        </is>
+      </c>
+      <c r="AV75" s="20" t="n"/>
+      <c r="AW75" s="20" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="15" t="n">
@@ -16927,9 +16686,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG76" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG76" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH76" s="15" t="n"/>
       <c r="AI76" s="15" t="n"/>
@@ -16952,16 +16712,18 @@
         <f>IF(V76&lt;&gt;"",V76,S76)</f>
         <v/>
       </c>
-      <c r="AN76" s="18">
-        <f>IF(AG76="","","A weekly 6-a-side pitch 11 minutes from Old Street")</f>
-        <v/>
+      <c r="AN76" s="15" t="inlineStr">
+        <is>
+          <t>Office football near Old Street?</t>
+        </is>
       </c>
       <c r="AO76" s="19" t="inlineStr">
         <is>
           <t>Hi Northdoor team,
-We've got a floodlit 3G pitch at Moreland School, just off Old Street, an 11-minute walk from your office on Old Street. There's a 6-a-side slot free on Monday 12 October at 18:00, or 19:00 if that suits better, and it can easily become a regular weekly game for your team.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Would your team be up for it?
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about an 11-minute walk from your office on Old Street.
+We're looking for someone at Northdoor who'd enjoy helping start a regular office kickabout for the team, something that could easily become a standing weekly fixture. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+More on how it works: FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates).
 Best,
 Brian
 FC Urban</t>
@@ -16969,41 +16731,35 @@
       </c>
       <c r="AP76" s="19" t="inlineStr">
         <is>
-          <t>Following up on Monday 12 October — the 6-a-side slot at Moreland School (18:00 or 19:00) is still free, an 11-minute walk from your office. It's {PRICE} a player, and we handle the pitch booking and payments end to end. Keen to get Northdoor a regular weekly game.
+          <t>Hi Northdoor team,
+Just following up on my note about a regular office football game for the team near Old Street. If there's interest, or you can point me to whoever looks after socials, I'd love to hear.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ76" s="20">
-        <f>IF(OR(AG76="",AO76=""),"",SUBSTITUTE(AO76,"{PRICE}","£"&amp;IF(AG76=INT(AG76),TEXT(AG76,"0"),TEXT(AG76,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR76" s="20">
-        <f>IF(OR(AG76="",AP76=""),"",SUBSTITUTE(AP76,"{PRICE}","£"&amp;IF(AG76=INT(AG76),TEXT(AG76,"0"),TEXT(AG76,"0.00"))))</f>
-        <v/>
+      <c r="AQ76" s="15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="AR76" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
       </c>
       <c r="AS76" s="15" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>website may be a different company</t>
         </is>
       </c>
       <c r="AT76" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU76" s="15" t="inlineStr">
-        <is>
-          <t>website may be a different company</t>
-        </is>
-      </c>
-      <c r="AV76" s="18">
-        <f>IF(AU76&lt;&gt;"","No – hold: "&amp;AU76,IF(AG76="","No – no confirmed London price per player",IF(AM76="","No – no email",IF(AO76="","No – no personalised email",IF(AS76&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX76" s="21" t="n"/>
-      <c r="AY76" s="21" t="n"/>
+          <t>No – hold: website may be a different company</t>
+        </is>
+      </c>
+      <c r="AV76" s="20" t="n"/>
+      <c r="AW76" s="20" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="15" t="n">
@@ -17138,9 +16894,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG77" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG77" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH77" s="15" t="n"/>
       <c r="AI77" s="15" t="n"/>
@@ -17163,16 +16920,18 @@
         <f>IF(V77&lt;&gt;"",V77,S77)</f>
         <v/>
       </c>
-      <c r="AN77" s="18">
-        <f>IF(AG77="","","A weekly 6-a-side game, 12 minutes from Amwell Street")</f>
-        <v/>
+      <c r="AN77" s="15" t="inlineStr">
+        <is>
+          <t>Office football near Amwell Street?</t>
+        </is>
       </c>
       <c r="AO77" s="19" t="inlineStr">
         <is>
           <t>Hi Lightbox Media team,
-We've a floodlit 3G pitch at Moreland School, just off Old Street, a 12-minute walk from Amwell Street. There's a 6-a-side slot free on Monday 12 October at 18:00, or 19:00 if that works better, and it can become your regular weekly game.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Would your team be up for it?
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 12-minute walk from your office on Amwell Street.
+We're looking for someone at Lightbox Media who'd enjoy helping start a regular office kickabout for the studio, something that could easily become a standing weekly game. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+More on how it works: FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates).
 Best,
 Brian
 FC Urban</t>
@@ -17180,41 +16939,35 @@
       </c>
       <c r="AP77" s="19" t="inlineStr">
         <is>
-          <t>Following up on Monday 12 October — the 6-a-side slot at Moreland School (18:00 or 19:00) is still free, 12 minutes from Amwell Street. It's {PRICE} a player, and we handle the pitch booking and payments end to end. Would this work as your weekly game?
+          <t>Hi Lightbox Media team,
+Just following up on my note about a regular office football game for the studio near Amwell Street. If there's interest, or you can point me to whoever looks after socials, I'd love to hear.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ77" s="20">
-        <f>IF(OR(AG77="",AO77=""),"",SUBSTITUTE(AO77,"{PRICE}","£"&amp;IF(AG77=INT(AG77),TEXT(AG77,"0"),TEXT(AG77,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR77" s="20">
-        <f>IF(OR(AG77="",AP77=""),"",SUBSTITUTE(AP77,"{PRICE}","£"&amp;IF(AG77=INT(AG77),TEXT(AG77,"0"),TEXT(AG77,"0.00"))))</f>
-        <v/>
+      <c r="AQ77" s="15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="AR77" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
       </c>
       <c r="AS77" s="15" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>website may be a different company</t>
         </is>
       </c>
       <c r="AT77" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU77" s="15" t="inlineStr">
-        <is>
-          <t>website may be a different company</t>
-        </is>
-      </c>
-      <c r="AV77" s="18">
-        <f>IF(AU77&lt;&gt;"","No – hold: "&amp;AU77,IF(AG77="","No – no confirmed London price per player",IF(AM77="","No – no email",IF(AO77="","No – no personalised email",IF(AS77&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX77" s="21" t="n"/>
-      <c r="AY77" s="21" t="n"/>
+          <t>No – hold: website may be a different company</t>
+        </is>
+      </c>
+      <c r="AV77" s="20" t="n"/>
+      <c r="AW77" s="20" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="15" t="n">
@@ -17345,9 +17098,10 @@
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="AG78" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG78" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH78" s="15" t="n"/>
       <c r="AI78" s="15" t="n"/>
@@ -17370,16 +17124,18 @@
         <f>IF(V78&lt;&gt;"",V78,S78)</f>
         <v/>
       </c>
-      <c r="AN78" s="18">
-        <f>IF(AG78="","","A weekly 6-a-side pitch, 12 minutes from your N1 office")</f>
-        <v/>
+      <c r="AN78" s="15" t="inlineStr">
+        <is>
+          <t>Office football for Creative Monster?</t>
+        </is>
       </c>
       <c r="AO78" s="19" t="inlineStr">
         <is>
           <t>Hi Creative Monster team,
-We've a floodlit 3G pitch at Moreland School, just off Old Street, a 12-minute walk from your N1 office. There's a 6-a-side slot free on Monday 12 October at 18:00, or 19:00 if that suits better, and it can become a regular weekly fixture for the team.
-It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team.
-Would your team be up for it?
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 12-minute walk from your office at N1 6AD.
+We're looking for someone at Creative Monster who'd enjoy helping start a regular office kickabout for the studio, something that could easily become a standing weekly fixture. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+More on how it works: FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates).
 Best,
 Brian
 FC Urban</t>
@@ -17387,41 +17143,35 @@
       </c>
       <c r="AP78" s="19" t="inlineStr">
         <is>
-          <t>Following up on Monday 12 October — the 6-a-side slot at Moreland School (18:00 or 19:00) is still free, 12 minutes from your N1 office. It's {PRICE} a player, and we handle the pitch booking and payments end to end. Would this suit as a weekly game?
+          <t>Hi Creative Monster team,
+Just following up on my note about a regular office football game for the studio near N1 6AD. If there's interest, or you can point me to whoever looks after socials, I'd love to hear.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ78" s="20">
-        <f>IF(OR(AG78="",AO78=""),"",SUBSTITUTE(AO78,"{PRICE}","£"&amp;IF(AG78=INT(AG78),TEXT(AG78,"0"),TEXT(AG78,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR78" s="20">
-        <f>IF(OR(AG78="",AP78=""),"",SUBSTITUTE(AP78,"{PRICE}","£"&amp;IF(AG78=INT(AG78),TEXT(AG78,"0"),TEXT(AG78,"0.00"))))</f>
-        <v/>
+      <c r="AQ78" s="15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="AR78" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
       </c>
       <c r="AS78" s="15" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>website may be a different company</t>
         </is>
       </c>
       <c r="AT78" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU78" s="15" t="inlineStr">
-        <is>
-          <t>website may be a different company</t>
-        </is>
-      </c>
-      <c r="AV78" s="18">
-        <f>IF(AU78&lt;&gt;"","No – hold: "&amp;AU78,IF(AG78="","No – no confirmed London price per player",IF(AM78="","No – no email",IF(AO78="","No – no personalised email",IF(AS78&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX78" s="21" t="n"/>
-      <c r="AY78" s="21" t="n"/>
+          <t>No – hold: website may be a different company</t>
+        </is>
+      </c>
+      <c r="AV78" s="20" t="n"/>
+      <c r="AW78" s="20" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="15" t="n">
@@ -17552,9 +17302,10 @@
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="AG79" s="17">
-        <f>IF(Offer!$D$5="","",Offer!$D$5)</f>
-        <v/>
+      <c r="AG79" s="17" t="inlineStr">
+        <is>
+          <t>Not in first email</t>
+        </is>
       </c>
       <c r="AH79" s="15" t="inlineStr">
         <is>
@@ -17585,14 +17336,18 @@
         <f>IF(V79&lt;&gt;"",V79,S79)</f>
         <v/>
       </c>
-      <c r="AN79" s="18">
-        <f>IF(AG79="","","Stakingverse's $14M TVL and a weekly kickabout")</f>
-        <v/>
+      <c r="AN79" s="15" t="inlineStr">
+        <is>
+          <t>Weekly football for the Sigmatic team?</t>
+        </is>
       </c>
       <c r="AO79" s="19" t="inlineStr">
         <is>
           <t>Hi Sigmatic team,
-Great to see what you've built with Stakingverse, reaching $14M in peak TVL, sounds like a team that could use a regular break from the screens. We have a five-a-side pitch at Powerleague Shoreditch, Braithwaite Street, a 15-minute walk from EC3A. There's a slot on Monday 28 September at 17:40, or 19:40 if that suits, and it can become your regular weekly game. It's {PRICE} a player, and we book the pitch and handle sign-ups and payments, so someone just shares one link with the team. Would your team be up for it?
+Great to see what you've built with Stakingverse, reaching $14M in peak TVL, sounds like a team that could use a regular break from the screens.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 15-minute walk from your office at EC3A 8BE.
+We're looking for someone at Sigmatic who'd enjoy helping start a regular after-work game for the team. We handle the pitch, extra players if you're short, payments and organisation.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
 Brian
 FC Urban</t>
@@ -17600,69 +17355,63 @@
       </c>
       <c r="AP79" s="19" t="inlineStr">
         <is>
-          <t>Hi again, still fancy a weekly five-a-side for the Sigmatic team? Powerleague Shoreditch has Thursday 1 October at 18:20 free, 15 minutes from EC3A. It's {PRICE} a player, we handle the booking, one link for everyone. Worth a try?
+          <t>Hi Sigmatic team,
+Just following up on my note about a regular after-work football game for the team. If there's interest, or you know who'd be best placed to look at it, I'd love to hear.
 Best,
 Brian
 FC Urban</t>
         </is>
       </c>
-      <c r="AQ79" s="20">
-        <f>IF(OR(AG79="",AO79=""),"",SUBSTITUTE(AO79,"{PRICE}","£"&amp;IF(AG79=INT(AG79),TEXT(AG79,"0"),TEXT(AG79,"0.00"))))</f>
-        <v/>
-      </c>
-      <c r="AR79" s="20">
-        <f>IF(OR(AG79="",AP79=""),"",SUBSTITUTE(AP79,"{PRICE}","£"&amp;IF(AG79=INT(AG79),TEXT(AG79,"0"),TEXT(AG79,"0.00"))))</f>
-        <v/>
+      <c r="AQ79" s="15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="AR79" s="15" t="inlineStr">
+        <is>
+          <t>MX ok · mailbox not verified</t>
+        </is>
       </c>
       <c r="AS79" s="15" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>website may be a different company</t>
         </is>
       </c>
       <c r="AT79" s="15" t="inlineStr">
         <is>
-          <t>MX ok · mailbox not verified</t>
-        </is>
-      </c>
-      <c r="AU79" s="15" t="inlineStr">
-        <is>
-          <t>website may be a different company</t>
-        </is>
-      </c>
-      <c r="AV79" s="18">
-        <f>IF(AU79&lt;&gt;"","No – hold: "&amp;AU79,IF(AG79="","No – no confirmed London price per player",IF(AM79="","No – no email",IF(AO79="","No – no personalised email",IF(AS79&lt;&gt;"pass","No – suppressed","Yes")))))</f>
-        <v/>
-      </c>
-      <c r="AX79" s="21" t="n"/>
-      <c r="AY79" s="21" t="n"/>
+          <t>No – hold: website may be a different company</t>
+        </is>
+      </c>
+      <c r="AV79" s="20" t="n"/>
+      <c r="AW79" s="20" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:BE79"/>
+  <autoFilter ref="A2:BC79"/>
   <mergeCells count="6">
-    <mergeCell ref="AC1:AR1"/>
+    <mergeCell ref="AQ1:AT1"/>
     <mergeCell ref="X1:AB1"/>
-    <mergeCell ref="AW1:BE1"/>
     <mergeCell ref="A1:O1"/>
+    <mergeCell ref="AC1:AP1"/>
     <mergeCell ref="P1:W1"/>
-    <mergeCell ref="AS1:AV1"/>
+    <mergeCell ref="AU1:BC1"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation sqref="AW3:AW1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AU3:AU1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Brian"</formula1>
     </dataValidation>
+    <dataValidation sqref="AX3:AX1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
     <dataValidation sqref="AZ3:AZ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="BA3:BA1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation sqref="BB3:BB1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="BC3:BC1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="BD3:BD1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="BA3:BA1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AY3:AY1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Interested,Call requested,Not now,Not interested,Wrong person,Opt-out,Bounce,Out of office"</formula1>
     </dataValidation>
   </dataValidations>
@@ -17937,95 +17686,95 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="22" t="inlineStr">
+      <c r="B1" s="21" t="inlineStr">
         <is>
           <t>Confirmed price per player (one row per city)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="23" t="inlineStr">
-        <is>
-          <t>Drafts stay empty and Draftable says No until the London price is filled in. Never type TBC.</t>
+      <c r="B2" s="22" t="inlineStr">
+        <is>
+          <t>Not used in the first (interest-check) email. Used later in the group-invite email once a company says yes. Never type TBC.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>Price per player</t>
         </is>
       </c>
-      <c r="E4" s="24" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>Confirmed by</t>
         </is>
       </c>
-      <c r="F4" s="24" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t>Confirmed on</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>London</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="D5" s="26" t="n"/>
-      <c r="E5" s="27" t="n"/>
-      <c r="F5" s="28" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="27" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Stockholm</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>SEK</t>
         </is>
       </c>
-      <c r="D6" s="29" t="n"/>
-      <c r="E6" s="27" t="n"/>
-      <c r="F6" s="28" t="n"/>
+      <c r="D6" s="28" t="n"/>
+      <c r="E6" s="26" t="n"/>
+      <c r="F6" s="27" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Sender for this sheet</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>Brian</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>Sending inbox</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>brian@fcurban.com</t>
         </is>
@@ -18056,194 +17805,194 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>Pitch</t>
         </is>
       </c>
-      <c r="B1" s="30" t="inlineStr">
+      <c r="B1" s="29" t="inlineStr">
         <is>
           <t>Offer in email</t>
         </is>
       </c>
-      <c r="C1" s="30" t="inlineStr">
+      <c r="C1" s="29" t="inlineStr">
         <is>
           <t>Recurring or one-off</t>
         </is>
       </c>
-      <c r="D1" s="30" t="inlineStr">
+      <c r="D1" s="29" t="inlineStr">
         <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="E1" s="30" t="inlineStr">
+      <c r="E1" s="29" t="inlineStr">
         <is>
           <t>First date</t>
         </is>
       </c>
-      <c r="F1" s="30" t="inlineStr">
+      <c r="F1" s="29" t="inlineStr">
         <is>
           <t>Kick-off</t>
         </is>
       </c>
-      <c r="G1" s="30" t="inlineStr">
+      <c r="G1" s="29" t="inlineStr">
         <is>
           <t>Open Mon–Thu 17:30–20:00 slots (next 3 weeks)</t>
         </is>
       </c>
-      <c r="H1" s="30" t="inlineStr">
+      <c r="H1" s="29" t="inlineStr">
         <is>
           <t>Booking source</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>Market Road</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="22" t="inlineStr">
         <is>
           <t>Monday 28 September at 18:00</t>
         </is>
       </c>
-      <c r="C2" s="23" t="inlineStr">
+      <c r="C2" s="22" t="inlineStr">
         <is>
           <t>One-off</t>
         </is>
       </c>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="D2" s="22" t="inlineStr">
         <is>
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="E2" s="31" t="n">
+      <c r="E2" s="30" t="n">
         <v>46293</v>
       </c>
-      <c r="F2" s="23" t="inlineStr">
+      <c r="F2" s="22" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="G2" s="23" t="n">
+      <c r="G2" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="23" t="inlineStr">
+      <c r="H2" s="22" t="inlineStr">
         <is>
           <t>Better (GLL) - Islington Tennis Centre</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>Old St - Moreland Primary School</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>Monday 12 October at 18:00</t>
         </is>
       </c>
-      <c r="C3" s="23" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>One-off</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>6-a-side</t>
         </is>
       </c>
-      <c r="E3" s="31" t="n">
+      <c r="E3" s="30" t="n">
         <v>46307</v>
       </c>
-      <c r="F3" s="23" t="inlineStr">
+      <c r="F3" s="22" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="G3" s="23" t="n">
+      <c r="G3" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="H3" s="23" t="inlineStr">
+      <c r="H3" s="22" t="inlineStr">
         <is>
           <t>PlayFootball</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>Shoreditch Powerleague</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>Monday 28 September at 17:40</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>One-off</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="22" t="inlineStr">
         <is>
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="E4" s="31" t="n">
+      <c r="E4" s="30" t="n">
         <v>46293</v>
       </c>
-      <c r="F4" s="23" t="inlineStr">
+      <c r="F4" s="22" t="inlineStr">
         <is>
           <t>17:40</t>
         </is>
       </c>
-      <c r="G4" s="23" t="n">
+      <c r="G4" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="H4" s="23" t="inlineStr">
+      <c r="H4" s="22" t="inlineStr">
         <is>
           <t>Powerleague official website (online booking)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>Shoreditch Rooftop</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Monday 28 September at 18:00</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>One-off</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>5-a-side</t>
         </is>
       </c>
-      <c r="E5" s="31" t="n">
+      <c r="E5" s="30" t="n">
         <v>46293</v>
       </c>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="F5" s="22" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="G5" s="23" t="n">
+      <c r="G5" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="23" t="inlineStr">
+      <c r="H5" s="22" t="inlineStr">
         <is>
           <t>Better (GLL)</t>
         </is>
@@ -18267,104 +18016,104 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>FC Urban · London after-work football leads</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>77 companies (60 ready once the price is set, 17 on hold) with a published email on their own domain, an office within a 15-minute walk of a pitch that has an open Mon–Thu 17:30–20:00 slot in the next 3 weeks.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="23" t="inlineStr"/>
+      <c r="A3" s="22" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>How it was built</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>1. Companies House bulk data: active London companies filing full, medium or group accounts; SIC for law, finance/accounting, insurance, consultancy, tech/software, architecture, recruitment, marketing/agencies (LLPs by name).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>2. Removed shells, holding/fund/property vehicles, schools, charities, public bodies, hospitality, retail, clinics, formation-agent addresses (&gt;12 brands at one address), and anything in an earlier FC Urban sheet.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>3. Suppression: brian@fcurban.com Sent (last 90 days) checked domain by domain, plus senders of opt-out / "no thanks" / "not interested" replies.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>4. Website found and read for each firm: working office from its own contact page (registered office only when the site shows no address, labelled in Office basis).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>5. Walk = straight line × 1.3 at 4.8 km/h to the nearest pitch with a confirmed open slot (Slots tab). Kept ≤ 15 minutes.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>6. Contact order: named HR / People / Office / Operations person → named partner/director/founder (firms under ~100) → general inbox on the firm's own domain. No press, privacy, careers, support, sales or other-country inboxes. Emails were only taken where published; none guessed.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>7. Headcount from the firm's own site where stated; firms under 20 or over 500 removed; "Not stated" otherwise.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>8. Personal line: one fact from the firm's own pages (source linked). Blank when nothing real was found.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="inlineStr">
-        <is>
-          <t>9. Every email was written individually from that research (Personalised email column). {PRICE} is replaced by the confirmed price on the Offer tab; until then Email draft stays empty. Rows the research flagged are on Hold with the reason.</t>
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>9. Every email was written individually from that research. First email = interest check only (no price, no dates): who we are, that we already run games nearby, and a request to forward to whoever runs staff socials / wellbeing if the reader is not the right person (per Joep's learnings). Price (£8–£10 pp guide) comes in the group-invite email after a yes. Rows the research flagged are on Hold with the reason.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="inlineStr"/>
+      <c r="A14" s="22" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>Sending rules (for when the n8n workflow is switched on)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>Max 150 per inbox per day, spread across working hours; one sender name per inbox (Brian on brian@fcurban.com); stop the batch if bounces exceed 3%; log Contacted on here and reply categories in Notion.</t>
         </is>

--- a/corporates/FC_Urban_London_after_work_leads.xlsx
+++ b/corporates/FC_Urban_London_after_work_leads.xlsx
@@ -10860,7 +10860,7 @@
       <c r="AO48" s="19" t="inlineStr">
         <is>
           <t>Hi Allford Hall Monaghan Morris team,
-Morelands, your office on Old Street, is actually one of AHMM's own projects - nice to design the building you then work in.
+Morelands, your office at Old Street, is actually one of AHMM's own projects - nice to design the building you then work in.
 I'm Brian from FC Urban. We organise social football across London, and already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 10-minute walk from your office.
 We're looking for someone at AHMM who'd enjoy starting a regular kickabout for the studio - we handle the pitch, extra players if short, payments and organisation.
 Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
@@ -13940,7 +13940,7 @@
         <is>
           <t>Hi Quantexa team,
 Congratulations on ten years in business, especially with a new office just opening in Malaga.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 7-minute walk from your office on EC2M 4AG.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 7-minute walk from your office near EC2M 4AG.
 We're looking for someone at Quantexa who'd enjoy helping start a regular office kickabout for colleagues after work. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 More on how it works: FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates).
@@ -17569,7 +17569,7 @@
         <is>
           <t>Hi La,
 I saw Little Dot Studios has been named a Great Place To Work UK for the third year running.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 6-minute walk from your office on E1 6QL.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 6-minute walk from your office near E1 6QL.
 We're looking for someone at Little Dot Studios who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would you be up for it, or is there someone better placed? Either way, feel free to forward this to whoever looks after socials.
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -19526,7 +19526,7 @@
         <is>
           <t>Hi Catriona,
 I saw Page White &amp; Farrer has over 160 years of experience as specialist patent and trade mark attorneys.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), about a 10-minute walk from your office on WC1R 4HE.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), about a 10-minute walk from your office near WC1R 4HE.
 We're looking for someone at Page White &amp; Farrer who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would you be up for it, or is there someone better placed? Either way, feel free to forward this to whoever looks after socials.
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -19968,7 +19968,7 @@
         <is>
           <t>Hi Ashok,
 Congratulations on JMAN's new Chief People Officer, Trish Unwin, joining the team this year.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 12-minute walk from your office on EC3N 3AJ.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 12-minute walk from your office near EC3N 3AJ.
 We're looking for someone at JMAN who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would you be up for it, or is there someone better placed? Either way, feel free to forward this to whoever looks after socials.
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -21958,7 +21958,7 @@
       <c r="AO100" s="19" t="inlineStr">
         <is>
           <t>Hi David,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Whittington Park (https://www.fcurban.com/locations/whittington-park), about a 6-minute walk from your office on Riley Studios, 724 Holloway Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Whittington Park (https://www.fcurban.com/locations/whittington-park), about a 6-minute walk from your office at Riley Studios, 724 Holloway Road.
 We're looking for someone at Moneynet who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -22373,7 +22373,7 @@
       <c r="AO102" s="19" t="inlineStr">
         <is>
           <t>Hi Procurement Leaders team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 6-minute walk from your office on SE1 1GA.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 6-minute walk from your office near SE1 1GA.
 We're looking for someone at Procurement Leaders who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -24330,7 +24330,7 @@
         <is>
           <t>Hi Mike,
 xpate was founded in Riga back in 2019, and now runs offices in both Latvia and the UK.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/locations/poplar), about an 11-minute walk from your office on Level 18, 40 Bank Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/locations/poplar), about an 11-minute walk from your office at Level 18, 40 Bank Street.
 We're looking for someone at xpate who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -24556,7 +24556,7 @@
         <is>
           <t>Hi Tomasz,
 We saw that VirtusLab was founded in 2010, marking 16 years in business this year.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/locations/poplar), about a 11-minute walk from your office on 40 Bank Street, Canary Wharf.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/locations/poplar), about a 11-minute walk from your office at 40 Bank Street, Canary Wharf.
 We're looking for someone at VirtusLab who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -25195,7 +25195,7 @@
         <is>
           <t>Hi RHEON Labs team,
 The RHEON Labs team already runs its own Run Club, plus a gym in the office and monthly Lab Lunches.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Battersea - Griffin Primary School (https://www.fcurban.com/locations/battersea-griffin-primary-school), about a 14-minute walk from your office on SW8 3QJ.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Battersea - Griffin Primary School (https://www.fcurban.com/locations/battersea-griffin-primary-school), about a 14-minute walk from your office near SW8 3QJ.
 We're looking for someone at RHEON Labs who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -26951,7 +26951,7 @@
         <is>
           <t>Hi Build Hollywood team,
 I saw the BUILDHOLLYWOOD 2025 annual film has just landed, marking another year of placing creativity in the heart of your cities.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/locations/ark-king-solomon), just a 2-minute walk from your office on NW1 5BY.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/locations/ark-king-solomon), just a 2-minute walk from your office near NW1 5BY.
 We're looking for someone at Build Hollywood who'd enjoy helping start a weekly office kickabout for the studio; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -27364,7 +27364,7 @@
         <is>
           <t>Hi PrismFP team,
 PrismFP describes its culture as R&amp;D-centred, blending market practitioners, quantitative analysts and technologists in a fast-paced, agile environment.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/locations/ark-king-solomon), about a 6-minute walk from your office on The Grove, Third Floor, 248A Marylebone Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/locations/ark-king-solomon), about a 6-minute walk from your office at The Grove, Third Floor, 248A Marylebone Road.
 We're looking for someone at PrismFP who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -27788,7 +27788,7 @@
         <is>
           <t>Hi Heatherwick Studio team,
 I saw your team has grown to more than 250 architects, designers, makers and engineers.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), about a 6-minute walk from your office on Making House, 55 Argyle Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), about a 6-minute walk from your office at Making House, 55 Argyle Street.
 We're looking for someone at Heatherwick Studio who'd enjoy helping start a weekly office kickabout for the studio; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -28002,7 +28002,7 @@
         <is>
           <t>Hi IFF Research team,
 We noticed that IFF Research runs on a four-day working week, built around flexibility and wellbeing for the team.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 7-minute walk from your office on 5th Floor, The Harlequin Building.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 7-minute walk from your office at 5th Floor, The Harlequin Building.
 We're looking for someone at IFF Research who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -28211,7 +28211,7 @@
         <is>
           <t>Hi MetroPress team,
 You launched MetroPress this year with a simple idea: that promoting a brand through real creators should be as easy as browsing a marketplace.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 7-minute walk from your office on SE1 0HR.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 7-minute walk from your office near SE1 0HR.
 We're looking for someone at MetroPress who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -28619,7 +28619,7 @@
       <c r="AO131" s="19" t="inlineStr">
         <is>
           <t>Hi Trive team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/locations/poplar), about a 7-minute walk from your office on E14 5AB.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/locations/poplar), about a 7-minute walk from your office near E14 5AB.
 We're looking for someone at Trive who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -28832,7 +28832,7 @@
         <is>
           <t>Hi Transferra team,
 We saw that Transferra has been authorised by the Financial Conduct Authority since December 2021.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/locations/poplar), about a 7-minute walk from your office on 1 Canada Square, Canary Wharf.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/locations/poplar), about a 7-minute walk from your office at 1 Canada Square, Canary Wharf.
 We're looking for someone at Transferra who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -29468,7 +29468,7 @@
         <is>
           <t>Hi KIT-AR team,
 Congratulations on completing your 3.3 million euro funding round.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), about an 8-minute walk from your office on WC1X 8BP.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), about an 8-minute walk from your office near WC1X 8BP.
 We're looking for someone at KIT-AR who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -30521,7 +30521,7 @@
         <is>
           <t>Hi SRC Infrastructure team,
 I saw your recent piece on this year's interns and their reflections on their time at SRC.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/locations/poplar), about a 9-minute walk from your office on E14 5EU.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/locations/poplar), about a 9-minute walk from your office near E14 5EU.
 We're looking for someone at SRC Infrastructure who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -31369,7 +31369,7 @@
         <is>
           <t>Hi Red Planet Pictures team,
 We saw that the BBC has recommissioned Death in Paradise for another two series, with cameras already rolling in Guadeloupe.
-I'm Brian from FC Urban. We organise social football games across London, and we run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), about a 9-minute walk from your office on WC1X 0BJ.
+I'm Brian from FC Urban. We organise social football games across London, and we run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), about a 9-minute walk from your office near WC1X 0BJ.
 We're looking for someone at Red Planet Pictures who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -31782,7 +31782,7 @@
       <c r="AO146" s="19" t="inlineStr">
         <is>
           <t>Hi Everforth Quinnox team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 10-minute walk from your office on EC3N 1LQ.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 10-minute walk from your office near EC3N 1LQ.
 We're looking for someone at Everforth Quinnox who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -32208,7 +32208,7 @@
         <is>
           <t>Hi Eleven team,
 I saw Eleven was named one of Broadcast's Best Places to Work in TV.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/locations/ark-king-solomon), about an 11-minute walk from your office on 12th Floor, Brunel Building, 2 Canalside Walk.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/locations/ark-king-solomon), about an 11-minute walk from your office at 12th Floor, Brunel Building, 2 Canalside Walk.
 We're looking for someone at Eleven who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -32422,7 +32422,7 @@
         <is>
           <t>Hi Blue Zoo team,
 I saw Blue Zoo became the world's first B Corp-certified independent animation studio, back in September 2021.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Camden - Castlehaven (https://www.fcurban.com/locations/camden-castlehaven-ba0af), about an 11-minute walk from your office on Acre House, 11-15 William Road, London, NW1 7AA.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Camden - Castlehaven (https://www.fcurban.com/locations/camden-castlehaven-ba0af), about an 11-minute walk from your office at Acre House, 11-15 William Road, London, NW1 7AA.
 We're looking for someone at Blue Zoo who'd enjoy helping start a weekly office kickabout for the studio; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -33245,7 +33245,7 @@
       <c r="AO153" s="19" t="inlineStr">
         <is>
           <t>Hi Turlock TEC team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 12-minute walk from your office on EC3N 3AE.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 12-minute walk from your office near EC3N 3AE.
 We're looking for someone at Turlock TEC who'd enjoy helping start a regular team social or after-work game; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -34082,7 +34082,7 @@
       <c r="AO157" s="19" t="inlineStr">
         <is>
           <t>Hi Kobre &amp; Kim team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 13-minute walk from your office on EC2N 1HQ.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 13-minute walk from your office near EC2N 1HQ.
 We're looking for someone at Kobre &amp; Kim who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -34931,7 +34931,7 @@
         <is>
           <t>Hi Carpmaels &amp; Ransford team,
 Congratulations on Christopher Stothers and Kevin Cordina joining as partners.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), about a 14-minute walk from your office on WC1B 5HA.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), about a 14-minute walk from your office near WC1B 5HA.
 We're looking for someone at Carpmaels &amp; Ransford to help start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -35127,7 +35127,7 @@
       <c r="AO162" s="19" t="inlineStr">
         <is>
           <t>Hi Mewburn Ellis team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 14-minute walk from your office on EC2N 4BQ.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 14-minute walk from your office near EC2N 4BQ.
 We're looking for someone at Mewburn Ellis who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -35336,7 +35336,7 @@
         <is>
           <t>Hi Sanza team,
 Sanza Teaching Agency was originally founded in 1999 to recruit teachers and support staff for London schools.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), about a 14-minute walk from your office on WC1V 6JS.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), about a 14-minute walk from your office near WC1V 6JS.
 We're looking for someone at Sanza who'd enjoy helping start a regular team game or friendly competition against other firms; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -35745,7 +35745,7 @@
       <c r="AO165" s="19" t="inlineStr">
         <is>
           <t>Hi RiverSafe team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/locations/poplar), about a 14-minute walk from your office on E14 9SH.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/locations/poplar), about a 14-minute walk from your office near E14 9SH.
 We're looking for someone at RiverSafe who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -36159,7 +36159,7 @@
       <c r="AO167" s="19" t="inlineStr">
         <is>
           <t>Hi UK First Fintech team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 15-minute walk from your office on 3rd Floor, The News Building, 3 London Bridge Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 15-minute walk from your office at 3rd Floor, The News Building, 3 London Bridge Street.
 We're looking for someone at UK First Fintech who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -36579,7 +36579,7 @@
         <is>
           <t>Hi Saffron team,
 Saw that Peterborough Football Foundation launched your Create Your Own Future platform last year.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Brixton (https://www.fcurban.com/locations/brixton-03dac), about a 15-minute walk from your office on SW9 9RX.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Brixton (https://www.fcurban.com/locations/brixton-03dac), about a 15-minute walk from your office near SW9 9RX.
 We're looking for someone at Saffron who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -37176,7 +37176,7 @@
       <c r="AO172" s="19" t="inlineStr">
         <is>
           <t>Hi Xpedition team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/locations/ark-king-solomon), about a 15-minute walk from your office on W2 6BD.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/locations/ark-king-solomon), about a 15-minute walk from your office near W2 6BD.
 We're looking for someone at Xpedition who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -37819,7 +37819,7 @@
         <is>
           <t>Hi Christofer,
 I saw Parkopedia was founded back in 2007 and has grown into the world's leading parking service, working with the likes of Apple, BMW and Volkswagen.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 10-minute walk from your office on SE1 4PL.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 10-minute walk from your office near SE1 4PL.
 We're looking for someone at Parkopedia who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would you be up for it, or is there someone better placed? Either way, feel free to forward this to whoever looks after socials.
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)

--- a/corporates/FC_Urban_London_after_work_leads.xlsx
+++ b/corporates/FC_Urban_London_after_work_leads.xlsx
@@ -1161,7 +1161,7 @@
         <is>
           <t>Hi Leadscale team,
 You describe Team Leadscale as growing and close-knit, valuing circles of knowledge over hierarchy, which sounds like a team that would enjoy playing together.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 9-minute walk from your office on Owen Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), about a 9-minute walk from your office on Owen Street.
 We're looking for someone at Leadscale who'd enjoy helping start a regular office kickabout for colleagues; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -1380,7 +1380,7 @@
         <is>
           <t>Hi Martin,
 Exigere's team benefits include an annual company conference and a paid volunteering day, so the team clearly matters to you.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 10-minute walk from your office on Old Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), about a 10-minute walk from your office on Old Street.
 We're looking for someone at Exigere to start a regular after-work kickabout for colleagues; we handle the pitch, extra players if you're short, payments and organisation.
 Would that be of interest to the team? If it's not for you, would you mind pointing me to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -1597,7 +1597,7 @@
         <is>
           <t>Hi Sandra,
 Veretec's careers page describes your studio as vibrant, enthusiastic and collaborative, with a genuinely friendly, social culture, which sounds like a team that would enjoy playing together.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 10-minute walk from your office on Bonhill Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 10-minute walk from your office on Bonhill Street.
 We're looking for someone at Veretec who'd enjoy helping start a regular kickabout for the studio; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -1818,7 +1818,7 @@
         <is>
           <t>Hi Robert,
 Codurance's own story page calls your engineers software craftspeople, rooted in the London Software Craftsmanship Community you helped start in 2010.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), an 11-minute walk from your office on Sutton Lane.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), an 11-minute walk from your office on Sutton Lane.
 We're looking for someone at Codurance to start a regular office kickabout for colleagues; we handle the pitch, extra players if you're short, payments and organisation.
 Would that be of interest to the team? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -2035,7 +2035,7 @@
         <is>
           <t>Hi Sophie,
 Precise Consultants have gone a step further than carbon neutral to carbon negative, offsetting 82.66 tonnes of CO2e through verified projects.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 12-minute walk from your office on Devonshire Square.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 12-minute walk from your office on Devonshire Square.
 We're looking for someone at Precise Consultants to start a regular team game, perhaps a friendly against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -2256,7 +2256,7 @@
         <is>
           <t>Hi Jamie,
 Guy Butler's website traces your roots back over 50 years as an independent bond house in the City, a team built to last.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), a 14-minute walk from your office on Old Broad Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), a 14-minute walk from your office on Old Broad Street.
 We're looking for someone at Guy Butler to start a regular after-work social, or perhaps a game against another firm; we handle the pitch, extra players if you're short, payments and organisation.
 Would that interest the team? If it's not for you, could you forward this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -2475,7 +2475,7 @@
         <is>
           <t>Hi Iain,
 Goodman Masson was named the UK's Best Workplace for Wellbeing in 2023, reflecting how you look after the team.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), a 14-minute walk from your office on Aldersgate Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), a 14-minute walk from your office on Aldersgate Street.
 We're looking for someone at Goodman Masson to start a regular team game, perhaps a friendly against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -2696,7 +2696,7 @@
         <is>
           <t>Hi Tracey,
 Congratulations on Embassy, starring Anna Kendrick and J.K. Simmons, landing at Prime Video, must be a good week at Turbine.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), an 8-minute walk from your office on Dallington Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), an 8-minute walk from your office on Dallington Street.
 We're looking for someone at Turbine Studios who'd enjoy helping start a regular kickabout for the studio; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -2913,7 +2913,7 @@
         <is>
           <t>Hi Nick,
 Congratulations on the new 10-year, $120M manufacturing partnership, quite a deal to land.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Market Road (Caledonian Road) (https://www.fcurban.com/locations/market-road), a 9-minute walk from your office near N7 9AA.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Market Road (Caledonian Road) (https://www.fcurban.com/location/market-road), a 9-minute walk from your office near N7 9AA.
 We're looking for someone at Ori Biotech who'd enjoy helping start a regular office kickabout for colleagues; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -3134,7 +3134,7 @@
         <is>
           <t>Hi Sabrina,
 You've built a culture around giving a share of profits to charity, flexible hybrid working and real personal development, which sounds like a team that plays well together.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), an 11-minute walk from your office on Hoxton Square.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), an 11-minute walk from your office on Hoxton Square.
 We're looking for someone at Human Made Machine to start a regular office kickabout for colleagues; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -3353,7 +3353,7 @@
         <is>
           <t>Hi Patrick,
 Going from a team of two in 2009 to a Sunday Times Best Places to Work winner in 2023 is quite a run.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), an 11-minute walk from your office on Great Sutton Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), an 11-minute walk from your office on Great Sutton Street.
 We're looking for someone at Artiq who'd enjoy helping start a regular office kickabout for colleagues; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -3578,7 +3578,7 @@
         <is>
           <t>Hi David,
 Congratulations on becoming CEO last year, and on the ISO 27001 certification and EcoVadis Bronze this year, good momentum to keep going.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), an 11-minute walk from your office on Worship Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), an 11-minute walk from your office on Worship Street.
 We're looking for someone at OSF Digital who'd enjoy helping start a regular office kickabout for colleagues; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -3801,7 +3801,7 @@
         <is>
           <t>Hi Carlo,
 Congratulations on being named Best Places to Work in TV 2026 at the Broadcast Awards, a great sign for the team.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), a 13-minute walk from your office on St Peter's Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), a 13-minute walk from your office on St Peter's Street.
 We're looking for someone at Windfall Films who'd enjoy helping start a regular office kickabout for colleagues; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -4024,7 +4024,7 @@
         <is>
           <t>Hi David,
 Congratulations on being ranked the UK's number two independent production company in Broadcast's 2026 Annual Peer Poll, quite a year for the team.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), a 13-minute walk from your office on Amwell Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), a 13-minute walk from your office on Amwell Street.
 We're looking for someone at 72 Films who'd enjoy helping start a regular office kickabout for colleagues; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -4247,7 +4247,7 @@
         <is>
           <t>Hi Jane,
 October Films has been turning out award-winning documentaries from Benwell Road since 1989, picking up over 100 prizes including EMMY, Prix Italia and BAFTA.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Market Road (Caledonian Road) (https://www.fcurban.com/locations/market-road), a 14-minute walk from your office on Benwell Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Market Road (Caledonian Road) (https://www.fcurban.com/location/market-road), a 14-minute walk from your office on Benwell Road.
 We're looking for someone at October Films who'd enjoy helping start a regular office kickabout for colleagues; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -4472,7 +4472,7 @@
         <is>
           <t>Hi Martin,
 Since your move to Dashwood House on Old Broad Street in 2024, it's a good moment to get the team out together.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), a 14-minute walk from your office.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), a 14-minute walk from your office.
 We're looking for someone at Yendall Hunter to start a regular after-work social, or perhaps a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would that be of interest to the team? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -4693,7 +4693,7 @@
         <is>
           <t>Hi Mahboob,
 JENOA launched in 2020 as a digital-first broker, backed by Abdul Latif Jameel's 80-year heritage, sounds like a team worth bringing together.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 15-minute walk from your office at St Mary Axe.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 15-minute walk from your office at St Mary Axe.
 We're looking for someone at JENOA who'd enjoy helping start a regular team social or after-work game for colleagues; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -4902,7 +4902,7 @@
         <is>
           <t>Hi Gill Jennings &amp; Every team,
 With around 125 of you in Broadgate Tower, and a habit of getting together socially, a regular game sounds like a natural fit.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 6-minute walk from your office.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 6-minute walk from your office.
 We're looking for someone at Gill Jennings &amp; Every to start a regular team social or after-work game for colleagues; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, could you forward this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -5109,7 +5109,7 @@
         <is>
           <t>Hi RBB Economics team,
 RBB grew from 16 founding staff in 2002 to over 300 economists across 18 offices, quite a team to bring together.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 7-minute walk from your office.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 7-minute walk from your office.
 We're looking for someone at RBB Economics to start a regular team social, or perhaps a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -5318,7 +5318,7 @@
         <is>
           <t>Hi Montash team,
 Between the seasonal socials and wellbeing days you already run, a regular match sounds like a natural fit for the team.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), an 8-minute walk from your office on Clifton Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), an 8-minute walk from your office on Clifton Street.
 We're looking for someone at Montash to start a regular team game, perhaps a friendly against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -5531,7 +5531,7 @@
         <is>
           <t>Hi Atelier Ten team,
 Congratulations on winning the 2026 Best of Practice Award from The Architect's Newspaper, a great moment for the studio.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 9-minute walk from your office at E2 8DD.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 9-minute walk from your office at E2 8DD.
 We're looking for someone at Atelier Ten who enjoys football and could help start a weekly kickabout for the studio. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -5737,7 +5737,7 @@
         <is>
           <t>Hi Aptem team,
 Congratulations on being named Learning Technologies Organisation of the Year.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 9-minute walk from Eagle House on City Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), about a 9-minute walk from Eagle House on City Road.
 We're looking for someone at Aptem who enjoys football and could help start a weekly office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
 Would that be of interest to the team? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -5943,7 +5943,7 @@
         <is>
           <t>Hi Elsewhen team,
 With more than 100 strategists, designers and engineers across 11 nationalities, you've got plenty of people for a five-a-side.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 10-minute walk from your office on St Peter's Square.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 10-minute walk from your office on St Peter's Square.
 We're looking for someone at Elsewhen who enjoys football and could help start a weekly office kickabout for the studio. We handle the pitch, extra players if you're short, payments and organisation.
 Would that be of interest to the team? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -6149,7 +6149,7 @@
         <is>
           <t>Hi Veed team,
 Loved hearing that the VEED team danced to 'Mamma Mia' at your last offsite, sounds like a group that knows how to have fun together.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 10-minute walk from your office on Clere Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 10-minute walk from your office on Clere Street.
 We're looking for someone at Veed who enjoys football and could help start a weekly office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
 Would that be of interest to the team? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -6355,7 +6355,7 @@
         <is>
           <t>Hi Tryzens team,
 Congratulations to Phil Hoggarth on stepping in as CEO, leading Tryzens' 350-plus team into a new chapter.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 10-minute walk from your office on Appold Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 10-minute walk from your office on Appold Street.
 We're looking for someone at Tryzens who enjoys football and could help start a weekly office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
 Would that be of interest to the team? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -6563,7 +6563,7 @@
         <is>
           <t>Hi Karakusevic Carson Architects team,
 Congratulations to Abigail Batchelor on joining the judging panel for the Inspire Future Generations Awards 2026.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch Rooftop (Britannia Leisure Centre, Pitfield Street) (https://www.fcurban.com/locations/shoreditch-rooftop), about an 11-minute walk from your office on Cremer Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch Rooftop (Britannia Leisure Centre, Pitfield Street) (https://www.fcurban.com/location/shoreditch-rooftop), about an 11-minute walk from your office on Cremer Street.
 We're looking for someone at Karakusevic Carson Architects who enjoys football and could help start a weekly kickabout for the studio. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -6775,7 +6775,7 @@
         <is>
           <t>Hi Permutive team,
 With your 120-plus team already meeting in London every week and celebrating together at a yearly offsite, a regular match feels like a natural fit.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about an 11-minute walk from your office near Old Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), about an 11-minute walk from your office near Old Street.
 We're looking for someone at Permutive who enjoys football and could help start a weekly office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
 Would that be of interest to the team? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -6987,7 +6987,7 @@
         <is>
           <t>Hi Eric Parry Architects team,
 Congratulations on One Liverpool Street reaching practical completion this July, after nearly fifteen years on the project.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about an 11-minute walk from your office on Banner Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), about an 11-minute walk from your office on Banner Street.
 We're looking for someone at Eric Parry Architects who enjoys football and could help start a weekly kickabout for the studio. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -7199,7 +7199,7 @@
         <is>
           <t>Hi Push Gaming team,
 Congratulations on launching in the Alberta market this July, good momentum for the team.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 12-minute walk from your office on East Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), about a 12-minute walk from your office on East Road.
 We're looking for someone at Push Gaming who enjoys football and could help start a weekly office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
 Would that be of interest to the team? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -7411,7 +7411,7 @@
         <is>
           <t>Hi Oliver Bernard team,
 With 45 of you running regular tech meetups and roundtables, it sounds like a team that enjoys getting together.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 13-minute walk from your office on Finsbury Avenue.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 13-minute walk from your office on Finsbury Avenue.
 We're looking for someone at Oliver Bernard who'd enjoy helping start a regular team game, or even a friendly competition against other firms. We handle the pitch, extra players if you're short, payments and organisation.
 Would that be of interest to the team? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -7623,7 +7623,7 @@
         <is>
           <t>Hi Wellcom London team,
 Your Clerkenwell studio has been the set for Ben &amp; Jerry's shoots since 2022, proof the team knows how to turn a shared space into something fun.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 5-minute walk from your office on Berry Place.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), about a 5-minute walk from your office on Berry Place.
 We're looking for someone at Wellcom London who enjoys football and could help start a weekly kickabout for the studio. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest, or could you point us to whoever's best placed to look into it?
 Best,
@@ -7831,7 +7831,7 @@
         <is>
           <t>Hi Mention Me team,
 Mentioneers already run their own clubs, from running to poker and board games, plus quarterly socials and monthly pub drinks, sounds like a team that would enjoy a regular match too.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 6-minute walk from your office.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), about a 6-minute walk from your office.
 We're looking for someone at Mention Me who enjoys football and could help start a weekly office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest, or could you point us to whoever's best placed to look into it?
 Best,
@@ -8055,7 +8055,7 @@
         <is>
           <t>Hi Simon,
 Oakleaf has been building teams internationally since 2005, with 1,400-plus placements across 80-plus firms in 16 countries.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 7-minute walk from your office on Primrose Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 7-minute walk from your office on Primrose Street.
 We're looking for someone at Oakleaf who'd enjoy helping start a regular after-work game for colleagues, or perhaps a friendly against another firm nearby. We handle the pitch, extra players if you're short, payments and organisation.
 Would you be up for it, or is there someone else better placed to run with it? Either way, feel free to forward this on to whoever looks after socials for the team.
 Best,
@@ -8275,7 +8275,7 @@
         <is>
           <t>Hi Tyler,
 Since the LSEG partnership landed in December, it sounds like the Hoptroff team has had plenty to celebrate.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 10-minute walk from your office on Paul Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 10-minute walk from your office on Paul Street.
 We're looking for someone at Hoptroff who enjoys football and could help start a weekly office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
 Would you be up for it, or is there someone else better placed to run with it? Either way, feel free to forward this on to whoever looks after socials for the team.
 Best,
@@ -8493,7 +8493,7 @@
         <is>
           <t>Hi Melanie,
 Stanton House's team has grown past 50 professionals since you started the consultancy in 2010.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 10-minute walk from your office on Christopher Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 10-minute walk from your office on Christopher Street.
 We're looking for someone at Stanton House who'd enjoy helping start a regular team game, or even a friendly against another firm. We handle the pitch, extra players if you're short, payments and organisation.
 Would you be up for it, or is there someone else better placed to run with it? Either way, feel free to forward this on to whoever looks after socials for the team.
 Best,
@@ -8705,7 +8705,7 @@
         <is>
           <t>Hi Travelfusion team,
 Your careers page promises a comfortable, friendly work environment with flexible hours, sounds like a team that would enjoy playing together after work.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 15-minute walk from your office on St Mary Axe.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 15-minute walk from your office on St Mary Axe.
 We're looking for someone at Travelfusion who enjoys football and could help start a weekly office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -8925,7 +8925,7 @@
         <is>
           <t>Hi Hollie,
 Running recruitment across 18 counties from six offices takes a lot of running around, a regular game closer to base might be a nice change of pace.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 10-minute walk from your office on Paul Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 10-minute walk from your office on Paul Street.
 We're looking for someone at Simply Education who'd enjoy helping start a regular team game, or even a friendly against another firm. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -9145,7 +9145,7 @@
         <is>
           <t>Hi Jamie,
 You built the first version of ecoDriver back in 2007 and won a Microsoft award for it, quite a foundation to have built the business on.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 10-minute walk from your office on Bonhill Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 10-minute walk from your office on Bonhill Street.
 We're looking for someone at Ecodriver who enjoys football and could help start a weekly office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -9365,7 +9365,7 @@
         <is>
           <t>Hi Manish,
 It's great to see TestingXperts running customised wellness programmes, with staff wellbeing clearly core to how the team works.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 13-minute walk from your office in E2 6AH.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 13-minute walk from your office in E2 6AH.
 We're looking for someone at TestingXperts who enjoys football and could help start a weekly office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -9585,7 +9585,7 @@
         <is>
           <t>Hi Marc,
 Congratulations on Fenergo's three category wins in the Chartis RiskTech100 2027 rankings, a great moment for the team.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 14-minute walk from your office in EC2M 7LS.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 14-minute walk from your office in EC2M 7LS.
 We're looking for someone at Fenergo who enjoys football and could help start a weekly office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -9809,7 +9809,7 @@
         <is>
           <t>Hi Julian,
 Building the battery storage technology that's helping power the clean energy transition sounds like demanding work, and a regular game can be a good outlet for the team.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 14-minute walk from your office on Pine Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), about a 14-minute walk from your office on Pine Street.
 We're looking for someone at Fluence Energy who'd enjoy starting a regular office kickabout for colleagues - we handle the pitch, extra players if short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -10017,7 +10017,7 @@
         <is>
           <t>Hi Vendavo team,
 Congratulations on the July acquisition of Model N's high-tech business unit - sounds like a busy stretch, and a regular game can be a good way for everyone to unwind together.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), just a 3-minute walk from your office.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), just a 3-minute walk from your office.
 We're looking for someone at Vendavo who'd enjoy helping start a regular office kickabout for the team - we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -10229,7 +10229,7 @@
         <is>
           <t>Hi Whitepaperco team,
 Good to see the studio's recent projects across London, including the Scalpel and Fusion Group - a regular game could be a good way to switch off together.
-I'm Brian from FC Urban. We organise social football across London, and already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 4-minute walk from your office on Elder Street.
+I'm Brian from FC Urban. We organise social football across London, and already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 4-minute walk from your office on Elder Street.
 We're looking for someone at Whitepaperco who'd enjoy starting a regular office kickabout for the team - we handle the pitch, extra players if short, payments and organisation.
 Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -10437,7 +10437,7 @@
         <is>
           <t>Hi Hadean Supercomputing team,
 Good to see the funding Hadean secured in March, backing the push to become the UK's next defence tech unicorn - fast-growing teams can do with a regular way to switch off.
-I'm Brian from FC Urban. We organise social football across London, and already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 7-minute walk from your office.
+I'm Brian from FC Urban. We organise social football across London, and already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 7-minute walk from your office.
 We're looking for someone at Hadean who'd enjoy starting a regular office kickabout for the team - we handle the pitch, extra players if short, payments and organisation.
 Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -10649,7 +10649,7 @@
         <is>
           <t>Hi Vivacity Labs team,
 Good to see Vivacity on such an upward trajectory, expanding internationally and doubling headcount - a regular game is a good way to get new starters mixing.
-I'm Brian from FC Urban. We organise social football across London, and already run games at Shoreditch Rooftop (Britannia Leisure Centre, Pitfield Street) (https://www.fcurban.com/locations/shoreditch-rooftop), about a 9-minute walk from Haberdasher Street.
+I'm Brian from FC Urban. We organise social football across London, and already run games at Shoreditch Rooftop (Britannia Leisure Centre, Pitfield Street) (https://www.fcurban.com/location/shoreditch-rooftop), about a 9-minute walk from Haberdasher Street.
 We're looking for someone at Vivacity Labs who'd enjoy starting a regular office kickabout for the team - we handle the pitch, extra players if short, payments and organisation.
 Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -10861,7 +10861,7 @@
         <is>
           <t>Hi Allford Hall Monaghan Morris team,
 Morelands, your office at Old Street, is actually one of AHMM's own projects - nice to design the building you then work in.
-I'm Brian from FC Urban. We organise social football across London, and already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 10-minute walk from your office.
+I'm Brian from FC Urban. We organise social football across London, and already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), about a 10-minute walk from your office.
 We're looking for someone at AHMM who'd enjoy starting a regular kickabout for the studio - we handle the pitch, extra players if short, payments and organisation.
 Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -11071,7 +11071,7 @@
         <is>
           <t>Hi Censuswide team,
 Good to see your research for the Mayor of London's "Have A Word" campaign on billboards in Piccadilly Circus - proof it travels, and a game is a good way to get the office out.
-I'm Brian from FC Urban. We organise social football across London, and already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 10-minute walk from Berry Street.
+I'm Brian from FC Urban. We organise social football across London, and already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), about a 10-minute walk from Berry Street.
 We're looking for someone at Censuswide who'd enjoy starting a regular office kickabout for the team - we handle the pitch, extra players, payments and organisation.
 Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -11270,7 +11270,7 @@
       <c r="AO50" s="19" t="inlineStr">
         <is>
           <t>Hi Atech Support team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 10-minute walk from your office.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 10-minute walk from your office.
 We're looking for someone at Atech Support who'd enjoy helping start a regular office kickabout for the team, nothing fancy, just an excuse to get out from behind the desk - we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -11469,7 +11469,7 @@
       <c r="AO51" s="19" t="inlineStr">
         <is>
           <t>Hi McBains team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about an 11-minute walk from your office.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about an 11-minute walk from your office.
 We're looking for someone at McBains who'd enjoy helping start a regular kickabout for the studio, an easy way to get colleagues together outside the office - we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -11675,7 +11675,7 @@
         <is>
           <t>Hi Fincore team,
 With a 24-person team built by a CFO-turned-founder, you've easily got the numbers for a proper weekly kickabout.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 14-minute walk from your office.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 14-minute walk from your office.
 We're looking for someone at Fincore who'd enjoy helping start a regular office kickabout for the team - we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -11887,7 +11887,7 @@
         <is>
           <t>Hi GTN team,
 Congratulations on GTN being named a Best Accounting Firm to Work For, seventh year running - a good excuse to get the team together outside the office too.
-I'm Brian from FC Urban. We organise social football across London, and already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 14-minute walk from Charterhouse Mews.
+I'm Brian from FC Urban. We organise social football across London, and already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), about a 14-minute walk from Charterhouse Mews.
 We're looking for someone at GTN who'd enjoy starting a regular after-work game for colleagues, or a game against another firm nearby - we handle the pitch, extra players, payments and organisation.
 Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -12098,7 +12098,7 @@
       <c r="AO54" s="19" t="inlineStr">
         <is>
           <t>Hi Esme,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 13-minute walk from your office on Mallow Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), about a 13-minute walk from your office on Mallow Street.
 We're looking for someone at YuLife who'd enjoy helping start a regular office kickabout for the team - we handle the pitch, extra players if you're short, payments and organisation.
 Would you be up for it, or is there someone else at YuLife who'd be better placed to look at this?
 Best,
@@ -12319,7 +12319,7 @@
       <c r="AO55" s="19" t="inlineStr">
         <is>
           <t>Hi Emma,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about an 11-minute walk from your office on City Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), about an 11-minute walk from your office on City Road.
 We're looking for someone at Creditex Brokerage who'd enjoy helping start a regular after-work game for colleagues, or even a game against another firm nearby - we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -12522,7 +12522,7 @@
       <c r="AO56" s="19" t="inlineStr">
         <is>
           <t>Hi Made Tech team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 5-minute walk from your office on Folgate Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 5-minute walk from your office on Folgate Street.
 We're looking for someone at Made Tech who'd enjoy helping start a regular office kickabout for the team - we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -12725,7 +12725,7 @@
       <c r="AO57" s="19" t="inlineStr">
         <is>
           <t>Hi Clover Technology team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 10-minute walk from your office on Paul Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 10-minute walk from your office on Paul Street.
 We're looking for someone at Clover Technology who'd enjoy helping start a regular office kickabout for the team - we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -12924,7 +12924,7 @@
       <c r="AO58" s="19" t="inlineStr">
         <is>
           <t>Hi Louder Productions team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 10-minute walk from your office.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 10-minute walk from your office.
 We're looking for someone at Louder Productions who'd enjoy helping start a regular office kickabout for the team - we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -13127,7 +13127,7 @@
       <c r="AO59" s="19" t="inlineStr">
         <is>
           <t>Hi Arcontech team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 10-minute walk from your office on Paul Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 10-minute walk from your office on Paul Street.
 We're looking for someone at Arcontech who'd enjoy helping start a regular office kickabout for the team - we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -13326,7 +13326,7 @@
       <c r="AO60" s="19" t="inlineStr">
         <is>
           <t>Hi Blue Square Marketing team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 12-minute walk from your office.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), about a 12-minute walk from your office.
 We're looking for someone at Blue Square Marketing who'd enjoy helping start a regular office kickabout for the team - we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -13529,7 +13529,7 @@
       <c r="AO61" s="19" t="inlineStr">
         <is>
           <t>Hi Container Solutions team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 13-minute walk from your office on Clerkenwell Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), about a 13-minute walk from your office on Clerkenwell Road.
 We're looking for someone at Container Solutions who'd enjoy helping start a regular office kickabout for the team - we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -13732,7 +13732,7 @@
       <c r="AO62" s="19" t="inlineStr">
         <is>
           <t>Hi Parseq team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 15-minute walk from your office on Finsbury Circus.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 15-minute walk from your office on Finsbury Circus.
 We're looking for someone at Parseq who'd enjoy helping start a regular office kickabout for the team - we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -13940,7 +13940,7 @@
         <is>
           <t>Hi Quantexa team,
 Congratulations on ten years in business, especially with a new office just opening in Malaga.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 7-minute walk from your office near EC2M 4AG.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 7-minute walk from your office near EC2M 4AG.
 We're looking for someone at Quantexa who'd enjoy helping start a regular office kickabout for colleagues after work. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 More on how it works: FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates).
@@ -14155,7 +14155,7 @@
         <is>
           <t>Hi Maccreanor Lavington team,
 Congratulations on the RIBA Stirling Prize recognition, quite the achievement for a practice of around 80 people.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 7-minute walk from your office on Gee Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), about a 7-minute walk from your office on Gee Street.
 We're looking for someone at Maccreanor Lavington who'd enjoy helping start a regular office kickabout for the studio. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -14371,7 +14371,7 @@
         <is>
           <t>Hi Valeo Foods team,
 Great to see your KETTLE Chips brand named Official Partner of the ICC Women's T20 World Cup 2026.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 9-minute walk from your office on Perseverance Works.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 9-minute walk from your office on Perseverance Works.
 We're looking for someone at Valeo Foods who'd enjoy helping start a regular after-work game for colleagues, maybe even a friendly against another firm nearby. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -14583,7 +14583,7 @@
         <is>
           <t>Hi Your World Recruitment team,
 Great to see you supplied 5,565 staff to healthcare providers and worked with 770 organisations in 2025.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about an 11-minute walk from your office on Wilson Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about an 11-minute walk from your office on Wilson Street.
 We're looking for someone at Your World Recruitment who'd enjoy helping start a regular team game, perhaps a friendly against other firms. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -14795,7 +14795,7 @@
         <is>
           <t>Hi Beeline team,
 Congratulations on 25 years of leading the extended workforce industry, a good year to get the team together.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about an 11-minute walk from your office on City Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), about an 11-minute walk from your office on City Road.
 We're looking for someone at Beeline who'd enjoy helping start a regular after-work game for colleagues, maybe even a friendly against another firm nearby. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -15007,7 +15007,7 @@
         <is>
           <t>Hi Optimove team,
 Comradery is one of your core values, with wellness and team events built into life at Optimove, and a five-a-side game would fit right in.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about an 11-minute walk from your office on Bonhill Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about an 11-minute walk from your office on Bonhill Street.
 We're looking for someone at Optimove who'd enjoy helping start a regular office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -15235,7 +15235,7 @@
         <is>
           <t>Hi Ivan,
 Congratulations on this week's North Capital acquisition, a big step into onchain capital markets, and a good moment for the team to blow off some steam together.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 6-minute walk from your office on Wenlock Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), about a 6-minute walk from your office on Wenlock Road.
 We're looking for someone at Moonpay who'd enjoy helping start a regular office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
 Would you be up for it, or is there someone else on the team better placed to look at this?
 Best,
@@ -15451,7 +15451,7 @@
         <is>
           <t>Hi TVF team,
 Your TVF Communications team has spent over 30 years helping pharma and biotech clients explain complex science clearly, which takes real team spirit to sustain.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about an 8-minute walk from your office on 375 City Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), about an 8-minute walk from your office on 375 City Road.
 We're looking for someone at TVF who'd enjoy helping start a regular office kickabout for the team. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -15660,7 +15660,7 @@
       <c r="AO71" s="19" t="inlineStr">
         <is>
           <t>Hi Datasite team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about an 11-minute walk from your office at EC2A 4DN.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about an 11-minute walk from your office at EC2A 4DN.
 We're looking for someone at Datasite who'd enjoy helping start a regular office kickabout for colleagues, something that could easily become a standing weekly fixture. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 More on how it works: FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates).
@@ -15868,7 +15868,7 @@
       <c r="AO72" s="19" t="inlineStr">
         <is>
           <t>Hi there,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Market Road (Caledonian Road) (https://www.fcurban.com/locations/market-road), about a 6-minute walk from your office on Blundell Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Market Road (Caledonian Road) (https://www.fcurban.com/location/market-road), about a 6-minute walk from your office on Blundell Street.
 We're looking for someone at Side who'd enjoy helping start a regular office kickabout for the team, something that could easily become a standing weekly game. We handle the pitch, extra players if you're short, payments and organisation.
 Would you be up for it, or is there someone else on the team better placed to look at this?
 More on how it works: FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates).
@@ -16084,7 +16084,7 @@
       <c r="AO73" s="19" t="inlineStr">
         <is>
           <t>Hi Mother London team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), just a 2-minute walk from your office on Redchurch Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), just a 2-minute walk from your office on Redchurch Street.
 We're looking for someone at Mother London who'd enjoy helping start a regular office kickabout for the studio, something that could easily become a standing weekly game. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 More on how it works: FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates).
@@ -16309,7 +16309,7 @@
         <is>
           <t>Hi Donald,
 You spend your days backing fund managers with the capital and infrastructure to focus on performance. A weekly five-a-side could do something similar for your own team.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 7-minute walk from your office at EC2A 2DA.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 7-minute walk from your office at EC2A 2DA.
 We're looking for someone at Paloma who'd enjoy helping start a regular after-work game for the team. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -16512,7 +16512,7 @@
       <c r="AO75" s="19" t="inlineStr">
         <is>
           <t>Hi Squadron team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 6-minute walk from your office at E1 6AD.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 6-minute walk from your office at E1 6AD.
 We're looking for someone at Squadron who'd enjoy helping start a regular after-work game for the team, maybe even a friendly against another firm nearby. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 More on how it works: FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates).
@@ -16720,7 +16720,7 @@
       <c r="AO76" s="19" t="inlineStr">
         <is>
           <t>Hi Northdoor team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about an 11-minute walk from your office on Old Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), about an 11-minute walk from your office on Old Street.
 We're looking for someone at Northdoor who'd enjoy helping start a regular office kickabout for the team, something that could easily become a standing weekly fixture. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 More on how it works: FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates).
@@ -16928,7 +16928,7 @@
       <c r="AO77" s="19" t="inlineStr">
         <is>
           <t>Hi Lightbox Media team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 12-minute walk from your office on Amwell Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), about a 12-minute walk from your office on Amwell Street.
 We're looking for someone at Lightbox Media who'd enjoy helping start a regular office kickabout for the studio, something that could easily become a standing weekly game. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 More on how it works: FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates).
@@ -17132,7 +17132,7 @@
       <c r="AO78" s="19" t="inlineStr">
         <is>
           <t>Hi Creative Monster team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/locations/old-st-moreland-primary-school), about a 12-minute walk from your office at N1 6AD.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old Street (Moreland School, Gard Street) (https://www.fcurban.com/location/old-st-moreland-primary-school), about a 12-minute walk from your office at N1 6AD.
 We're looking for someone at Creative Monster who'd enjoy helping start a regular office kickabout for the studio, something that could easily become a standing weekly fixture. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 More on how it works: FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates).
@@ -17345,7 +17345,7 @@
         <is>
           <t>Hi Sigmatic team,
 Great to see what you've built with Stakingverse, reaching $14M in peak TVL, sounds like a team that could use a regular break from the screens.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/locations/shoreditch-powerleague), about a 15-minute walk from your office at EC3A 8BE.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch (Powerleague, Braithwaite Street) (https://www.fcurban.com/location/shoreditch-powerleague), about a 15-minute walk from your office at EC3A 8BE.
 We're looking for someone at Sigmatic who'd enjoy helping start a regular after-work game for the team. We handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -17569,7 +17569,7 @@
         <is>
           <t>Hi La,
 I saw Little Dot Studios has been named a Great Place To Work UK for the third year running.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 6-minute walk from your office near E1 6QL.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), about a 6-minute walk from your office near E1 6QL.
 We're looking for someone at Little Dot Studios who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would you be up for it, or is there someone better placed? Either way, feel free to forward this to whoever looks after socials.
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -17781,7 +17781,7 @@
       <c r="AO81" s="19" t="inlineStr">
         <is>
           <t>Hi Peter,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/locations/poplar), about a 7-minute walk from your office at Canary Wharf.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/location/poplar), about a 7-minute walk from your office at Canary Wharf.
 We're looking for someone at Lucera who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would you be up for it, or is there someone better placed? Either way, feel free to forward this to whoever looks after socials.
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -18002,7 +18002,7 @@
         <is>
           <t>Hi Eddie,
 Four launched in 2001 with just seven people and has now grown into a 250-strong team marking its first 20 years.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Whitechapel (https://www.fcurban.com/locations/whitechapel), about an 8-minute walk from your office on Whitechapel Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Whitechapel (https://www.fcurban.com/location/whitechapel), about an 8-minute walk from your office on Whitechapel Road.
 We're looking for someone at Four who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players, payments and organisation.
 Would you be up for it, or is there someone better placed? Either way, feel free to forward this to whoever looks after socials.
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -18226,7 +18226,7 @@
         <is>
           <t>Hi Sam,
 I saw Xcede raised over £6,700 for the National Autistic Society last year, 134% over target, and is now backing the Alzheimer's Society.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras Rooftop 4G (https://www.fcurban.com/locations/st-pancras-rooftop-4g), about an 8-minute walk from your office on 24 Eversholt St.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras Rooftop 4G (https://www.fcurban.com/location/st-pancras-rooftop-4g), about an 8-minute walk from your office on 24 Eversholt St.
 We're looking for someone at Xcede who'd enjoy helping start a regular team game or friendly competition against other firms; we handle the pitch, extra players if you're short, payments and organisation.
 Would you be up for it, or is there someone better placed? Feel free to forward this to whoever looks after socials.
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -18449,7 +18449,7 @@
         <is>
           <t>Hi Hannah,
 Meet started from one London office in 2009 and has grown into a 140-plus person global team.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about an 8-minute walk from your office at EC3A 7LP.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), about an 8-minute walk from your office at EC3A 7LP.
 We're looking for someone at Meet Life Sciences who'd enjoy helping start a regular team game or friendly competition against other firms; we handle the pitch, extra players if you're short, payments and organisation.
 Would you be up for it, or is there someone better placed? Either way, feel free to forward this to whoever looks after socials.
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -18662,7 +18662,7 @@
         <is>
           <t>Hi James,
 I saw Charcoalblue has won the King's Award for Enterprise, real recognition for a firm doing distinctive work in theatre and venue design.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 9-minute walk from your office on 17 Short Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/location/borough-academy), about a 9-minute walk from your office on 17 Short Street.
 We're looking for someone at Charcoalblue who'd enjoy helping start a weekly office kickabout for the studio; we handle the pitch, extra players if you're short, payments and organisation.
 Would you be up for it, or is there someone better placed? Either way, feel free to forward this to whoever looks after socials.
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -18885,7 +18885,7 @@
         <is>
           <t>Hi Sarah,
 I saw that Virgo Health now has a team of more than 100 healthcare specialists here in Shoreditch.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch Powerleague (https://www.fcurban.com/locations/shoreditch-powerleague), about a 9-minute walk from your office on 99 Clifton Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Shoreditch Powerleague (https://www.fcurban.com/location/shoreditch-powerleague), about a 9-minute walk from your office on 99 Clifton Street.
 We're looking for someone at Virgo Health who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would you be up for it, or is there someone better placed? Either way, feel free to forward this to whoever looks after socials.
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -19103,7 +19103,7 @@
         <is>
           <t>Hi Luckson,
 REGIS-TR UK was founded here in 2019, and now counts around 100 experts across London and its other European hubs.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 10-minute walk from your office on 33 St Mary Axe.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), about a 10-minute walk from your office on 33 St Mary Axe.
 We're looking for someone at REGIS-TR who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players, payments and organisation.
 Would you be up for it, or is there someone better placed? Either way, feel free to forward this to whoever looks after socials.
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -19313,7 +19313,7 @@
         <is>
           <t>Hi PAMIA team,
 PAMIA has insured UK and Irish patent and trade mark attorneys since 1989, now covering 350 firms.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 10-minute walk from your office on Fenchurch Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), about a 10-minute walk from your office on Fenchurch Street.
 We're looking for someone at PAMIA who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -19526,7 +19526,7 @@
         <is>
           <t>Hi Catriona,
 I saw Page White &amp; Farrer has over 160 years of experience as specialist patent and trade mark attorneys.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), about a 10-minute walk from your office near WC1R 4HE.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/location/st-pancras-corams-fields-3g), about a 10-minute walk from your office near WC1R 4HE.
 We're looking for someone at Page White &amp; Farrer who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would you be up for it, or is there someone better placed? Either way, feel free to forward this to whoever looks after socials.
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -19747,7 +19747,7 @@
         <is>
           <t>Hi Chris,
 Noticed Tysers has been trading for more than 200 years, a serious run for a London insurance broker.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 12-minute walk from your office on 70 Fenchurch Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), about a 12-minute walk from your office on 70 Fenchurch Street.
 We're looking for someone at Tysers to help start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players, payments and organisation.
 Would you be up for it, or is there someone better placed? Either way, feel free to forward this to whoever looks after socials.
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -19968,7 +19968,7 @@
         <is>
           <t>Hi Ashok,
 Congratulations on JMAN's new Chief People Officer, Trish Unwin, joining the team this year.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 12-minute walk from your office near EC3N 3AJ.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), about a 12-minute walk from your office near EC3N 3AJ.
 We're looking for someone at JMAN who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would you be up for it, or is there someone better placed? Either way, feel free to forward this to whoever looks after socials.
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -20192,7 +20192,7 @@
         <is>
           <t>Hi Adam,
 We saw HW Fisher is part of the Sumer Group, a top 15 UK accountancy practice - a real milestone.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras Rooftop 4G (https://www.fcurban.com/locations/st-pancras-rooftop-4g), about a 13-minute walk from your office on William Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras Rooftop 4G (https://www.fcurban.com/location/st-pancras-rooftop-4g), about a 13-minute walk from your office on William Road.
 We're looking for someone at HW Fisher who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players, payments and organisation.
 Would you be up for it, or is there someone better placed? Either way, feel free to forward this to whoever looks after socials.
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -20415,7 +20415,7 @@
         <is>
           <t>Hi Adrian,
 We saw that Chapman Taylor runs 13 studios worldwide, all working as one global team - impressive scale for an architecture practice.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/locations/ark-king-solomon), about a 13-minute walk from your office on Eastbourne Terrace.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/location/ark-king-solomon), about a 13-minute walk from your office on Eastbourne Terrace.
 We're looking for someone at Chapman Taylor who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would you be up for it, or is there someone better placed? Either way, feel free to forward this to whoever looks after socials.
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -20640,7 +20640,7 @@
         <is>
           <t>Hi Matt,
 Investigo has grown from a small London team founded in 2003 into a 200-plus consultant business with global offices.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 15-minute walk from your office at SE1 9SG.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/location/borough-academy), about a 15-minute walk from your office at SE1 9SG.
 We're looking for someone at Investigo who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would you be up for it, or is there someone better placed? Either way, feel free to forward this to whoever looks after socials.
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -20861,7 +20861,7 @@
         <is>
           <t>Hi Narcisa,
 I saw Taskize moved into a new London HQ at One Leadenhall earlier this year, calling it a new chapter for the team.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 15-minute walk from your office on Leadenhall Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), about a 15-minute walk from your office on Leadenhall Street.
 We're looking for someone at Taskize who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players, payments and organisation.
 Would you be up for it, or is there someone better placed? Either way, feel free to forward this to whoever looks after socials.
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -21083,7 +21083,7 @@
         <is>
           <t>Hi Jacob,
 I saw that eduMe has grown a long way since you founded it in 2016, now supporting over 32 million frontline workers worldwide.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 4-minute walk from your office in SE1 0DW.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/location/borough-academy), about a 4-minute walk from your office in SE1 0DW.
 We're looking for someone at eduMe who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -21308,7 +21308,7 @@
         <is>
           <t>Hi Charlie,
 I saw that Plandek has just appointed Craig Smiley as Chief Product Officer as the team keeps growing.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 4-minute walk from your office on Union Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/location/borough-academy), about a 4-minute walk from your office on Union Street.
 We're looking for someone at Plandek who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -21520,7 +21520,7 @@
         <is>
           <t>Hi Hopkins Architects team,
 We saw Hopkins Architects moved to an Employee Ownership Trust in 2019, giving everyone in the practice a stake in its future.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/locations/ark-king-solomon), about a 6-minute walk from your office near NW1 6LG.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/location/ark-king-solomon), about a 6-minute walk from your office near NW1 6LG.
 We're looking for someone at Hopkins Architects who'd enjoy helping start a weekly office kickabout for the studio; we handle the pitch, extra players, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -21733,7 +21733,7 @@
       <c r="AO99" s="19" t="inlineStr">
         <is>
           <t>Hi David,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Whittington Park (https://www.fcurban.com/locations/whittington-park), about a 6-minute walk from your office at Riley Studios, 724 Holloway Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Whittington Park (https://www.fcurban.com/location/whittington-park), about a 6-minute walk from your office at Riley Studios, 724 Holloway Road.
 We're looking for someone at Moneynet who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -21947,7 +21947,7 @@
         <is>
           <t>Hi PLP Architecture team,
 We saw PLP Architecture has just submitted plans for the new Whitechapel Healthcare and Research Campus, in the same neighbourhood as your studio.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), a 6-minute walk from your office on Whitechapel High Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), a 6-minute walk from your office on Whitechapel High Street.
 We're looking for someone at PLP Architecture who'd enjoy helping start a weekly office kickabout for the studio; we handle the pitch, extra players if short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -22148,7 +22148,7 @@
       <c r="AO101" s="19" t="inlineStr">
         <is>
           <t>Hi Procurement Leaders team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 6-minute walk from your office near SE1 1GA.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/location/borough-academy), about a 6-minute walk from your office near SE1 1GA.
 We're looking for someone at Procurement Leaders who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -22371,7 +22371,7 @@
         <is>
           <t>Hi Rasul,
 OneCall24 has grown from a small team back in August 2015 to more than 100 consultants and a candidate workforce of over 12,000 today.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/locations/ark-king-solomon), about a 6-minute walk from your office on Old Marylebone Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/location/ark-king-solomon), about a 6-minute walk from your office on Old Marylebone Road.
 We're looking for someone at OneCall24 who'd enjoy helping start a regular team game or friendly competition against other firms; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -22584,7 +22584,7 @@
         <is>
           <t>Hi Allies and Morrison team,
 We noticed Allies and Morrison brings together more than forty nationalities in one collaborative, friendly studio.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 7-minute walk from your office on Southwark Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/location/borough-academy), about a 7-minute walk from your office on Southwark Street.
 We're looking for someone at Allies and Morrison who'd enjoy helping start a weekly office kickabout for the studio; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -22798,7 +22798,7 @@
         <is>
           <t>Hi Objectway team,
 It's great to see Objectway expanding into capital markets with the SLIB acquisition, building on your 30 years in wealth and asset management technology.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/locations/poplar), about a 7-minute walk from your office in Canary Wharf.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/location/poplar), about a 7-minute walk from your office in Canary Wharf.
 We're looking for someone at Objectway who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -23012,7 +23012,7 @@
         <is>
           <t>Hi Syntura team,
 I saw that hSo has recently rebranded as Syntura, as the business repositions itself for its next chapter.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about an 8-minute walk from your office on 50 Leman Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), about an 8-minute walk from your office on 50 Leman Street.
 We're looking for someone at Syntura who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -23236,7 +23236,7 @@
         <is>
           <t>Hi Juliane,
 I saw that Simkins was founded in 1962, originally to represent up-and-coming clients from the music and film businesses.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), about an 8-minute walk from your office on Tavistock Square.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/location/st-pancras-corams-fields-3g), about an 8-minute walk from your office on Tavistock Square.
 We're looking for someone at Simkins who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -23433,7 +23433,7 @@
       <c r="AO107" s="19" t="inlineStr">
         <is>
           <t>Hi Accuracy team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 9-minute walk from your office near EC3A 7BA.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), about a 9-minute walk from your office near EC3A 7BA.
 We're looking for someone at Accuracy who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -23655,7 +23655,7 @@
         <is>
           <t>Hi Mattie,
 I saw TP Bennett's acquisition of Bluehaus in Dubai, a milestone in the practice's international expansion.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 10-minute walk from your office on Blackfriars Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/location/borough-academy), about a 10-minute walk from your office on Blackfriars Road.
 We're looking for someone at TP Bennett who'd enjoy helping start a weekly office kickabout for the studio; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -23880,7 +23880,7 @@
         <is>
           <t>Hi Ioannis,
 We saw that Signal Ocean recently announced its acquisition of AXSMarine, aimed at accelerating innovation across its maritime data platform.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old St - Moreland Primary School (https://www.fcurban.com/locations/old-st-moreland-primary-school), about an 11-minute walk from your office on 128 City Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Old St - Moreland Primary School (https://www.fcurban.com/location/old-st-moreland-primary-school), about an 11-minute walk from your office on 128 City Road.
 We're looking for someone at Signal Ocean who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -24105,7 +24105,7 @@
         <is>
           <t>Hi Mike,
 xpate was founded in Riga back in 2019, and now runs offices in both Latvia and the UK.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/locations/poplar), about an 11-minute walk from your office at Level 18, 40 Bank Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/location/poplar), about an 11-minute walk from your office at Level 18, 40 Bank Street.
 We're looking for someone at xpate who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -24331,7 +24331,7 @@
         <is>
           <t>Hi Tomasz,
 We saw that VirtusLab was founded in 2010, marking 16 years in business this year.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/locations/poplar), about a 11-minute walk from your office at 40 Bank Street, Canary Wharf.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/location/poplar), about a 11-minute walk from your office at 40 Bank Street, Canary Wharf.
 We're looking for someone at VirtusLab who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -24544,7 +24544,7 @@
         <is>
           <t>Hi RSHP team,
 We saw that construction has just begun on your British Library Extension, with the groundbreaking ceremony held on 21 September.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 13-minute walk from your office on 122 Leadenhall Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), about a 13-minute walk from your office on 122 Leadenhall Street.
 We're looking for someone at RSHP who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -24761,7 +24761,7 @@
         <is>
           <t>Hi Nicola,
 I saw MTS Health celebrated 25 years in business, growing from early PFI advisory work to leading clinical technology management for the NHS.
-I'm Brian from FC Urban. We organise football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), about a 14-minute walk from your office in WC1B 5HA.
+I'm Brian from FC Urban. We organise football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/location/st-pancras-corams-fields-3g), about a 14-minute walk from your office in WC1B 5HA.
 We're looking for someone at MTS Health who'd enjoy helping start a regular team social or a game against another firm nearby; we handle the pitch, extra players, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -24970,7 +24970,7 @@
         <is>
           <t>Hi RHEON Labs team,
 The RHEON Labs team already runs its own Run Club, plus a gym in the office and monthly Lab Lunches.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Battersea - Griffin Primary School (https://www.fcurban.com/locations/battersea-griffin-primary-school), about a 14-minute walk from your office near SW8 3QJ.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Battersea - Griffin Primary School (https://www.fcurban.com/location/battersea-griffin-primary-school), about a 14-minute walk from your office near SW8 3QJ.
 We're looking for someone at RHEON Labs who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -25195,7 +25195,7 @@
         <is>
           <t>Hi Chris,
 I saw Thor is marking a new chapter this year as a mission-critical talent provider, having started out in Clapham back in 2012.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Kennington (https://www.fcurban.com/locations/kennington), about a 14-minute walk from your office on South Lambeth Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Kennington (https://www.fcurban.com/location/kennington), about a 14-minute walk from your office on South Lambeth Road.
 We're looking for someone at Thor who'd enjoy helping start a regular team game or friendly competition against other firms; we handle the pitch, extra players, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -25419,7 +25419,7 @@
         <is>
           <t>Hi Joe,
 I saw the Kelliher Insurance Group gives staff their birthday off and marks milestones in style.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 14-minute walk from your office on 40 Lime Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), about a 14-minute walk from your office on 40 Lime Street.
 We're looking for someone at Kelliher Insurance Group who'd enjoy helping start a regular team social or after-work game, or a game against another firm; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If not, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -25644,7 +25644,7 @@
         <is>
           <t>Hi Ross,
 The Preston Turnbull team took on the Maritime Mountain Race in July for the Mission to Seafarers.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 14-minute walk from your office on Seething Lane.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), about a 14-minute walk from your office on Seething Lane.
 We're looking for someone at Preston Turnbull who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -25858,7 +25858,7 @@
         <is>
           <t>Hi Mathys &amp; Squire team,
 Mathys &amp; Squire has clocked up more than 115 years protecting IP rights, since being founded in 1910.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 15-minute walk from your office in SE1 9SG.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/location/borough-academy), about a 15-minute walk from your office in SE1 9SG.
 We're looking for someone at Mathys &amp; Squire who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -26066,7 +26066,7 @@
         <is>
           <t>Hi X4 Group team,
 We loved reading that X4 Group started out in 2008, offering recruitment from a founder's living room in London, and is now multi-award-winning.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Whitechapel (https://www.fcurban.com/locations/whitechapel), about a 15-minute walk from your office near E1W 1YW.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Whitechapel (https://www.fcurban.com/location/whitechapel), about a 15-minute walk from your office near E1W 1YW.
 We're looking for someone at X4 Group who'd enjoy helping start a regular team game or friendly competition against other firms; we handle the pitch, extra players if short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -26292,7 +26292,7 @@
         <is>
           <t>Hi Daniel,
 I saw Thornbridge has just announced a new partnership with Arbor, bringing new digital tools into your fund platforms.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 15-minute walk from your office on Austin Friars.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), about a 15-minute walk from your office on Austin Friars.
 We're looking for someone at Thornbridge who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -26517,7 +26517,7 @@
         <is>
           <t>Hi John,
 We saw that AXA XL went live on PPL in December, using ACORD Solutions Group's ADEPT Gateway to expand its London Market connectivity.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 15-minute walk from your office on 34 Lime Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), about a 15-minute walk from your office on 34 Lime Street.
 We're looking for someone at PPL who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -26726,7 +26726,7 @@
         <is>
           <t>Hi Build Hollywood team,
 I saw the BUILDHOLLYWOOD 2025 annual film has just landed, marking another year of placing creativity in the heart of your cities.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/locations/ark-king-solomon), just a 2-minute walk from your office near NW1 5BY.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/location/ark-king-solomon), just a 2-minute walk from your office near NW1 5BY.
 We're looking for someone at Build Hollywood who'd enjoy helping start a weekly office kickabout for the studio; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -26926,7 +26926,7 @@
       <c r="AO123" s="19" t="inlineStr">
         <is>
           <t>Hi Venture Commodities Partners team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Chelsea (https://www.fcurban.com/locations/chelsea), about a 4-minute walk from your office on 113 Doverhouse Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Chelsea (https://www.fcurban.com/location/chelsea), about a 4-minute walk from your office on 113 Doverhouse Street.
 We're looking for someone at Venture Commodities Partners who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -27139,7 +27139,7 @@
         <is>
           <t>Hi PrismFP team,
 PrismFP describes its culture as R&amp;D-centred, blending market practitioners, quantitative analysts and technologists in a fast-paced, agile environment.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/locations/ark-king-solomon), about a 6-minute walk from your office at The Grove, Third Floor, 248A Marylebone Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/location/ark-king-solomon), about a 6-minute walk from your office at The Grove, Third Floor, 248A Marylebone Road.
 We're looking for someone at PrismFP who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -27352,7 +27352,7 @@
         <is>
           <t>Hi LACE Partners team,
 We saw Ellen Leonard from LACE Partners was named in Reward Strategy's 30 Under 30 for 2026.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 6-minute walk from your office on Great Guildford Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/location/borough-academy), about a 6-minute walk from your office on Great Guildford Street.
 We're looking for someone at LACE Partners who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -27563,7 +27563,7 @@
         <is>
           <t>Hi Heatherwick Studio team,
 I saw your team has grown to more than 250 architects, designers, makers and engineers.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), about a 6-minute walk from your office at Making House, 55 Argyle Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/location/st-pancras-corams-fields-3g), about a 6-minute walk from your office at Making House, 55 Argyle Street.
 We're looking for someone at Heatherwick Studio who'd enjoy helping start a weekly office kickabout for the studio; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -27777,7 +27777,7 @@
         <is>
           <t>Hi IFF Research team,
 We noticed that IFF Research runs on a four-day working week, built around flexibility and wellbeing for the team.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 7-minute walk from your office at 5th Floor, The Harlequin Building.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/location/borough-academy), about a 7-minute walk from your office at 5th Floor, The Harlequin Building.
 We're looking for someone at IFF Research who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -27986,7 +27986,7 @@
         <is>
           <t>Hi MetroPress team,
 You launched MetroPress this year with a simple idea: that promoting a brand through real creators should be as easy as browsing a marketplace.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 7-minute walk from your office near SE1 0HR.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/location/borough-academy), about a 7-minute walk from your office near SE1 0HR.
 We're looking for someone at MetroPress who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -28197,7 +28197,7 @@
         <is>
           <t>Hi Unilink team,
 Unilink's story goes back to 1994, when it was founded to build technology for justice and custodial services, and has grown into a global team of over 180 people.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 7-minute walk from your office on Lavington Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/location/borough-academy), about a 7-minute walk from your office on Lavington Street.
 We're looking for someone at Unilink who would enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -28394,7 +28394,7 @@
       <c r="AO130" s="19" t="inlineStr">
         <is>
           <t>Hi Trive team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/locations/poplar), about a 7-minute walk from your office near E14 5AB.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/location/poplar), about a 7-minute walk from your office near E14 5AB.
 We're looking for someone at Trive who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -28607,7 +28607,7 @@
         <is>
           <t>Hi Transferra team,
 We saw that Transferra has been authorised by the Financial Conduct Authority since December 2021.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/locations/poplar), about a 7-minute walk from your office at 1 Canada Square, Canary Wharf.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/location/poplar), about a 7-minute walk from your office at 1 Canada Square, Canary Wharf.
 We're looking for someone at Transferra who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -28820,7 +28820,7 @@
         <is>
           <t>Hi Wanstor team,
 We saw that Wanstor was recently named in the Oxygen 250 2025 report, recognising it among the UK's fastest-growing technology companies.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about an 8-minute walk from your office on 124-126 Borough High Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/location/borough-academy), about an 8-minute walk from your office on 124-126 Borough High Street.
 We're looking for someone at Wanstor who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -29033,7 +29033,7 @@
         <is>
           <t>Hi Ptarmigan Media team,
 Ptarmigan Media has spent over 25 years growing into a specialist financial services media agency with offices around the world.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about an 8-minute walk from your office on Southwark Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/location/borough-academy), about an 8-minute walk from your office on Southwark Street.
 We're looking for someone at Ptarmigan Media who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -29243,7 +29243,7 @@
         <is>
           <t>Hi KIT-AR team,
 Congratulations on completing your 3.3 million euro funding round.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), about an 8-minute walk from your office near WC1X 8BP.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/location/st-pancras-corams-fields-3g), about an 8-minute walk from your office near WC1X 8BP.
 We're looking for someone at KIT-AR who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -29457,7 +29457,7 @@
         <is>
           <t>Hi Career Legal team,
 For over 35 years Career Legal has built its reputation on relationships, and you already bring clients and colleagues together through regular breakfasts and client events.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about an 8-minute walk from your office on Alie Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), about an 8-minute walk from your office on Alie Street.
 We're looking for someone at Career Legal who'd enjoy helping start a regular team game or friendly competition against other firms; we handle the pitch, extra players if short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -29657,7 +29657,7 @@
       <c r="AO136" s="19" t="inlineStr">
         <is>
           <t>Hi Big Health team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), about an 8-minute walk from your office near WC1H 9LT.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/location/st-pancras-corams-fields-3g), about an 8-minute walk from your office near WC1H 9LT.
 We're looking for someone at Big Health who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -29871,7 +29871,7 @@
         <is>
           <t>Hi Fulkers Bailey Russell team,
 We saw that Fulkers Bailey Russell became a Certified B Corporation in October 2023.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 9-minute walk from your office on 1 Long Lane.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/location/borough-academy), about a 9-minute walk from your office on 1 Long Lane.
 We're looking for someone at Fulkers Bailey Russell who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -30082,7 +30082,7 @@
         <is>
           <t>Hi Ingleton Wood team,
 We saw Ingleton Wood was recognised in Building Magazine's Good Employer Guide 2025.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Whitechapel (https://www.fcurban.com/locations/whitechapel), about a 9-minute walk from your office on Gower's Walk.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Whitechapel (https://www.fcurban.com/location/whitechapel), about a 9-minute walk from your office on Gower's Walk.
 We're looking for someone at Ingleton Wood who'd enjoy helping start a weekly office kickabout for the practice; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -30296,7 +30296,7 @@
         <is>
           <t>Hi SRC Infrastructure team,
 I saw your recent piece on this year's interns and their reflections on their time at SRC.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/locations/poplar), about a 9-minute walk from your office near E14 5EU.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/location/poplar), about a 9-minute walk from your office near E14 5EU.
 We're looking for someone at SRC Infrastructure who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -30510,7 +30510,7 @@
         <is>
           <t>Hi Bishop &amp; Sewell team,
 We noticed the firm merged with Monro Wright &amp; Wasbrough in 2021, now operating together as one full-service Central London practice.
-I'm Brian from FC Urban. We organise social football games across London, and already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), a 9-minute walk from your office on 59-60 Russell Square.
+I'm Brian from FC Urban. We organise social football games across London, and already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/location/st-pancras-corams-fields-3g), a 9-minute walk from your office on 59-60 Russell Square.
 We're looking for someone at Bishop &amp; Sewell who'd enjoy helping start a regular team social or after-work game, or a game against another firm; we handle the pitch, players, payments and organisation.
 Would there be any interest? If not, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -30721,7 +30721,7 @@
         <is>
           <t>Hi Ancora Finance team,
 Ancora Finance Group was founded back in 2012 and has grown into a business with offices in London, Munich and Zurich.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Chelsea (https://www.fcurban.com/locations/chelsea), about a 9-minute walk from your office on Chelsea Manor Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Chelsea (https://www.fcurban.com/location/chelsea), about a 9-minute walk from your office on Chelsea Manor Street.
 We're looking for someone at Ancora Finance who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -30935,7 +30935,7 @@
         <is>
           <t>Hi Adthena team,
 Between the summer parties, quarterly off-sites and monthly get-togethers you run, Adthena clearly makes time for the team to connect outside of work.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/locations/poplar), about a 9-minute walk from your office on Churchill Place.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/location/poplar), about a 9-minute walk from your office on Churchill Place.
 We're looking for someone at Adthena who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -31144,7 +31144,7 @@
         <is>
           <t>Hi Red Planet Pictures team,
 We saw that the BBC has recommissioned Death in Paradise for another two series, with cameras already rolling in Guadeloupe.
-I'm Brian from FC Urban. We organise social football games across London, and we run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), about a 9-minute walk from your office near WC1X 0BJ.
+I'm Brian from FC Urban. We organise social football games across London, and we run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/location/st-pancras-corams-fields-3g), about a 9-minute walk from your office near WC1X 0BJ.
 We're looking for someone at Red Planet Pictures who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -31357,7 +31357,7 @@
         <is>
           <t>Hi BestX team,
 We saw that BestX recently published research on how AI could reshape FX execution choices.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/locations/poplar), about a 9-minute walk from your office on 20 Churchill Place.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/location/poplar), about a 9-minute walk from your office on 20 Churchill Place.
 We're looking for someone at BestX who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -31557,7 +31557,7 @@
       <c r="AO145" s="19" t="inlineStr">
         <is>
           <t>Hi Everforth Quinnox team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 10-minute walk from your office near EC3N 1LQ.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), about a 10-minute walk from your office near EC3N 1LQ.
 We're looking for someone at Everforth Quinnox who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -31770,7 +31770,7 @@
         <is>
           <t>Hi Max Fordham team,
 We saw that four of the six projects shortlisted for the 2026 RIBA Stirling Prize are Max Fordham's - a strong showing.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Camden - Castlehaven (https://www.fcurban.com/locations/camden-castlehaven-ba0af), about a 10-minute walk from your office on Gloucester Crescent.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Camden - Castlehaven (https://www.fcurban.com/location/camden-castlehaven-ba0af), about a 10-minute walk from your office on Gloucester Crescent.
 We're looking for someone at Max Fordham who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -31983,7 +31983,7 @@
         <is>
           <t>Hi Eleven team,
 I saw Eleven was named one of Broadcast's Best Places to Work in TV.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/locations/ark-king-solomon), about an 11-minute walk from your office at 12th Floor, Brunel Building, 2 Canalside Walk.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/location/ark-king-solomon), about an 11-minute walk from your office at 12th Floor, Brunel Building, 2 Canalside Walk.
 We're looking for someone at Eleven who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -32197,7 +32197,7 @@
         <is>
           <t>Hi Blue Zoo team,
 I saw Blue Zoo became the world's first B Corp-certified independent animation studio, back in September 2021.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Camden - Castlehaven (https://www.fcurban.com/locations/camden-castlehaven-ba0af), about an 11-minute walk from your office at Acre House, 11-15 William Road, London, NW1 7AA.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Camden - Castlehaven (https://www.fcurban.com/location/camden-castlehaven-ba0af), about an 11-minute walk from your office at Acre House, 11-15 William Road, London, NW1 7AA.
 We're looking for someone at Blue Zoo who'd enjoy helping start a weekly office kickabout for the studio; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -32410,7 +32410,7 @@
         <is>
           <t>Hi Sturrock &amp; Robson team,
 Sturrock &amp; Robson has been going for over a century, with roots in 1920s South African mining and shipping, and is still a fourth-generation family business today.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), an 11-minute walk from your office on Borough High Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/location/borough-academy), an 11-minute walk from your office on Borough High Street.
 We're looking for someone at Sturrock &amp; Robson who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, players, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -32623,7 +32623,7 @@
         <is>
           <t>Hi Handle Recruitment team,
 I saw you've been supporting organisations at the forefront of the UK's creative industries since 1978.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), about an 11-minute walk from your office on Easton Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/location/st-pancras-corams-fields-3g), about an 11-minute walk from your office on Easton Street.
 We're looking for someone at Handle Recruitment who'd enjoy helping start a regular team game or friendly competition against other firms; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -32823,7 +32823,7 @@
       <c r="AO151" s="19" t="inlineStr">
         <is>
           <t>Hi Attento team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 12-minute walk from your office on 70 Fenchurch Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), about a 12-minute walk from your office on 70 Fenchurch Street.
 We're looking for someone at Attento who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -33020,7 +33020,7 @@
       <c r="AO152" s="19" t="inlineStr">
         <is>
           <t>Hi Turlock TEC team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 12-minute walk from your office near EC3N 3AE.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), about a 12-minute walk from your office near EC3N 3AE.
 We're looking for someone at Turlock TEC who'd enjoy helping start a regular team social or after-work game; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -33233,7 +33233,7 @@
         <is>
           <t>Hi esynergy team,
 Alongside your client work, esynergy has partnered with the charity Separated Child, helping set up their IT systems so they can keep supporting unaccompanied child refugees.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 12-minute walk from your office on Lloyd's Avenue.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), about a 12-minute walk from your office on Lloyd's Avenue.
 We're looking for someone at esynergy who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -33446,7 +33446,7 @@
         <is>
           <t>Hi Cherry team,
 Congratulations on being named a Great Place to Work for six years running, including for wellbeing and for women in the industry.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 13-minute walk from your office on 2A Southwark Bridge Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/location/borough-academy), about a 13-minute walk from your office on 2A Southwark Bridge Road.
 We're looking for someone at Cherry who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -33659,7 +33659,7 @@
         <is>
           <t>Hi Company85 team,
 I noticed your careers page mentions the team already has its own 5-a-side football team, alongside the monthly socials and summer BBQ.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 13-minute walk from your office on Leadenhall Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), about a 13-minute walk from your office on Leadenhall Street.
 We're looking for someone at Company85 who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -33857,7 +33857,7 @@
       <c r="AO156" s="19" t="inlineStr">
         <is>
           <t>Hi Kobre &amp; Kim team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 13-minute walk from your office near EC2N 1HQ.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), about a 13-minute walk from your office near EC2N 1HQ.
 We're looking for someone at Kobre &amp; Kim who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -34070,7 +34070,7 @@
         <is>
           <t>Hi Vortexa team,
 Since founder Fabio Kuhn spotted the opportunity back in 2016, Vortexa has grown to more than 160 people across six offices worldwide.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 13-minute walk from your office at Tower 42, 25 Old Broad Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), about a 13-minute walk from your office at Tower 42, 25 Old Broad Street.
 We're looking for someone at Vortexa who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -34284,7 +34284,7 @@
         <is>
           <t>Hi Daemon team,
 Congratulations on being named the 2025 EMEA AWS Innovation Partner of the Year - great recognition for the team.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/locations/ark-king-solomon), about a 13-minute walk from your office on Conduit Place.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/location/ark-king-solomon), about a 13-minute walk from your office on Conduit Place.
 We're looking for someone at Daemon who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -34497,7 +34497,7 @@
         <is>
           <t>Hi RiskSave team,
 I saw RiskSave is a registered B-Corp and was named a 'Best for the World' winner for the impact of its work.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/locations/ark-king-solomon), about a 13-minute walk from your office on Eastbourne Terrace.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/location/ark-king-solomon), about a 13-minute walk from your office on Eastbourne Terrace.
 We're looking for someone at RiskSave who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -34706,7 +34706,7 @@
         <is>
           <t>Hi Carpmaels &amp; Ransford team,
 Congratulations on Christopher Stothers and Kevin Cordina joining as partners.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), about a 14-minute walk from your office near WC1B 5HA.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/location/st-pancras-corams-fields-3g), about a 14-minute walk from your office near WC1B 5HA.
 We're looking for someone at Carpmaels &amp; Ransford to help start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -34902,7 +34902,7 @@
       <c r="AO161" s="19" t="inlineStr">
         <is>
           <t>Hi Mewburn Ellis team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 14-minute walk from your office near EC2N 4BQ.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), about a 14-minute walk from your office near EC2N 4BQ.
 We're looking for someone at Mewburn Ellis who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -35111,7 +35111,7 @@
         <is>
           <t>Hi Sanza team,
 Sanza Teaching Agency was originally founded in 1999 to recruit teachers and support staff for London schools.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), about a 14-minute walk from your office near WC1V 6JS.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/location/st-pancras-corams-fields-3g), about a 14-minute walk from your office near WC1V 6JS.
 We're looking for someone at Sanza who'd enjoy helping start a regular team game or friendly competition against other firms; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -35324,7 +35324,7 @@
         <is>
           <t>Hi Egremont Group team,
 We noticed Egremont Group is a certified B Corp.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), about a 14-minute walk from your office on 24-28 Bloomsbury Way.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/location/st-pancras-corams-fields-3g), about a 14-minute walk from your office on 24-28 Bloomsbury Way.
 We're looking for someone at Egremont Group who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -35520,7 +35520,7 @@
       <c r="AO164" s="19" t="inlineStr">
         <is>
           <t>Hi RiverSafe team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/locations/poplar), about a 14-minute walk from your office near E14 9SH.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Poplar (https://www.fcurban.com/location/poplar), about a 14-minute walk from your office near E14 9SH.
 We're looking for someone at RiverSafe who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -35733,7 +35733,7 @@
         <is>
           <t>Hi ADP Architecture team,
 I saw ADP Architecture's projects were just shortlisted for the Education Estates and Healthcare Estates Awards.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 14-minute walk from your office on Hatfields.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/location/borough-academy), about a 14-minute walk from your office on Hatfields.
 We're looking for someone at ADP Architecture who'd enjoy helping start a weekly office kickabout for the studio; we handle the pitch, extra players, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -35934,7 +35934,7 @@
       <c r="AO166" s="19" t="inlineStr">
         <is>
           <t>Hi UK First Fintech team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 15-minute walk from your office at 3rd Floor, The News Building, 3 London Bridge Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/location/borough-academy), about a 15-minute walk from your office at 3rd Floor, The News Building, 3 London Bridge Street.
 We're looking for someone at UK First Fintech who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -36145,7 +36145,7 @@
         <is>
           <t>Hi EIP team,
 Noticed EIP has grown from a single London office founded in 2000 to over 180 staff today.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/locations/st-pancras-corams-fields-3g), about a 15-minute walk from your office on 15 Fulwood Place.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at St Pancras - Coram's Fields 3G (https://www.fcurban.com/location/st-pancras-corams-fields-3g), about a 15-minute walk from your office on 15 Fulwood Place.
 We're looking for someone at EIP to help start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -36354,7 +36354,7 @@
         <is>
           <t>Hi Saffron team,
 Saw that Peterborough Football Foundation launched your Create Your Own Future platform last year.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Brixton (https://www.fcurban.com/locations/brixton-03dac), about a 15-minute walk from your office near SW9 9RX.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Brixton (https://www.fcurban.com/location/brixton-03dac), about a 15-minute walk from your office near SW9 9RX.
 We're looking for someone at Saffron who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -36554,7 +36554,7 @@
       <c r="AO169" s="19" t="inlineStr">
         <is>
           <t>Hi Elan Capital team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at South Kensington (https://www.fcurban.com/locations/south-kensington), about a 15-minute walk from your office on Brompton Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at South Kensington (https://www.fcurban.com/location/south-kensington), about a 15-minute walk from your office on Brompton Road.
 We're looking for someone at Elan Capital who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -36755,7 +36755,7 @@
       <c r="AO170" s="19" t="inlineStr">
         <is>
           <t>Hi BioTalent team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 15-minute walk from your office on London Bridge Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/location/borough-academy), about a 15-minute walk from your office on London Bridge Street.
 We're looking for someone at BioTalent who'd enjoy helping start a regular team game or friendly competition against other firms; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -36951,7 +36951,7 @@
       <c r="AO171" s="19" t="inlineStr">
         <is>
           <t>Hi Xpedition team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/locations/ark-king-solomon), about a 15-minute walk from your office near W2 6BD.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/location/ark-king-solomon), about a 15-minute walk from your office near W2 6BD.
 We're looking for someone at Xpedition who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -37164,7 +37164,7 @@
         <is>
           <t>Hi Transparity team,
 Saw that you run weekly Wellbeing Wednesdays and use the Hub to bring the team together in person.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/locations/ark-king-solomon), about a 15-minute walk from your office on 2 Kingdom Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/location/ark-king-solomon), about a 15-minute walk from your office on 2 Kingdom Street.
 We're looking for someone at Transparity who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -37377,7 +37377,7 @@
         <is>
           <t>Hi Shop Circle team,
 We saw that Shop Circle was founded in London in 2021 and has since raised over $250 million to grow its software portfolio.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/locations/ark-king-solomon), about a 15-minute walk from your office at One Kingdom Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Ark King Solomon (https://www.fcurban.com/location/ark-king-solomon), about a 15-minute walk from your office at One Kingdom Street.
 We're looking for someone at Shop Circle who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -37594,7 +37594,7 @@
         <is>
           <t>Hi Christofer,
 I saw Parkopedia was founded back in 2007 and has grown into the world's leading parking service, working with the likes of Apple, BMW and Volkswagen.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/locations/borough-academy), about a 10-minute walk from your office near SE1 4PL.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy (https://www.fcurban.com/location/borough-academy), about a 10-minute walk from your office near SE1 4PL.
 We're looking for someone at Parkopedia who'd enjoy helping start a weekly office kickabout for the team; we handle the pitch, extra players if you're short, payments and organisation.
 Would you be up for it, or is there someone better placed? Either way, feel free to forward this to whoever looks after socials.
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
@@ -37809,7 +37809,7 @@
         <is>
           <t>Hi Kaizen team,
 Kaizen has just appointed Rob Bernstein as Chief Financial Officer, its latest senior hire as the business scales.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/locations/liverpool-st-attlee-centre), about a 10-minute walk from your office at 30 St Mary Axe.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Liverpool St - Attlee Centre (https://www.fcurban.com/location/liverpool-st-attlee-centre), about a 10-minute walk from your office at 30 St Mary Axe.
 We're looking for someone at Kaizen who'd enjoy helping start a regular team social or after-work game, or a game against another firm nearby; we handle the pitch, extra players, payments and organisation.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 FC Urban for companies (https://www.fcurban.com/groups-and-company-pitch-rental/football-pitch-rental-for-groups-corporates)
